--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O331"/>
+  <dimension ref="A1:P331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -445,9 +445,10 @@
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="76" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="56" customWidth="1" min="13" max="13"/>
-    <col width="84" customWidth="1" min="14" max="14"/>
-    <col width="86" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="84" customWidth="1" min="15" max="15"/>
+    <col width="86" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,15 +514,20 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Shortened_Tables</t>
+          <t>First_To_Last_Only</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Left_Out</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Previous_Mod_Desc</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Previous_Mod_LvUp</t>
         </is>
@@ -564,8 +570,8 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5
-Speed: 1.5x -&gt; 1.63x -&gt; 1.76x -&gt; 1.89x -&gt; 2x</t>
+          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max) | TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5
+Speed: 1.5x -&gt; 2x</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -577,12 +583,13 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>Attract single-target attacks. | Fast turn recovery.</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | Speed: +50% -&gt; +100% (+12.5%/Lv)
 TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5</t>
@@ -626,8 +633,8 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8
-Speed: 1.25x -&gt; 1.77x (+0.13x/Lv)</t>
+          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max) | TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8
+Speed: 1.25x -&gt; 1.77x</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -639,12 +646,13 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Attract all enemies' attacks to user with high speed turn recovery.</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | Speed: +40% -&gt; +80% (+10%/Lv)
 TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 11</t>
@@ -688,8 +696,8 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ATK increase: 8% -&gt; 10% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5) | Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8
-TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 | Speed: 1.08x -&gt; 1.1x -&gt; 1.12x -&gt; 1.14x -&gt; 1.15x</t>
+          <t>ATK: +8% -&gt; +10% -&gt; +12% -&gt; +15% -&gt; +18% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -703,10 +711,15 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>Raise party physical ATK &amp; cleanse debuffs. Usable out of battle.</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>ATK: +8% -&gt; +10% -&gt; +12% -&gt; +14% -&gt; +18% (L1-5 Max)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
@@ -750,7 +763,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ATK: 125% -&gt; 200% (avg +8.33%/Lv, L1-10) | Accuracy: +20% -&gt; +38% (+2%/Lv)
+          <t>ATK: 125% -&gt; 134 -&gt; 143 -&gt; 152 -&gt; 161 -&gt; 170 -&gt; 178 -&gt; 186 -&gt; 193 -&gt; 200% (L10)
 TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 | Speed: 0.8x -&gt; 0.9x</t>
         </is>
       </c>
@@ -762,17 +775,18 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>ATK, Speed</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>Short-range strike. | Hit Rate: +20% -&gt; +38% (+2%/Lv)</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>ATK (L1-10): 125% -&gt; 133 -&gt; 141 -&gt; 150 -&gt; 158 -&gt; 166 -&gt; 175 -&gt; 183 -&gt; 191 -&gt; 200%
 TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28  (Lv1 to Max)</t>
@@ -816,7 +830,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Accuracy: +20% -&gt; +35% (avg +1.67%/Lv, L1-10) | Buff cancel rate: 68% -&gt; 85%
+          <t>Accuracy: +20% -&gt; +22 -&gt; +24 -&gt; +26 -&gt; +28 -&gt; +30 -&gt; +31 -&gt; +32 -&gt; +33 -&gt; +35% (L10)
 TP Cost: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 | Speed: 0.9x</t>
         </is>
       </c>
@@ -828,17 +842,18 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Accuracy, Buff cancel rate</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
+          <t>Buff cancel rate</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>Short-range strike to one enemy. May cancel enemy active buffs.</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Dispel Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -882,8 +897,8 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ATK increase: 20% -&gt; 30% -&gt; 40% -&gt; 45% -&gt; 50% (L1-5) | DEF decrease: 11% -&gt; 25%
-Turns: 4 -&gt; 8 (+1/Lv) | TP Cost: 8 -&gt; 16 (+2/Lv) | Speed: 1.25x -&gt; 1.77x (+0.13x/Lv)</t>
+          <t>ATK: +20% -&gt; +30% -&gt; +40% -&gt; +45% -&gt; +50% (L1-5 Max) | DEF: -11% -&gt; -25%
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -896,15 +911,20 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>DEF decrease</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>Greatly boost own physical ATK at the cost of lowering own DEF.</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>ATK: +25% -&gt; +65% (+10%/Lv) | DEF: -15% -&gt; -35% (-5%/Lv)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -948,8 +968,8 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DEF increase: 20% -&gt; 30% -&gt; 40% -&gt; 45% -&gt; 50% (L1-5) | ATK decrease: 11% -&gt; 25%
-Turns: 4 -&gt; 8 (+1/Lv) | TP Cost: 8 -&gt; 16 (+2/Lv) | Speed: 1.25x -&gt; 1.77x (+0.13x/Lv)</t>
+          <t>DEF: +20% -&gt; +30% -&gt; +40% -&gt; +45% -&gt; +50% (L1-5 Max) | ATK: -11% -&gt; -25%
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -962,15 +982,20 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ATK decrease</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>Increase own DEF at the cost of ATK (ATK debuff can be cleansed).</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>DEF: +20% -&gt; +27% -&gt; +35% -&gt; +42% -&gt; +50% (L1-5 Max)
 ATK: -11% -&gt; -25% (-3.5%/Lv) | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -1014,8 +1039,8 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ATK: 85% -&gt; 90% -&gt; 94% -&gt; 98% -&gt; 102% (L1-5) | Accuracy: +6% -&gt; +20% (avg +3.5%/Lv)
-Stun: 30% -&gt; 38% (+2%/Lv) | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 | Speed: 0.55x</t>
+          <t>ATK: 85% -&gt; 90% -&gt; 94% -&gt; 98% -&gt; 102% (L1-5 Max) | Accuracy: +6% -&gt; +20%
+Stun: 30% -&gt; 32% -&gt; 34% -&gt; 36% -&gt; 38% | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1033,10 +1058,15 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>Shield skill. Deal bash damage to one enemy. May stun.</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>ATK: 110% -&gt; 150% (+10%/Lv) | Stun: 20% -&gt; 40% (+5%/Lv)
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 | Requires equipped shield</t>
@@ -1080,8 +1110,8 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ATK: 106% -&gt; 150% (avg +4.89%/Lv, L1-10) | Accuracy: +5% -&gt; +28% (avg +2.56%/Lv)
-Paralysis: 20% -&gt; 50% (avg +3.33%/Lv) | TP Cost: 6 -&gt; 24 (+2/Lv) | Speed: 0.85x</t>
+          <t>ATK: 106% -&gt; 112 -&gt; 118 -&gt; 124 -&gt; 130 -&gt; 134 -&gt; 138 -&gt; 142 -&gt; 146 -&gt; 150% (L10)
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 | Speed: 0.85x</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1092,17 +1122,18 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ATK, Accuracy, Paralysis</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
+          <t>Accuracy, Paralysis</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>Katana skill. Deal bash damage to one enemy. May paralyze.</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 180% (+15%/Lv) | Paralysis: 25% -&gt; 50% (+6.25%/Lv)
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -1146,8 +1177,8 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Critical rate UP | Enemy critical rate UP | Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5)
-TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 | Speed: 1.5x -&gt; 1.63x -&gt; 1.76x -&gt; 1.89x -&gt; 2x</t>
+          <t>Critical rate UP | Enemy critical rate UP
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max) | TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1169,10 +1200,15 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>Greatly boost own critical rate, but increase vulnerability to crits.</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Crit Rate: +25% -&gt; +55% (+7.5%/Lv) | Enemy Crit: +15% -&gt; +25%
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -1216,8 +1252,8 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 80% -&gt; 83 -&gt; 86 -&gt; 89 -&gt; 91 -&gt; 94 -&gt; 97 -&gt; 100 -&gt; 105 -&gt; 110%
-Instakill: 10% -&gt; 20% | TP Cost: 38 -&gt; 74 (+4/Lv) | Speed: 0.65x -&gt; 0.75x</t>
+          <t>ATK: 80% -&gt; 83 -&gt; 86 -&gt; 89 -&gt; 91 -&gt; 94 -&gt; 97 -&gt; 100 -&gt; 105 -&gt; 110% (L10)
+TP Cost: 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58 -&gt; 62 -&gt; 66 -&gt; 70 -&gt; 74</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1228,17 +1264,18 @@
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Instakill, Speed</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Katana skill. Deal slash damage to an enemy row. May instakill.</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>ATK: 115% -&gt; 175% (+15%/Lv) | Instakill: 10% -&gt; 25% (+3.75%/Lv)
 TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28</t>
@@ -1282,8 +1319,8 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ATK: 84% -&gt; 120% (+4%/Lv, L1-10) | Enemy DEF decrease: 16% -&gt; 25% (+1%/Lv) | Turns: 4
-TP Cost: 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 | Speed: 0.8x</t>
+          <t>ATK: 84% -&gt; 88 -&gt; 92 -&gt; 96 -&gt; 100 -&gt; 104 -&gt; 108 -&gt; 112 -&gt; 116 -&gt; 120% (L10)
+Turns: 4 | TP Cost: 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1297,10 +1334,15 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
+          <t>Enemy DEF, Speed</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>Katana skill. Deal defense-piercing damage and lower target DEF.</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 180% (+15%/Lv) | DEF Debuff: -15% -&gt; -30% (-3.75%/Lv)
 TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 | Bypasses enemy armor</t>
@@ -1344,8 +1386,8 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ATK: 104% -&gt; 140% (+4%/Lv, L1-10) | TP Cost: 22 -&gt; 58 (+4/Lv)
-Speed: 0.7x -&gt; 0.72 -&gt; 0.74 -&gt; 0.76 -&gt; 0.78 -&gt; 0.8 -&gt; 0.81 -&gt; 0.82 -&gt; 0.83 -&gt; 0.85x</t>
+          <t>ATK: 104% -&gt; 108 -&gt; 112 -&gt; 116 -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140% (L10)
+TP Cost: 22 -&gt; 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1359,10 +1401,15 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>Katana skill. Strike an enemy row with fierce slashing blades.</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>ATK: 130% -&gt; 145% -&gt; 160% -&gt; 175% -&gt; 190% (L1-5)
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
@@ -1406,8 +1453,8 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 118% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 146 -&gt; 152 -&gt; 158%
-TP Cost: 36 -&gt; 61 (avg +2.78/Lv) | Speed: 0.7x -&gt; 0.8x</t>
+          <t>ATK: 118% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 146 -&gt; 152 -&gt; 158% (L10)
+TP Cost: 36 -&gt; 38 -&gt; 40 -&gt; 43 -&gt; 46 -&gt; 49 -&gt; 52 -&gt; 55 -&gt; 58 -&gt; 61</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1418,17 +1465,18 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>TP Cost, Speed</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>Katana skill. Strike 3 times against one living enemy.</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>ATK: 70% -&gt; 80% -&gt; 90% -&gt; 100% -&gt; 110% per hit (3 hits total)
 TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 | Target must be living (not undead)</t>
@@ -1472,7 +1520,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ATK: 74% -&gt; 110% (+4%/Lv, L1-10) | HP Absorb: 15% -&gt; 25% (avg +1.11%/Lv)
+          <t>ATK: 74% -&gt; 78 -&gt; 82 -&gt; 86 -&gt; 90 -&gt; 94 -&gt; 98 -&gt; 102 -&gt; 106 -&gt; 110% (L10)
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36 | Speed: 0.9x</t>
         </is>
       </c>
@@ -1484,17 +1532,18 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>HP Absorb</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Short-range strike to one enemy. Absorb a portion of damage as HP.</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)
 HP Absorb: 20% -&gt; 30% -&gt; 40% -&gt; 50% -&gt; 60% | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -1538,8 +1587,8 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 65% -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 84 -&gt; 88 -&gt; 91 -&gt; 94 -&gt; 97 -&gt; 100%
-TP Absorb: 10% -&gt; 20% (avg +1.11%/Lv) | TP Cost: 6 -&gt; 24 (+2/Lv) | Speed: 0.9x</t>
+          <t>ATK: 65% -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 84 -&gt; 88 -&gt; 91 -&gt; 94 -&gt; 97 -&gt; 100% (L10)
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1550,17 +1599,18 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>TP Absorb</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Short-range strike to one enemy. Absorb a portion of damage as TP.</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>ATK: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% (L1-5)
 TP Absorb: 5% -&gt; 8% -&gt; 11% -&gt; 14% -&gt; 18% | TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8</t>
@@ -1604,8 +1654,8 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 130% -&gt; 144 -&gt; 157 -&gt; 170 -&gt; 182 -&gt; 194 -&gt; 204 -&gt; 212 -&gt; 220 -&gt; 228%
-Freeze: 20% -&gt; 50% (avg +3.33%/Lv) | TP Cost: 9 -&gt; 36 (+3/Lv) | Speed: 0.75x -&gt; 0.85x</t>
+          <t>ATK: 130% -&gt; 144 -&gt; 157 -&gt; 170 -&gt; 182 -&gt; 194 -&gt; 204 -&gt; 212 -&gt; 220 -&gt; 228% (L10)
+Freeze: 20% -&gt; 50% | TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1618,15 +1668,20 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Freeze, Speed</t>
+          <t>Freeze</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>Short-range strike dealing mid-range water damage. May freeze.</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 180% (+15%/Lv) | Freeze: 20% -&gt; 40% (+5%/Lv)
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
@@ -1670,8 +1725,8 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 135% -&gt; 149 -&gt; 163 -&gt; 176 -&gt; 189 -&gt; 201 -&gt; 213 -&gt; 225 -&gt; 236 -&gt; 247%
-Petrify: 20% -&gt; 35% (avg +1.67%/Lv) | TP Cost: 9 -&gt; 42 | Speed: 0.85x -&gt; 0.95x</t>
+          <t>ATK: 135% -&gt; 149 -&gt; 163 -&gt; 176 -&gt; 189 -&gt; 201 -&gt; 213 -&gt; 225 -&gt; 236 -&gt; 247% (L10)
+TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 37 -&gt; 42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1682,17 +1737,18 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Petrify, TP Cost, Speed</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
+          <t>Petrify, Speed</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>Axe skill. Strike one enemy with earth damage. May petrify.</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>ATK: 130% -&gt; 210% (+20%/Lv) | Petrify: 15% -&gt; 30% (+3.75%/Lv)
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
@@ -1736,8 +1792,8 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 120% -&gt; 130 -&gt; 140 -&gt; 148 -&gt; 156 -&gt; 164 -&gt; 170 -&gt; 176 -&gt; 180 -&gt; 184%
-Targets: 2 -&gt; 5 (avg +0.33/Lv) | TP Cost: 26 -&gt; 68 | Speed: 0.8x -&gt; 0.9x</t>
+          <t>ATK: 120% -&gt; 130 -&gt; 140 -&gt; 148 -&gt; 156 -&gt; 164 -&gt; 170 -&gt; 176 -&gt; 180 -&gt; 184% (L10)
+Targets: 2 -&gt; 5 | TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 47 -&gt; 53 -&gt; 58 -&gt; 63 -&gt; 68</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1750,15 +1806,20 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Targets, TP Cost, Speed</t>
+          <t>Targets</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>Axe skill. Strike target and the next immediate enemy in turn order.</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>ATK: 140% -&gt; 160% -&gt; 180% -&gt; 200% -&gt; 220% (L1-5)
 TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28 | Hits 2 sequential turn targets</t>
@@ -1802,8 +1863,8 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | TP Cost: 10 -&gt; 14 -&gt; 18 -&gt; 21 -&gt; 24
-Speed: 0.9x -&gt; 0.92x -&gt; 0.93x -&gt; 0.94x -&gt; 0.95x</t>
+          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5 Max) | TP Cost: 10 -&gt; 14 -&gt; 18 -&gt; 21 -&gt; 24
+Speed: 0.9x -&gt; 0.95x</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1819,12 +1880,13 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
         <is>
           <t>Step forward to intercept physical attacks aimed at allies.</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Guard: 30% -&gt; 60% (+7.5%/Lv)
 TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24 | Requires 1H weapon &amp; shield</t>
@@ -1868,8 +1930,8 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26
-Speed: 0.9x -&gt; 0.92x -&gt; 0.93x -&gt; 0.94x -&gt; 0.95x</t>
+          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max) | TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26
+Speed: 0.9x -&gt; 0.95x</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1885,12 +1947,13 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
         <is>
           <t>Short-range skill. Block physical attacks with equipped weapon.</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | Recovery Speed: 1.30x
 TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22 | May break on repeat blocks</t>
@@ -1934,8 +1997,8 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 130% -&gt; 140 -&gt; 150 -&gt; 160 -&gt; 170 -&gt; 180 -&gt; 190 -&gt; 200 -&gt; 211 -&gt; 222%
-Accuracy: +6% -&gt; +20% | TP Cost: 12 -&gt; 39 (+3/Lv) | Speed: 0.8x -&gt; 0.9x</t>
+          <t>ATK: 130% -&gt; 140 -&gt; 150 -&gt; 160 -&gt; 170 -&gt; 180 -&gt; 190 -&gt; 200 -&gt; 211 -&gt; 222% (L10)
+TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1946,17 +2009,18 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
         <is>
           <t>Accuracy, Speed</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Sword and lance skill. Strike one enemy. Effective vs. Unholy foes.</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>ATK: 140% -&gt; 155% -&gt; 170% -&gt; 185% -&gt; 200% (L1-5) | Unholy Bonus: 1.50x
 TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
@@ -2000,8 +2064,8 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Damage reduction rate: 12% -&gt; 30% (+2%/Lv, L1-10) | Turns: 5
-TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45 | Speed: 0.9x</t>
+          <t>Damage reduction rate: 12% -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30%
+Turns: 5 | TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2015,10 +2079,15 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>Shield skill. Erect a physical barrier mitigating party damage once.</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Damage Reduction: -30% -&gt; -50% (-5%/Lv) | Levels: L1-5
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 | Requires shield</t>
@@ -2062,8 +2131,8 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Damage reduction rate: 12% -&gt; 30% (+2%/Lv, L1-10) | Turns: 5
-TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45 | Speed: 0.9x</t>
+          <t>Damage reduction rate: 12% -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30%
+Turns: 5 | TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2077,10 +2146,15 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>Shield skill. Erect a magic barrier mitigating party magic damage once.</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Magic Reduction: -30% -&gt; -50% (-5%/Lv) | Levels: L1-5
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 | Requires shield</t>
@@ -2124,7 +2198,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ATK: 96% -&gt; 138% (avg +4.67%/Lv, L1-10) | Paralysis: 20% -&gt; 40% (avg +2.22%/Lv)
+          <t>ATK: 96% -&gt; 100 -&gt; 104 -&gt; 108 -&gt; 113 -&gt; 118 -&gt; 123 -&gt; 128 -&gt; 133 -&gt; 138% (L10)
 TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 59 -&gt; 64 | Speed: 0.8x</t>
         </is>
       </c>
@@ -2136,17 +2210,18 @@
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>ATK, Paralysis</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
+          <t>Paralysis</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>Short-range skill. Deal lightning damage to an enemy row. May paralyze.</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>ATK: 110% -&gt; 170% (+15%/Lv) | Paralysis: 20% -&gt; 40% (+5%/Lv)
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
@@ -2190,8 +2265,8 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 135% -&gt; 149 -&gt; 163 -&gt; 176 -&gt; 189 -&gt; 201 -&gt; 213 -&gt; 223 -&gt; 234 -&gt; 245%
-Silence: 20% -&gt; 50% | TP Cost: 7 -&gt; 34 (+3/Lv) | Speed: 0.85x -&gt; 0.95x</t>
+          <t>ATK: 135% -&gt; 149 -&gt; 163 -&gt; 176 -&gt; 189 -&gt; 201 -&gt; 213 -&gt; 223 -&gt; 234 -&gt; 245% (L10)
+TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28 -&gt; 31 -&gt; 34</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -2202,17 +2277,18 @@
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
         <is>
           <t>Silence, Speed</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Lance skill. Strike one enemy with wind damage. May silence.</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>ATK: 125% -&gt; 185% (+15%/Lv) | Silence: 20% -&gt; 40% (+5%/Lv)
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
@@ -2256,8 +2332,8 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 116% -&gt; 118 -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 146 -&gt; 152%
-TP Cost: 36 -&gt; 71 (avg +3.89/Lv) | Speed: 0.7x -&gt; 0.8x</t>
+          <t>ATK: 116% -&gt; 118 -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 146 -&gt; 152% (L10)
+TP Cost: 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 51 -&gt; 55 -&gt; 59 -&gt; 65 -&gt; 71</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -2268,17 +2344,18 @@
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>TP Cost, Speed</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
           <t>Lance skill. Rapidly strike random enemies 3 to 5 times.</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>ATK: 65% -&gt; 75% -&gt; 85% -&gt; 95% -&gt; 105% per hit (L1-5)
 TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 | Heavy Lance bonus: +20% dmg</t>
@@ -2322,8 +2399,8 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 120% -&gt; 130 -&gt; 142 -&gt; 154 -&gt; 165 -&gt; 176 -&gt; 186 -&gt; 196 -&gt; 204 -&gt; 212%
-Accuracy: +5% -&gt; +15% (avg +1.11%/Lv) | TP Cost: 32 -&gt; 59 (+3/Lv) | Speed: 0.8x</t>
+          <t>ATK: 120% -&gt; 130 -&gt; 142 -&gt; 154 -&gt; 165 -&gt; 176 -&gt; 186 -&gt; 196 -&gt; 204 -&gt; 212% (L10)
+TP Cost: 32 -&gt; 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 59 | Speed: 0.8x</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -2334,17 +2411,18 @@
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Sword and lance skill. Pierces through to the back row.</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>ATK: 135% -&gt; 195% (+15%/Lv) | Hits front and back target
 TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
@@ -2388,8 +2466,8 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Damage UP | Turns: 2 | TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 (L1-5)
-Speed: 0.84x -&gt; 0.85x -&gt; 0.86x -&gt; 0.88x -&gt; 0.9x</t>
+          <t>Damage UP
+Turns: 2 | TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 | Speed: 0.84x -&gt; 0.9x</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -2409,12 +2487,13 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
         <is>
           <t>Concentrate strength to deal massive physical damage next turn.</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Next Physical Hit: +80% -&gt; +110% -&gt; +140% -&gt; +170% -&gt; +200% (L1-5)
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 | Applies to next physical action</t>
@@ -2457,8 +2536,8 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Steal success: 40% -&gt; 45% -&gt; 50% -&gt; 57% -&gt; 64% (L1-5)
-Speed: 1x -&gt; 1.15x -&gt; 1.3x -&gt; 1.45x -&gt; 1.5x</t>
+          <t>Steal success: 40% -&gt; 45% -&gt; 50% -&gt; 57% -&gt; 64% (L1-5 Max)
+Speed: 1x -&gt; 1.5x</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -2470,12 +2549,13 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
         <is>
           <t>Attempt to pilfer pocket money from an enemy.</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Success Rate: 40% -&gt; 70% (+7.5%/Lv) | Gold: 1.0x -&gt; 2.5x (+0.375x/Lv)
 TP Cost: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6</t>
@@ -2518,8 +2598,8 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Steal success: 30% -&gt; 50% (+5%/Lv, L1-5)
-Speed: 0.6x -&gt; 0.8x (+0.05x/Lv)</t>
+          <t>Steal success: 30% -&gt; 35% -&gt; 40% -&gt; 45% -&gt; 50% (L1-5 Max)
+Speed: 0.6x -&gt; 0.8x</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -2531,12 +2611,13 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
         <is>
           <t>Attempt to steal an item from an enemy.</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Success Rate: 25% -&gt; 55% (+7.5%/Lv) | Levels: L1-5
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -2580,7 +2661,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 105% -&gt; 109 -&gt; 113 -&gt; 116 -&gt; 119 -&gt; 121 -&gt; 123 -&gt; 125 -&gt; 127 -&gt; 129%
+          <t>ATK: 105% -&gt; 109 -&gt; 113 -&gt; 116 -&gt; 119 -&gt; 121 -&gt; 123 -&gt; 125 -&gt; 127 -&gt; 129% (L10)
 TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 -&gt; 28 -&gt; 30 | Speed: 0.9x</t>
         </is>
       </c>
@@ -2593,12 +2674,13 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
         <is>
           <t>Dagger skill. Strike for guaranteed critical stab damage.</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>ATK: 130% -&gt; 145% -&gt; 160% -&gt; 175% -&gt; 190% (L1-5) | 100% Critical Hit
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -2642,7 +2724,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ATK: 170% -&gt; 182% -&gt; 194% -&gt; 204% -&gt; 212% (L1-5)
+          <t>ATK: 170% -&gt; 182% -&gt; 194% -&gt; 204% -&gt; 212% (L1-5 Max)
 TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 35 -&gt; 38 | Speed: 0.85x</t>
         </is>
       </c>
@@ -2655,12 +2737,13 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
         <is>
           <t>Dagger skill. Damage scales higher per buff and debuff on the target.</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Base ATK: 120% -&gt; 160% (+10%/Lv) | +25% dmg per active buff/debuff
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
@@ -2704,8 +2787,8 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Evasion increase: 10% -&gt; 13% -&gt; 16% -&gt; 18% -&gt; 20% (L1-5) | Turns: 4 -&gt; 8 (+1/Lv)
-TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 | Speed: 1.08x -&gt; 1.1x -&gt; 1.12x -&gt; 1.14x -&gt; 1.15x</t>
+          <t>Evasion: +10% -&gt; +13% -&gt; +16% -&gt; +18% -&gt; +20% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2719,10 +2802,15 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
           <t>Increase own physical evasion rate.</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>EVA: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
@@ -2767,7 +2855,7 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep
-TP Cost: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5)</t>
+TP Cost: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -2783,12 +2871,13 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
         <is>
           <t>Cure status ailments for a single ally.</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep
 TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 11 (L1-5)</t>
@@ -2832,8 +2921,8 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Accuracy increase (L1-10): 15% -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 -&gt; 26 -&gt; 27 -&gt; 28 -&gt; 30%
-Turns: 5 -&gt; 9 (avg +0.44/Lv) | TP Cost: 5 -&gt; 28 (avg +2.56/Lv) | Speed: 1.1x -&gt; 1.46x</t>
+          <t>Accuracy: +15% -&gt; +17 -&gt; +19 -&gt; +21 -&gt; +23 -&gt; +25 -&gt; +26 -&gt; +27 -&gt; +28 -&gt; +30% (L10)
+Turns: 5 -&gt; 9 | TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2846,15 +2935,20 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Turns, TP Cost, Speed</t>
+          <t>Turns</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
           <t>Concentrate to boost own accuracy and critical hit rate.</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Accuracy: +20% -&gt; +35% (+3.75%/Lv) | Crit: +10% -&gt; +20% (+2.5%/Lv)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
@@ -2898,8 +2992,8 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Speed increase (L1-10): 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 20%
-Turns: 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 5 -&gt; 6 | TP Cost: 14 -&gt; 32 (+2/Lv)</t>
+          <t>Speed increase: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 20% (L10)
+Turns: 3 -&gt; 6 | TP Cost: 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2910,13 +3004,18 @@
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Turns</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
         <is>
           <t>Enhance own movement and agility for increased turn speed.</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>Speed: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -2960,8 +3059,8 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Evasion increases UP | Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5)
-TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 | Speed: 0.9x</t>
+          <t>Evasion increases UP
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max) | TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2983,10 +3082,15 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
           <t>Increase own physical evasion and magic evasion.</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>Physical &amp; Magic EVA: +12% -&gt; +28% (+4%/Lv) | Levels: L1-5
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -3030,8 +3134,8 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 116% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150 -&gt; 156%
-Sleep: 20% -&gt; 50% (avg +3.33%/Lv) | TP Cost: 7 -&gt; 25 (+2/Lv) | Speed: 0.9x</t>
+          <t>ATK: 116% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150 -&gt; 156% (L10)
+TP Cost: 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -3042,17 +3146,18 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
         <is>
           <t>Sleep</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Short-range strike to one enemy. May inflict Sleep.</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>ATK: 110% -&gt; 170% (+15%/Lv) | Sleep: 30% -&gt; 60% (+7.5%/Lv)
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -3096,8 +3201,8 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 116% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150 -&gt; 156%
-Silence: 20% -&gt; 50% (avg +3.33%/Lv) | TP Cost: 7 -&gt; 25 (+2/Lv) | Speed: 0.9x</t>
+          <t>ATK: 116% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150 -&gt; 156% (L10)
+TP Cost: 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -3108,17 +3213,18 @@
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
         <is>
           <t>Silence</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Short-range strike to one enemy. May inflict Silence.</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>ATK: 110% -&gt; 170% (+15%/Lv) | Silence: 30% -&gt; 60% (+7.5%/Lv)
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -3162,8 +3268,8 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 112% -&gt; 116 -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150%
-Stun: 20% -&gt; 50% (avg +3.33%/Lv) | TP Cost: 7 -&gt; 25 (+2/Lv) | Speed: 0.9x</t>
+          <t>ATK: 112% -&gt; 116 -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150% (L10)
+TP Cost: 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -3174,17 +3280,18 @@
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
         <is>
           <t>Stun</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Short-range strike to one enemy. May inflict Stun.</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>ATK: 110% -&gt; 170% (+15%/Lv) | Stun: 25% -&gt; 50% (+6.25%/Lv)
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -3228,8 +3335,8 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Number of attacks: 3 -&gt; 5 (avg +0.22/Lv, L1-10) | ATK: 104% -&gt; 148% (avg +4.89%/Lv)
-Power decrease: 25% -&gt; 14% | TP Cost: 30 -&gt; 72 (avg +4.67/Lv) | Speed: 0.75x -&gt; 0.85x</t>
+          <t>Number of attacks: 3 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 | ATK: 104% -&gt; 148%
+TP Cost: 30 -&gt; 34 -&gt; 38 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 58 -&gt; 64 -&gt; 68 -&gt; 72</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -3242,15 +3349,20 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Number of attacks, ATK, Power decrease, TP Cost, Speed</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
+          <t>Power, Speed</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
           <t>Bow and gun skill. Rapid fire multiple shots with escalating crit rate.</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>Hits: 2 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 | ATK: 65% -&gt; 85% per hit (+5%/Lv)
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25</t>
@@ -3294,8 +3406,8 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ATK: 114% -&gt; 130% (+4%/Lv, L1-5)
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 | Speed: 1x -&gt; 1.12x (+0.03x/Lv)</t>
+          <t>ATK: 114% -&gt; 118% -&gt; 122% -&gt; 126% -&gt; 130% (L1-5 Max)
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 | Speed: 1x -&gt; 1.12x</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -3307,12 +3419,13 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
         <is>
           <t>Bow and gun skill. Fire a precision shot guaranteed to never miss.</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>ATK: 125% -&gt; 140% -&gt; 155% -&gt; 170% -&gt; 185% (L1-5) | 100% Accuracy
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -3357,7 +3470,7 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>Damage UP
-TP Cost: 42 -&gt; 50 -&gt; 57 -&gt; 63 -&gt; 68 (L1-5) | Speed: 0.4x</t>
+TP Cost: 42 -&gt; 50 -&gt; 57 -&gt; 63 -&gt; 68 (L1-5 Max) | Speed: 0.4x</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -3377,12 +3490,13 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
         <is>
           <t>Bow skill. Unleash a piercing arrow with boosted critical strike rate.</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>ATK: 150% -&gt; 170% -&gt; 190% -&gt; 210% -&gt; 230% (L1-5) | Crit Rate: +30%
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
@@ -3426,8 +3540,8 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170%
-Poison: 20% -&gt; 50% (avg +3.33%/Lv) | TP Cost: 7 -&gt; 25 (+2/Lv)</t>
+          <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170% (L10)
+Poison: 20% -&gt; 50% | TP Cost: 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -3443,12 +3557,13 @@
           <t>Poison</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
         <is>
           <t>Bow and gun skill. Attack one enemy with a toxic shot. May poison.</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>ATK: 110% -&gt; 170% (+15%/Lv) | Poison: 30% -&gt; 60% (+7.5%/Lv)
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -3492,8 +3607,8 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170%
-Freeze: 20% -&gt; 50% (avg +3.33%/Lv) | TP Cost: 8 -&gt; 26 (+2/Lv)</t>
+          <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170% (L10)
+Freeze: 20% -&gt; 50% | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -3509,12 +3624,13 @@
           <t>Freeze</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
         <is>
           <t>Bow skill. Attack one enemy with a chilling shot. May freeze.</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>ATK: 115% -&gt; 175% (+15%/Lv) | Freeze: 25% -&gt; 50% (+6.25%/Lv)
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -3558,8 +3674,8 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170%
-Paralysis: 20% -&gt; 50% (avg +3.33%/Lv) | TP Cost: 8 -&gt; 26 (+2/Lv)</t>
+          <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170% (L10)
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -3570,17 +3686,18 @@
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
         <is>
           <t>Paralysis</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Bow skill. Attack one enemy with an electric shot. May paralyze.</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>ATK: 115% -&gt; 175% (+15%/Lv) | Paralysis: 25% -&gt; 50% (+6.25%/Lv)
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -3624,8 +3741,8 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 116% -&gt; 122 -&gt; 128 -&gt; 134 -&gt; 140 -&gt; 145 -&gt; 150 -&gt; 155 -&gt; 160 -&gt; 165%
-Slow: 20% -&gt; 50% (avg +3.33%/Lv) | TP Cost: 9 -&gt; 27 (+2/Lv) | Speed: 0.95x</t>
+          <t>ATK: 116% -&gt; 122 -&gt; 128 -&gt; 134 -&gt; 140 -&gt; 145 -&gt; 150 -&gt; 155 -&gt; 160 -&gt; 165% (L10)
+TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 -&gt; 27 | Speed: 0.95x</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -3636,17 +3753,18 @@
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
         <is>
           <t>Slow</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Bow skill. Deal stab damage to one enemy. May slow.</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>ATK: 115% -&gt; 175% (+15%/Lv) | Slow: 25% -&gt; 50% (+6.25%/Lv)
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -3690,7 +3808,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 84% -&gt; 88 -&gt; 92 -&gt; 96 -&gt; 100 -&gt; 103 -&gt; 106 -&gt; 109 -&gt; 112 -&gt; 115%
+          <t>ATK: 84% -&gt; 88 -&gt; 92 -&gt; 96 -&gt; 100 -&gt; 103 -&gt; 106 -&gt; 109 -&gt; 112 -&gt; 115% (L10)
 TP Cost: 20 -&gt; 23 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 | Speed: 0.65x</t>
         </is>
       </c>
@@ -3703,12 +3821,13 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
         <is>
           <t>Bow skill. Fire an arrow volley striking all enemies on screen.</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>ATK: 95% -&gt; 110% -&gt; 125% -&gt; 140% -&gt; 155% (L1-5 Max)
 TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28</t>
@@ -3752,8 +3871,8 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Damage UP | TP Cost (L1-10): 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 59 -&gt; 62
-Speed: 0.82x</t>
+          <t>Damage UP
+TP Cost: 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 59 -&gt; 62 | Speed: 0.82x</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -3773,12 +3892,13 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
         <is>
           <t>Bow skill. Shower random enemies with arrows over multiple turns.</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>Hits: 3-5 arrows per wave | ATK: 70% -&gt; 95% per arrow (+6.25%/Lv)
 Duration: 2 -&gt; 3 turns | TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
@@ -3822,7 +3942,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ATK: 130% -&gt; 234% (avg +11.56%/Lv, L1-10) | Critical rate: 5 -&gt; 25 (avg +2.22/Lv)
+          <t>ATK: 130% -&gt; 144 -&gt; 158 -&gt; 171 -&gt; 184 -&gt; 196 -&gt; 207 -&gt; 217 -&gt; 226 -&gt; 234% (L10)
 TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 36 -&gt; 40 -&gt; 43 -&gt; 46 -&gt; 49 -&gt; 52 -&gt; 55 | Speed: 0.7x</t>
         </is>
       </c>
@@ -3834,17 +3954,18 @@
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>ATK, Critical rate</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
+          <t>Critical rate</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
           <t>Bow skill. Massive piercing shot that penetrates through to the back row.</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>ATK: 175% -&gt; 200% -&gt; 225% -&gt; 250% -&gt; 280% (L1-5 Max)
 TP Cost: 18 -&gt; 22 -&gt; 26 -&gt; 30 -&gt; 34 | Hits both front and back target</t>
@@ -3888,7 +4009,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 94% -&gt; 97 -&gt; 100 -&gt; 103 -&gt; 106 -&gt; 110 -&gt; 114 -&gt; 119 -&gt; 124 -&gt; 130%
+          <t>ATK: 94% -&gt; 97 -&gt; 100 -&gt; 103 -&gt; 106 -&gt; 110 -&gt; 114 -&gt; 119 -&gt; 124 -&gt; 130% (L10)
 Turns: 4 | TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50</t>
         </is>
       </c>
@@ -3904,13 +4025,14 @@
           <t>effect_4</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3949,7 +4071,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ATK: 120% -&gt; 192% (avg +8%/Lv, L1-10) | Stun: 10% -&gt; 20% (avg +1.11%/Lv)
+          <t>ATK: 120% -&gt; 126 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 154 -&gt; 162 -&gt; 170 -&gt; 180 -&gt; 192% (L10)
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36 | Speed: 0.45x</t>
         </is>
       </c>
@@ -3961,17 +4083,18 @@
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>ATK, Stun</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
+          <t>Stun</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
           <t>Deal bash damage to one enemy. May stun.</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>ATK: 130% -&gt; 190% (+15%/Lv) | Stun: 30% -&gt; 60% (+7.5%/Lv)
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
@@ -4014,7 +4137,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Identification success rate: 32% -&gt; 80% (+12%/Lv, L1-5)
+          <t>Identification success rate: 32% -&gt; 44% -&gt; 56% -&gt; 68% -&gt; 80% (L1-5 Max)
 TP Cost: 10 -&gt; 8 -&gt; 6 -&gt; 4 -&gt; 2</t>
         </is>
       </c>
@@ -4027,12 +4150,13 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
         <is>
           <t>Identify unknown dungeon loot items.</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>Success Rate: 70% -&gt; 98% (+7%/Lv) | Levels: L1-5
 TP Cost: 5 -&gt; 4 -&gt; 3 -&gt; 2 -&gt; 1 (Max)</t>
@@ -4076,8 +4200,8 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Magic damage increase: 38% -&gt; 42% -&gt; 47% -&gt; 53% -&gt; 60% (L1-5)
-Magic accuracy decrease: 2% -&gt; 10% (+2%/Lv) | TP Cost: 20 -&gt; 32 | Speed: 1.5x -&gt; 2.1x</t>
+          <t>Magic damage: +38% -&gt; +42% -&gt; +47% -&gt; +53% -&gt; +60% (L1-5 Max)
+Turns: 6 | TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 32 | Speed: 1.5x -&gt; 2.1x</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -4088,13 +4212,14 @@
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Turns, TP Cost, Speed</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Magic accuracy</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4133,7 +4258,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: +10% -&gt; +30% (avg +2.22%/Lv, L1-10)
+          <t>Accuracy: +10% -&gt; +12 -&gt; +14 -&gt; +16 -&gt; +18 -&gt; +20 -&gt; +22 -&gt; +24 -&gt; +26 -&gt; +30% (L10)
 TP Cost: 28 -&gt; 32 -&gt; 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 56 -&gt; 60 -&gt; 64 | Speed: 0.75x</t>
         </is>
       </c>
@@ -4153,17 +4278,18 @@
           <t>effect_3</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
+          <t>Damage UP</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
           <t>Mace skill. Heavy bash strike with boosted accuracy.</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>ATK: 140% -&gt; 200% (+15%/Lv) | Accuracy: +25% -&gt; +45% (+5%/Lv)
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
@@ -4207,8 +4333,8 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 135% -&gt; 147 -&gt; 159 -&gt; 171 -&gt; 183 -&gt; 193 -&gt; 203 -&gt; 213 -&gt; 220 -&gt; 225%
-Turns: 4 | TP Cost: 25 -&gt; 57 (avg +3.56/Lv) | Speed: 0.9x -&gt; 1.16x</t>
+          <t>ATK: 135% -&gt; 147 -&gt; 159 -&gt; 171 -&gt; 183 -&gt; 193 -&gt; 203 -&gt; 213 -&gt; 220 -&gt; 225% (L10)
+Turns: 4 | TP Cost: 25 -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 48 -&gt; 51 -&gt; 54 -&gt; 57</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -4219,17 +4345,18 @@
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>TP Cost, Speed</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
           <t>Mace skill. Strike target and reduce enemy physical DEF by 10%.</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>ATK: 125% -&gt; 185% (+15%/Lv) | Inflicts -10% DEF debuff
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 | Fast turn recovery (0.85x delay)</t>
@@ -4273,8 +4400,8 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 120% -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 148 -&gt; 154 -&gt; 160%
-TP Cost: 36 -&gt; 79 (avg +4.78/Lv) | Speed: 0.8x -&gt; 0.98x (+0.02x/Lv)</t>
+          <t>ATK: 120% -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 148 -&gt; 154 -&gt; 160% (L10)
+TP Cost: 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 57 -&gt; 62 -&gt; 67 -&gt; 73 -&gt; 79</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -4285,17 +4412,18 @@
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>TP Cost</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
           <t>Sword skill. Deal slash damage to all enemies on screen.</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 160% (+10%/Lv, L1-5) | Hits all foes
 TP Cost: 36 -&gt; 46 -&gt; 57 -&gt; 68 -&gt; 79 | Action delay: 0.80x -&gt; 0.98x</t>
@@ -4339,8 +4467,8 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Damage reduction: 18% -&gt; 36% (+2%/Lv, L1-10) | Turns: 4 -&gt; 7 (avg +0.33/Lv)
-TP Cost: 22 -&gt; 56 (avg +3.78/Lv) | Speed: 0.75x -&gt; 0.85x</t>
+          <t>Damage reduction: 18% -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36% (L10)
+Turns: 4 -&gt; 7 | TP Cost: 22 -&gt; 25 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 56</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -4353,11 +4481,16 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Turns, TP Cost, Speed</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>Turns</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4396,7 +4529,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Stat increase: 20% -&gt; 32% (+3%/Lv, L1-5)
+          <t>Stat: +20% -&gt; +23% -&gt; +26% -&gt; +29% -&gt; +32% (L1-5 Max)
 Turns: 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 6 | TP Cost: 52 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 92 | Speed: 1.25x</t>
         </is>
       </c>
@@ -4409,12 +4542,13 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
         <is>
           <t>Transform into Magical Princess, raising all stats.</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>All Stats: +15% -&gt; +35% (+5%/Lv) | Levels: L1-5
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32</t>
@@ -4458,7 +4592,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>ATK: 136% -&gt; 216% (avg +8.89%/Lv, L1-10) | Accuracy: +10% -&gt; +20% (avg +1.11%/Lv)
+          <t>ATK: 136% -&gt; 142 -&gt; 148 -&gt; 155 -&gt; 162 -&gt; 172 -&gt; 182 -&gt; 193 -&gt; 204 -&gt; 216% (L10)
 TP Cost: 13 -&gt; 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 | Speed: 0.9x -&gt; 1x</t>
         </is>
       </c>
@@ -4470,17 +4604,18 @@
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>ATK, Accuracy, Speed</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
           <t>Short-range strike dealing heavy lightning damage to one enemy.</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>ATK: 136% -&gt; 216% (+20%/Lv, L1-5) | Lightning element
 TP Cost: 13 -&gt; 20 -&gt; 28 -&gt; 36 -&gt; 45</t>
@@ -4524,8 +4659,8 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 150% -&gt; 162 -&gt; 174 -&gt; 186 -&gt; 198 -&gt; 208 -&gt; 218 -&gt; 228 -&gt; 236 -&gt; 244%
-Freeze: 20% -&gt; 50% (avg +3.33%/Lv) | Silence: 20% -&gt; 50% | TP Cost: 9 -&gt; 36 (+3/Lv)</t>
+          <t>ATK: 150% -&gt; 162 -&gt; 174 -&gt; 186 -&gt; 198 -&gt; 208 -&gt; 218 -&gt; 228 -&gt; 236 -&gt; 244% (L10)
+Freeze: 20% -&gt; 50% | TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -4538,11 +4673,16 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Freeze, Silence</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>Freeze</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Silence</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4581,7 +4721,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Turns (L1-10): 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24
+          <t>Turns: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24
 TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 36 -&gt; 40 -&gt; 43 -&gt; 46 -&gt; 49 -&gt; 52 -&gt; 55</t>
         </is>
       </c>
@@ -4596,6 +4736,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4639,6 +4780,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4676,7 +4818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>HP recovery: 12% -&gt; 15% -&gt; 18% -&gt; 21% -&gt; 25% (L1-5)</t>
+          <t>HP recovery: 12% -&gt; 15% -&gt; 18% -&gt; 21% -&gt; 25% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -4688,12 +4830,13 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
         <is>
           <t>Heal one ally's HP.</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>Heal: 12% -&gt; 15% -&gt; 18% -&gt; 21% -&gt; 25% Max HP (L1-5 Max)
 TP Cost: 2 -&gt; 4 -&gt; 6 -&gt; 8 -&gt; 10 | Affected by Maid Mastery (+10% cap)</t>
@@ -4736,7 +4879,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>TP recovery: 10% -&gt; 11% -&gt; 12% -&gt; 13% -&gt; 15% (L1-5)
+          <t>TP recovery: 10% -&gt; 11% -&gt; 12% -&gt; 13% -&gt; 15% (L1-5 Max)
 Speed: 0.85x</t>
         </is>
       </c>
@@ -4749,12 +4892,13 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
         <is>
           <t>Prepare a snack to restore one ally's TP.</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>TP Heal: 10% -&gt; 11% -&gt; 12% -&gt; 13% -&gt; 15% Max TP (L1-5)
 Action delay: 0.85x | TP Cost: 0 (Costs no TP to use)</t>
@@ -4797,7 +4941,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>TP transfer bonus: 100% -&gt; 140% (+10%/Lv, L1-5)</t>
+          <t>TP transfer bonus: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -4809,12 +4953,13 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
         <is>
           <t>Sacrifice all user TP to transfer a magnified amount to an ally.</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>TP Transferred: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% of user's TP (L1-5)
 Leaves user at 0 TP | Fast recovery</t>
@@ -4857,7 +5002,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Speed increase: 12% -&gt; 20% (+2%/Lv, L1-5)
+          <t>Speed increase: 12% -&gt; 14% -&gt; 16% -&gt; 18% -&gt; 20% (L1-5 Max)
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10</t>
         </is>
       </c>
@@ -4870,12 +5015,13 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
         <is>
           <t>Clean up battle area to grant party action speed boost.</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>Speed: +12% -&gt; +14% -&gt; +16% -&gt; +18% -&gt; +20% (L1-5)
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
@@ -4918,7 +5064,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>TP recovery: 16% -&gt; 18% -&gt; 20% -&gt; 22% -&gt; 25% (L1-5)
+          <t>TP recovery: 16% -&gt; 18% -&gt; 20% -&gt; 22% -&gt; 25% (L1-5 Max)
 Speed: 0.9x</t>
         </is>
       </c>
@@ -4931,12 +5077,13 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
         <is>
           <t>Focus divine power to restore own TP.</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>TP Restore: 16% -&gt; 25% Max TP (+2.25%/Lv) | Levels: L1-5
 TP Cost: 0 | Action delay: 1.00x</t>
@@ -4979,7 +5126,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ATK decrease (L1-10): 4% -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16%
+          <t>ATK: -4% -&gt; -6 -&gt; -8 -&gt; -10 -&gt; -11 -&gt; -12 -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16% (L10)
 Speed: 0.75x</t>
         </is>
       </c>
@@ -4992,12 +5139,13 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
         <is>
           <t>Dance skill. Lower all enemies' physical ATK while dance lasts.</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>Enemy ATK: -12% -&gt; -24% (-3%/Lv) | Levels: L1-5
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -5040,7 +5188,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>DEF decrease: 5% -&gt; 23% (+2%/Lv, L1-10)
+          <t>DEF: -5% -&gt; -7 -&gt; -9 -&gt; -11 -&gt; -13 -&gt; -15 -&gt; -17 -&gt; -19 -&gt; -21 -&gt; -23% (L10)
 Speed: 0.75x</t>
         </is>
       </c>
@@ -5053,12 +5201,13 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
         <is>
           <t>Dance skill. Lower all enemies' physical DEF while dance lasts.</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>Enemy DEF: -12% -&gt; -24% (-3%/Lv) | Levels: L1-5
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -5101,7 +5250,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Accuracy decrease: 4% -&gt; 13% (+1%/Lv, L1-10)
+          <t>Accuracy: -4% -&gt; -5 -&gt; -6 -&gt; -7 -&gt; -8 -&gt; -9 -&gt; -10 -&gt; -11 -&gt; -12 -&gt; -13% (L10)
 Speed: 0.75x</t>
         </is>
       </c>
@@ -5116,6 +5265,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5153,7 +5303,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Evasion decrease: 5% -&gt; 23% (+2%/Lv, L1-10)
+          <t>Evasion: -5% -&gt; -7 -&gt; -9 -&gt; -11 -&gt; -13 -&gt; -15 -&gt; -17 -&gt; -19 -&gt; -21 -&gt; -23% (L10)
 Speed: 0.75x</t>
         </is>
       </c>
@@ -5168,6 +5318,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5229,6 +5380,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5266,7 +5418,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Speed decrease: 5% -&gt; 14% (+1%/Lv, L1-10)
+          <t>Speed decrease: 5% -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14% (L10)
 Speed: 0.75x</t>
         </is>
       </c>
@@ -5281,6 +5433,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5318,7 +5471,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Resistance decrease: 7 -&gt; 25 (+2/Lv, L1-10)
+          <t>Resistance decrease: 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 (L10)
 Speed: 0.75x</t>
         </is>
       </c>
@@ -5333,6 +5486,7 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5371,8 +5525,8 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 120% -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 145 -&gt; 150 -&gt; 155 -&gt; 160%
-TP Cost: 22 -&gt; 50 (avg +3.11/Lv) | Speed: 0.75x -&gt; 0.85x</t>
+          <t>ATK: 120% -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 145 -&gt; 150 -&gt; 155 -&gt; 160% (L10)
+TP Cost: 22 -&gt; 25 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 46 -&gt; 50</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -5383,17 +5537,18 @@
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>TP Cost, Speed</t>
-        </is>
-      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
           <t>Whip skill. Deal bash damage to an enemy row from mid-range.</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 180% (+15%/Lv) | Row bash attack
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 (L1-5)</t>
@@ -5437,8 +5592,8 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ATK: 107% -&gt; 114% -&gt; 121% -&gt; 128% -&gt; 136% (L1-5)
-TP Cost: 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 | Speed: 0.75x -&gt; 0.77x -&gt; 0.78x -&gt; 0.79x -&gt; 0.8x</t>
+          <t>ATK: 107% -&gt; 114% -&gt; 121% -&gt; 128% -&gt; 136% (L1-5 Max)
+TP Cost: 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 | Speed: 0.75x -&gt; 0.8x</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -5452,6 +5607,7 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5490,8 +5646,8 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ATK: 135% -&gt; 142% -&gt; 149% -&gt; 157% -&gt; 165% (L1-5) | Silence: 25% -&gt; 37% (+3%/Lv)
-Paralysis: 20% -&gt; 32% (+3%/Lv) | TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 | Speed: 0.9x</t>
+          <t>ATK: 135% -&gt; 142% -&gt; 149% -&gt; 157% -&gt; 165% (L1-5 Max) | Silence: 25% (+3%/Lv)
+Paralysis: 20% -&gt; 23% -&gt; 26% -&gt; 29% -&gt; 32% | TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -5503,8 +5659,13 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5543,8 +5704,8 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 104% -&gt; 108 -&gt; 112 -&gt; 116 -&gt; 120 -&gt; 124 -&gt; 127 -&gt; 130 -&gt; 133 -&gt; 136%
-TP Cost: 27 -&gt; 60 (avg +3.67/Lv) | Speed: 0.6x -&gt; 0.7x</t>
+          <t>ATK: 104% -&gt; 108 -&gt; 112 -&gt; 116 -&gt; 120 -&gt; 124 -&gt; 127 -&gt; 130 -&gt; 133 -&gt; 136% (L10)
+TP Cost: 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 56 -&gt; 60</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -5555,17 +5716,18 @@
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>TP Cost, Speed</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
           <t>High risk gamble. Unleash 0 to 4 strikes on random enemies.</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>ATK per hit: 90% -&gt; 110% -&gt; 130% -&gt; 150% -&gt; 180% (L1-5)
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 | Boosted by Trump / High Risk</t>
@@ -5609,7 +5771,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>HP recovery: 20% -&gt; 40% (+5%/Lv, L1-5)
+          <t>HP recovery: 20% -&gt; 25% -&gt; 30% -&gt; 35% -&gt; 40% (L1-5 Max)
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Speed: 1.5x</t>
         </is>
       </c>
@@ -5622,12 +5784,13 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
         <is>
           <t>Take a rest to restore own HP and raise Pep. Fast turn recovery.</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>Heal: 20% -&gt; 25% -&gt; 30% -&gt; 35% -&gt; 40% Max HP (L1-5 Max)
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Action delay: 1.50x (fast)</t>
@@ -5676,6 +5839,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5714,8 +5878,8 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 120% -&gt; 126 -&gt; 132 -&gt; 138 -&gt; 142 -&gt; 150 -&gt; 158 -&gt; 168 -&gt; 178 -&gt; 190%
-Instakill: 15% -&gt; 25% (avg +1.11%/Lv) | TP Cost: 17 -&gt; 35 (+2/Lv) | Speed: 0.88x</t>
+          <t>ATK: 120% -&gt; 126 -&gt; 132 -&gt; 138 -&gt; 142 -&gt; 150 -&gt; 158 -&gt; 168 -&gt; 178 -&gt; 190% (L10)
+TP Cost: 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 -&gt; 27 -&gt; 29 -&gt; 31 -&gt; 33 -&gt; 35 | Speed: 0.88x</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -5726,17 +5890,18 @@
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
         <is>
           <t>Instakill</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>Attack one enemy. May instakill.</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>ATK: 140% -&gt; 200% (+15%/Lv) | Instakill Chance: 15% -&gt; 35% (+5%/Lv)
 TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28 (L1-5)</t>
@@ -5780,7 +5945,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>ATK: 95% -&gt; 131% (+4%/Lv, L1-10) | Stun: 40% -&gt; 70% (avg +3.33%/Lv)
+          <t>ATK: 95% -&gt; 99 -&gt; 103 -&gt; 107 -&gt; 111 -&gt; 115 -&gt; 119 -&gt; 123 -&gt; 127 -&gt; 131% (L10)
 TP Cost: 32 -&gt; 34 -&gt; 36 -&gt; 38 -&gt; 40 -&gt; 42 -&gt; 44 -&gt; 46 -&gt; 48 -&gt; 50 | Speed: 0.65x</t>
         </is>
       </c>
@@ -5792,13 +5957,14 @@
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
         <is>
           <t>Stun</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5837,8 +6003,8 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ATK: 15% -&gt; 35% (+5%/Lv, L1-5) | DEF decrease: 11% -&gt; 14% -&gt; 17% -&gt; 21% -&gt; 25%
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 16 (+2/Lv) | Speed: 1.25x -&gt; 2x</t>
+          <t>ATK: 15% -&gt; 20% -&gt; 25% -&gt; 30% -&gt; 35% (L1-5 Max) | DEF: -11% -&gt; -25%
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -5851,15 +6017,20 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>Greatly boost own physical ATK at the cost of reducing DEF to 0.</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>ATK: +40% -&gt; +80% (+10%/Lv) | User DEF reduced to 0
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
@@ -5908,6 +6079,7 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5946,7 +6118,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Conversion success: 35% -&gt; 42% -&gt; 49% -&gt; 57% -&gt; 65% (L1-5)
+          <t>Conversion success: 35% -&gt; 42% -&gt; 49% -&gt; 57% -&gt; 65% (L1-5 Max)
 TP Cost: 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 | Speed: 0.85x</t>
         </is>
       </c>
@@ -5961,6 +6133,7 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5999,8 +6172,8 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 164 -&gt; 170 -&gt; 176%
-Poison: 50% -&gt; 80% (avg +3.33%/Lv) | TP Cost: 22 -&gt; 58 (+4/Lv) | Speed: 0.6x -&gt; 0.7x</t>
+          <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 164 -&gt; 170 -&gt; 176% (L10)
+TP Cost: 22 -&gt; 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -6011,13 +6184,14 @@
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
         <is>
           <t>Poison, Speed</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6056,7 +6230,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ATK: 150% -&gt; 256% (avg +11.78%/Lv, L1-10) | Turn delay rate: 25% -&gt; 43% (+2%/Lv)
+          <t>ATK: 150% -&gt; 162 -&gt; 174 -&gt; 186 -&gt; 198 -&gt; 208 -&gt; 218 -&gt; 228 -&gt; 240 -&gt; 256% (L10)
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 32 | Speed: 0.95x</t>
         </is>
       </c>
@@ -6068,17 +6242,18 @@
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
+          <t>Turn delay rate</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
           <t>Fan skill. Deal bash damage to one enemy and delay target turn.</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 180% (+15%/Lv) | Action Delay: -20% -&gt; -40%
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
@@ -6132,6 +6307,7 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6170,7 +6346,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ATK: 130% -&gt; 202% (+8%/Lv, L1-10) | Slow: 25% -&gt; 45% | Accuracy: -5% -&gt; +13% (+2%/Lv)
+          <t>ATK: 130% (+8%/Lv) -&gt; 202% (L10 Max) | Slow: 25% -&gt; 45% | Accuracy: -5% (+2%/Lv)
 TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50 | Speed: 0.75x</t>
         </is>
       </c>
@@ -6189,6 +6365,7 @@
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6227,7 +6404,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>ATK: 88% -&gt; 92% -&gt; 97% -&gt; 103% -&gt; 110% (L1-5) | Max HP reduction: 50% -&gt; 100%
+          <t>ATK: 88% -&gt; 92% -&gt; 97% -&gt; 103% -&gt; 110% (L1-5 Max) | Max HP reduction: 50% -&gt; 100%
 Turns: 6 | TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 23 -&gt; 25 | Speed: 0.85x</t>
         </is>
       </c>
@@ -6246,6 +6423,7 @@
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6284,7 +6462,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>DEF conversion bonus: 60% -&gt; 80% -&gt; 100% -&gt; 125% -&gt; 150% (L1-5)
+          <t>DEF conversion bonus: 60% -&gt; 80% -&gt; 100% -&gt; 125% -&gt; 150% (L1-5 Max)
 Turns: 2 | TP Cost: 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 | Speed: 1.15x</t>
         </is>
       </c>
@@ -6297,12 +6475,13 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr">
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
         <is>
           <t>Convert current DEF to bonus ATK (user DEF becomes 0).</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>ATK Bonus: 100% -&gt; 150% of converted DEF value (+12.5%/Lv)
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
@@ -6351,6 +6530,7 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6389,7 +6569,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>ATK (L1-10): 118% -&gt; 122 -&gt; 126 -&gt; 130 -&gt; 134 -&gt; 138 -&gt; 142 -&gt; 145 -&gt; 148 -&gt; 151%
+          <t>ATK: 118% -&gt; 122 -&gt; 126 -&gt; 130 -&gt; 134 -&gt; 138 -&gt; 142 -&gt; 145 -&gt; 148 -&gt; 151% (L10)
 Accuracy UP | TP Cost: 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40</t>
         </is>
       </c>
@@ -6405,13 +6585,14 @@
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6450,8 +6631,8 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>ATK UP | Duration UP | TP Cost: 20 -&gt; 42 (avg +2.44/Lv, L1-10)
-Speed: 0.85x -&gt; 0.86 -&gt; 0.87 -&gt; 0.88 -&gt; 0.89 -&gt; 0.9 -&gt; 0.92 -&gt; 0.94 -&gt; 0.96 -&gt; 0.98x</t>
+          <t>ATK UP | Duration UP
+TP Cost: 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -6470,17 +6651,18 @@
           <t>effect_1, effect_3</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>TP Cost</t>
-        </is>
-      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
           <t>Summon puppet Spartan to attack enemies with short-range bash strikes.</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
+      <c r="P97" t="inlineStr">
         <is>
           <t>Puppet Power: 100% -&gt; 160% (+15%/Lv) | Duration: 4 -&gt; 6 turns
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 (L1-5)</t>
@@ -6525,7 +6707,7 @@
       <c r="H98" t="inlineStr">
         <is>
           <t>ATK UP | Duration UP | Paralysis rate UP
-TP Cost (L1-10): 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 44 -&gt; 46 -&gt; 48</t>
+TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 44 -&gt; 46 -&gt; 48 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -6544,13 +6726,10 @@
           <t>effect_1, effect_3</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6590,7 +6769,7 @@
       <c r="H99" t="inlineStr">
         <is>
           <t>HP recovery UP | Duration UP
-TP Cost: 30 -&gt; 33 -&gt; 37 -&gt; 42 -&gt; 48 (L1-5) | Speed: 0.9x</t>
+TP Cost: 30 -&gt; 33 -&gt; 37 -&gt; 42 -&gt; 48 (L1-5 Max) | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -6610,12 +6789,13 @@
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr">
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
         <is>
           <t>Summon puppet Catalina to heal party members' HP.</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>Heal Potency: 20% -&gt; 40% Max HP (+5%/Lv) | Duration: 4 -&gt; 6 turns
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 (L1-5)</t>
@@ -6660,7 +6840,7 @@
       <c r="H100" t="inlineStr">
         <is>
           <t>ATK UP | Duration UP
-TP Cost (L1-10): 42 -&gt; 44 -&gt; 46 -&gt; 48 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 60 -&gt; 64 -&gt; 70</t>
+TP Cost: 42 -&gt; 44 -&gt; 46 -&gt; 48 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 60 -&gt; 64 -&gt; 70 | Speed: 0.75x</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -6679,13 +6859,10 @@
           <t>effect_1, effect_3</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6725,7 +6902,7 @@
       <c r="H101" t="inlineStr">
         <is>
           <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
-TP Cost (L1-8): 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 38 | Speed: 1.15x</t>
+TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 38 | Speed: 1.15x</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -6741,12 +6918,13 @@
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr">
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
         <is>
           <t>Summon puppet Perdurabo to cure allies' status ailments.</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>Cures status ailments for 2 allies per turn | Duration: 4 -&gt; 6 turns
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 (L1-5)</t>
@@ -6791,7 +6969,7 @@
       <c r="H102" t="inlineStr">
         <is>
           <t>Doll magic damage UP | Doll magic accuracy UP
-TP Cost (L1-7): 38 -&gt; 42 -&gt; 46 -&gt; 51 -&gt; 56 -&gt; 62 -&gt; 68 | Speed: 0.82x -&gt; 0.92x</t>
+TP Cost: 38 -&gt; 42 -&gt; 46 -&gt; 51 -&gt; 56 -&gt; 62 -&gt; 68 | Speed: 0.82x -&gt; 0.92x</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -6810,17 +6988,14 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
         <is>
           <t>Summon puppet Musiy to cast immediate single-target attack spells.</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
+      <c r="P102" t="inlineStr">
         <is>
           <t>Spell Pwr: 120 -&gt; 240 (+30/Lv) | Duration: 4 -&gt; 6 turns
 TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 (L1-5)</t>
@@ -6879,6 +7054,7 @@
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6932,6 +7108,7 @@
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6985,6 +7162,7 @@
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7038,6 +7216,7 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7091,6 +7270,7 @@
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7144,6 +7324,7 @@
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7197,6 +7378,7 @@
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7250,6 +7432,7 @@
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7303,6 +7486,7 @@
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7356,6 +7540,7 @@
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7409,6 +7594,7 @@
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7462,6 +7648,7 @@
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7515,6 +7702,7 @@
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7568,6 +7756,7 @@
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7621,6 +7810,7 @@
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7674,6 +7864,7 @@
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7727,6 +7918,7 @@
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7780,6 +7972,7 @@
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7833,6 +8026,7 @@
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7886,6 +8080,7 @@
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7939,6 +8134,7 @@
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7992,6 +8188,7 @@
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8045,6 +8242,7 @@
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8098,6 +8296,7 @@
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8151,6 +8350,7 @@
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8204,6 +8404,7 @@
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8257,6 +8458,7 @@
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8310,6 +8512,7 @@
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8363,6 +8566,7 @@
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8416,6 +8620,7 @@
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8469,6 +8674,7 @@
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8522,6 +8728,7 @@
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8575,6 +8782,7 @@
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8628,6 +8836,7 @@
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8681,6 +8890,7 @@
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8734,6 +8944,7 @@
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8787,6 +8998,7 @@
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8840,6 +9052,7 @@
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8893,6 +9106,7 @@
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8946,6 +9160,7 @@
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8999,6 +9214,7 @@
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9052,6 +9268,7 @@
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9090,8 +9307,8 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Pwr: 70 -&gt; 520 (avg +50/Lv, L1-10) | Accuracy: 86% -&gt; 95% (+1%/Lv)
-TP Cost: 5 -&gt; 32 (avg +3/Lv) | Speed: 2.25x | Chant: 1.15x -&gt; 1.06x (-0.01x/Lv)</t>
+          <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
+TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Speed: 2.25x</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -9102,17 +9319,18 @@
       </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>Pwr, TP Cost</t>
-        </is>
-      </c>
+      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
           <t>Deal fire damage to one enemy.</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr">
+      <c r="P145" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
 TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
@@ -9156,8 +9374,8 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Pwr: 90 -&gt; 530 (avg +48.89/Lv, L1-10) | Accuracy: 80% -&gt; 90% (avg +1.11%/Lv)
-TP Cost: 15 -&gt; 60 (avg +5/Lv) | Speed: 1.7x | Chant: 0.88x -&gt; 0.78x</t>
+          <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
+TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 | Speed: 1.7x</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -9168,17 +9386,18 @@
       </c>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>Pwr, Accuracy, TP Cost, Chant</t>
-        </is>
-      </c>
+      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
           <t>Deal fire damage to an enemy row.</t>
         </is>
       </c>
-      <c r="O146" t="inlineStr">
+      <c r="P146" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
 TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
@@ -9222,8 +9441,8 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Pwr: 300 -&gt; 750 (avg +50/Lv, L1-10) | Accuracy: 75% -&gt; 85% (avg +1.11%/Lv)
-TP Cost: 42 -&gt; 120 (avg +8.67/Lv) | Speed: 1.3x | Chant: 0.7x -&gt; 0.6x</t>
+          <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
+TP Cost: 42 -&gt; 50 -&gt; 58 -&gt; 64 -&gt; 73 -&gt; 82 -&gt; 91 -&gt; 100 -&gt; 110 -&gt; 120 | Speed: 1.3x</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -9234,17 +9453,18 @@
       </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>Pwr, Accuracy, TP Cost, Chant</t>
-        </is>
-      </c>
+      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
           <t>Deal fire damage to all enemies.</t>
         </is>
       </c>
-      <c r="O147" t="inlineStr">
+      <c r="P147" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
 TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
@@ -9288,7 +9508,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5) | Accuracy: 82% -&gt; 90% (+2%/Lv)
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max) | Accuracy: 82% (+2%/Lv)
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84 | Speed: 1.5x | Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
@@ -9300,17 +9520,14 @@
       </c>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>Chant</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
         <is>
           <t>Unleash devastating master fire magic on one enemy. Pierces 50 Elemental Res.</t>
         </is>
       </c>
-      <c r="O148" t="inlineStr">
+      <c r="P148" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
 TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
@@ -9354,8 +9571,8 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Pwr: 70 -&gt; 520 (avg +50/Lv, L1-10) | Accuracy: 86% -&gt; 95% (+1%/Lv)
-TP Cost: 5 -&gt; 32 (avg +3/Lv) | Speed: 2.25x | Chant: 1.15x -&gt; 1.06x (-0.01x/Lv)</t>
+          <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
+TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Speed: 2.25x</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -9366,17 +9583,18 @@
       </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>Pwr, TP Cost</t>
-        </is>
-      </c>
+      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
           <t>Deal water damage to one enemy.</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr">
+      <c r="P149" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
 TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 (Lv1 to Max)</t>
@@ -9420,8 +9638,8 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Pwr: 90 -&gt; 530 (avg +48.89/Lv, L1-10) | Accuracy: 80% -&gt; 90% (avg +1.11%/Lv)
-TP Cost: 15 -&gt; 60 (avg +5/Lv) | Speed: 1.7x | Chant: 0.88x -&gt; 0.78x</t>
+          <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
+TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 | Speed: 1.7x</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -9432,17 +9650,18 @@
       </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>Pwr, Accuracy, TP Cost, Chant</t>
-        </is>
-      </c>
+      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
           <t>Deal water damage to an enemy row.</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr">
+      <c r="P150" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
 TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
@@ -9486,8 +9705,8 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Pwr: 300 -&gt; 750 (avg +50/Lv, L1-10) | Accuracy: 75% -&gt; 85% (avg +1.11%/Lv)
-TP Cost: 42 -&gt; 120 (avg +8.67/Lv) | Speed: 1.3x | Chant: 0.7x -&gt; 0.6x</t>
+          <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
+TP Cost: 42 -&gt; 50 -&gt; 58 -&gt; 64 -&gt; 73 -&gt; 82 -&gt; 91 -&gt; 100 -&gt; 110 -&gt; 120 | Speed: 1.3x</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -9498,17 +9717,18 @@
       </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>Pwr, Accuracy, TP Cost, Chant</t>
-        </is>
-      </c>
+      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
           <t>Deal water damage to all enemies.</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr">
+      <c r="P151" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
 TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
@@ -9552,7 +9772,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5) | Accuracy: 82% -&gt; 90% (+2%/Lv)
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max) | Accuracy: 82% (+2%/Lv)
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84 | Speed: 1.5x | Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
@@ -9564,17 +9784,14 @@
       </c>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>Chant</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr">
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
         <is>
           <t>Unleash devastating master water magic on one enemy. Pierces 50 Elemental Res.</t>
         </is>
       </c>
-      <c r="O152" t="inlineStr">
+      <c r="P152" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
 TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
@@ -9618,8 +9835,8 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Pwr: 70 -&gt; 520 (avg +50/Lv, L1-10) | Accuracy: 86% -&gt; 95% (+1%/Lv)
-TP Cost: 5 -&gt; 32 (avg +3/Lv) | Speed: 2.25x | Chant: 1.15x -&gt; 1.06x (-0.01x/Lv)</t>
+          <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
+TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Speed: 2.25x</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -9630,17 +9847,18 @@
       </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>Pwr, TP Cost</t>
-        </is>
-      </c>
+      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
           <t>Deal lightning damage to one enemy.</t>
         </is>
       </c>
-      <c r="O153" t="inlineStr">
+      <c r="P153" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
 TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
@@ -9684,8 +9902,8 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Pwr: 90 -&gt; 530 (avg +48.89/Lv, L1-10) | Accuracy: 80% -&gt; 90% (avg +1.11%/Lv)
-TP Cost: 15 -&gt; 60 (avg +5/Lv) | Speed: 1.7x | Chant: 0.88x -&gt; 0.78x</t>
+          <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
+TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 | Speed: 1.7x</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -9696,17 +9914,18 @@
       </c>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>Pwr, Accuracy, TP Cost, Chant</t>
-        </is>
-      </c>
+      <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
           <t>Deal lightning damage to an enemy row.</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr">
+      <c r="P154" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
 TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
@@ -9750,8 +9969,8 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Pwr: 300 -&gt; 750 (avg +50/Lv, L1-10) | Accuracy: 75% -&gt; 85% (avg +1.11%/Lv)
-TP Cost: 42 -&gt; 120 (avg +8.67/Lv) | Speed: 1.3x | Chant: 0.7x -&gt; 0.6x</t>
+          <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
+TP Cost: 42 -&gt; 50 -&gt; 58 -&gt; 64 -&gt; 73 -&gt; 82 -&gt; 91 -&gt; 100 -&gt; 110 -&gt; 120 | Speed: 1.3x</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -9762,17 +9981,18 @@
       </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>Pwr, Accuracy, TP Cost, Chant</t>
-        </is>
-      </c>
+      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
           <t>Deal lightning damage to all enemies.</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr">
+      <c r="P155" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
 TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
@@ -9816,7 +10036,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5) | Accuracy: 82% -&gt; 90% (+2%/Lv)
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max) | Accuracy: 82% (+2%/Lv)
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84 | Speed: 1.5x | Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
@@ -9828,17 +10048,14 @@
       </c>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>Chant</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr">
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
         <is>
           <t>Unleash devastating master lightning magic on one enemy. Pierces 50 Elemental Res.</t>
         </is>
       </c>
-      <c r="O156" t="inlineStr">
+      <c r="P156" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
 TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
@@ -9882,8 +10099,8 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Pwr: 70 -&gt; 520 (avg +50/Lv, L1-10) | Accuracy: 86% -&gt; 95% (+1%/Lv)
-TP Cost: 5 -&gt; 32 (avg +3/Lv) | Speed: 2.25x | Chant: 1.15x -&gt; 1.06x (-0.01x/Lv)</t>
+          <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
+TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Speed: 2.25x</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -9894,17 +10111,18 @@
       </c>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>Pwr, TP Cost</t>
-        </is>
-      </c>
+      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
           <t>Deal wind damage to one enemy.</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr">
+      <c r="P157" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
 TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
@@ -9948,8 +10166,8 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Pwr: 90 -&gt; 530 (avg +48.89/Lv, L1-10) | Accuracy: 80% -&gt; 90% (avg +1.11%/Lv)
-TP Cost: 15 -&gt; 60 (avg +5/Lv) | Speed: 1.7x | Chant: 0.88x -&gt; 0.78x</t>
+          <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
+TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 | Speed: 1.7x</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -9960,17 +10178,18 @@
       </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>Pwr, Accuracy, TP Cost, Chant</t>
-        </is>
-      </c>
+      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
           <t>Deal wind damage to an enemy row.</t>
         </is>
       </c>
-      <c r="O158" t="inlineStr">
+      <c r="P158" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
 TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
@@ -10014,8 +10233,8 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Pwr: 300 -&gt; 750 (avg +50/Lv, L1-10) | Accuracy: 75% -&gt; 85% (avg +1.11%/Lv)
-TP Cost: 42 -&gt; 120 (avg +8.67/Lv) | Speed: 1.3x | Chant: 0.7x -&gt; 0.6x</t>
+          <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
+TP Cost: 42 -&gt; 50 -&gt; 58 -&gt; 64 -&gt; 73 -&gt; 82 -&gt; 91 -&gt; 100 -&gt; 110 -&gt; 120 | Speed: 1.3x</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -10026,17 +10245,18 @@
       </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>Pwr, Accuracy, TP Cost, Chant</t>
-        </is>
-      </c>
+      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
           <t>Deal wind damage to all enemies.</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr">
+      <c r="P159" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
 TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
@@ -10080,7 +10300,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5) | Accuracy: 82% -&gt; 90% (+2%/Lv)
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max) | Accuracy: 82% (+2%/Lv)
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84 | Speed: 1.5x | Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
@@ -10092,17 +10312,14 @@
       </c>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>Chant</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr">
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
         <is>
           <t>Unleash devastating master wind magic on one enemy. Pierces 50 Elemental Res.</t>
         </is>
       </c>
-      <c r="O160" t="inlineStr">
+      <c r="P160" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
 TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
@@ -10146,8 +10363,8 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Pwr: 70 -&gt; 520 (avg +50/Lv, L1-10) | Accuracy: 86% -&gt; 95% (+1%/Lv)
-TP Cost: 5 -&gt; 32 (avg +3/Lv) | Speed: 2.25x | Chant: 1.15x -&gt; 1.06x (-0.01x/Lv)</t>
+          <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
+TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Speed: 2.25x</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -10158,17 +10375,18 @@
       </c>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>Pwr, TP Cost</t>
-        </is>
-      </c>
+      <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
           <t>Deal earth damage to one enemy.</t>
         </is>
       </c>
-      <c r="O161" t="inlineStr">
+      <c r="P161" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
 TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
@@ -10212,8 +10430,8 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Pwr: 90 -&gt; 530 (avg +48.89/Lv, L1-10) | Accuracy: 80% -&gt; 90% (avg +1.11%/Lv)
-TP Cost: 15 -&gt; 60 (avg +5/Lv) | Speed: 1.7x | Chant: 0.88x -&gt; 0.78x</t>
+          <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
+TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 | Speed: 1.7x</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -10224,17 +10442,18 @@
       </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>Pwr, Accuracy, TP Cost, Chant</t>
-        </is>
-      </c>
+      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
           <t>Deal earth damage to an enemy row.</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr">
+      <c r="P162" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
 TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
@@ -10278,8 +10497,8 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Pwr: 300 -&gt; 750 (avg +50/Lv, L1-10) | Accuracy: 75% -&gt; 85% (avg +1.11%/Lv)
-TP Cost: 42 -&gt; 120 (avg +8.67/Lv) | Speed: 1.3x | Chant: 0.7x -&gt; 0.6x</t>
+          <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
+TP Cost: 42 -&gt; 50 -&gt; 58 -&gt; 64 -&gt; 73 -&gt; 82 -&gt; 91 -&gt; 100 -&gt; 110 -&gt; 120 | Speed: 1.3x</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -10290,17 +10509,18 @@
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>Pwr, Accuracy, TP Cost, Chant</t>
-        </is>
-      </c>
+      <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
           <t>Deal earth damage to all enemies.</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr">
+      <c r="P163" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
 TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
@@ -10344,7 +10564,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5) | Accuracy: 82% -&gt; 90% (+2%/Lv)
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max) | Accuracy: 82% (+2%/Lv)
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84 | Speed: 1.5x | Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
@@ -10356,17 +10576,14 @@
       </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>Chant</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr">
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
         <is>
           <t>Unleash devastating master earth magic on one enemy. Pierces 50 Elemental Res.</t>
         </is>
       </c>
-      <c r="O164" t="inlineStr">
+      <c r="P164" t="inlineStr">
         <is>
           <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
 TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
@@ -10410,8 +10627,8 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Pwr: 60 -&gt; 350 (avg +32.22/Lv, L1-10) | Accuracy: 80% -&gt; 90% (avg +1.11%/Lv)
-TP Cost: 9 -&gt; 18 (+1/Lv) | Speed: 2x | Chant: 1.25x -&gt; 1.07x (-0.02x/Lv)</t>
+          <t>Pwr: 60 -&gt; 95 -&gt; 130 -&gt; 165 -&gt; 200 -&gt; 230 -&gt; 260 -&gt; 290 -&gt; 320 -&gt; 350 (L10)
+TP Cost: 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 | Speed: 2x</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -10422,17 +10639,18 @@
       </c>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>Pwr, Accuracy</t>
-        </is>
-      </c>
+      <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
           <t>Neutral magic strike to one enemy. Absorb damage dealt as HP.</t>
         </is>
       </c>
-      <c r="O165" t="inlineStr">
+      <c r="P165" t="inlineStr">
         <is>
           <t>Pwr: 60 -&gt; 120 -&gt; 180 -&gt; 260 -&gt; 350 (L1-5) | Bypasses elemental resists
 TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 18</t>
@@ -10476,8 +10694,8 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Pwr: 22 -&gt; 82 (avg +6.67/Lv, L1-10) | Accuracy: 80% -&gt; 90% (avg +1.11%/Lv)
-TP Cost: 6 -&gt; 15 (+1/Lv) | Speed: 1.75x | Chant: 1.25x -&gt; 1.07x (-0.02x/Lv)</t>
+          <t>Pwr: 22 -&gt; 30 -&gt; 38 -&gt; 46 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 78 -&gt; 82 | Accuracy: 80% -&gt; 90%
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 | Speed: 1.75x</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -10490,15 +10708,20 @@
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Pwr, Accuracy</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
+          <t>Chant</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
           <t>Neutral magic strike to one enemy. Absorb damage dealt as TP.</t>
         </is>
       </c>
-      <c r="O166" t="inlineStr">
+      <c r="P166" t="inlineStr">
         <is>
           <t>Pwr: 22 -&gt; 35 -&gt; 50 -&gt; 65 -&gt; 82 (L1-5) | Restores TP equal to damage dealt
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 15</t>
@@ -10542,8 +10765,8 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Max HP increase rate: 20% -&gt; 28% -&gt; 36% -&gt; 45% -&gt; 50% (L1-5) | Turns: 6 -&gt; 10 (+1/Lv)
-TP Cost: 27 -&gt; 31 -&gt; 35 -&gt; 39 -&gt; 43 | Speed: 1.5x | Chant: 1.7x -&gt; 2.1x (+0.1x/Lv)</t>
+          <t>Max HP increase rate: 20% -&gt; 28% -&gt; 36% -&gt; 45% -&gt; 50% (L1-5 Max)
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 27 -&gt; 31 -&gt; 35 -&gt; 39 -&gt; 43 | Speed: 1.5x</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -10557,10 +10780,15 @@
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
+          <t>Chant</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
           <t>Boost own magic attack power at the cost of consuming HP.</t>
         </is>
       </c>
-      <c r="O167" t="inlineStr">
+      <c r="P167" t="inlineStr">
         <is>
           <t>Magic ATK: +20% -&gt; +40% (+5%/Lv) | HP Cost: 10% Max HP
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
@@ -10604,8 +10832,8 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Pwr (L1-10): 75 -&gt; 120 -&gt; 165 -&gt; 210 -&gt; 255 -&gt; 295 -&gt; 335 -&gt; 375 -&gt; 415 -&gt; 450
-Accuracy: 65% -&gt; 87% (avg +2.44%/Lv) | TP Cost: 18 -&gt; 50 | Speed: 1.5x | Chant: 1.25x</t>
+          <t>Pwr: 75 -&gt; 120 -&gt; 165 -&gt; 210 -&gt; 255 -&gt; 295 -&gt; 335 -&gt; 375 -&gt; 415 -&gt; 450 (L10)
+TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 | Speed: 1.5x</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -10616,17 +10844,18 @@
       </c>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>Accuracy, TP Cost</t>
-        </is>
-      </c>
+      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr">
         <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
           <t>Transfer a portion of user HP to restore an ally's HP.</t>
         </is>
       </c>
-      <c r="O168" t="inlineStr">
+      <c r="P168" t="inlineStr">
         <is>
           <t>Heal: 30% -&gt; 60% (+7.5%/Lv) of target Max HP | Consumes 20% user HP
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 (L1-5)</t>
@@ -10670,8 +10899,8 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Accuracy: 65% -&gt; 68% -&gt; 71% -&gt; 73% -&gt; 75% (L1-5)
-TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 | Speed: 0.8x -&gt; 0.92x (+0.03x/Lv) | Chant: 1.25x</t>
+          <t>Accuracy: 65% -&gt; 68% -&gt; 71% -&gt; 73% -&gt; 75% (L1-5 Max)
+TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 | Speed: 0.8x -&gt; 0.92x | Chant: 1.25x</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -10683,12 +10912,13 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr">
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
         <is>
           <t>Deal magic damage to one enemy. May stun.</t>
         </is>
       </c>
-      <c r="O169" t="inlineStr">
+      <c r="P169" t="inlineStr">
         <is>
           <t>Stun Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -10732,8 +10962,8 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Accuracy: 75% -&gt; 78% -&gt; 81% -&gt; 83% -&gt; 85% (L1-5)
-TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | Speed: 2.15x | Chant: 1.2x -&gt; 1.4x (+0.05x/Lv)</t>
+          <t>Accuracy: 75% -&gt; 78% -&gt; 81% -&gt; 83% -&gt; 85% (L1-5 Max)
+TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | Speed: 2.15x | Chant: 1.2x -&gt; 1.4x</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -10745,12 +10975,13 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr">
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
         <is>
           <t>Poison all enemies (5% Max HP damage per enemy turn, cap 250).</t>
         </is>
       </c>
-      <c r="O170" t="inlineStr">
+      <c r="P170" t="inlineStr">
         <is>
           <t>Accuracy: +15% -&gt; +35% (+5%/Lv) | Chant: 1.20x -&gt; 1.40x
 TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5)</t>
@@ -10794,8 +11025,8 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Accuracy: 70% -&gt; 78% (+2%/Lv, L1-5)
-TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Speed: 1.5x | Chant: 1.5x -&gt; 1.66x (+0.04x/Lv)</t>
+          <t>Accuracy: 70% -&gt; 72% -&gt; 74% -&gt; 76% -&gt; 78% (L1-5 Max)
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Speed: 1.5x | Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -10807,12 +11038,13 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr">
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
         <is>
           <t>Deal water magic damage to one enemy. May freeze.</t>
         </is>
       </c>
-      <c r="O171" t="inlineStr">
+      <c r="P171" t="inlineStr">
         <is>
           <t>Freeze Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -10856,8 +11088,8 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Accuracy: 65% -&gt; 68% -&gt; 71% -&gt; 73% -&gt; 75% (L1-5)
-TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Speed: 1.5x | Chant: 1x -&gt; 1.2x (+0.05x/Lv)</t>
+          <t>Accuracy: 65% -&gt; 68% -&gt; 71% -&gt; 73% -&gt; 75% (L1-5 Max)
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Speed: 1.5x | Chant: 1x -&gt; 1.2x</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -10869,12 +11101,13 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr">
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
         <is>
           <t>Deal lightning magic damage to one enemy. May paralyze.</t>
         </is>
       </c>
-      <c r="O172" t="inlineStr">
+      <c r="P172" t="inlineStr">
         <is>
           <t>Paralysis Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -10918,8 +11151,8 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Accuracy: 65% -&gt; 68% -&gt; 71% -&gt; 73% -&gt; 75% (L1-5)
-TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 | Chant: 0.75x -&gt; 0.87x (+0.03x/Lv)</t>
+          <t>Accuracy: 65% -&gt; 68% -&gt; 71% -&gt; 73% -&gt; 75% (L1-5 Max)
+TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 | Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -10931,12 +11164,13 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr">
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
         <is>
           <t>Put an enemy to sleep with magic.</t>
         </is>
       </c>
-      <c r="O173" t="inlineStr">
+      <c r="P173" t="inlineStr">
         <is>
           <t>Sleep Chance: 40% -&gt; 70% (+7.5%/Lv) | Levels: L1-5
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -10980,8 +11214,8 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Accuracy: 70% -&gt; 78% (+2%/Lv, L1-5)
-TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Speed: 1.5x | Chant: 1.5x -&gt; 1.66x (+0.04x/Lv)</t>
+          <t>Accuracy: 70% -&gt; 72% -&gt; 74% -&gt; 76% -&gt; 78% (L1-5 Max)
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Speed: 1.5x | Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -10993,12 +11227,13 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr">
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr">
         <is>
           <t>Silence an enemy to prevent spell casting.</t>
         </is>
       </c>
-      <c r="O174" t="inlineStr">
+      <c r="P174" t="inlineStr">
         <is>
           <t>Silence Chance: 40% -&gt; 70% (+7.5%/Lv) | Levels: L1-5
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -11042,8 +11277,8 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Accuracy: 70% -&gt; 78% (+2%/Lv, L1-5)
-TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 | Chant: 0.75x -&gt; 0.87x (+0.03x/Lv)</t>
+          <t>Accuracy: 70% -&gt; 72% -&gt; 74% -&gt; 76% -&gt; 78% (L1-5 Max)
+TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 | Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -11055,12 +11290,13 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr">
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr">
         <is>
           <t>Turn one enemy to stone with earth magic.</t>
         </is>
       </c>
-      <c r="O175" t="inlineStr">
+      <c r="P175" t="inlineStr">
         <is>
           <t>Petrify Chance: 20% -&gt; 40% (+5%/Lv) | Levels: L1-5
 TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
@@ -11104,8 +11340,8 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Accuracy: 50% -&gt; 52% -&gt; 55% -&gt; 58% -&gt; 60% (L1-5)
-TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 | Chant: 0.75x -&gt; 0.87x (+0.03x/Lv)</t>
+          <t>Accuracy: 50% -&gt; 52% -&gt; 55% -&gt; 58% -&gt; 60% (L1-5 Max)
+TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 | Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -11117,12 +11353,13 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr">
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr">
         <is>
           <t>Attempt to instantly slay one living enemy.</t>
         </is>
       </c>
-      <c r="O176" t="inlineStr">
+      <c r="P176" t="inlineStr">
         <is>
           <t>Instakill Chance: 15% -&gt; 35% (+5%/Lv) | Levels: L1-5
 TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28</t>
@@ -11166,8 +11403,8 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Accuracy: 50% -&gt; 55% -&gt; 60% -&gt; 64% -&gt; 68% (L1-5)
-TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 | Chant: 1x -&gt; 1.12x (+0.03x/Lv)</t>
+          <t>Accuracy: 50% -&gt; 55% -&gt; 60% -&gt; 64% -&gt; 68% (L1-5 Max)
+TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 | Chant: 1x -&gt; 1.12x</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -11179,12 +11416,13 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr">
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr">
         <is>
           <t>Inflict Slow on an enemy row, cutting action speed by -50%.</t>
         </is>
       </c>
-      <c r="O177" t="inlineStr">
+      <c r="P177" t="inlineStr">
         <is>
           <t>Slow Chance: 35% -&gt; 65% (+7.5%/Lv) | Inflicts -50% Speed
 TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 (L1-5)</t>
@@ -11228,8 +11466,8 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Accuracy: 54% -&gt; 70% (+4%/Lv, L1-5) | TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30
-Speed: 0.4x -&gt; 0.43x -&gt; 0.46x -&gt; 0.48x -&gt; 0.5x | Chant: 1.25x</t>
+          <t>Accuracy: 54% -&gt; 58% -&gt; 62% -&gt; 66% -&gt; 70% (L1-5 Max)
+TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 | Speed: 0.4x -&gt; 0.5x | Chant: 1.25x</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -11241,12 +11479,13 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr">
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr">
         <is>
           <t>Terrify an enemy with dark magic to inflict Stun.</t>
         </is>
       </c>
-      <c r="O178" t="inlineStr">
+      <c r="P178" t="inlineStr">
         <is>
           <t>Stun Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -11290,8 +11529,8 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Accuracy: 55% -&gt; 95% (+10%/Lv, L1-5)
-TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 18 -&gt; 22 | Speed: 1.25x | Chant: 1.25x -&gt; 1.45x (+0.05x/Lv)</t>
+          <t>Accuracy: 55% -&gt; 65% -&gt; 75% -&gt; 85% -&gt; 95% (L1-5 Max)
+TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 18 -&gt; 22 | Speed: 1.25x | Chant: 1.25x -&gt; 1.45x</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -11305,6 +11544,7 @@
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11343,7 +11583,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Pwr: 250 -&gt; 640 (avg +43.33/Lv, L1-10) | Accuracy: 60% -&gt; 70% (avg +1.11%/Lv)
+          <t>Pwr: 250 -&gt; 300 -&gt; 350 -&gt; 400 -&gt; 440 -&gt; 480 -&gt; 520 -&gt; 560 -&gt; 600 -&gt; 640 (L10)
 TP Cost: 45 -&gt; 52 -&gt; 59 -&gt; 66 -&gt; 74 -&gt; 80 -&gt; 86 -&gt; 90 -&gt; 95 -&gt; 100 | Speed: 1.75x</t>
         </is>
       </c>
@@ -11355,13 +11595,14 @@
       </c>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>Pwr, Accuracy, Chant</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
       <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11400,8 +11641,8 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
-Speed: 1.5x -&gt; 1.7x (+0.05x/Lv) | Chant: 1.75x -&gt; 1.9x -&gt; 2.05x -&gt; 2.15x -&gt; 2.25x</t>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x | Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -11413,12 +11654,13 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr">
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr">
         <is>
           <t>Imbue an ally's weapon with Fire element.</t>
         </is>
       </c>
-      <c r="O181" t="inlineStr">
+      <c r="P181" t="inlineStr">
         <is>
           <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Fire damage to weapon strikes
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -11462,8 +11704,8 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
-Speed: 1.5x -&gt; 1.7x (+0.05x/Lv) | Chant: 1.75x -&gt; 1.9x -&gt; 2.05x -&gt; 2.15x -&gt; 2.25x</t>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x | Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -11475,12 +11717,13 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr">
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr">
         <is>
           <t>Imbue an ally's weapon with Water element.</t>
         </is>
       </c>
-      <c r="O182" t="inlineStr">
+      <c r="P182" t="inlineStr">
         <is>
           <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Water damage to weapon strikes
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -11524,8 +11767,8 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
-Speed: 1.5x -&gt; 1.7x (+0.05x/Lv) | Chant: 1.75x -&gt; 1.9x -&gt; 2.05x -&gt; 2.15x -&gt; 2.25x</t>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x | Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -11537,12 +11780,13 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr">
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
         <is>
           <t>Imbue an ally's weapon with Lightning element.</t>
         </is>
       </c>
-      <c r="O183" t="inlineStr">
+      <c r="P183" t="inlineStr">
         <is>
           <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Lightning damage to weapon strikes
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -11586,8 +11830,8 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
-Speed: 1.5x -&gt; 1.7x (+0.05x/Lv) | Chant: 1.75x -&gt; 1.9x -&gt; 2.05x -&gt; 2.15x -&gt; 2.25x</t>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x | Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -11599,12 +11843,13 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr">
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
         <is>
           <t>Imbue an ally's weapon with Wind element.</t>
         </is>
       </c>
-      <c r="O184" t="inlineStr">
+      <c r="P184" t="inlineStr">
         <is>
           <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Wind damage to weapon strikes
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -11648,8 +11893,8 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
-Speed: 1.5x -&gt; 1.7x (+0.05x/Lv) | Chant: 1.75x -&gt; 1.9x -&gt; 2.05x -&gt; 2.15x -&gt; 2.25x</t>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x | Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -11661,12 +11906,13 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr">
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr">
         <is>
           <t>Imbue an ally's weapon with Earth element.</t>
         </is>
       </c>
-      <c r="O185" t="inlineStr">
+      <c r="P185" t="inlineStr">
         <is>
           <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Earth damage to weapon strikes
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -11710,8 +11956,8 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Resistance: 20 -&gt; 36 (+4/Lv, L1-5) | Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8
-TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 | Speed: 1.75x -&gt; 2x | Chant: 1.75x -&gt; 2.25x</t>
+          <t>Resistance: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -11722,17 +11968,18 @@
       </c>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr">
+      <c r="O186" t="inlineStr">
         <is>
           <t>Raise one row of allies' resistance to stab damage.</t>
         </is>
       </c>
-      <c r="O186" t="inlineStr">
+      <c r="P186" t="inlineStr">
         <is>
           <t>Stab Resistance: +15 -&gt; +35 (+5/Lv) | Levels: L1-5
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
@@ -11776,8 +12023,8 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Resistance: 18 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5) | Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8
-TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 | Speed: 1.75x -&gt; 2x | Chant: 1.75x -&gt; 2.25x</t>
+          <t>Resistance: 18 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -11788,17 +12035,18 @@
       </c>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr">
+      <c r="O187" t="inlineStr">
         <is>
           <t>Raise one row of allies' resistance to slash damage.</t>
         </is>
       </c>
-      <c r="O187" t="inlineStr">
+      <c r="P187" t="inlineStr">
         <is>
           <t>Slash Resistance: +15 -&gt; +35 (+5/Lv) | Levels: L1-5
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
@@ -11842,8 +12090,8 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Resistance: 18 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5) | Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8
-TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 | Speed: 1.75x -&gt; 2x | Chant: 1.75x -&gt; 2.25x</t>
+          <t>Resistance: 18 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -11854,17 +12102,18 @@
       </c>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr">
+      <c r="O188" t="inlineStr">
         <is>
           <t>Raise one row of allies' resistance to bash damage.</t>
         </is>
       </c>
-      <c r="O188" t="inlineStr">
+      <c r="P188" t="inlineStr">
         <is>
           <t>Bash Resistance: +15 -&gt; +35 (+5/Lv) | Levels: L1-5
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
@@ -11908,7 +12157,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>HP recovery: 8 -&gt; 26 (+2/Lv, L1-10) | Heal Cap: 100 -&gt; 800 (avg +77.78/Lv)
+          <t>HP recovery: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 (L10)
 TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 | Speed: 1.75x</t>
         </is>
       </c>
@@ -11920,17 +12169,18 @@
       </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
         <is>
           <t>Heal Cap, Chant</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr">
+      <c r="O189" t="inlineStr">
         <is>
           <t>Heal an ally's HP.</t>
         </is>
       </c>
-      <c r="O189" t="inlineStr">
+      <c r="P189" t="inlineStr">
         <is>
           <t>Heal Cap (L1-10): 100 -&gt; 150 -&gt; 200 -&gt; 270 -&gt; 350 -&gt; 440 -&gt; 540 -&gt; 650 -&gt; 720 -&gt; 800
 TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26  (Lv1 to Max)</t>
@@ -11974,7 +12224,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>HP recovery: 5 -&gt; 14 (+1/Lv, L1-10) | Heal Cap: 80 -&gt; 600 (avg +57.78/Lv)
+          <t>HP recovery: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 (L10)
 TP Cost: 15 -&gt; 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 46 -&gt; 52 -&gt; 58 -&gt; 64 | Speed: 1.35x</t>
         </is>
       </c>
@@ -11986,17 +12236,18 @@
       </c>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
         <is>
           <t>Heal Cap, Chant</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr">
+      <c r="O190" t="inlineStr">
         <is>
           <t>Heal the entire party's HP.</t>
         </is>
       </c>
-      <c r="O190" t="inlineStr">
+      <c r="P190" t="inlineStr">
         <is>
           <t>Heal Cap (L1-10): 80 -&gt; 120 -&gt; 160 -&gt; 210 -&gt; 270 -&gt; 340 -&gt; 420 -&gt; 510 -&gt; 600 -&gt; 700
 TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 21 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 46  (Lv1 to Max)</t>
@@ -12039,8 +12290,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>TP Cost: 48 -&gt; 45 -&gt; 42 -&gt; 39 -&gt; 36 (L1-5) | Speed: 1.15x
-Chant: 1.5x -&gt; 1.6x -&gt; 1.65x -&gt; 1.7x -&gt; 1.75x</t>
+          <t>TP Cost: 48 -&gt; 45 -&gt; 42 -&gt; 39 -&gt; 36 (L1-5 Max) | Speed: 1.15x | Chant: 1.5x -&gt; 1.75x</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -12052,12 +12302,13 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr">
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
         <is>
           <t>Fully restore one ally's HP to maximum.</t>
         </is>
       </c>
-      <c r="O191" t="inlineStr">
+      <c r="P191" t="inlineStr">
         <is>
           <t>Heals 100% Max HP (9,999 HP cap) | Chant: 2 turns -&gt; 1 turn
 TP Cost: 35 -&gt; 30 -&gt; 25 -&gt; 20 -&gt; 16 (L1-5)</t>
@@ -12102,7 +12353,7 @@
       <c r="H192" t="inlineStr">
         <is>
           <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
-TP Cost (L1-8): 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 | Speed: 2.25x | Chant: 2.75x</t>
+TP Cost: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 | Speed: 2.25x | Chant: 2.75x</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -12118,12 +12369,13 @@
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr">
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
         <is>
           <t>Cure status ailments for a single ally.</t>
         </is>
       </c>
-      <c r="O192" t="inlineStr">
+      <c r="P192" t="inlineStr">
         <is>
           <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep -&gt; Petrify -&gt; Slow
 TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 (L1-7)</t>
@@ -12168,7 +12420,7 @@
       <c r="H193" t="inlineStr">
         <is>
           <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
-TP Cost (L1-8): 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25 -&gt; 30 -&gt; 36 | Speed: 1.5x | Chant: 2x</t>
+TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25 -&gt; 30 -&gt; 36 | Speed: 1.5x | Chant: 2x</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -12184,12 +12436,13 @@
         </is>
       </c>
       <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr">
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr">
         <is>
           <t>Cure status ailments for the entire party.</t>
         </is>
       </c>
-      <c r="O193" t="inlineStr">
+      <c r="P193" t="inlineStr">
         <is>
           <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep -&gt; Petrify -&gt; Slow
 TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 (L1-7)</t>
@@ -12233,8 +12486,8 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Amount of HP on revival: 40% -&gt; 88% (+12%/Lv, L1-5)
-TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 | Speed: 1.25x | Chant: 1.3x -&gt; 1.5x (+0.05x/Lv)</t>
+          <t>Amount of HP on revival: 40% -&gt; 52% -&gt; 64% -&gt; 76% -&gt; 88% (L1-5 Max)
+TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 | Speed: 1.25x | Chant: 1.3x -&gt; 1.5x</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -12246,12 +12499,13 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr">
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr">
         <is>
           <t>Revive a fallen ally.</t>
         </is>
       </c>
-      <c r="O194" t="inlineStr">
+      <c r="P194" t="inlineStr">
         <is>
           <t>Revival HP: 20% -&gt; 35% -&gt; 50% -&gt; 70% -&gt; 100% Max HP (L1-5)
 Chant time decreases per level | TP Cost: 18 -&gt; 22 -&gt; 26 -&gt; 30 -&gt; 35</t>
@@ -12295,8 +12549,8 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>ATK increase: 10% -&gt; 22% (+3%/Lv, L1-5) | Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9
-TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 | Speed: 1.25x -&gt; 1.41x (+0.04x/Lv) | Chant: 1.25x</t>
+          <t>ATK: +10% -&gt; +13% -&gt; +16% -&gt; +19% -&gt; +22% (L1-5 Max)
+Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 | TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 | Chant: 1.25x</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -12310,10 +12564,15 @@
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
           <t>Raise an ally's physical ATK.</t>
         </is>
       </c>
-      <c r="O195" t="inlineStr">
+      <c r="P195" t="inlineStr">
         <is>
           <t>ATK: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -12357,8 +12616,8 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>DEF increase: 10% -&gt; 14% -&gt; 18% -&gt; 22% -&gt; 25% (L1-5) | Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9
-TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 | Speed: 1.25x -&gt; 1.41x (+0.04x/Lv) | Chant: 1.25x</t>
+          <t>DEF: +10% -&gt; +14% -&gt; +18% -&gt; +22% -&gt; +25% (L1-5 Max)
+Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 | TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 | Chant: 1.25x</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -12372,10 +12631,15 @@
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
           <t>Raise an ally's physical DEF.</t>
         </is>
       </c>
-      <c r="O196" t="inlineStr">
+      <c r="P196" t="inlineStr">
         <is>
           <t>DEF: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -12419,8 +12683,8 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Magic defense increase: 10% -&gt; 18% (+2%/Lv, L1-5) | Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
-TP Cost: 16 -&gt; 32 (+4/Lv) | Speed: 1.25x -&gt; 1.37x (+0.03x/Lv) | Chant: 1.25x</t>
+          <t>Magic defense: +10% -&gt; +12% -&gt; +14% -&gt; +16% -&gt; +18% (L1-5 Max)
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Chant: 1.25x</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -12434,10 +12698,15 @@
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
           <t>Raise the party's magical defense against incoming spells.</t>
         </is>
       </c>
-      <c r="O197" t="inlineStr">
+      <c r="P197" t="inlineStr">
         <is>
           <t>Magic DEF: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
@@ -12481,8 +12750,8 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Elemental resistance increase: 5 -&gt; 25 (+5/Lv, L1-5) | Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
-TP Cost: 16 -&gt; 32 (+4/Lv) | Speed: 1.25x -&gt; 1.37x (+0.03x/Lv) | Chant: 1.25x</t>
+          <t>Elemental resistance increase: 5 -&gt; 10 -&gt; 15 -&gt; 20 -&gt; 25 (L1-5 Max)
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Chant: 1.25x</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -12496,10 +12765,15 @@
       <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
           <t>Raise party resistance to Fire, Water, Lightning, Wind, and Earth.</t>
         </is>
       </c>
-      <c r="O198" t="inlineStr">
+      <c r="P198" t="inlineStr">
         <is>
           <t>Resist: +15 -&gt; +20 -&gt; +25 -&gt; +30 -&gt; +35 all elements (L1-5)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
@@ -12543,8 +12817,8 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Speed increase: 8% -&gt; 12% (+1%/Lv, L1-5) | Turns: 3 | TP Cost: 15 -&gt; 27 (+3/Lv)
-Speed: 1.25x -&gt; 1.41x (+0.04x/Lv) | Chant: 1x -&gt; 1.2x (+0.05x/Lv)</t>
+          <t>Speed increase: 8% -&gt; 9% -&gt; 10% -&gt; 11% -&gt; 12% (L1-5 Max)
+Turns: 3 | TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 | Speed: 1.25x -&gt; 1.41x</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -12558,10 +12832,15 @@
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr">
         <is>
+          <t>Chant</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
           <t>Raise an ally's action speed.</t>
         </is>
       </c>
-      <c r="O199" t="inlineStr">
+      <c r="P199" t="inlineStr">
         <is>
           <t>Speed: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
 Chant time decreases per level | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -12605,8 +12884,8 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Max HP increase: 20% -&gt; 47% (+3%/Lv, L1-10) | Turns: 5 -&gt; 10 (avg +0.56/Lv)
-TP Cost: 18 -&gt; 45 (+3/Lv) | Speed: 1.5x -&gt; 1.82x | Chant: 1.5x -&gt; 1.81x</t>
+          <t>Max HP: +20% -&gt; +23 -&gt; +26 -&gt; +29 -&gt; +32 -&gt; +35 -&gt; +38 -&gt; +41 -&gt; +44 -&gt; +47% (L10)
+Turns: 5 -&gt; 10 | TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -12619,15 +12898,20 @@
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Turns, Speed, Chant</t>
+          <t>Turns</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
+          <t>Speed, Chant</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
           <t>Temporarily raise an ally's maximum HP cap.</t>
         </is>
       </c>
-      <c r="O200" t="inlineStr">
+      <c r="P200" t="inlineStr">
         <is>
           <t>Max HP: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
@@ -12672,7 +12956,7 @@
       <c r="H201" t="inlineStr">
         <is>
           <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
-TP Cost (L1-8): 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 21 -&gt; 24 -&gt; 28 | Speed: 1.75x</t>
+TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 21 -&gt; 24 -&gt; 28 | Speed: 1.75x | Chant: 2.25x</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -12687,17 +12971,14 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>Chant</t>
-        </is>
-      </c>
-      <c r="N201" t="inlineStr">
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr">
         <is>
           <t>Cure status ailments for one row of allies.</t>
         </is>
       </c>
-      <c r="O201" t="inlineStr">
+      <c r="P201" t="inlineStr">
         <is>
           <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep -&gt; Petrify -&gt; Slow
 TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24 -&gt; 28 (L1-7)</t>
@@ -12741,8 +13022,8 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 (L1-3) | TP Cost: 30 -&gt; 38 -&gt; 46 | Speed: 0.85x
-Chant: 0.75x -&gt; 0.65x (-0.05x/Lv)</t>
+          <t>Turns: 3 -&gt; 4 -&gt; 5 (L1-3 Max) | TP Cost: 30 -&gt; 38 -&gt; 46 | Speed: 0.85x
+Chant: 0.75x -&gt; 0.65x</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -12754,12 +13035,13 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr">
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr">
         <is>
           <t>Create magical afterimages that let user dodge incoming attacks.</t>
         </is>
       </c>
-      <c r="O202" t="inlineStr">
+      <c r="P202" t="inlineStr">
         <is>
           <t>Dodges: 2 guaranteed physical attacks avoided
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
@@ -12803,7 +13085,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Amount of damage reduced: 30% -&gt; 33% -&gt; 37% -&gt; 41% -&gt; 45% (L1-5)
+          <t>Amount of damage reduced: 30% -&gt; 33% -&gt; 37% -&gt; 41% -&gt; 45% (L1-5 Max)
 Turns: 4 | TP Cost: 24 -&gt; 28 -&gt; 33 -&gt; 37 -&gt; 42 | Speed: 1.5x | Chant: 0.75x</t>
         </is>
       </c>
@@ -12816,12 +13098,13 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr">
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr">
         <is>
           <t>Enchant self with a barrier reducing incoming physical damage.</t>
         </is>
       </c>
-      <c r="O203" t="inlineStr">
+      <c r="P203" t="inlineStr">
         <is>
           <t>Physical Damage Reduction: -20% -&gt; -35% (-3.75%/Lv) | Levels: L1-5
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
@@ -12865,8 +13148,8 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Amount of HP on revival: 10% -&gt; 50% (+10%/Lv, L1-5) | Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
-TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 45 | Speed: 1.5x | Chant: 0.6x -&gt; 0.72x (+0.03x/Lv)</t>
+          <t>Amount of HP on revival: 10% -&gt; 20% -&gt; 30% -&gt; 40% -&gt; 50% (L1-5 Max)
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 45 | Speed: 1.5x</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -12878,8 +13161,13 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Chant</t>
+        </is>
+      </c>
       <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12917,7 +13205,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Turns (L1-10): 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30</t>
+          <t>Turns: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -12929,12 +13217,13 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr">
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr">
         <is>
           <t>Illuminate dark dungeons to reveal secret passages and hidden doors.</t>
         </is>
       </c>
-      <c r="O205" t="inlineStr">
+      <c r="P205" t="inlineStr">
         <is>
           <t>Duration: 50 -&gt; 100 -&gt; 150 -&gt; 200 -&gt; 300 steps (L1-5)
 TP Cost: 4 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 4</t>
@@ -12977,7 +13266,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>TP Cost: 28 -&gt; 21 -&gt; 14 -&gt; 7 -&gt; 1 (L1-5)</t>
+          <t>TP Cost: 28 -&gt; 21 -&gt; 14 -&gt; 7 -&gt; 1 (L1-5 Max)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -12989,12 +13278,13 @@
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr">
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr">
         <is>
           <t>Immediately teleport the party safely out of the dungeon.</t>
         </is>
       </c>
-      <c r="O206" t="inlineStr">
+      <c r="P206" t="inlineStr">
         <is>
           <t>TP Cost: 20 -&gt; 15 -&gt; 10 -&gt; 6 -&gt; 2 (L1-5 Max)
 Works identical to an Emergency Exit item</t>
@@ -13037,8 +13327,8 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Accuracy: 70% -&gt; 82% (+3%/Lv, L1-5)
-Speed: 1.5x | Chant: 1.5x -&gt; 1.66x (+0.04x/Lv)</t>
+          <t>Accuracy: 70% -&gt; 73% -&gt; 76% -&gt; 79% -&gt; 82% (L1-5 Max)
+Speed: 1.5x | Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -13050,12 +13340,13 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr">
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr">
         <is>
           <t>Sing a soothing lullaby. May put target enemy to sleep.</t>
         </is>
       </c>
-      <c r="O207" t="inlineStr">
+      <c r="P207" t="inlineStr">
         <is>
           <t>Sleep Chance: 40% -&gt; 70% (+7.5%/Lv) | Levels: L1-5
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
@@ -13108,6 +13399,7 @@
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13145,8 +13437,8 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Critical rate: 10 -&gt; 28 (+2/Lv, L1-10) | Speed: 1.35x
-Chant: 1.4x -&gt; 1.45 -&gt; 1.5 -&gt; 1.55 -&gt; 1.6 -&gt; 1.65 -&gt; 1.7 -&gt; 1.8 -&gt; 1.9 -&gt; 2x</t>
+          <t>Critical rate: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 (L10)
+Speed: 1.35x | Chant: 1.4x -&gt; 2x</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -13160,6 +13452,7 @@
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13197,8 +13490,8 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Magic attack increase: 10% -&gt; 20% (avg +1.11%/Lv, L1-10)
-Speed: 1.35x | Chant: 1.25x -&gt; 1.7x (+0.05x/Lv)</t>
+          <t>Magic attack: +10% -&gt; +11 -&gt; +12 -&gt; +13 -&gt; +14 -&gt; +15 -&gt; +16 -&gt; +17 -&gt; +18 -&gt; +20%
+Speed: 1.35x | Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -13209,13 +13502,10 @@
       </c>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>Magic attack increase</t>
-        </is>
-      </c>
+      <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13253,8 +13543,8 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Magic defense increase: 10% -&gt; 20% (avg +1.11%/Lv, L1-10)
-Speed: 1.35x | Chant: 1.25x -&gt; 1.7x (+0.05x/Lv)</t>
+          <t>Magic defense: +10% -&gt; +11 -&gt; +12 -&gt; +13 -&gt; +14 -&gt; +15 -&gt; +16 -&gt; +17 -&gt; +18 -&gt; +20%
+Speed: 1.35x | Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -13265,13 +13555,10 @@
       </c>
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>Magic defense increase</t>
-        </is>
-      </c>
+      <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -13309,8 +13596,8 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Chant time decrease: 10% -&gt; 20% (avg +1.11%/Lv, L1-10) | Speed: 1.35x
-Chant: 1.4x -&gt; 1.45 -&gt; 1.5 -&gt; 1.55 -&gt; 1.6 -&gt; 1.65 -&gt; 1.7 -&gt; 1.8 -&gt; 1.9 -&gt; 2x</t>
+          <t>Chant time: -10% -&gt; -11 -&gt; -12 -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -20%
+Speed: 1.35x | Chant: 1.4x -&gt; 2x</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -13321,13 +13608,10 @@
       </c>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>Chant time decrease</t>
-        </is>
-      </c>
+      <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -13365,8 +13649,8 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>HP recovery (L1-10): 20 -&gt; 35 -&gt; 50 -&gt; 65 -&gt; 80 -&gt; 100 -&gt; 130 -&gt; 170 -&gt; 210 -&gt; 250
-Speed: 1.35x | Chant: 1.25x -&gt; 1.7x (+0.05x/Lv)</t>
+          <t>HP recovery: 20 -&gt; 35 -&gt; 50 -&gt; 65 -&gt; 80 -&gt; 100 -&gt; 130 -&gt; 170 -&gt; 210 -&gt; 250 (L10)
+Speed: 1.35x | Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -13378,12 +13662,13 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr">
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr">
         <is>
           <t>Perform a song that regenerates party HP every turn while singing.</t>
         </is>
       </c>
-      <c r="O213" t="inlineStr">
+      <c r="P213" t="inlineStr">
         <is>
           <t>HP Regen: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% Max HP per turn (L1-5)
 Chant Time: 2 turns -&gt; 1 turn | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
@@ -13426,7 +13711,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>TP recovery (L1-10): 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30
+          <t>TP recovery: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30 (L10)
 Speed: 1.35x | Chant: 1.1x -&gt; 1.5x</t>
         </is>
       </c>
@@ -13438,17 +13723,14 @@
       </c>
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>Chant</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr">
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr">
         <is>
           <t>Perform a song that regenerates party TP every turn while singing.</t>
         </is>
       </c>
-      <c r="O214" t="inlineStr">
+      <c r="P214" t="inlineStr">
         <is>
           <t>TP Regen: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 12 TP per turn (L1-5)
 Chant Time: 2 turns -&gt; 1 turn | TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
@@ -13491,8 +13773,8 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Speed increase: 6% -&gt; 15% (+1%/Lv, L1-10) | Speed: 1.35x
-Chant: 1.1x -&gt; 1.15 -&gt; 1.2 -&gt; 1.25 -&gt; 1.3 -&gt; 1.35 -&gt; 1.39 -&gt; 1.43 -&gt; 1.47 -&gt; 1.5x</t>
+          <t>Speed increase: 6% -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)
+Speed: 1.35x | Chant: 1.1x -&gt; 1.5x</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -13504,12 +13786,13 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr">
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr">
         <is>
           <t>Perform a lively march boosting party action speed while singing.</t>
         </is>
       </c>
-      <c r="O215" t="inlineStr">
+      <c r="P215" t="inlineStr">
         <is>
           <t>Party Speed: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
 TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
@@ -13552,8 +13835,8 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>EXP increase: 16% -&gt; 25% (+1%/Lv, L1-10)
-Speed: 1.35x | Chant: 1.25x -&gt; 1.7x (+0.05x/Lv)</t>
+          <t>EXP: +16% -&gt; +17 -&gt; +18 -&gt; +19 -&gt; +20 -&gt; +21 -&gt; +22 -&gt; +23 -&gt; +24 -&gt; +25% (L10)
+Speed: 1.35x | Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -13565,12 +13848,13 @@
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr">
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr">
         <is>
           <t>Perform a song that increases combat EXP gained by the party.</t>
         </is>
       </c>
-      <c r="O216" t="inlineStr">
+      <c r="P216" t="inlineStr">
         <is>
           <t>EXP Bonus: +10% -&gt; +15% -&gt; +20% -&gt; +25% -&gt; +30% (L1-5)
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
@@ -13613,8 +13897,8 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Magic accuracy increase: 6% -&gt; 15% (+1%/Lv, L1-10)
-Speed: 1.35x | Chant: 1.25x -&gt; 1.7x (+0.05x/Lv)</t>
+          <t>Magic accuracy: +6% -&gt; +7 -&gt; +8 -&gt; +9 -&gt; +10 -&gt; +11 -&gt; +12 -&gt; +13 -&gt; +14 -&gt; +15%
+Speed: 1.35x | Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -13628,6 +13912,7 @@
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13666,8 +13951,8 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Number of dodges: 1 -&gt; 5 (+1/Lv, L1-5) | Turns: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5
-TP Cost: 23 -&gt; 27 -&gt; 32 -&gt; 38 -&gt; 45 | Speed: 0.85x | Chant: 0.75x -&gt; 0.53x</t>
+          <t>Number of dodges: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 (L1-5 Max)
+Turns: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5 | TP Cost: 23 -&gt; 27 -&gt; 32 -&gt; 38 -&gt; 45 | Speed: 0.85x</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -13678,13 +13963,14 @@
       </c>
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13723,8 +14009,8 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Shadow Sew Success: 30% -&gt; 32% -&gt; 35% -&gt; 37% -&gt; 40% (L1-5) | Turns: 3
-TP Cost: 36 -&gt; 39 -&gt; 43 -&gt; 47 -&gt; 52 | Speed: 0.8x | Chant: 0.8x -&gt; 0.88x (+0.02x/Lv)</t>
+          <t>Shadow Sew Success: 30% -&gt; 32% -&gt; 35% -&gt; 37% -&gt; 40% (L1-5 Max)
+Turns: 3 | TP Cost: 36 -&gt; 39 -&gt; 43 -&gt; 47 -&gt; 52 | Speed: 0.8x | Chant: 0.8x -&gt; 0.88x</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -13738,6 +14024,7 @@
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13776,8 +14063,8 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Accuracy decrease: 10% -&gt; 18% (+2%/Lv, L1-5) | Turns: 3
-TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 | Chant: 1.15x -&gt; 1.19x -&gt; 1.23x -&gt; 1.27x -&gt; 1.3x</t>
+          <t>Accuracy: -10% -&gt; -12% -&gt; -14% -&gt; -16% -&gt; -18% (L1-5 Max)
+Turns: 3 | TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 | Chant: 1.15x -&gt; 1.3x</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -13791,6 +14078,7 @@
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13829,8 +14117,8 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% -&gt; 80% (+4%/Lv, L1-5) | ATK decrease: 4% -&gt; 8% (+1%/Lv)
-Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Chant: 1x -&gt; 1.25x</t>
+          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | Damage cap UP
+Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x | Chant: 1x -&gt; 1.25x</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -13849,13 +14137,14 @@
           <t>effect_1, effect_3</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>Speed, Chant</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
       <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13894,8 +14183,8 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% -&gt; 80% (+4%/Lv, L1-5) | Magic defense decrease: 7% -&gt; 18%
-Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Chant: 1x -&gt; 1.25x</t>
+          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | Damage cap UP
+Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x | Chant: 1x -&gt; 1.25x</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -13914,13 +14203,14 @@
           <t>effect_1, effect_3</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>Magic defense decrease, Speed, Chant</t>
-        </is>
-      </c>
-      <c r="N222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Magic defense</t>
+        </is>
+      </c>
       <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13959,8 +14249,8 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% -&gt; 80% (+4%/Lv, L1-5) | Speed decrease: 4% -&gt; 8% (+1%/Lv)
-Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Chant: 1x -&gt; 1.25x</t>
+          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | Damage cap UP
+Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x | Chant: 1x -&gt; 1.25x</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -13979,13 +14269,14 @@
           <t>effect_1, effect_3</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>Speed, Chant</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Speed decrease</t>
+        </is>
+      </c>
       <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -14024,8 +14315,8 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% -&gt; 80% (+4%/Lv, L1-5) | Evasion decrease: 7% -&gt; 15%
-Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Chant: 1x -&gt; 1.25x</t>
+          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | Damage cap UP
+Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x | Chant: 1x -&gt; 1.25x</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -14044,13 +14335,14 @@
           <t>effect_1, effect_3</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>Evasion decrease, Speed, Chant</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Evasion</t>
+        </is>
+      </c>
       <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -14089,8 +14381,8 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% -&gt; 80% (+4%/Lv, L1-5) | DEF decrease: 4% -&gt; 8% (+1%/Lv)
-Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Chant: 1x -&gt; 1.25x</t>
+          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | Damage cap UP
+Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x | Chant: 1x -&gt; 1.25x</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -14109,13 +14401,14 @@
           <t>effect_1, effect_3</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>Speed, Chant</t>
-        </is>
-      </c>
-      <c r="N225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
       <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -14154,8 +14447,8 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Pwr: 350 -&gt; 720 (avg +41.11/Lv, L1-10) | Accuracy: 86% -&gt; 95% (+1%/Lv)
-TP Cost: 22 -&gt; 66 (avg +4.89/Lv) | Speed: 1.3x | Chant: 0.85x -&gt; 0.76x (-0.01x/Lv)</t>
+          <t>Pwr: 350 -&gt; 390 -&gt; 430 -&gt; 470 -&gt; 510 -&gt; 550 -&gt; 590 -&gt; 630 -&gt; 680 -&gt; 720 (L10)
+TP Cost: 22 -&gt; 28 -&gt; 34 -&gt; 40 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58 -&gt; 62 -&gt; 66 | Speed: 1.3x</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -14166,13 +14459,14 @@
       </c>
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>Pwr, TP Cost</t>
-        </is>
-      </c>
-      <c r="N226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
       <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -14211,8 +14505,8 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Pwr: 240 -&gt; 600 (+40/Lv, L1-10) | Accuracy: 76% -&gt; 85% (+1%/Lv) | Stun: 25%
-TP Cost: 36 -&gt; 96 (avg +6.67/Lv) | Speed: 1.5x | Chant: 0.8x -&gt; 0.71x (-0.01x/Lv)</t>
+          <t>Pwr: 240 -&gt; 280 -&gt; 320 -&gt; 360 -&gt; 400 -&gt; 440 -&gt; 480 -&gt; 520 -&gt; 560 -&gt; 600 | Stun: 25%
+TP Cost: 36 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 80 -&gt; 88 -&gt; 96 | Speed: 1.5x</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -14223,13 +14517,14 @@
       </c>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>TP Cost</t>
-        </is>
-      </c>
-      <c r="N227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
       <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -14268,8 +14563,8 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>ATK increase: 8% -&gt; 16% (+2%/Lv, L1-5) | Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8
-TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22 | Speed: 1.5x -&gt; 1.7x (+0.05x/Lv) | Chant: 1.15x</t>
+          <t>ATK: +8% -&gt; +10% -&gt; +12% -&gt; +14% -&gt; +16% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22 | Chant: 1.15x</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -14283,10 +14578,15 @@
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
           <t>Raise the entire party's physical ATK.</t>
         </is>
       </c>
-      <c r="O228" t="inlineStr">
+      <c r="P228" t="inlineStr">
         <is>
           <t>Party ATK: +10% -&gt; +13% -&gt; +16% -&gt; +20% -&gt; +25% (L1-5)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30</t>
@@ -14330,8 +14630,8 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>DEF increase: 8% -&gt; 16% (+2%/Lv, L1-5) | Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8
-TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22 | Speed: 1.5x -&gt; 1.7x (+0.05x/Lv) | Chant: 1.15x</t>
+          <t>DEF: +8% -&gt; +10% -&gt; +12% -&gt; +14% -&gt; +16% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22 | Chant: 1.15x</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -14345,10 +14645,15 @@
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr">
         <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
           <t>Raise the entire party's physical DEF.</t>
         </is>
       </c>
-      <c r="O229" t="inlineStr">
+      <c r="P229" t="inlineStr">
         <is>
           <t>Party DEF: +10% -&gt; +13% -&gt; +16% -&gt; +20% -&gt; +25% (L1-5)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30</t>
@@ -14392,7 +14697,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Damage reduction: 25% -&gt; 27% -&gt; 29% -&gt; 32% -&gt; 35% (L1-5)
+          <t>Damage reduction: 25% -&gt; 27% -&gt; 29% -&gt; 32% -&gt; 35% (L1-5 Max)
 Turns: 3 | TP Cost: 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 | Speed: 0.75x | Chant: 1.75x</t>
         </is>
       </c>
@@ -14407,6 +14712,7 @@
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -14445,7 +14751,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Turns (L1-10): 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28
+          <t>Turns: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28
 TP Cost: 12 -&gt; 11 -&gt; 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3</t>
         </is>
       </c>
@@ -14460,6 +14766,7 @@
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -14521,6 +14828,7 @@
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14559,8 +14867,8 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Defense decrease UP | Accuracy: 80% -&gt; 90% (avg +2.5%/Lv, L1-5) | HP recovery DOWN
-Turns: 3 | TP Cost: 18 -&gt; 22 -&gt; 24 -&gt; 28 -&gt; 32 | Speed: 0.85x | Chant: 1.5x -&gt; 1.36x</t>
+          <t>Defense decrease UP | Accuracy: 80% -&gt; 83% -&gt; 86% -&gt; 88% -&gt; 90% (L1-5 Max)
+HP recovery DOWN | Turns: 3 | TP Cost: 18 -&gt; 22 -&gt; 24 -&gt; 28 -&gt; 32 | Speed: 0.85x</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -14579,13 +14887,14 @@
           <t>effect_1, effect_2, effect_3</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>Accuracy, Chant</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Chant</t>
+        </is>
+      </c>
       <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14624,8 +14933,8 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Pwr: 100 -&gt; 480 (avg +42.22/Lv, L1-10) | Accuracy: 80% -&gt; 90% (avg +1.11%/Lv)
-TP Cost: 30 -&gt; 66 (+4/Lv) | Speed: 0.85x | Chant: 1.25x -&gt; 1.15x</t>
+          <t>Pwr: 100 -&gt; 130 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 280 -&gt; 320 -&gt; 370 -&gt; 420 -&gt; 480 (L10)
+TP Cost: 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58 -&gt; 62 -&gt; 66 | Speed: 0.85x</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -14636,13 +14945,14 @@
       </c>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>Pwr, Accuracy, Chant</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Accuracy, Chant</t>
+        </is>
+      </c>
       <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14681,8 +14991,8 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Pwr: 360 -&gt; 740 (avg +42.22/Lv, L1-10) | Accuracy: 76% -&gt; 85% (+1%/Lv)
-Instakill: 12% | TP Cost: 32 -&gt; 56 | Speed: 1.2x | Chant: 0.88x -&gt; 0.8x</t>
+          <t>Pwr: 360 -&gt; 400 -&gt; 440 -&gt; 480 -&gt; 520 -&gt; 560 -&gt; 600 -&gt; 640 -&gt; 690 -&gt; 740 (L10)
+Instakill: 12% | TP Cost: 32 -&gt; 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 52 -&gt; 54 -&gt; 56</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -14693,13 +15003,14 @@
       </c>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>Pwr, TP Cost, Chant</t>
-        </is>
-      </c>
-      <c r="N235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Accuracy, Speed, Chant</t>
+        </is>
+      </c>
       <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14738,8 +15049,8 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Maximum damage UP | Maximum heal UP | TP Cost: 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 (L1-5)
-Speed: 1.5x | Chant: 0.84x -&gt; 0.8x (-0.01x/Lv)</t>
+          <t>Maximum damage UP | Maximum heal UP
+TP Cost: 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 (L1-5 Max) | Speed: 1.5x | Chant: 0.84x -&gt; 0.8x</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -14761,6 +15072,7 @@
       <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14814,6 +15126,7 @@
       <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14867,6 +15180,7 @@
       <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14920,6 +15234,7 @@
       <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14973,6 +15288,7 @@
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -15026,6 +15342,7 @@
       <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -15077,12 +15394,13 @@
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr">
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr">
         <is>
           <t>Occasionally reflects incoming damage back as fixed neutral damage.</t>
         </is>
       </c>
-      <c r="O242" t="inlineStr">
+      <c r="P242" t="inlineStr">
         <is>
           <t>Reflect Rate: 20% chance to reflect 30% of received damage to attacker
 Heroine: Melvy</t>
@@ -15125,7 +15443,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>ATK bonus (L1-10): 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%</t>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -15137,12 +15455,13 @@
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr">
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr">
         <is>
           <t>Increases equipped sword base ATK.</t>
         </is>
       </c>
-      <c r="O243" t="inlineStr">
+      <c r="P243" t="inlineStr">
         <is>
           <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
 Scales off weapon base ATK (not total character ATK)</t>
@@ -15185,7 +15504,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>ATK bonus (L1-10): 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%</t>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -15197,12 +15516,13 @@
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr">
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr">
         <is>
           <t>Increases equipped axe base ATK.</t>
         </is>
       </c>
-      <c r="O244" t="inlineStr">
+      <c r="P244" t="inlineStr">
         <is>
           <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
 Scales off weapon base ATK</t>
@@ -15245,7 +15565,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>ATK bonus (L1-10): 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17%</t>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17% (L10)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -15257,12 +15577,13 @@
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr">
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr">
         <is>
           <t>Increases equipped dagger base ATK.</t>
         </is>
       </c>
-      <c r="O245" t="inlineStr">
+      <c r="P245" t="inlineStr">
         <is>
           <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
 Scales off weapon base ATK</t>
@@ -15305,7 +15626,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>ATK bonus (L1-10): 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%</t>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -15317,12 +15638,13 @@
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr">
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr">
         <is>
           <t>Increases equipped mace base ATK.</t>
         </is>
       </c>
-      <c r="O246" t="inlineStr">
+      <c r="P246" t="inlineStr">
         <is>
           <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
 Scales off weapon base ATK</t>
@@ -15365,7 +15687,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>ATK bonus (L1-10): 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%</t>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -15377,12 +15699,13 @@
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
       <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr">
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr">
         <is>
           <t>Increases equipped lance base ATK.</t>
         </is>
       </c>
-      <c r="O247" t="inlineStr">
+      <c r="P247" t="inlineStr">
         <is>
           <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
 Scales off weapon base ATK</t>
@@ -15425,7 +15748,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>ATK bonus (L1-10): 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%</t>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -15437,12 +15760,13 @@
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr">
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr">
         <is>
           <t>Increases equipped bow base ATK.</t>
         </is>
       </c>
-      <c r="O248" t="inlineStr">
+      <c r="P248" t="inlineStr">
         <is>
           <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
 Scales off weapon base ATK</t>
@@ -15485,7 +15809,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>ATK bonus (L1-10): 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%</t>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -15497,12 +15821,13 @@
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr"/>
       <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr">
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr">
         <is>
           <t>Increases equipped katana base ATK.</t>
         </is>
       </c>
-      <c r="O249" t="inlineStr">
+      <c r="P249" t="inlineStr">
         <is>
           <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
 Scales off weapon base ATK</t>
@@ -15545,7 +15870,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>ATK bonus (L1-10): 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20%</t>
+          <t>ATK bonus: 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% (L10)</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -15557,12 +15882,13 @@
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr"/>
       <c r="M250" t="inlineStr"/>
-      <c r="N250" t="inlineStr">
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr">
         <is>
           <t>Increases equipped projectile weapon base ATK.</t>
         </is>
       </c>
-      <c r="O250" t="inlineStr">
+      <c r="P250" t="inlineStr">
         <is>
           <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
 Scales off weapon base ATK</t>
@@ -15605,7 +15931,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>ATK bonus (L1-10): 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17%</t>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17% (L10)</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -15617,12 +15943,13 @@
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr"/>
       <c r="M251" t="inlineStr"/>
-      <c r="N251" t="inlineStr">
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr">
         <is>
           <t>Increases equipped whip base ATK.</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr">
+      <c r="P251" t="inlineStr">
         <is>
           <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
 Scales off weapon base ATK</t>
@@ -15665,7 +15992,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>ATK bonus (L1-10): 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20%</t>
+          <t>ATK bonus: 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% (L10)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -15677,12 +16004,13 @@
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr"/>
       <c r="M252" t="inlineStr"/>
-      <c r="N252" t="inlineStr">
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr">
         <is>
           <t>Increases equipped fan base ATK.</t>
         </is>
       </c>
-      <c r="O252" t="inlineStr">
+      <c r="P252" t="inlineStr">
         <is>
           <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
 Scales off weapon base ATK</t>
@@ -15725,7 +16053,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>ATK bonus (L1-10): 2% -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 12%</t>
+          <t>ATK bonus: 2% -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 12% (L10)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -15737,12 +16065,13 @@
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr"/>
-      <c r="N253" t="inlineStr">
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr">
         <is>
           <t>Increases equipped base ATK for all weapon types.</t>
         </is>
       </c>
-      <c r="O253" t="inlineStr">
+      <c r="P253" t="inlineStr">
         <is>
           <t>ATK (L1-10): +2% -&gt; +3% -&gt; +4% -&gt; +5% -&gt; +6% -&gt; +7% -&gt; +8% -&gt; +9% -&gt; +10% -&gt; +12%
 Universal weapon scaling</t>
@@ -15785,7 +16114,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Magic attack bonus: 6% -&gt; 15% (+1%/Lv, L1-10)</t>
+          <t>Magic attack bonus: 6% -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -15797,12 +16126,13 @@
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr"/>
       <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr">
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr">
         <is>
           <t>Increase magic attack power bonus for all spells.</t>
         </is>
       </c>
-      <c r="O254" t="inlineStr">
+      <c r="P254" t="inlineStr">
         <is>
           <t>Magic Power (L1-10): +6% (L1) -&gt; +15% (L10 Max) | Step: +1%/Lv (+6% base)
 Applies to all offensive spell damage</t>
@@ -15865,12 +16195,13 @@
         </is>
       </c>
       <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr">
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr">
         <is>
           <t>Boost potency and maximum HP healing cap of healing magic.</t>
         </is>
       </c>
-      <c r="O255" t="inlineStr">
+      <c r="P255" t="inlineStr">
         <is>
           <t>Healing Bonus: +10% -&gt; +30% (+2%/Lv up to L5, then +3%/Lv, Max +30%)
 Also raises baseline healing cap on Heal and Circle Heal</t>
@@ -15913,7 +16244,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>HP recovery: 2% -&gt; 10% (+2%/Lv, L1-5)</t>
+          <t>HP recovery: 2% -&gt; 4% -&gt; 6% -&gt; 8% -&gt; 10% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -15925,12 +16256,13 @@
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr">
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr">
         <is>
           <t>Recover HP every turn during battle.</t>
         </is>
       </c>
-      <c r="O256" t="inlineStr">
+      <c r="P256" t="inlineStr">
         <is>
           <t>HP Regen: 10 -&gt; 20 -&gt; 30 -&gt; 40 -&gt; 50 HP per turn (L1-5)
 Triggers at start of user's action in combat</t>
@@ -15973,7 +16305,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>HP recovery: 1% -&gt; 5% (+1%/Lv, L1-5)</t>
+          <t>HP recovery: 1% -&gt; 2% -&gt; 3% -&gt; 4% -&gt; 5% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -15985,12 +16317,13 @@
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr"/>
       <c r="M257" t="inlineStr"/>
-      <c r="N257" t="inlineStr">
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr">
         <is>
           <t>Slightly recover HP every turn during battle.</t>
         </is>
       </c>
-      <c r="O257" t="inlineStr">
+      <c r="P257" t="inlineStr">
         <is>
           <t>HP Regen (L1-5): 1% -&gt; 2% -&gt; 3% -&gt; 4% -&gt; 5% (+1%/Lv)
 Triggers at start of user's action in combat</t>
@@ -16033,7 +16366,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>TP recovery: 3 -&gt; 6 -&gt; 9 -&gt; 12 -&gt; 16 (L1-5)</t>
+          <t>TP recovery: 3 -&gt; 6 -&gt; 9 -&gt; 12 -&gt; 16 (L1-5 Max)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -16045,12 +16378,13 @@
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr">
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr">
         <is>
           <t>Recover TP every turn during battle.</t>
         </is>
       </c>
-      <c r="O258" t="inlineStr">
+      <c r="P258" t="inlineStr">
         <is>
           <t>TP Regen (L1-10): 2 -&gt; 3 -&gt; 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 TP per turn
 Active on user turn in battle</t>
@@ -16093,7 +16427,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>TP recovery: 1 -&gt; 9 (+2/Lv, L1-5)</t>
+          <t>TP recovery: 1 -&gt; 3 -&gt; 5 -&gt; 7 -&gt; 9 (L1-5 Max)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -16105,12 +16439,13 @@
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr">
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr">
         <is>
           <t>Slightly recover TP every turn during battle.</t>
         </is>
       </c>
-      <c r="O259" t="inlineStr">
+      <c r="P259" t="inlineStr">
         <is>
           <t>TP Regen: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 TP per turn (L1-8)
 Triggers on user turn in combat</t>
@@ -16153,7 +16488,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Elemental resistance: 6 -&gt; 15 (+1/Lv, L1-10)</t>
+          <t>Elemental resistance: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 (L10)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -16165,12 +16500,13 @@
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr">
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr">
         <is>
           <t>Raise innate resistance to all elements.</t>
         </is>
       </c>
-      <c r="O260" t="inlineStr">
+      <c r="P260" t="inlineStr">
         <is>
           <t>Elemental Resist: +5 -&gt; +10 -&gt; +15 -&gt; +20 -&gt; +25 all elements (L1-5)
 Applies to Fire, Water, Lightning, Wind, and Earth</t>
@@ -16213,7 +16549,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Counterattack rate: 6% -&gt; 18% (+3%/Lv, L1-5)</t>
+          <t>Counterattack rate: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -16225,12 +16561,13 @@
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr">
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr">
         <is>
           <t>Counterattack short/medium physical hits with equipped weapon.</t>
         </is>
       </c>
-      <c r="O261" t="inlineStr">
+      <c r="P261" t="inlineStr">
         <is>
           <t>Counter Rate: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5) | Step: +3%/Lv
 Note: Short-range retaliations will trigger enemy Dark Aura</t>
@@ -16273,7 +16610,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Activation rate: 4% -&gt; 12% (+2%/Lv, L1-5)</t>
+          <t>Activation rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -16285,12 +16622,13 @@
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr"/>
       <c r="M262" t="inlineStr"/>
-      <c r="N262" t="inlineStr">
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr">
         <is>
           <t>Occasionally parry and counterattack when targeted by an enemy.</t>
         </is>
       </c>
-      <c r="O262" t="inlineStr">
+      <c r="P262" t="inlineStr">
         <is>
           <t>Parry &amp; Counter: 10% -&gt; 25% (+3.75%/Lv) | Levels: L1-5
 Nullifies incoming attack and strikes back</t>
@@ -16333,7 +16671,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Double attack rate: 9% -&gt; 21% (+3%/Lv, L1-5)</t>
+          <t>Double attack rate: 9% -&gt; 12% -&gt; 15% -&gt; 18% -&gt; 21% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -16345,12 +16683,13 @@
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr"/>
       <c r="M263" t="inlineStr"/>
-      <c r="N263" t="inlineStr">
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr">
         <is>
           <t>Chance to attack twice when using normal attacks.</t>
         </is>
       </c>
-      <c r="O263" t="inlineStr">
+      <c r="P263" t="inlineStr">
         <is>
           <t>Trigger Rate: 9% -&gt; 12% -&gt; 15% -&gt; 18% -&gt; 21% (L1-5) | Step: +3%/Lv
 Can stack with Triple Attack (up to 5 strikes total)</t>
@@ -16393,7 +16732,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Triple attack rate: 5% -&gt; 17% (+3%/Lv, L1-5)</t>
+          <t>Triple attack rate: 5% -&gt; 8% -&gt; 11% -&gt; 14% -&gt; 17% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -16405,12 +16744,13 @@
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
       <c r="M264" t="inlineStr"/>
-      <c r="N264" t="inlineStr">
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr">
         <is>
           <t>Chance to attack thrice when using normal attacks.</t>
         </is>
       </c>
-      <c r="O264" t="inlineStr">
+      <c r="P264" t="inlineStr">
         <is>
           <t>Trigger Rate: 5% -&gt; 7.5% -&gt; 10% -&gt; 12.5% -&gt; 15% (L1-5) | Step: +2.5%/Lv
 Stacks with Double Attack</t>
@@ -16453,7 +16793,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Evasion rate: 20% -&gt; 36% (+4%/Lv, L1-5)</t>
+          <t>Evasion rate: 20% -&gt; 24% -&gt; 28% -&gt; 32% -&gt; 36% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -16467,6 +16807,7 @@
       <c r="M265" t="inlineStr"/>
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr"/>
+      <c r="P265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -16504,7 +16845,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Activation rate: 10% -&gt; 30% (+5%/Lv, L1-5)</t>
+          <t>Activation rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -16518,6 +16859,7 @@
       <c r="M266" t="inlineStr"/>
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr"/>
+      <c r="P266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -16555,7 +16897,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Survival rate: 10% -&gt; 30% (+5%/Lv, L1-5)</t>
+          <t>Survival rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -16567,12 +16909,13 @@
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr"/>
       <c r="M267" t="inlineStr"/>
-      <c r="N267" t="inlineStr">
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr">
         <is>
           <t>Occasionally survive at 1 HP after receiving fatal damage.</t>
         </is>
       </c>
-      <c r="O267" t="inlineStr">
+      <c r="P267" t="inlineStr">
         <is>
           <t>Survival Rate: 20% -&gt; 30% -&gt; 40% -&gt; 50% -&gt; 60% (L1-5) | Step: +10%/Lv
 Prevents death when hit by lethal blows</t>
@@ -16615,7 +16958,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Auto-guard rate: 4% -&gt; 12% (+2%/Lv, L1-5)</t>
+          <t>Auto-guard rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -16627,12 +16970,13 @@
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
       <c r="M268" t="inlineStr"/>
-      <c r="N268" t="inlineStr">
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr">
         <is>
           <t>Occasionally Defend automatically when receiving physical attacks.</t>
         </is>
       </c>
-      <c r="O268" t="inlineStr">
+      <c r="P268" t="inlineStr">
         <is>
           <t>Auto-Guard Rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5) | Step: +5%/Lv
 Halves incoming damage when triggered</t>
@@ -16675,7 +17019,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Sub-weapon ATK (L1-10): 30% -&gt; 35 -&gt; 40 -&gt; 45 -&gt; 50 -&gt; 54 -&gt; 58 -&gt; 62 -&gt; 68 -&gt; 72%</t>
+          <t>Sub-weapon ATK: 30% -&gt; 35 -&gt; 40 -&gt; 45 -&gt; 50 -&gt; 54 -&gt; 58 -&gt; 62 -&gt; 68 -&gt; 72% (L10)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -16687,12 +17031,13 @@
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr"/>
       <c r="M269" t="inlineStr"/>
-      <c r="N269" t="inlineStr">
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr">
         <is>
           <t>Equip two one-handed weapons simultaneously.</t>
         </is>
       </c>
-      <c r="O269" t="inlineStr">
+      <c r="P269" t="inlineStr">
         <is>
           <t>Off-Hand ATK: 50% -&gt; 57.5% -&gt; 65% -&gt; 72.5% -&gt; 80% (L1-5) | Step: +7.5%/Lv
 Main hand weapon deals 100% ATK</t>
@@ -16735,7 +17080,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>TP conversion: 4% -&gt; 20% (+4%/Lv, L1-5)</t>
+          <t>TP conversion: 4% -&gt; 8% -&gt; 12% -&gt; 16% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -16749,6 +17094,7 @@
       <c r="M270" t="inlineStr"/>
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr"/>
+      <c r="P270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -16786,7 +17132,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Activation rate: 8% -&gt; 20% (+3%/Lv, L1-5)</t>
+          <t>Activation rate: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -16800,6 +17146,7 @@
       <c r="M271" t="inlineStr"/>
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr"/>
+      <c r="P271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -16837,7 +17184,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Activation rate: 2% -&gt; 6% (+1%/Lv, L1-5)</t>
+          <t>Activation rate: 2% -&gt; 3% -&gt; 4% -&gt; 5% -&gt; 6% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -16851,6 +17198,7 @@
       <c r="M272" t="inlineStr"/>
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr"/>
+      <c r="P272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -16888,7 +17236,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Activation rate: 4% -&gt; 12% (+2%/Lv, L1-5)</t>
+          <t>Activation rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -16902,6 +17250,7 @@
       <c r="M273" t="inlineStr"/>
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
+      <c r="P273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16939,7 +17288,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Speed increase: 15% -&gt; 16% -&gt; 17% -&gt; 18% -&gt; 20% (L1-5)</t>
+          <t>Speed increase: 15% -&gt; 16% -&gt; 17% -&gt; 18% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -16953,6 +17302,7 @@
       <c r="M274" t="inlineStr"/>
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr"/>
+      <c r="P274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -16990,7 +17340,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Number of possible debuffs: 1 -&gt; 6 (+1/Lv, L1-6)</t>
+          <t>Number of possible debuffs: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 (L6)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -17004,6 +17354,7 @@
       <c r="M275" t="inlineStr"/>
       <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr"/>
+      <c r="P275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -17041,7 +17392,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>ATK increase: 15% -&gt; 27% (+3%/Lv, L1-5)</t>
+          <t>ATK: +15% -&gt; +18% -&gt; +21% -&gt; +24% -&gt; +27% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -17055,6 +17406,7 @@
       <c r="M276" t="inlineStr"/>
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr"/>
+      <c r="P276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -17098,6 +17450,7 @@
       <c r="M277" t="inlineStr"/>
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr"/>
+      <c r="P277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -17141,6 +17494,7 @@
       <c r="M278" t="inlineStr"/>
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr"/>
+      <c r="P278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -17178,7 +17532,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Physical damage decrease: 6% -&gt; 10% (+1%/Lv, L1-5)</t>
+          <t>Physical damage: -6% -&gt; -7% -&gt; -8% -&gt; -9% -&gt; -10% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -17192,6 +17546,7 @@
       <c r="M279" t="inlineStr"/>
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="inlineStr"/>
+      <c r="P279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -17229,7 +17584,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Activation rate: 8% -&gt; 12% (+1%/Lv, L1-5)</t>
+          <t>Activation rate: 8% -&gt; 9% -&gt; 10% -&gt; 11% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -17241,12 +17596,13 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr"/>
-      <c r="N280" t="inlineStr">
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr">
         <is>
           <t>Occasionally nullify physical damage.</t>
         </is>
       </c>
-      <c r="O280" t="inlineStr">
+      <c r="P280" t="inlineStr">
         <is>
           <t>Nullify Rate: 8% -&gt; 20% (+3%/Lv) | Levels: L1-5
 Completely negates incoming physical attacks when triggered</t>
@@ -17305,12 +17661,13 @@
         </is>
       </c>
       <c r="M281" t="inlineStr"/>
-      <c r="N281" t="inlineStr">
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr">
         <is>
           <t>Automatically cure own status ailments at start of turn.</t>
         </is>
       </c>
-      <c r="O281" t="inlineStr">
+      <c r="P281" t="inlineStr">
         <is>
           <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep -&gt; Slow
 Triggers automatically at start of user's combat turn</t>
@@ -17353,7 +17710,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>ATK/DEX increase: 10% -&gt; 11% -&gt; 12% -&gt; 13% -&gt; 15% (L1-5)</t>
+          <t>ATK/DEX: +10% -&gt; +11% -&gt; +12% -&gt; +13% -&gt; +15% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -17365,12 +17722,13 @@
       <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr"/>
       <c r="M282" t="inlineStr"/>
-      <c r="N282" t="inlineStr">
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr">
         <is>
           <t>Boost physical ATK and DEX when HP drops below 50%.</t>
         </is>
       </c>
-      <c r="O282" t="inlineStr">
+      <c r="P282" t="inlineStr">
         <is>
           <t>ATK &amp; DEX: +20% -&gt; +40% (+5%/Lv) when HP &lt; 50% | Levels: L1-5
 Immediate combat stat trigger</t>
@@ -17413,7 +17771,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Interruption rate: -10% -&gt; -50% (-10%/Lv, L1-5)</t>
+          <t>Interruption rate: -10% -&gt; -20% -&gt; -30% -&gt; -40% -&gt; -50% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -17425,12 +17783,13 @@
       <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr"/>
-      <c r="N283" t="inlineStr">
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr">
         <is>
           <t>Make it harder for chants, songs, and dances to be interrupted.</t>
         </is>
       </c>
-      <c r="O283" t="inlineStr">
+      <c r="P283" t="inlineStr">
         <is>
           <t>Interruption Resist: +20% -&gt; +50% (+7.5%/Lv) | 80% Crit Interrupt Res at Lv 5</t>
         </is>
@@ -17472,7 +17831,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Chant time: -8% -&gt; -20% (-3%/Lv, L1-5)</t>
+          <t>Chant time: -8% -&gt; -11% -&gt; -14% -&gt; -17% -&gt; -20% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -17484,12 +17843,13 @@
       <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr"/>
       <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr">
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr">
         <is>
           <t>Reduce chant time required to cast spells.</t>
         </is>
       </c>
-      <c r="O284" t="inlineStr">
+      <c r="P284" t="inlineStr">
         <is>
           <t>Chant Time Reduction: -10% -&gt; -30% (-5%/Lv) | Levels: L1-5
 Accelerates offensive and healing magic activation</t>
@@ -17532,7 +17892,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>TP Cost reduction: 10% -&gt; 30% (+5%/Lv, L1-5)</t>
+          <t>TP Cost reduction: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -17544,12 +17904,13 @@
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr"/>
       <c r="M285" t="inlineStr"/>
-      <c r="N285" t="inlineStr">
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr">
         <is>
           <t>Reduce TP consumption in battle.</t>
         </is>
       </c>
-      <c r="O285" t="inlineStr">
+      <c r="P285" t="inlineStr">
         <is>
           <t>TP Cost Reduction: -10% -&gt; -15% -&gt; -20% -&gt; -25% -&gt; -30% (L1-5)
 Lowers cost of all techniques and spells</t>
@@ -17592,7 +17953,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Accuracy: 3% -&gt; 5% -&gt; 7% -&gt; 9% -&gt; 12% (L1-5)</t>
+          <t>Accuracy: 3% -&gt; 5% -&gt; 7% -&gt; 9% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
@@ -17604,12 +17965,13 @@
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr"/>
-      <c r="N286" t="inlineStr">
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr">
         <is>
           <t>Heighten magic accuracy for all cast spells.</t>
         </is>
       </c>
-      <c r="O286" t="inlineStr">
+      <c r="P286" t="inlineStr">
         <is>
           <t>Magic Accuracy: +15% -&gt; +35% (+5%/Lv) | Levels: L1-5
 Significantly reduces spell evasion by high RES targets</t>
@@ -17652,7 +18014,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Enemy preemptive attack rate: -20% -&gt; -28% -&gt; -36% -&gt; -44% -&gt; -50% (L1-5)</t>
+          <t>Enemy preemptive attack rate: -20% -&gt; -28% -&gt; -36% -&gt; -44% -&gt; -50% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
@@ -17664,12 +18026,13 @@
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr"/>
-      <c r="N287" t="inlineStr">
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr">
         <is>
           <t>Reduce enemy preemptive strike rate in dungeons.</t>
         </is>
       </c>
-      <c r="O287" t="inlineStr">
+      <c r="P287" t="inlineStr">
         <is>
           <t>Preemptive Reduction: -20% -&gt; -60% (-10%/Lv) | Levels: L1-5
 Protects party from surprise enemy encounters</t>
@@ -17712,7 +18075,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Preemptive attack rate: 8% -&gt; 20% (+3%/Lv, L1-5)</t>
+          <t>Preemptive attack rate: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -17724,12 +18087,13 @@
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr"/>
       <c r="M288" t="inlineStr"/>
-      <c r="N288" t="inlineStr">
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr">
         <is>
           <t>Increase party's preemptive strike rate against foes.</t>
         </is>
       </c>
-      <c r="O288" t="inlineStr">
+      <c r="P288" t="inlineStr">
         <is>
           <t>Party Preemptive Rate: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
 Grants free initial turn before enemies act</t>
@@ -17772,7 +18136,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Battle escape rate: 20% -&gt; 40% (+5%/Lv, L1-5)</t>
+          <t>Battle escape rate: 20% -&gt; 25% -&gt; 30% -&gt; 35% -&gt; 40% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -17784,12 +18148,13 @@
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr"/>
       <c r="M289" t="inlineStr"/>
-      <c r="N289" t="inlineStr">
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr">
         <is>
           <t>Increase success rate when attempting to flee from battle.</t>
         </is>
       </c>
-      <c r="O289" t="inlineStr">
+      <c r="P289" t="inlineStr">
         <is>
           <t>Escape Success: +20% -&gt; +50% (+7.5%/Lv) | Levels: L1-5
 Does not apply to scripted boss battles</t>
@@ -17832,7 +18197,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Item drop rate: 4% -&gt; 12% (+2%/Lv, L1-5)</t>
+          <t>Item drop rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
@@ -17844,12 +18209,13 @@
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr"/>
-      <c r="N290" t="inlineStr">
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr">
         <is>
           <t>Increase enemies' item drop rate after battle.</t>
         </is>
       </c>
-      <c r="O290" t="inlineStr">
+      <c r="P290" t="inlineStr">
         <is>
           <t>Item Drop Rate: +10% -&gt; +15% -&gt; +20% -&gt; +25% -&gt; +30% (L1-5)
 Boosts party equipment and material acquisition</t>
@@ -17892,7 +18258,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Gold drop rate: 25% -&gt; 125% (+25%/Lv, L1-5)</t>
+          <t>Gold drop rate: 25% -&gt; 50% -&gt; 75% -&gt; 100% -&gt; 125% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
@@ -17904,12 +18270,13 @@
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr"/>
       <c r="M291" t="inlineStr"/>
-      <c r="N291" t="inlineStr">
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr">
         <is>
           <t>Increase amount of gold dropped by defeated enemies.</t>
         </is>
       </c>
-      <c r="O291" t="inlineStr">
+      <c r="P291" t="inlineStr">
         <is>
           <t>Gold Gain: +15% -&gt; +23% -&gt; +32% -&gt; +41% -&gt; +50% (L1-5)
 Earn bonus currency after every battle</t>
@@ -17952,7 +18319,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Found item quality: 1 -&gt; 5 (+1/Lv, L1-5)</t>
+          <t>Found item quality: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 (L1-5 Max)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
@@ -17964,12 +18331,13 @@
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr"/>
-      <c r="N292" t="inlineStr">
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr">
         <is>
           <t>Occasionally discover items while exploring dungeons.</t>
         </is>
       </c>
-      <c r="O292" t="inlineStr">
+      <c r="P292" t="inlineStr">
         <is>
           <t>Item Find Rate: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
 Finds consumables and crafting materials while walking</t>
@@ -18032,12 +18400,13 @@
         </is>
       </c>
       <c r="M293" t="inlineStr"/>
-      <c r="N293" t="inlineStr">
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr">
         <is>
           <t>Restore party HP and TP slightly after winning a battle.</t>
         </is>
       </c>
-      <c r="O293" t="inlineStr">
+      <c r="P293" t="inlineStr">
         <is>
           <t>Post-Battle Recovery: 5% -&gt; 15% HP &amp; TP (+2.5%/Lv) | Levels: L1-5
 Restores whole party after combat conclusion</t>
@@ -18080,7 +18449,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Item keep rate: 25% -&gt; 27% -&gt; 29% -&gt; 32% -&gt; 35% (L1-5)</t>
+          <t>Item keep rate: 25% -&gt; 27% -&gt; 29% -&gt; 32% -&gt; 35% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -18092,12 +18461,13 @@
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr"/>
-      <c r="N294" t="inlineStr">
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" t="inlineStr">
         <is>
           <t>Occasionally retain disposable items after using them in combat.</t>
         </is>
       </c>
-      <c r="O294" t="inlineStr">
+      <c r="P294" t="inlineStr">
         <is>
           <t>Item Retain Chance: 15% -&gt; 35% (+5%/Lv) | Levels: L1-5
 Item is not consumed from inventory when triggered</t>
@@ -18140,7 +18510,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Item effects: 10% -&gt; 100% (+10%/Lv, L1-10)</t>
+          <t>Item effects: 10% -&gt; 20 -&gt; 30 -&gt; 40 -&gt; 50 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 90 -&gt; 100% (L10)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
@@ -18152,12 +18522,13 @@
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr"/>
-      <c r="N295" t="inlineStr">
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr">
         <is>
           <t>Increase effects of HP and TP recovery items during battle.</t>
         </is>
       </c>
-      <c r="O295" t="inlineStr">
+      <c r="P295" t="inlineStr">
         <is>
           <t>Item Potency: +20% -&gt; +30% -&gt; +40% -&gt; +50% -&gt; +60% (L1-5)
 Applies to all consumable recovery items used in combat</t>
@@ -18200,7 +18571,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Speed: 6% -&gt; 18% (+3%/Lv, L1-5)</t>
+          <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -18212,12 +18583,13 @@
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr">
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr">
         <is>
           <t>Become capable of performing two songs simultaneously.</t>
         </is>
       </c>
-      <c r="O296" t="inlineStr">
+      <c r="P296" t="inlineStr">
         <is>
           <t>Singing Speed: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
 Allows maintaining 2 active Bard songs at once</t>
@@ -18260,7 +18632,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Speed: 6% -&gt; 18% (+3%/Lv, L1-5)</t>
+          <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -18272,12 +18644,13 @@
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr"/>
-      <c r="N297" t="inlineStr">
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr">
         <is>
           <t>Become capable of performing two dances simultaneously.</t>
         </is>
       </c>
-      <c r="O297" t="inlineStr">
+      <c r="P297" t="inlineStr">
         <is>
           <t>Dancing Speed: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
 Allows maintaining 2 active Dancer dances at once</t>
@@ -18320,7 +18693,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Speed: 6% -&gt; 18% (+3%/Lv, L1-5)</t>
+          <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -18332,12 +18705,13 @@
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr"/>
       <c r="M298" t="inlineStr"/>
-      <c r="N298" t="inlineStr">
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" t="inlineStr">
         <is>
           <t>Become capable of controlling two summoned dolls at once. Dolls gain Guts.</t>
         </is>
       </c>
-      <c r="O298" t="inlineStr">
+      <c r="P298" t="inlineStr">
         <is>
           <t>Doll Control Speed: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
 Maintains 2 active summoned dolls simultaneously</t>
@@ -18380,7 +18754,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Sealbook ability increase: 15% -&gt; 27% (+3%/Lv, L1-5)</t>
+          <t>Sealbook ability: +15% -&gt; +18% -&gt; +21% -&gt; +24% -&gt; +27% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
@@ -18392,12 +18766,13 @@
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr"/>
       <c r="M299" t="inlineStr"/>
-      <c r="N299" t="inlineStr">
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr">
         <is>
           <t>Increase doll power with strength of equipped Sealbook.</t>
         </is>
       </c>
-      <c r="O299" t="inlineStr">
+      <c r="P299" t="inlineStr">
         <is>
           <t>Doll Power Bonus: +10% -&gt; +30% (+5%/Lv) based on Sealbook level
 Levels: L1-5</t>
@@ -18440,7 +18815,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Maid skill bonus: 1% -&gt; 10% (+1%/Lv, L1-10)</t>
+          <t>Maid skill bonus: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10% (L10)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -18452,12 +18827,13 @@
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr"/>
       <c r="M300" t="inlineStr"/>
-      <c r="N300" t="inlineStr">
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr">
         <is>
           <t>Increased potency and effectiveness for all maid skills.</t>
         </is>
       </c>
-      <c r="O300" t="inlineStr">
+      <c r="P300" t="inlineStr">
         <is>
           <t>Maid Skill Bonus: +2% -&gt; +4% -&gt; +6% -&gt; +8% -&gt; +10% (L1-5)
 Empowers First Aid, Cook, and Clean</t>
@@ -18500,7 +18876,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Singing skill bonus: 3% -&gt; 12% (+1%/Lv, L1-10)</t>
+          <t>Singing skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -18512,12 +18888,13 @@
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr"/>
       <c r="M301" t="inlineStr"/>
-      <c r="N301" t="inlineStr">
+      <c r="N301" t="inlineStr"/>
+      <c r="O301" t="inlineStr">
         <is>
           <t>Increased potency and effectiveness for all songs.</t>
         </is>
       </c>
-      <c r="O301" t="inlineStr">
+      <c r="P301" t="inlineStr">
         <is>
           <t>Song Potency: +3% -&gt; +6% -&gt; +9% -&gt; +12% -&gt; +15% (L1-5)
 Empowers Bard songs and regeneration rates</t>
@@ -18560,7 +18937,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Dancing skill bonus: 3% -&gt; 12% (+1%/Lv, L1-10)</t>
+          <t>Dancing skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -18572,12 +18949,13 @@
       <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr"/>
-      <c r="N302" t="inlineStr">
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr">
         <is>
           <t>Increased potency and effectiveness for all dances.</t>
         </is>
       </c>
-      <c r="O302" t="inlineStr">
+      <c r="P302" t="inlineStr">
         <is>
           <t>Dance Potency: +3% -&gt; +6% -&gt; +9% -&gt; +12% -&gt; +15% (L1-5)
 Empowers Dancer dances and status effects</t>
@@ -18620,7 +18998,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Doll skill bonus: 3% -&gt; 12% (+1%/Lv, L1-10)</t>
+          <t>Doll skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -18632,12 +19010,13 @@
       <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr"/>
-      <c r="N303" t="inlineStr">
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr">
         <is>
           <t>Increased potency and effectiveness for all doll skills.</t>
         </is>
       </c>
-      <c r="O303" t="inlineStr">
+      <c r="P303" t="inlineStr">
         <is>
           <t>Doll Stat Bonus: +3% -&gt; +15% (+3%/Lv) | Levels: L1-5
 Increases damage, healing, and durability of summoned dolls</t>
@@ -18680,7 +19059,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Double attack rate: 20% -&gt; 32% (avg +1.33%/Lv, L1-10)</t>
+          <t>Double attack rate: 20% -&gt; 21 -&gt; 22 -&gt; 23 -&gt; 24 -&gt; 25 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32% (L10)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -18691,17 +19070,14 @@
       </c>
       <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr"/>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>Double attack rate</t>
-        </is>
-      </c>
-      <c r="N304" t="inlineStr">
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr">
         <is>
           <t>Occasionally attack twice when performing normal attacks.</t>
         </is>
       </c>
-      <c r="O304" t="inlineStr">
+      <c r="P304" t="inlineStr">
         <is>
           <t>Double Attack Rate: 8% -&gt; 20% (+3%/Lv) | Levels: L1-5
 Normal attack trigger</t>
@@ -18744,7 +19120,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Song chant time: -10% -&gt; -20% (avg -1.11%/Lv, L1-10)</t>
+          <t>Song chant time: -10% -&gt; -11 -&gt; -12 -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -20%</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -18755,17 +19131,14 @@
       </c>
       <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr"/>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>Song chant time</t>
-        </is>
-      </c>
-      <c r="N305" t="inlineStr">
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr">
         <is>
           <t>Reduce chant time required to start songs.</t>
         </is>
       </c>
-      <c r="O305" t="inlineStr">
+      <c r="P305" t="inlineStr">
         <is>
           <t>Song Chant Reduction: -10% -&gt; -30% (-5%/Lv) | Levels: L1-5
 Accelerates Bard song activation</t>
@@ -18808,7 +19181,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Negotiation rate: 10% -&gt; 14% -&gt; 18% -&gt; 22% -&gt; 25% (L1-5)</t>
+          <t>Negotiation rate: 10% -&gt; 14% -&gt; 18% -&gt; 22% -&gt; 25% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -18820,12 +19193,13 @@
       <c r="K306" t="inlineStr"/>
       <c r="L306" t="inlineStr"/>
       <c r="M306" t="inlineStr"/>
-      <c r="N306" t="inlineStr">
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr">
         <is>
           <t>Reduce purchase and identification prices at shops.</t>
         </is>
       </c>
-      <c r="O306" t="inlineStr">
+      <c r="P306" t="inlineStr">
         <is>
           <t>Shop Discount: -5% -&gt; -25% (-5%/Lv) | Levels: L1-5
 Lowers gold cost for item purchases and item identification</t>
@@ -18868,7 +19242,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Occurrence rate: 3% -&gt; 7% (+1%/Lv, L1-5)</t>
+          <t>Occurrence rate: 3% -&gt; 4% -&gt; 5% -&gt; 6% -&gt; 7% (L1-5 Max)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -18880,12 +19254,13 @@
       <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr"/>
       <c r="M307" t="inlineStr"/>
-      <c r="N307" t="inlineStr">
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr">
         <is>
           <t>Mesmerize enemies with dance steps, causing them to lose turns.</t>
         </is>
       </c>
-      <c r="O307" t="inlineStr">
+      <c r="P307" t="inlineStr">
         <is>
           <t>Mesmerize Rate: 5% -&gt; 15% (+2.5%/Lv) | Levels: L1-5
 Enemy skips turn when mesmerized</t>
@@ -18932,12 +19307,13 @@
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr"/>
-      <c r="N308" t="inlineStr">
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr">
         <is>
           <t>Nullify first hit of battle against user.</t>
         </is>
       </c>
-      <c r="O308" t="inlineStr">
+      <c r="P308" t="inlineStr">
         <is>
           <t>100% nullification of the very first physical attack received
 Fixed passive (Level 1)</t>
@@ -18984,12 +19360,13 @@
       <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr"/>
       <c r="M309" t="inlineStr"/>
-      <c r="N309" t="inlineStr">
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr">
         <is>
           <t>Heighten probability of beneficial results for random skills.</t>
         </is>
       </c>
-      <c r="O309" t="inlineStr">
+      <c r="P309" t="inlineStr">
         <is>
           <t>Drastically increases odds of favorable outcomes on Gamble skills
 Fixed passive (Level 1)</t>
@@ -19038,6 +19415,7 @@
       <c r="M310" t="inlineStr"/>
       <c r="N310" t="inlineStr"/>
       <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -19081,6 +19459,7 @@
       <c r="M311" t="inlineStr"/>
       <c r="N311" t="inlineStr"/>
       <c r="O311" t="inlineStr"/>
+      <c r="P311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -19122,12 +19501,13 @@
       <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr"/>
-      <c r="N312" t="inlineStr">
+      <c r="N312" t="inlineStr"/>
+      <c r="O312" t="inlineStr">
         <is>
           <t>Occasionally land critical hits with offensive spells.</t>
         </is>
       </c>
-      <c r="O312" t="inlineStr">
+      <c r="P312" t="inlineStr">
         <is>
           <t>Spell Crit Rate: +10% -&gt; +13.75% -&gt; +17.5% -&gt; +21.25% -&gt; +25% (L1-5)
 Spell criticals deal 1.50x normal magic damage</t>
@@ -19174,12 +19554,13 @@
       <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr"/>
-      <c r="N313" t="inlineStr">
+      <c r="N313" t="inlineStr"/>
+      <c r="O313" t="inlineStr">
         <is>
           <t>Increase doll summon duration on battlefield.</t>
         </is>
       </c>
-      <c r="O313" t="inlineStr">
+      <c r="P313" t="inlineStr">
         <is>
           <t>Doll Summon Duration: +1 turn (Summons persist longer in battle)
 Fixed passive (Level 1)</t>
@@ -19214,7 +19595,7 @@
       <c r="G314" t="inlineStr">
         <is>
           <t>Significantly increase damage according to Pep.
-Lv1-9: 10 -&gt; 2 (-1/Lv) | Crown EX: 1</t>
+Lv1-9: 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3 -&gt; 2 | Crown EX: 1</t>
         </is>
       </c>
       <c r="H314" t="inlineStr"/>
@@ -19227,14 +19608,15 @@
       <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr"/>
       <c r="M314" t="inlineStr"/>
-      <c r="N314" t="inlineStr">
+      <c r="N314" t="inlineStr"/>
+      <c r="O314" t="inlineStr">
         <is>
           <t>Heroine: Luco | Damage scales with Pep.
 Effect: +1% damage per Pep point (up to +100% damage at Max Pep).
 [Crown EX]: Scales up to +150% damage bonus at Max Pep.</t>
         </is>
       </c>
-      <c r="O314" t="inlineStr"/>
+      <c r="P314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -19264,7 +19646,7 @@
       <c r="G315" t="inlineStr">
         <is>
           <t>Occasionally inflict enemies with status ailments or Dispel at random.
-Lv1-9: 7% -&gt; 15% (+1%/Lv) | Crown EX: 25%</t>
+Lv1-9: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 25%</t>
         </is>
       </c>
       <c r="H315" t="inlineStr"/>
@@ -19277,14 +19659,15 @@
       <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr"/>
       <c r="M315" t="inlineStr"/>
-      <c r="N315" t="inlineStr">
+      <c r="N315" t="inlineStr"/>
+      <c r="O315" t="inlineStr">
         <is>
           <t>Heroine: Mefmera | 15% trigger chance on enemy action.
 Inflicts Poison, Paralyze, Silence, or cancels enemy buffs.
 [Crown EX]: Trigger chance increases to 25% on any enemy action.</t>
         </is>
       </c>
-      <c r="O315" t="inlineStr"/>
+      <c r="P315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -19327,14 +19710,15 @@
       <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr"/>
       <c r="M316" t="inlineStr"/>
-      <c r="N316" t="inlineStr">
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr">
         <is>
           <t>Heroine: Souffle | 25% counter chance on physical contact.
 Inflicts Slow and -30% Speed on attacker.
 [Crown EX]: Counter chance increases to 40% on physical contact.</t>
         </is>
       </c>
-      <c r="O316" t="inlineStr"/>
+      <c r="P316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -19364,7 +19748,7 @@
       <c r="G317" t="inlineStr">
         <is>
           <t>Increase weapon modifier when attacking with weapon-based skills.
-Lv1-9: 10% -&gt; 18% (+1%/Lv) | Crown EX: 25%</t>
+Lv1-9: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18% | Crown EX: 25%</t>
         </is>
       </c>
       <c r="H317" t="inlineStr"/>
@@ -19377,14 +19761,15 @@
       <c r="K317" t="inlineStr"/>
       <c r="L317" t="inlineStr"/>
       <c r="M317" t="inlineStr"/>
-      <c r="N317" t="inlineStr">
+      <c r="N317" t="inlineStr"/>
+      <c r="O317" t="inlineStr">
         <is>
           <t>Heroine: Grishna | Weapon Scaling Bonus.
 Grants +25% extra damage to all weapon-based techniques.
 [Crown EX]: Weapon technique damage bonus increases to +40%.</t>
         </is>
       </c>
-      <c r="O317" t="inlineStr"/>
+      <c r="P317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -19414,7 +19799,7 @@
       <c r="G318" t="inlineStr">
         <is>
           <t>May guarantee a hit and bypass DEF with physical attacks or skills.
-Lv1-9: 12% -&gt; 20% (+1%/Lv) | Crown EX: 30%</t>
+Lv1-9: 12% -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% | Crown EX: 30%</t>
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
@@ -19427,14 +19812,15 @@
       <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr"/>
       <c r="M318" t="inlineStr"/>
-      <c r="N318" t="inlineStr">
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr">
         <is>
           <t>Heroine: Yae | 20% activation rate on physical attacks.
 Guarantees 100% hit rate and completely ignores target DEF.
 [Crown EX]: Activation rate increases to 30% (ignores target DEF).</t>
         </is>
       </c>
-      <c r="O318" t="inlineStr"/>
+      <c r="P318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -19464,7 +19850,7 @@
       <c r="G319" t="inlineStr">
         <is>
           <t>Occasionally nullify all damage received from enemies.
-Lv1-9: 7% -&gt; 15% (+1%/Lv) | Crown EX: 20%</t>
+Lv1-9: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
         </is>
       </c>
       <c r="H319" t="inlineStr"/>
@@ -19477,14 +19863,15 @@
       <c r="K319" t="inlineStr"/>
       <c r="L319" t="inlineStr"/>
       <c r="M319" t="inlineStr"/>
-      <c r="N319" t="inlineStr">
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr">
         <is>
           <t>Heroine: Lize | 10% nullification rate.
 Chance to completely negate all incoming damage.
 [Crown EX]: Total damage nullification rate increases to 15%.</t>
         </is>
       </c>
-      <c r="O319" t="inlineStr"/>
+      <c r="P319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -19514,7 +19901,7 @@
       <c r="G320" t="inlineStr">
         <is>
           <t>Before acting, may erase enemy puppets, familiars, shikigami, or slaves.
-Lv1-9: 25% -&gt; 57% (+4%/Lv) | Crown EX: 75%</t>
+Lv1-9: 25% -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 49 -&gt; 53 -&gt; 57% | Crown EX: 75%</t>
         </is>
       </c>
       <c r="H320" t="inlineStr"/>
@@ -19527,14 +19914,15 @@
       <c r="K320" t="inlineStr"/>
       <c r="L320" t="inlineStr"/>
       <c r="M320" t="inlineStr"/>
-      <c r="N320" t="inlineStr">
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr">
         <is>
           <t>Heroine: Lilian | 25% banish rate before acting.
 Instantly eliminates enemy summon entities, puppets, and familiars.
 [Crown EX]: Enemy summon and minion banish rate increases to 40%.</t>
         </is>
       </c>
-      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -19564,7 +19952,7 @@
       <c r="G321" t="inlineStr">
         <is>
           <t>Before acting, may use an item from her own personal stock.
-Lv1-9: 10% -&gt; 18% (+1%/Lv) | Crown EX: 25%</t>
+Lv1-9: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18% | Crown EX: 25%</t>
         </is>
       </c>
       <c r="H321" t="inlineStr"/>
@@ -19577,14 +19965,15 @@
       <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr"/>
       <c r="M321" t="inlineStr"/>
-      <c r="N321" t="inlineStr">
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr">
         <is>
           <t>Heroine: Monica | 20% trigger rate at start of turn.
 Uses a free recovery item from personal stock without turn cost.
 [Crown EX]: Free item trigger rate increases to 30% without turn cost.</t>
         </is>
       </c>
-      <c r="O321" t="inlineStr"/>
+      <c r="P321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -19614,7 +20003,7 @@
       <c r="G322" t="inlineStr">
         <is>
           <t>Decrease turn delay after using skills or magic.
-Lv1-9: 7% -&gt; 15% (+1%/Lv) | Crown EX: 20%</t>
+Lv1-9: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
         </is>
       </c>
       <c r="H322" t="inlineStr"/>
@@ -19627,14 +20016,15 @@
       <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr"/>
       <c r="M322" t="inlineStr"/>
-      <c r="N322" t="inlineStr">
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr">
         <is>
           <t>Heroine: Alisia | Action Recovery Acceleration.
 Decreases action recovery delay by 20% after using skills or magic.
 [Crown EX]: Action recovery delay reduction increases to 30%.</t>
         </is>
       </c>
-      <c r="O322" t="inlineStr"/>
+      <c r="P322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -19677,14 +20067,15 @@
       <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr"/>
       <c r="M323" t="inlineStr"/>
-      <c r="N323" t="inlineStr">
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr">
         <is>
           <t>Heroine: Conette | Maid Mastery Booster.
 Increases potency and effectiveness of all Maid skills by +15%.
 [Crown EX]: Maid skill effectiveness bonus increases to +25%.</t>
         </is>
       </c>
-      <c r="O323" t="inlineStr"/>
+      <c r="P323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -19714,7 +20105,7 @@
       <c r="G324" t="inlineStr">
         <is>
           <t>May occasionally act twice in one turn.
-Lv1-9: 7% -&gt; 15% (+1%/Lv) | Crown EX: 20%</t>
+Lv1-9: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
         </is>
       </c>
       <c r="H324" t="inlineStr"/>
@@ -19727,14 +20118,15 @@
       <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr"/>
       <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr">
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr">
         <is>
           <t>Heroine: Yuni | 15% double action chance.
 Grants an immediate second action in the same turn.
 [Crown EX]: Immediate second action trigger rate increases to 25%.</t>
         </is>
       </c>
-      <c r="O324" t="inlineStr"/>
+      <c r="P324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -19764,7 +20156,7 @@
       <c r="G325" t="inlineStr">
         <is>
           <t>If killed, revive after a certain number of turns.
-Lv1-9: 8% -&gt; 24% (+2%/Lv) | Crown EX: 30%</t>
+Lv1-9: 8% -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24% | Crown EX: 30%</t>
         </is>
       </c>
       <c r="H325" t="inlineStr"/>
@@ -19777,14 +20169,15 @@
       <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr"/>
       <c r="M325" t="inlineStr"/>
-      <c r="N325" t="inlineStr">
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr">
         <is>
           <t>Heroine: Gina | Auto-Resurrection.
 Resurrects with 50% Max HP 3 turns after falling in combat.
 [Crown EX]: Resurrects with 100% Max HP after 2 turns.</t>
         </is>
       </c>
-      <c r="O325" t="inlineStr"/>
+      <c r="P325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -19814,7 +20207,7 @@
       <c r="G326" t="inlineStr">
         <is>
           <t>Whole row takes less damage from Demons, Undead, and Apparitions.
-Lv1-9: -12% -&gt; -20% (-1%/Lv) | Crown EX: -25%</t>
+Lv1-9: -12% -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -19 -&gt; -20% | Crown EX: -25%</t>
         </is>
       </c>
       <c r="H326" t="inlineStr"/>
@@ -19827,14 +20220,15 @@
       <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr"/>
       <c r="M326" t="inlineStr"/>
-      <c r="N326" t="inlineStr">
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr">
         <is>
           <t>Heroine: Ist | Row Protection Barrier.
 Reduces incoming damage from Demons, Undead, and Apparitions by 20%.
 [Crown EX]: Damage reduction from Demons/Undead/Apparitions to 30%.</t>
         </is>
       </c>
-      <c r="O326" t="inlineStr"/>
+      <c r="P326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -19877,14 +20271,15 @@
       <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr"/>
-      <c r="N327" t="inlineStr">
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr">
         <is>
           <t>Heroine: Fiora | 15% trigger rate at start of turn.
 Inflicts -20% ATK and -20% INT on all enemies.
 [Crown EX]: Turn-start debuff trigger rate increases to 25%.</t>
         </is>
       </c>
-      <c r="O327" t="inlineStr"/>
+      <c r="P327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -19914,7 +20309,7 @@
       <c r="G328" t="inlineStr">
         <is>
           <t>Magic will occasionally activate immediately without the need to chant.
-Lv1-9: 7% -&gt; 15% (+1%/Lv) | Crown EX: 20%</t>
+Lv1-9: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
         </is>
       </c>
       <c r="H328" t="inlineStr"/>
@@ -19927,14 +20322,15 @@
       <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr"/>
       <c r="M328" t="inlineStr"/>
-      <c r="N328" t="inlineStr">
+      <c r="N328" t="inlineStr"/>
+      <c r="O328" t="inlineStr">
         <is>
           <t>Heroine: Eltricia | 15% instant cast chance.
 Offensive and support spells activate immediately with 0 chant time.
 [Crown EX]: Instant cast (0 chant delay) rate increases to 25%.</t>
         </is>
       </c>
-      <c r="O328" t="inlineStr"/>
+      <c r="P328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -19977,14 +20373,15 @@
       <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr"/>
       <c r="M329" t="inlineStr"/>
-      <c r="N329" t="inlineStr">
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr">
         <is>
           <t>Heroine: Melvy | 20% damage reflect rate.
 Reflects 30% of received damage back to attacker as neutral damage.
 [Crown EX]: Damage reflect rate increases to 30% with 45% reflected.</t>
         </is>
       </c>
-      <c r="O329" t="inlineStr"/>
+      <c r="P329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -20014,7 +20411,7 @@
       <c r="G330" t="inlineStr">
         <is>
           <t>Summons another self from the shadows to attack.
-Lv1-9: 4% -&gt; 12% (+1%/Lv) | Crown EX: 20%</t>
+Lv1-9: 4% -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% | Crown EX: 20%</t>
         </is>
       </c>
       <c r="H330" t="inlineStr"/>
@@ -20027,14 +20424,15 @@
       <c r="K330" t="inlineStr"/>
       <c r="L330" t="inlineStr"/>
       <c r="M330" t="inlineStr"/>
-      <c r="N330" t="inlineStr">
+      <c r="N330" t="inlineStr"/>
+      <c r="O330" t="inlineStr">
         <is>
           <t>Heroine: Tsurara | Shadow Clone Follow-up.
 Normal attacks trigger an extra strike dealing 75% damage.
 [Crown EX]: Shadow strike follow-up deals 100% full attack damage.</t>
         </is>
       </c>
-      <c r="O330" t="inlineStr"/>
+      <c r="P330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -20064,7 +20462,7 @@
       <c r="G331" t="inlineStr">
         <is>
           <t>Increased effects for all class modifiers.
-Lv1-9: 2 -&gt; 10 (+1/Lv) | Crown EX: 15</t>
+Lv1-9: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Crown EX: 15</t>
         </is>
       </c>
       <c r="H331" t="inlineStr"/>
@@ -20077,14 +20475,15 @@
       <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr"/>
       <c r="M331" t="inlineStr"/>
-      <c r="N331" t="inlineStr">
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr">
         <is>
           <t>Heroine: Siena | Class Mastery Booster.
 Increases all class stat bonuses and weapon masteries by +10%.
 [Crown EX]: Class and weapon mastery bonuses increase to +15%.</t>
         </is>
       </c>
-      <c r="O331" t="inlineStr"/>
+      <c r="P331" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20239,7 +20638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -20309,22 +20708,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Notation</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Label: 80% -&gt; 110% (+3%/Lv, L1-10)  |  Label: 10 -&gt; 14 -&gt; 18 (L1-3)  |  Label: 0.85x</t>
+          <t>docs/SKILL_DISPLAY_PHILOSOPHY_AND_SPECIFICATION.md. Line 1 vanilla, line 2 effect, line 3 costs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Notation</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ATK: 125% -&gt; 134 -&gt; ... -&gt; 200%  |  ATK: 130% (+8%/Lv) -&gt; 202% (L10 Max)  |  Speed: 0.8x -&gt; 0.9x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Averages such as "(avg +3.33%/Lv)". A step is written only when it is the same at every level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Previous_Mod_*</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Wording of the earlier mod, for reference only. Its numbers were not taken from the binary.</t>
         </is>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -445,8 +445,8 @@
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="76" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="84" customWidth="1" min="15" max="15"/>
     <col width="86" customWidth="1" min="16" max="16"/>
   </cols>
@@ -514,7 +514,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>First_To_Last_Only</t>
+          <t>Not_Level_By_Level</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -764,7 +764,7 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>ATK: 125% -&gt; 134 -&gt; 143 -&gt; 152 -&gt; 161 -&gt; 170 -&gt; 178 -&gt; 186 -&gt; 193 -&gt; 200% (L10)
-TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 | Speed: 0.8x -&gt; 0.9x</t>
+Accuracy: +20% (+2%/Lv) | TP Cost: 5 (+2-3/Lv) -&gt; 28 | Speed: 0.8x -&gt; 0.9x</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -775,12 +775,12 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>TP Cost</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>Short-range strike. | Hit Rate: +20% -&gt; +38% (+2%/Lv)</t>
@@ -831,7 +831,7 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>Accuracy: +20% -&gt; +22 -&gt; +24 -&gt; +26 -&gt; +28 -&gt; +30 -&gt; +31 -&gt; +32 -&gt; +33 -&gt; +35% (L10)
-TP Cost: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 | Speed: 0.9x</t>
+Buff cancel rate: 68% (+1-2%/Lv) -&gt; 85% | TP Cost: 5 (+1-2/Lv) -&gt; 18 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Buff cancel rate</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Buff cancel rate, TP Cost</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>Short-range strike to one enemy. May cancel enemy active buffs.</t>
@@ -897,8 +897,8 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ATK: +20% -&gt; +30% -&gt; +40% -&gt; +45% -&gt; +50% (L1-5 Max) | DEF: -11% -&gt; -25%
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+          <t>ATK: +20% -&gt; +30% -&gt; +40% -&gt; +45% -&gt; +50% (L1-5 Max)
+DEF: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25% | Turns: 4 -&gt; 8 | TP Cost: 8 (+2/Lv) -&gt; 16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -911,7 +911,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>Turns</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -968,8 +968,8 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DEF: +20% -&gt; +30% -&gt; +40% -&gt; +45% -&gt; +50% (L1-5 Max) | ATK: -11% -&gt; -25%
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+          <t>DEF: +20% -&gt; +30% -&gt; +40% -&gt; +45% -&gt; +50% (L1-5 Max)
+ATK: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25% | Turns: 4 -&gt; 8 | TP Cost: 8 (+2/Lv) -&gt; 16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -982,7 +982,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>Turns</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ATK: 85% -&gt; 90% -&gt; 94% -&gt; 98% -&gt; 102% (L1-5 Max) | Accuracy: +6% -&gt; +20%
+          <t>ATK: 85% -&gt; 90% -&gt; 94% -&gt; 98% -&gt; 102% (L1-5 Max) | Accuracy: +6% (+3-4%/Lv) -&gt; +20%
 Stun: 30% -&gt; 32% -&gt; 34% -&gt; 36% -&gt; 38% | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
@@ -1111,7 +1111,7 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>ATK: 106% -&gt; 112 -&gt; 118 -&gt; 124 -&gt; 130 -&gt; 134 -&gt; 138 -&gt; 142 -&gt; 146 -&gt; 150% (L10)
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 | Speed: 0.85x</t>
+Accuracy: +5% (+2-3%/Lv) -&gt; +28% | Paralysis: 20% -&gt; 50% | TP Cost: 6 (+2/Lv) -&gt; 24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1122,10 +1122,14 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Accuracy, Paralysis</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Accuracy, Paralysis</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1253,7 +1257,7 @@
       <c r="H12" t="inlineStr">
         <is>
           <t>ATK: 80% -&gt; 83 -&gt; 86 -&gt; 89 -&gt; 91 -&gt; 94 -&gt; 97 -&gt; 100 -&gt; 105 -&gt; 110% (L10)
-TP Cost: 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58 -&gt; 62 -&gt; 66 -&gt; 70 -&gt; 74</t>
+Instakill: 10% (+1-2%/Lv) -&gt; 20% | TP Cost: 38 (+4/Lv) -&gt; 74 | Speed: 0.65x -&gt; 0.75x</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1264,12 +1268,12 @@
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Instakill, Speed</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Instakill</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>Katana skill. Deal slash damage to an enemy row. May instakill.</t>
@@ -1320,7 +1324,7 @@
       <c r="H13" t="inlineStr">
         <is>
           <t>ATK: 84% -&gt; 88 -&gt; 92 -&gt; 96 -&gt; 100 -&gt; 104 -&gt; 108 -&gt; 112 -&gt; 116 -&gt; 120% (L10)
-Turns: 4 | TP Cost: 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32</t>
+Enemy DEF: -16% (-1%/Lv) | Turns: 4 | TP Cost: 14 (+2/Lv) -&gt; 32 | Speed: 0.8x</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1332,11 +1336,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Enemy DEF, Speed</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>Katana skill. Deal defense-piercing damage and lower target DEF.</t>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ATK: 74% -&gt; 78 -&gt; 82 -&gt; 86 -&gt; 90 -&gt; 94 -&gt; 98 -&gt; 102 -&gt; 106 -&gt; 110% (L10)
+          <t>ATK: 74% (+4%/Lv) -&gt; 110% (L10 Max) | HP Absorb: 15% (+1-2%/Lv) -&gt; 25%
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36 | Speed: 0.9x</t>
         </is>
       </c>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>HP Absorb</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>Short-range strike to one enemy. Absorb a portion of damage as HP.</t>
@@ -1588,7 +1588,7 @@
       <c r="H17" t="inlineStr">
         <is>
           <t>ATK: 65% -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 84 -&gt; 88 -&gt; 91 -&gt; 94 -&gt; 97 -&gt; 100% (L10)
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 | Speed: 0.9x</t>
+TP Absorb: 10% (+1-2%/Lv) -&gt; 20% | TP Cost: 6 (+2/Lv) -&gt; 24 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>TP Absorb</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>Short-range strike to one enemy. Absorb a portion of damage as TP.</t>
@@ -1655,7 +1655,7 @@
       <c r="H18" t="inlineStr">
         <is>
           <t>ATK: 130% -&gt; 144 -&gt; 157 -&gt; 170 -&gt; 182 -&gt; 194 -&gt; 204 -&gt; 212 -&gt; 220 -&gt; 228% (L10)
-Freeze: 20% -&gt; 50% | TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36</t>
+Freeze: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 9 (+3/Lv) -&gt; 36 | Speed: 0.75x -&gt; 0.85x</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1671,11 +1671,7 @@
           <t>Freeze</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>Short-range strike dealing mid-range water damage. May freeze.</t>
@@ -1726,7 +1722,7 @@
       <c r="H19" t="inlineStr">
         <is>
           <t>ATK: 135% -&gt; 149 -&gt; 163 -&gt; 176 -&gt; 189 -&gt; 201 -&gt; 213 -&gt; 225 -&gt; 236 -&gt; 247% (L10)
-TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 37 -&gt; 42</t>
+Petrify: 20% (+1-2%/Lv) -&gt; 35% | TP Cost: 9 (+3-5/Lv) -&gt; 42 | Speed: 0.85x -&gt; 0.95x</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1737,12 +1733,12 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Petrify, Speed</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Petrify, TP Cost</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>Axe skill. Strike one enemy with earth damage. May petrify.</t>
@@ -1793,7 +1789,7 @@
       <c r="H20" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 130 -&gt; 140 -&gt; 148 -&gt; 156 -&gt; 164 -&gt; 170 -&gt; 176 -&gt; 180 -&gt; 184% (L10)
-Targets: 2 -&gt; 5 | TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 47 -&gt; 53 -&gt; 58 -&gt; 63 -&gt; 68</t>
+Targets: 2 -&gt; 2 -&gt; 2 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 | TP Cost: 26 (+4-6/Lv) -&gt; 68</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1806,7 +1802,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Targets</t>
+          <t>TP Cost</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1998,7 +1994,7 @@
       <c r="H23" t="inlineStr">
         <is>
           <t>ATK: 130% -&gt; 140 -&gt; 150 -&gt; 160 -&gt; 170 -&gt; 180 -&gt; 190 -&gt; 200 -&gt; 211 -&gt; 222% (L10)
-TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39</t>
+Accuracy: +6% (+1-2%/Lv) -&gt; +20% | TP Cost: 12 (+3/Lv) -&gt; 39 | Speed: 0.8x -&gt; 0.9x</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2009,12 +2005,12 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Accuracy, Speed</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>Sword and lance skill. Strike one enemy. Effective vs. Unholy foes.</t>
@@ -2199,7 +2195,7 @@
       <c r="H26" t="inlineStr">
         <is>
           <t>ATK: 96% -&gt; 100 -&gt; 104 -&gt; 108 -&gt; 113 -&gt; 118 -&gt; 123 -&gt; 128 -&gt; 133 -&gt; 138% (L10)
-TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 59 -&gt; 64 | Speed: 0.8x</t>
+Paralysis: 20% (+2-3%/Lv) -&gt; 40% | TP Cost: 26 (+4-5/Lv) -&gt; 64 | Speed: 0.8x</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -2210,12 +2206,12 @@
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Paralysis</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Paralysis, TP Cost</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>Short-range skill. Deal lightning damage to an enemy row. May paralyze.</t>
@@ -2266,7 +2262,7 @@
       <c r="H27" t="inlineStr">
         <is>
           <t>ATK: 135% -&gt; 149 -&gt; 163 -&gt; 176 -&gt; 189 -&gt; 201 -&gt; 213 -&gt; 223 -&gt; 234 -&gt; 245% (L10)
-TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28 -&gt; 31 -&gt; 34</t>
+Silence: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 7 (+3/Lv) -&gt; 34 | Speed: 0.85x -&gt; 0.95x</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -2277,12 +2273,12 @@
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Silence, Speed</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Silence</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>Lance skill. Strike one enemy with wind damage. May silence.</t>
@@ -2400,7 +2396,7 @@
       <c r="H29" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 130 -&gt; 142 -&gt; 154 -&gt; 165 -&gt; 176 -&gt; 186 -&gt; 196 -&gt; 204 -&gt; 212% (L10)
-TP Cost: 32 -&gt; 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 59 | Speed: 0.8x</t>
+Accuracy: +5% (+1-2%/Lv) -&gt; +15% | TP Cost: 32 (+3/Lv) -&gt; 59 | Speed: 0.8x</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -2411,12 +2407,12 @@
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>Sword and lance skill. Pierces through to the back row.</t>
@@ -2993,7 +2989,7 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>Speed increase: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 20% (L10)
-Turns: 3 -&gt; 6 | TP Cost: 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32</t>
+Turns: 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 5 -&gt; 6 | TP Cost: 14 (+2/Lv) -&gt; 32</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -3004,11 +3000,7 @@
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Turns</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
@@ -3135,7 +3127,7 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>ATK: 116% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150 -&gt; 156% (L10)
-TP Cost: 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 | Speed: 0.9x</t>
+Sleep: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 7 (+2/Lv) -&gt; 25 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -3146,12 +3138,12 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Sleep</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>Short-range strike to one enemy. May inflict Sleep.</t>
@@ -3202,7 +3194,7 @@
       <c r="H41" t="inlineStr">
         <is>
           <t>ATK: 116% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150 -&gt; 156% (L10)
-TP Cost: 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 | Speed: 0.9x</t>
+Silence: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 7 (+2/Lv) -&gt; 25 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -3213,12 +3205,12 @@
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Silence</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>Short-range strike to one enemy. May inflict Silence.</t>
@@ -3269,7 +3261,7 @@
       <c r="H42" t="inlineStr">
         <is>
           <t>ATK: 112% -&gt; 116 -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150% (L10)
-TP Cost: 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 | Speed: 0.9x</t>
+Stun: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 7 (+2/Lv) -&gt; 25 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -3280,12 +3272,12 @@
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Stun</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>Short-range strike to one enemy. May inflict Stun.</t>
@@ -3336,7 +3328,7 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>Number of attacks: 3 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 | ATK: 104% -&gt; 148%
-TP Cost: 30 -&gt; 34 -&gt; 38 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 58 -&gt; 64 -&gt; 68 -&gt; 72</t>
+Power: -25% -&gt; -14% | TP Cost: 30 (+4-6/Lv) -&gt; 72 | Speed: 0.75x -&gt; 0.85x</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -3349,14 +3341,10 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Power, Speed</t>
-        </is>
-      </c>
+          <t>ATK, Power, TP Cost</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>Bow and gun skill. Rapid fire multiple shots with escalating crit rate.</t>
@@ -3541,7 +3529,7 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170% (L10)
-Poison: 20% -&gt; 50% | TP Cost: 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25</t>
+Poison: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 7 (+2/Lv) -&gt; 25</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -3608,7 +3596,7 @@
       <c r="H47" t="inlineStr">
         <is>
           <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170% (L10)
-Freeze: 20% -&gt; 50% | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26</t>
+Freeze: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 8 (+2/Lv) -&gt; 26</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -3675,7 +3663,7 @@
       <c r="H48" t="inlineStr">
         <is>
           <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170% (L10)
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26</t>
+Paralysis: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 8 (+2/Lv) -&gt; 26</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -3686,12 +3674,12 @@
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Paralysis</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>Bow skill. Attack one enemy with an electric shot. May paralyze.</t>
@@ -3742,7 +3730,7 @@
       <c r="H49" t="inlineStr">
         <is>
           <t>ATK: 116% -&gt; 122 -&gt; 128 -&gt; 134 -&gt; 140 -&gt; 145 -&gt; 150 -&gt; 155 -&gt; 160 -&gt; 165% (L10)
-TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 -&gt; 27 | Speed: 0.95x</t>
+Slow: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 9 (+2/Lv) -&gt; 27 | Speed: 0.95x</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -3753,12 +3741,12 @@
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Slow</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>Bow skill. Deal stab damage to one enemy. May slow.</t>
@@ -3943,7 +3931,7 @@
       <c r="H52" t="inlineStr">
         <is>
           <t>ATK: 130% -&gt; 144 -&gt; 158 -&gt; 171 -&gt; 184 -&gt; 196 -&gt; 207 -&gt; 217 -&gt; 226 -&gt; 234% (L10)
-TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 36 -&gt; 40 -&gt; 43 -&gt; 46 -&gt; 49 -&gt; 52 -&gt; 55 | Speed: 0.7x</t>
+Critical rate: 5 (+1-3/Lv) -&gt; 25 | TP Cost: 24 (+3-4/Lv) -&gt; 55 | Speed: 0.7x</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -3954,12 +3942,12 @@
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Critical rate</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Critical rate, TP Cost</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>Bow skill. Massive piercing shot that penetrates through to the back row.</t>
@@ -4072,7 +4060,7 @@
       <c r="H54" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 126 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 154 -&gt; 162 -&gt; 170 -&gt; 180 -&gt; 192% (L10)
-TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36 | Speed: 0.45x</t>
+Stun: 10% -&gt; 20% | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -4083,10 +4071,14 @@
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Stun</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Stun</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4201,7 +4193,7 @@
       <c r="H56" t="inlineStr">
         <is>
           <t>Magic damage: +38% -&gt; +42% -&gt; +47% -&gt; +53% -&gt; +60% (L1-5 Max)
-Turns: 6 | TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 32 | Speed: 1.5x -&gt; 2.1x</t>
+Magic accuracy: -2% (-2%/Lv) | Turns: 6 | TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 32</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -4215,7 +4207,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Magic accuracy</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
@@ -4258,7 +4250,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Accuracy: +10% -&gt; +12 -&gt; +14 -&gt; +16 -&gt; +18 -&gt; +20 -&gt; +22 -&gt; +24 -&gt; +26 -&gt; +30% (L10)
+          <t>Damage UP | Accuracy: +10% (+2-4%/Lv) -&gt; +30%
 TP Cost: 28 -&gt; 32 -&gt; 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 56 -&gt; 60 -&gt; 64 | Speed: 0.75x</t>
         </is>
       </c>
@@ -4278,12 +4270,12 @@
           <t>effect_3</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Damage UP</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>Mace skill. Heavy bash strike with boosted accuracy.</t>
@@ -4593,7 +4585,7 @@
       <c r="H62" t="inlineStr">
         <is>
           <t>ATK: 136% -&gt; 142 -&gt; 148 -&gt; 155 -&gt; 162 -&gt; 172 -&gt; 182 -&gt; 193 -&gt; 204 -&gt; 216% (L10)
-TP Cost: 13 -&gt; 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 | Speed: 0.9x -&gt; 1x</t>
+Accuracy: +10% (+1-2%/Lv) -&gt; +20% | TP Cost: 13 (+3-4/Lv) -&gt; 45 | Speed: 0.9x -&gt; 1x</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -4604,12 +4596,12 @@
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Accuracy, TP Cost</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>Short-range strike dealing heavy lightning damage to one enemy.</t>
@@ -4660,7 +4652,7 @@
       <c r="H63" t="inlineStr">
         <is>
           <t>ATK: 150% -&gt; 162 -&gt; 174 -&gt; 186 -&gt; 198 -&gt; 208 -&gt; 218 -&gt; 228 -&gt; 236 -&gt; 244% (L10)
-Freeze: 20% -&gt; 50% | TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36</t>
+Freeze: 20% (+3-4%/Lv) -&gt; 50% | Silence: 20% -&gt; 50% | TP Cost: 9 (+3/Lv) -&gt; 36</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -4673,14 +4665,10 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Silence</t>
-        </is>
-      </c>
+          <t>Freeze, Silence</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
     </row>
@@ -5879,7 +5867,7 @@
       <c r="H84" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 126 -&gt; 132 -&gt; 138 -&gt; 142 -&gt; 150 -&gt; 158 -&gt; 168 -&gt; 178 -&gt; 190% (L10)
-TP Cost: 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 -&gt; 27 -&gt; 29 -&gt; 31 -&gt; 33 -&gt; 35 | Speed: 0.88x</t>
+Instakill: 15% (+1-2%/Lv) -&gt; 25% | TP Cost: 17 (+2/Lv) -&gt; 35 | Speed: 0.88x</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -5890,12 +5878,12 @@
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>Instakill</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>Attack one enemy. May instakill.</t>
@@ -5946,7 +5934,7 @@
       <c r="H85" t="inlineStr">
         <is>
           <t>ATK: 95% -&gt; 99 -&gt; 103 -&gt; 107 -&gt; 111 -&gt; 115 -&gt; 119 -&gt; 123 -&gt; 127 -&gt; 131% (L10)
-TP Cost: 32 -&gt; 34 -&gt; 36 -&gt; 38 -&gt; 40 -&gt; 42 -&gt; 44 -&gt; 46 -&gt; 48 -&gt; 50 | Speed: 0.65x</t>
+Stun: 40% (+3-4%/Lv) -&gt; 70% | TP Cost: 32 (+2/Lv) -&gt; 50 | Speed: 0.65x</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -5957,12 +5945,12 @@
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>Stun</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
     </row>
@@ -6003,7 +5991,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ATK: 15% -&gt; 20% -&gt; 25% -&gt; 30% -&gt; 35% (L1-5 Max) | DEF: -11% -&gt; -25%
+          <t>ATK: 15% (+5%/Lv) -&gt; 35% (L5 Max) | DEF: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
@@ -6015,11 +6003,7 @@
       </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>Speed</t>
@@ -6173,7 +6157,7 @@
       <c r="H89" t="inlineStr">
         <is>
           <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 164 -&gt; 170 -&gt; 176% (L10)
-TP Cost: 22 -&gt; 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58</t>
+Poison: 50% (+3-4%/Lv) -&gt; 80% | TP Cost: 22 (+4/Lv) -&gt; 58 | Speed: 0.6x -&gt; 0.7x</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -6184,12 +6168,12 @@
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>Poison, Speed</t>
-        </is>
-      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Poison</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
     </row>
@@ -6231,7 +6215,7 @@
       <c r="H90" t="inlineStr">
         <is>
           <t>ATK: 150% -&gt; 162 -&gt; 174 -&gt; 186 -&gt; 198 -&gt; 208 -&gt; 218 -&gt; 228 -&gt; 240 -&gt; 256% (L10)
-TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 32 | Speed: 0.95x</t>
+Turn delay rate: 25% (+2%/Lv) | TP Cost: 10 (+2-3/Lv) -&gt; 32 | Speed: 0.95x</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -6242,12 +6226,12 @@
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>Turn delay rate</t>
-        </is>
-      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>TP Cost</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
           <t>Fan skill. Deal bash damage to one enemy and delay target turn.</t>
@@ -9308,7 +9292,7 @@
       <c r="H145" t="inlineStr">
         <is>
           <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
-TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Speed: 2.25x</t>
+Accuracy: 86% (+1%/Lv) | TP Cost: 5 (+2-4/Lv) -&gt; 32 | Speed: 2.25x</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -9319,10 +9303,14 @@
       </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>TP Cost</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -9375,7 +9363,7 @@
       <c r="H146" t="inlineStr">
         <is>
           <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
-TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 | Speed: 1.7x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 15 (+4-6/Lv) -&gt; 60 | Speed: 1.7x</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -9386,10 +9374,14 @@
       </c>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Accuracy, TP Cost</t>
+        </is>
+      </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -9442,7 +9434,7 @@
       <c r="H147" t="inlineStr">
         <is>
           <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
-TP Cost: 42 -&gt; 50 -&gt; 58 -&gt; 64 -&gt; 73 -&gt; 82 -&gt; 91 -&gt; 100 -&gt; 110 -&gt; 120 | Speed: 1.3x</t>
+Accuracy: 75% (+1-2%/Lv) -&gt; 85% | TP Cost: 42 (+6-10/Lv) -&gt; 120 | Speed: 1.3x</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -9453,10 +9445,14 @@
       </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Accuracy, TP Cost</t>
+        </is>
+      </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -9572,7 +9568,7 @@
       <c r="H149" t="inlineStr">
         <is>
           <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
-TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Speed: 2.25x</t>
+Accuracy: 86% (+1%/Lv) | TP Cost: 5 (+2-4/Lv) -&gt; 32 | Speed: 2.25x</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -9583,10 +9579,14 @@
       </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>TP Cost</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -9639,7 +9639,7 @@
       <c r="H150" t="inlineStr">
         <is>
           <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
-TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 | Speed: 1.7x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 15 (+4-6/Lv) -&gt; 60 | Speed: 1.7x</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -9650,10 +9650,14 @@
       </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Accuracy, TP Cost</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -9706,7 +9710,7 @@
       <c r="H151" t="inlineStr">
         <is>
           <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
-TP Cost: 42 -&gt; 50 -&gt; 58 -&gt; 64 -&gt; 73 -&gt; 82 -&gt; 91 -&gt; 100 -&gt; 110 -&gt; 120 | Speed: 1.3x</t>
+Accuracy: 75% (+1-2%/Lv) -&gt; 85% | TP Cost: 42 (+6-10/Lv) -&gt; 120 | Speed: 1.3x</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -9717,10 +9721,14 @@
       </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Accuracy, TP Cost</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -9836,7 +9844,7 @@
       <c r="H153" t="inlineStr">
         <is>
           <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
-TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Speed: 2.25x</t>
+Accuracy: 86% (+1%/Lv) | TP Cost: 5 (+2-4/Lv) -&gt; 32 | Speed: 2.25x</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -9847,10 +9855,14 @@
       </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>TP Cost</t>
+        </is>
+      </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -9903,7 +9915,7 @@
       <c r="H154" t="inlineStr">
         <is>
           <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
-TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 | Speed: 1.7x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 15 (+4-6/Lv) -&gt; 60 | Speed: 1.7x</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -9914,10 +9926,14 @@
       </c>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Accuracy, TP Cost</t>
+        </is>
+      </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -9970,7 +9986,7 @@
       <c r="H155" t="inlineStr">
         <is>
           <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
-TP Cost: 42 -&gt; 50 -&gt; 58 -&gt; 64 -&gt; 73 -&gt; 82 -&gt; 91 -&gt; 100 -&gt; 110 -&gt; 120 | Speed: 1.3x</t>
+Accuracy: 75% (+1-2%/Lv) -&gt; 85% | TP Cost: 42 (+6-10/Lv) -&gt; 120 | Speed: 1.3x</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -9981,10 +9997,14 @@
       </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Accuracy, TP Cost</t>
+        </is>
+      </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -10100,7 +10120,7 @@
       <c r="H157" t="inlineStr">
         <is>
           <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
-TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Speed: 2.25x</t>
+Accuracy: 86% (+1%/Lv) | TP Cost: 5 (+2-4/Lv) -&gt; 32 | Speed: 2.25x</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -10111,10 +10131,14 @@
       </c>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>TP Cost</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -10167,7 +10191,7 @@
       <c r="H158" t="inlineStr">
         <is>
           <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
-TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 | Speed: 1.7x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 15 (+4-6/Lv) -&gt; 60 | Speed: 1.7x</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -10178,10 +10202,14 @@
       </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Accuracy, TP Cost</t>
+        </is>
+      </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -10234,7 +10262,7 @@
       <c r="H159" t="inlineStr">
         <is>
           <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
-TP Cost: 42 -&gt; 50 -&gt; 58 -&gt; 64 -&gt; 73 -&gt; 82 -&gt; 91 -&gt; 100 -&gt; 110 -&gt; 120 | Speed: 1.3x</t>
+Accuracy: 75% (+1-2%/Lv) -&gt; 85% | TP Cost: 42 (+6-10/Lv) -&gt; 120 | Speed: 1.3x</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -10245,10 +10273,14 @@
       </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Accuracy, TP Cost</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -10364,7 +10396,7 @@
       <c r="H161" t="inlineStr">
         <is>
           <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
-TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Speed: 2.25x</t>
+Accuracy: 86% (+1%/Lv) | TP Cost: 5 (+2-4/Lv) -&gt; 32 | Speed: 2.25x</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -10375,10 +10407,14 @@
       </c>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>TP Cost</t>
+        </is>
+      </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -10431,7 +10467,7 @@
       <c r="H162" t="inlineStr">
         <is>
           <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
-TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 | Speed: 1.7x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 15 (+4-6/Lv) -&gt; 60 | Speed: 1.7x</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -10442,10 +10478,14 @@
       </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Accuracy, TP Cost</t>
+        </is>
+      </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -10498,7 +10538,7 @@
       <c r="H163" t="inlineStr">
         <is>
           <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
-TP Cost: 42 -&gt; 50 -&gt; 58 -&gt; 64 -&gt; 73 -&gt; 82 -&gt; 91 -&gt; 100 -&gt; 110 -&gt; 120 | Speed: 1.3x</t>
+Accuracy: 75% (+1-2%/Lv) -&gt; 85% | TP Cost: 42 (+6-10/Lv) -&gt; 120 | Speed: 1.3x</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -10509,10 +10549,14 @@
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Accuracy, TP Cost</t>
+        </is>
+      </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -10628,7 +10672,7 @@
       <c r="H165" t="inlineStr">
         <is>
           <t>Pwr: 60 -&gt; 95 -&gt; 130 -&gt; 165 -&gt; 200 -&gt; 230 -&gt; 260 -&gt; 290 -&gt; 320 -&gt; 350 (L10)
-TP Cost: 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 | Speed: 2x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 9 (+1/Lv) -&gt; 18 | Speed: 2x</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -10639,10 +10683,14 @@
       </c>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -10833,7 +10881,7 @@
       <c r="H168" t="inlineStr">
         <is>
           <t>Pwr: 75 -&gt; 120 -&gt; 165 -&gt; 210 -&gt; 255 -&gt; 295 -&gt; 335 -&gt; 375 -&gt; 415 -&gt; 450 (L10)
-TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 | Speed: 1.5x</t>
+Accuracy: 65% (+2-3%/Lv) -&gt; 87% | TP Cost: 18 (+3-4/Lv) -&gt; 50 | Speed: 1.5x</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -10844,10 +10892,14 @@
       </c>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Accuracy, TP Cost</t>
+        </is>
+      </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -11584,7 +11636,7 @@
       <c r="H180" t="inlineStr">
         <is>
           <t>Pwr: 250 -&gt; 300 -&gt; 350 -&gt; 400 -&gt; 440 -&gt; 480 -&gt; 520 -&gt; 560 -&gt; 600 -&gt; 640 (L10)
-TP Cost: 45 -&gt; 52 -&gt; 59 -&gt; 66 -&gt; 74 -&gt; 80 -&gt; 86 -&gt; 90 -&gt; 95 -&gt; 100 | Speed: 1.75x</t>
+Accuracy: 60% (+1-2%/Lv) -&gt; 70% | TP Cost: 45 (+4-8/Lv) -&gt; 100 | Speed: 1.75x</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -11595,10 +11647,14 @@
       </c>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Accuracy, TP Cost</t>
+        </is>
+      </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O180" t="inlineStr"/>
@@ -12157,7 +12213,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>HP recovery: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 (L10)
+          <t>HP recovery: 8 (+2/Lv) -&gt; 26 (L10 Max) | Heal Cap: 100 (+60-80/Lv) -&gt; 800
 TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 | Speed: 1.75x</t>
         </is>
       </c>
@@ -12169,10 +12225,14 @@
       </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Heal Cap</t>
+        </is>
+      </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>Heal Cap, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -12224,7 +12284,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>HP recovery: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 (L10)
+          <t>HP recovery: 5 (+1/Lv) -&gt; 14 (L10 Max) | Heal Cap: 80 (+50-60/Lv) -&gt; 600
 TP Cost: 15 -&gt; 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 46 -&gt; 52 -&gt; 58 -&gt; 64 | Speed: 1.35x</t>
         </is>
       </c>
@@ -12236,10 +12296,14 @@
       </c>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Heal Cap</t>
+        </is>
+      </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>Heal Cap, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -12885,7 +12949,7 @@
       <c r="H200" t="inlineStr">
         <is>
           <t>Max HP: +20% -&gt; +23 -&gt; +26 -&gt; +29 -&gt; +32 -&gt; +35 -&gt; +38 -&gt; +41 -&gt; +44 -&gt; +47% (L10)
-Turns: 5 -&gt; 10 | TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45</t>
+Turns: 5 -&gt; 5 -&gt; 6 -&gt; 6 -&gt; 7 -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 18 (+3/Lv) -&gt; 45</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -12896,11 +12960,7 @@
       </c>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>Turns</t>
-        </is>
-      </c>
+      <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
@@ -14117,8 +14177,8 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | Damage cap UP
-Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x | Chant: 1x -&gt; 1.25x</t>
+          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | ATK: -4% (-1%/Lv)
+Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -14140,7 +14200,7 @@
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O221" t="inlineStr"/>
@@ -14183,8 +14243,8 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | Damage cap UP
-Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x | Chant: 1x -&gt; 1.25x</t>
+          <t>Damage UP | Accuracy: 64% (+4%/Lv) -&gt; 80% (L5 Max) | Magic defense: -7% -&gt; -18%
+Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -14203,10 +14263,14 @@
           <t>effect_1, effect_3</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Magic defense</t>
+        </is>
+      </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>Magic defense</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O222" t="inlineStr"/>
@@ -14249,8 +14313,8 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | Damage cap UP
-Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x | Chant: 1x -&gt; 1.25x</t>
+          <t>Damage UP | Accuracy: 64% (+4%/Lv) -&gt; 80% (L5 Max) | Speed decrease: 4% (+1%/Lv)
+Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -14272,7 +14336,7 @@
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr">
         <is>
-          <t>Speed decrease</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O223" t="inlineStr"/>
@@ -14315,8 +14379,8 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | Damage cap UP
-Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x | Chant: 1x -&gt; 1.25x</t>
+          <t>Damage UP | Accuracy: 64% (+4%/Lv) -&gt; 80% (L5 Max) | Evasion: -7% (-2%/Lv)
+Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -14338,7 +14402,7 @@
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr">
         <is>
-          <t>Evasion</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O224" t="inlineStr"/>
@@ -14381,8 +14445,8 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | Damage cap UP
-Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x | Chant: 1x -&gt; 1.25x</t>
+          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | DEF: -4% (-1%/Lv)
+Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -14404,7 +14468,7 @@
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O225" t="inlineStr"/>
@@ -14448,7 +14512,7 @@
       <c r="H226" t="inlineStr">
         <is>
           <t>Pwr: 350 -&gt; 390 -&gt; 430 -&gt; 470 -&gt; 510 -&gt; 550 -&gt; 590 -&gt; 630 -&gt; 680 -&gt; 720 (L10)
-TP Cost: 22 -&gt; 28 -&gt; 34 -&gt; 40 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58 -&gt; 62 -&gt; 66 | Speed: 1.3x</t>
+Accuracy: 86% (+1%/Lv) | TP Cost: 22 (+4-6/Lv) -&gt; 66 | Speed: 1.3x</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -14459,10 +14523,14 @@
       </c>
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>TP Cost</t>
+        </is>
+      </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O226" t="inlineStr"/>
@@ -14505,7 +14573,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Pwr: 240 -&gt; 280 -&gt; 320 -&gt; 360 -&gt; 400 -&gt; 440 -&gt; 480 -&gt; 520 -&gt; 560 -&gt; 600 | Stun: 25%
+          <t>Pwr: 240 (+40/Lv) -&gt; 600 (L10 Max) | Accuracy: 76% (+1%/Lv) | Stun: 25%
 TP Cost: 36 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 80 -&gt; 88 -&gt; 96 | Speed: 1.5x</t>
         </is>
       </c>
@@ -14520,7 +14588,7 @@
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O227" t="inlineStr"/>
@@ -14934,7 +15002,7 @@
       <c r="H234" t="inlineStr">
         <is>
           <t>Pwr: 100 -&gt; 130 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 280 -&gt; 320 -&gt; 370 -&gt; 420 -&gt; 480 (L10)
-TP Cost: 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58 -&gt; 62 -&gt; 66 | Speed: 0.85x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 30 (+4/Lv) -&gt; 66 | Speed: 0.85x</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -14945,10 +15013,14 @@
       </c>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>Accuracy, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O234" t="inlineStr"/>
@@ -14991,8 +15063,8 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Pwr: 360 -&gt; 400 -&gt; 440 -&gt; 480 -&gt; 520 -&gt; 560 -&gt; 600 -&gt; 640 -&gt; 690 -&gt; 740 (L10)
-Instakill: 12% | TP Cost: 32 -&gt; 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 52 -&gt; 54 -&gt; 56</t>
+          <t>Pwr: 360 (+40-50/Lv) -&gt; 740 | Accuracy: 76% (+1%/Lv) | Instakill: 12%
+TP Cost: 32 -&gt; 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 52 -&gt; 54 -&gt; 56 | Speed: 1.2x</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -15003,10 +15075,14 @@
       </c>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Pwr</t>
+        </is>
+      </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>Accuracy, Speed, Chant</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="O235" t="inlineStr"/>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -5459,7 +5459,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Resistance decrease: 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 (L10)
+          <t>Resistance decrease: 7% -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25% (L10)
 Speed: 0.75x</t>
         </is>
       </c>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Resistance: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
+          <t>Resistance: 20% -&gt; 24% -&gt; 28% -&gt; 32% -&gt; 36% (L1-5 Max)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Resistance: 18 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
+          <t>Resistance: 18% -&gt; 24% -&gt; 28% -&gt; 32% -&gt; 36% (L1-5 Max)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Resistance: 18 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
+          <t>Resistance: 18% -&gt; 24% -&gt; 28% -&gt; 32% -&gt; 36% (L1-5 Max)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Elemental resistance increase: 5 -&gt; 10 -&gt; 15 -&gt; 20 -&gt; 25 (L1-5 Max)
+          <t>Elemental resistance increase: 5% -&gt; 10% -&gt; 15% -&gt; 20% -&gt; 25% (L1-5 Max)
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Chant: 1.25x</t>
         </is>
       </c>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Elemental resistance: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 (L10)</t>
+          <t>Elemental resistance: 6% -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P331"/>
+  <dimension ref="A1:Q331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -449,6 +449,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="84" customWidth="1" min="15" max="15"/>
     <col width="86" customWidth="1" min="16" max="16"/>
+    <col width="90" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,6 +531,11 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Previous_Mod_LvUp</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Line1_Notes</t>
         </is>
       </c>
     </row>
@@ -595,6 +601,7 @@
 TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -658,6 +665,7 @@
 TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 11</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -725,6 +733,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -758,7 +767,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Short-range skill. Powerful strike to one enemy.</t>
+          <t>Short-range skill. Major strike to one enemy.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -792,6 +801,7 @@
 TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28  (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -859,6 +869,7 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -930,6 +941,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1001,6 +1013,7 @@
 ATK: -11% -&gt; -25% (-3.5%/Lv) | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1034,7 +1047,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Shield skill. Deal bash damage to one enemy. May stun.</t>
+          <t>Shield skill. Deal minor bash damage to one enemy. May stun (30%+).</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1072,6 +1085,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 | Requires equipped shield</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1105,7 +1119,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Katana skill. Deal bash damage to one enemy. May paralyze.</t>
+          <t>Katana skill. Deal moderate bash damage to one enemy. May paralyze (20-50%).</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1143,6 +1157,7 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1218,6 +1233,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1251,7 +1267,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Katana skill. Deal slash damage to an enemy row. May instakill.</t>
+          <t>Katana skill. Deal slash damage to an enemy row. May instakill (10%+).</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1283,6 +1299,11 @@
         <is>
           <t>ATK: 115% -&gt; 175% (+15%/Lv) | Instakill: 10% -&gt; 25% (+3.75%/Lv)
 TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 136</t>
         </is>
       </c>
     </row>
@@ -1348,6 +1369,11 @@
 TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 | Bypasses enemy armor</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 69</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1381,7 +1407,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Katana skill. Deal slash damage to an enemy row.</t>
+          <t>Katana skill. Deal minor slash damage to an enemy row.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1415,6 +1441,7 @@
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1482,6 +1509,11 @@
 TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 | Target must be living (not undead)</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 31, 87, 90</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1515,7 +1547,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Short-range skill. Attack one enemy to regain HP.</t>
+          <t>Short-range skill. Deal minor damage to one enemy to regain HP.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1549,6 +1581,7 @@
 HP Absorb: 20% -&gt; 30% -&gt; 40% -&gt; 50% -&gt; 60% | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1582,7 +1615,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Short-range skill. Attack one enemy to regain TP.</t>
+          <t>Short-range skill. Deal minor damage to one enemy to regain TP.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1616,6 +1649,7 @@
 TP Absorb: 5% -&gt; 8% -&gt; 11% -&gt; 14% -&gt; 18% | TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1649,7 +1683,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Short-range skill. Deal mid-range water damage to one enemy. May freeze.</t>
+          <t>Short-range skill. Deal severe mid-range water damage to one enemy. May freeze.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1683,6 +1717,11 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>chance left out: the sentence would be 88 characters</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1716,7 +1755,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Axe skill. Deal earth damage to one enemy. May petrify.</t>
+          <t>Axe skill. Deal severe earth damage to one enemy. May petrify (20-35%).</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1750,6 +1789,7 @@
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1821,6 +1861,11 @@
 TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28 | Hits 2 sequential turn targets</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>damage is major but the sentence would be 90 characters</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1888,6 +1933,7 @@
 TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24 | Requires 1H weapon &amp; shield</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1955,6 +2001,7 @@
 TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22 | May break on repeat blocks</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2020,6 +2067,11 @@
         <is>
           <t>ATK: 140% -&gt; 155% -&gt; 170% -&gt; 185% -&gt; 200% (L1-5) | Unholy Bonus: 1.50x
 TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 88</t>
         </is>
       </c>
     </row>
@@ -2089,6 +2141,7 @@
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 | Requires shield</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2156,6 +2209,7 @@
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 | Requires shield</t>
         </is>
       </c>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2189,7 +2243,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Short-range skill. Deal lightning damage to an enemy row. May paralyze.</t>
+          <t>Short-range skill. Deal minor lightning damage to an enemy row. May paralyze.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2223,6 +2277,11 @@
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>chance left out: the sentence would be 86 characters</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2256,7 +2315,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lance skill. Deal wind damage to one enemy. May silence.</t>
+          <t>Lance skill. Deal severe wind damage to one enemy. May silence (20-50%).</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2290,6 +2349,7 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2357,6 +2417,11 @@
 TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 | Heavy Lance bonus: +20% dmg</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 96, 111</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2390,7 +2455,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sword/lance skill. Pierces through to the back row.</t>
+          <t>Sword/lance skill. Pierces through to the back row for major damage.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2424,6 +2489,7 @@
 TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
         </is>
       </c>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2495,6 +2561,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 | Applies to next physical action</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2557,6 +2624,7 @@
 TP Cost: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2619,6 +2687,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2682,6 +2751,11 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 70</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2745,6 +2819,11 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 71</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2812,6 +2891,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
         </is>
       </c>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2879,6 +2959,7 @@
 TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 11 (L1-5)</t>
         </is>
       </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2950,6 +3031,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
         </is>
       </c>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3013,6 +3095,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3088,6 +3171,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3121,7 +3205,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Short-range skill. Attack one enemy. May cause sleep.</t>
+          <t>Short-range skill. Deal moderate damage to one enemy. May cause sleep (20-50%).</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3155,6 +3239,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3188,7 +3273,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Short-range skill. Attack one enemy. May silence.</t>
+          <t>Short-range skill. Deal moderate damage to one enemy. May silence (20-50%).</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3222,6 +3307,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3255,7 +3341,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Short-range skill. Attack one enemy. May stun.</t>
+          <t>Short-range skill. Deal moderate damage to one enemy. May stun (20-50%).</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3289,6 +3375,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3354,6 +3441,11 @@
         <is>
           <t>Hits: 2 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 | ATK: 65% -&gt; 85% per hit (+5%/Lv)
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 93, 125, 136</t>
         </is>
       </c>
     </row>
@@ -3419,6 +3511,11 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 72</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3490,6 +3587,11 @@
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 73</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3523,7 +3625,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bow/gun skill. Attack one enemy. May poison.</t>
+          <t>Bow/gun skill. Deal moderate damage to one enemy. May poison (20-50%).</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3557,6 +3659,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3590,7 +3693,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bow skill. Deal stab damage to one enemy. May freeze.</t>
+          <t>Bow skill. Deal moderate stab damage to one enemy. May freeze (20-50%).</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3624,6 +3727,7 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3657,7 +3761,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bow skill. Deal stab damage to one enemy. May paralyze.</t>
+          <t>Bow skill. Deal moderate stab damage to one enemy. May paralyze (20-50%).</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3691,6 +3795,7 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3724,7 +3829,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bow skill. Deal stab damage to one enemy. May slow.</t>
+          <t>Bow skill. Deal moderate stab damage to one enemy. May slow (20-50%).</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3758,6 +3863,7 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3791,7 +3897,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bow skill. Shoot a barrage of arrows that rains upon all enemies.</t>
+          <t>Bow skill. Shoot a barrage of arrows that rains minor damage upon all enemies.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3821,6 +3927,7 @@
 TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28</t>
         </is>
       </c>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3892,6 +3999,11 @@
 Duration: 2 -&gt; 3 turns | TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
         </is>
       </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 146, 147</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3959,6 +4071,11 @@
 TP Cost: 18 -&gt; 22 -&gt; 26 -&gt; 30 -&gt; 34 | Hits both front and back target</t>
         </is>
       </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 31</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4021,6 +4138,11 @@
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 79, 168</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4054,7 +4176,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Deal bash damage to one enemy. May stun.</t>
+          <t>Deal major bash damage to one enemy. May stun (10%+).</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4092,6 +4214,7 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4154,6 +4277,7 @@
 TP Cost: 5 -&gt; 4 -&gt; 3 -&gt; 2 -&gt; 1 (Max)</t>
         </is>
       </c>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4212,6 +4336,7 @@
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4287,6 +4412,11 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 73</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4320,7 +4450,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Mace skill. Decrease the enemy's DEF as you attack.</t>
+          <t>Mace skill. Decrease the enemy's DEF as you deal severe damage.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4354,6 +4484,7 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 | Fast turn recovery (0.85x delay)</t>
         </is>
       </c>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4387,7 +4518,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sword skill. Deal slash damage to all enemies.</t>
+          <t>Sword skill. Deal moderate slash damage to all enemies.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4421,6 +4552,7 @@
 TP Cost: 36 -&gt; 46 -&gt; 57 -&gt; 68 -&gt; 79 | Action delay: 0.80x -&gt; 0.98x</t>
         </is>
       </c>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4483,6 +4615,7 @@
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4546,6 +4679,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32</t>
         </is>
       </c>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4579,7 +4713,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Short-range skill. Perform a powerful lightning strike to one enemy.</t>
+          <t>Short-range skill. Perform a major lightning strike to one enemy.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4613,6 +4747,7 @@
 TP Cost: 13 -&gt; 20 -&gt; 28 -&gt; 36 -&gt; 45</t>
         </is>
       </c>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4646,7 +4781,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tome skill. RES-based bash damage to one enemy. May freeze/silence.</t>
+          <t>Tome skill. RES-based bash damage to one enemy. May freeze/silence (20-50%).</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4671,6 +4806,11 @@
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 47</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4725,6 +4865,7 @@
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4769,6 +4910,7 @@
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4830,6 +4972,7 @@
 TP Cost: 2 -&gt; 4 -&gt; 6 -&gt; 8 -&gt; 10 | Affected by Maid Mastery (+10% cap)</t>
         </is>
       </c>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4892,6 +5035,7 @@
 Action delay: 0.85x | TP Cost: 0 (Costs no TP to use)</t>
         </is>
       </c>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4953,6 +5097,7 @@
 Leaves user at 0 TP | Fast recovery</t>
         </is>
       </c>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5015,6 +5160,7 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
         </is>
       </c>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5077,6 +5223,7 @@
 TP Cost: 0 | Action delay: 1.00x</t>
         </is>
       </c>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5139,6 +5286,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5201,6 +5349,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5254,6 +5403,7 @@
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5307,6 +5457,7 @@
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5369,6 +5520,7 @@
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5422,6 +5574,7 @@
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5475,6 +5628,7 @@
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5540,6 +5694,11 @@
         <is>
           <t>ATK: 120% -&gt; 180% (+15%/Lv) | Row bash attack
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 (L1-5)</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 136</t>
         </is>
       </c>
     </row>
@@ -5596,6 +5755,11 @@
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 95</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5654,6 +5818,11 @@
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 93; chance not stated: the ailments of this sentence have different chances, or one always happens</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5719,6 +5888,11 @@
         <is>
           <t>ATK per hit: 90% -&gt; 110% -&gt; 130% -&gt; 150% -&gt; 180% (L1-5)
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 | Boosted by Trump / High Risk</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 94</t>
         </is>
       </c>
     </row>
@@ -5784,6 +5958,7 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Action delay: 1.50x (fast)</t>
         </is>
       </c>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5828,6 +6003,7 @@
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5861,7 +6037,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Attack one enemy. May instakill.</t>
+          <t>Deal major damage to one enemy. May instakill (15%+).</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5895,6 +6071,7 @@
 TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28 (L1-5)</t>
         </is>
       </c>
+      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5928,7 +6105,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>50/50 chance of non-elemental damage to each enemy. May stun.</t>
+          <t>50/50 chance of minor non-elemental damage to each enemy. May stun (40-70%).</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5953,6 +6130,7 @@
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6020,6 +6198,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
+      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6064,6 +6243,7 @@
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6118,6 +6298,7 @@
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6151,7 +6332,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Deal non-elemental damage to all enemies with a storm of roses. May poison.</t>
+          <t>Deal moderate non-elemental damage to all enemies with a storm of roses. May poison.</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6176,6 +6357,11 @@
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>chance left out: the sentence would be 93 characters</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6209,7 +6395,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fan skill. Deal bashing damage to one enemy. May delay enemy turn.</t>
+          <t>Fan skill. Deal severe bashing damage to one enemy. May delay enemy turn.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6243,6 +6429,7 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6271,7 +6458,7 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fan skill. With increased ATK, deal long-range damage to one enemy.</t>
+          <t>Fan skill. With increased ATK, deal minor long-range damage to one enemy.</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6292,6 +6479,7 @@
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6325,7 +6513,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Short-range skill. Pierce through to the back row with stab damage. May slow.</t>
+          <t>Short-range skill. Pierce through to the back row with major stab damage. May slow.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6350,6 +6538,11 @@
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>chance left out: the sentence would be 92 characters</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6408,6 +6601,11 @@
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 133</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6471,6 +6669,7 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
+      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6515,6 +6714,7 @@
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6577,6 +6777,11 @@
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 99, 110</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6652,6 +6857,7 @@
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 (L1-5)</t>
         </is>
       </c>
+      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6714,6 +6920,7 @@
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6785,6 +6992,7 @@
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 (L1-5)</t>
         </is>
       </c>
+      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6847,6 +7055,7 @@
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6914,6 +7123,7 @@
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 (L1-5)</t>
         </is>
       </c>
+      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6985,6 +7195,7 @@
 TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 (L1-5)</t>
         </is>
       </c>
+      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7039,6 +7250,7 @@
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7093,6 +7305,7 @@
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7147,6 +7360,7 @@
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7201,6 +7415,7 @@
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7255,6 +7470,7 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7309,6 +7525,7 @@
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7363,6 +7580,7 @@
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7417,6 +7635,7 @@
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7471,6 +7690,7 @@
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7525,6 +7745,7 @@
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7579,6 +7800,7 @@
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7633,6 +7855,7 @@
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7687,6 +7910,7 @@
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7741,6 +7965,7 @@
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7795,6 +8020,7 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7849,6 +8075,7 @@
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7903,6 +8130,7 @@
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7957,6 +8185,7 @@
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8011,6 +8240,7 @@
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8065,6 +8295,7 @@
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8119,6 +8350,7 @@
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8173,6 +8405,7 @@
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8227,6 +8460,7 @@
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8281,6 +8515,7 @@
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8335,6 +8570,7 @@
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8389,6 +8625,7 @@
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8443,6 +8680,7 @@
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8497,6 +8735,7 @@
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8551,6 +8790,7 @@
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8605,6 +8845,7 @@
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8659,6 +8900,7 @@
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8713,6 +8955,7 @@
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8767,6 +9010,7 @@
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8821,6 +9065,7 @@
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8875,6 +9120,7 @@
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8929,6 +9175,7 @@
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8983,6 +9230,7 @@
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9037,6 +9285,7 @@
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9091,6 +9340,7 @@
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9145,6 +9395,7 @@
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9199,6 +9450,7 @@
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9253,6 +9505,7 @@
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9286,7 +9539,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Deal fire damage to one enemy.</t>
+          <t>Deal moderate fire damage to one enemy.</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9324,6 +9577,7 @@
 TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9357,7 +9611,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Deal fire damage to an enemy row.</t>
+          <t>Deal moderate fire damage to an enemy row.</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9395,6 +9649,7 @@
 TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9428,7 +9683,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Deal fire damage to all enemies.</t>
+          <t>Deal severe fire damage to all enemies.</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9466,6 +9721,7 @@
 TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9529,6 +9785,7 @@
 TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9562,7 +9819,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Deal water damage to one enemy.</t>
+          <t>Deal moderate water damage to one enemy.</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9600,6 +9857,7 @@
 TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9633,7 +9891,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Deal water damage to an enemy row.</t>
+          <t>Deal moderate water damage to an enemy row.</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9671,6 +9929,7 @@
 TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9704,7 +9963,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Deal water damage to all enemies.</t>
+          <t>Deal severe water damage to all enemies.</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9742,6 +10001,7 @@
 TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9805,6 +10065,7 @@
 TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9838,7 +10099,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Deal lightning damage to one enemy.</t>
+          <t>Deal moderate lightning damage to one enemy.</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9876,6 +10137,7 @@
 TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9909,7 +10171,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Deal lightning damage to an enemy row.</t>
+          <t>Deal moderate lightning damage to an enemy row.</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9947,6 +10209,7 @@
 TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9980,7 +10243,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Deal lightning damage to all enemies.</t>
+          <t>Deal severe lightning damage to all enemies.</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10018,6 +10281,7 @@
 TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10081,6 +10345,7 @@
 TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10114,7 +10379,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Deal wind damage to one enemy.</t>
+          <t>Deal moderate wind damage to one enemy.</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10152,6 +10417,7 @@
 TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10185,7 +10451,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Deal wind damage to an enemy row.</t>
+          <t>Deal moderate wind damage to an enemy row.</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10223,6 +10489,7 @@
 TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10256,7 +10523,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Deal wind damage to all enemies.</t>
+          <t>Deal severe wind damage to all enemies.</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10294,6 +10561,7 @@
 TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10357,6 +10625,7 @@
 TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10390,7 +10659,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Deal earth damage to one enemy.</t>
+          <t>Deal moderate earth damage to one enemy.</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10428,6 +10697,7 @@
 TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10461,7 +10731,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Deal earth damage to an enemy row.</t>
+          <t>Deal moderate earth damage to an enemy row.</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10499,6 +10769,7 @@
 TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10532,7 +10803,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Deal earth damage to all enemies.</t>
+          <t>Deal severe earth damage to all enemies.</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10570,6 +10841,7 @@
 TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10633,6 +10905,7 @@
 TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10666,7 +10939,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Deal non-elemental damage to one enemy to regain HP.</t>
+          <t>Deal minor non-elemental damage to one enemy to regain HP.</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10704,6 +10977,7 @@
 TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 18</t>
         </is>
       </c>
+      <c r="Q165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10737,7 +11011,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Deal non-elemental damage to one enemy to regain TP.</t>
+          <t>Deal negligible non-elemental damage to one enemy to regain TP.</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10775,6 +11049,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 15</t>
         </is>
       </c>
+      <c r="Q166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10842,6 +11117,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
+      <c r="Q167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10875,7 +11151,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Absorb HP from an enemy row.</t>
+          <t>Absorb HP from an enemy row with moderate damage.</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10913,6 +11189,7 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 (L1-5)</t>
         </is>
       </c>
+      <c r="Q168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10946,7 +11223,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Stun one enemy.</t>
+          <t>Stun one enemy (65%+).</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10976,6 +11253,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11009,7 +11287,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Poison all enemies.</t>
+          <t>Poison all enemies (75%+).</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11039,6 +11317,7 @@
 TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5)</t>
         </is>
       </c>
+      <c r="Q170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11072,7 +11351,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Freeze all enemies.</t>
+          <t>Freeze all enemies (70%+).</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11102,6 +11381,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11135,7 +11415,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Paralyze all enemies.</t>
+          <t>Paralyze all enemies (65%+).</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11165,6 +11445,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11198,7 +11479,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Put an enemy row to sleep.</t>
+          <t>Put an enemy row to sleep (65%+).</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11228,6 +11509,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11261,7 +11543,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Silence all enemies.</t>
+          <t>Silence all enemies (70%+).</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11291,6 +11573,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11324,7 +11607,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Petrify an enemy row.</t>
+          <t>Petrify an enemy row (70%+).</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11354,6 +11637,7 @@
 TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
         </is>
       </c>
+      <c r="Q175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11387,7 +11671,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Instakill one enemy.</t>
+          <t>Instakill one enemy (50%+).</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11417,6 +11701,7 @@
 TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28</t>
         </is>
       </c>
+      <c r="Q176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11450,7 +11735,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Slow an enemy row.</t>
+          <t>Slow an enemy row (50-68%).</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11480,6 +11765,7 @@
 TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 (L1-5)</t>
         </is>
       </c>
+      <c r="Q177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11513,7 +11799,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Stun an enemy row.</t>
+          <t>Stun an enemy row (54-70%).</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11543,6 +11829,7 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11597,6 +11884,7 @@
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11659,6 +11947,11 @@
       </c>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 88</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11722,6 +12015,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11785,6 +12079,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11848,6 +12143,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11911,6 +12207,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11974,6 +12271,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12041,6 +12339,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
+      <c r="Q186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12108,6 +12407,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
+      <c r="Q187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12175,6 +12475,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
+      <c r="Q188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12246,6 +12547,7 @@
 TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26  (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12317,6 +12619,7 @@
 TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 21 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 46  (Lv1 to Max)</t>
         </is>
       </c>
+      <c r="Q190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12378,6 +12681,7 @@
 TP Cost: 35 -&gt; 30 -&gt; 25 -&gt; 20 -&gt; 16 (L1-5)</t>
         </is>
       </c>
+      <c r="Q191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12445,6 +12749,7 @@
 TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 (L1-7)</t>
         </is>
       </c>
+      <c r="Q192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12512,6 +12817,7 @@
 TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 (L1-7)</t>
         </is>
       </c>
+      <c r="Q193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12575,6 +12881,7 @@
 Chant time decreases per level | TP Cost: 18 -&gt; 22 -&gt; 26 -&gt; 30 -&gt; 35</t>
         </is>
       </c>
+      <c r="Q194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12642,6 +12949,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -12709,6 +13017,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12776,6 +13085,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
+      <c r="Q197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -12843,6 +13153,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
+      <c r="Q198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12910,6 +13221,7 @@
 Chant time decreases per level | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12977,6 +13289,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
         </is>
       </c>
+      <c r="Q200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13044,6 +13357,7 @@
 TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24 -&gt; 28 (L1-7)</t>
         </is>
       </c>
+      <c r="Q201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13107,6 +13421,7 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
         </is>
       </c>
+      <c r="Q202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13170,6 +13485,7 @@
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
+      <c r="Q203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -13228,6 +13544,7 @@
       </c>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13289,6 +13606,7 @@
 TP Cost: 4 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 4</t>
         </is>
       </c>
+      <c r="Q205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -13350,6 +13668,7 @@
 Works identical to an Emergency Exit item</t>
         </is>
       </c>
+      <c r="Q206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -13382,7 +13701,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Put an enemy to sleep.</t>
+          <t>Put an enemy to sleep (70-82%).</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13412,6 +13731,7 @@
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="Q207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13460,6 +13780,7 @@
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13513,6 +13834,7 @@
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13566,6 +13888,7 @@
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13619,6 +13942,7 @@
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -13672,6 +13996,7 @@
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -13734,6 +14059,7 @@
 Chant Time: 2 turns -&gt; 1 turn | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
+      <c r="Q213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -13796,6 +14122,7 @@
 Chant Time: 2 turns -&gt; 1 turn | TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
         </is>
       </c>
+      <c r="Q214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13858,6 +14185,7 @@
 TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
         </is>
       </c>
+      <c r="Q215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13920,6 +14248,7 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="Q216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13973,6 +14302,7 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -14031,6 +14361,7 @@
       </c>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -14085,6 +14416,7 @@
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -14139,6 +14471,7 @@
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -14205,6 +14538,7 @@
       </c>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -14275,6 +14609,7 @@
       </c>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -14341,6 +14676,7 @@
       </c>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -14407,6 +14743,7 @@
       </c>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -14473,6 +14810,7 @@
       </c>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -14506,7 +14844,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Deal non-elemental damage to an enemy row.</t>
+          <t>Deal severe non-elemental damage to an enemy row.</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14535,6 +14873,7 @@
       </c>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -14568,7 +14907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Deal non-elemental damage to all enemies. May stun.</t>
+          <t>Deal major non-elemental damage to all enemies. May stun (25%).</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14593,6 +14932,7 @@
       </c>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -14660,6 +15000,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30</t>
         </is>
       </c>
+      <c r="Q228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -14727,6 +15068,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30</t>
         </is>
       </c>
+      <c r="Q229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -14781,6 +15123,7 @@
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -14835,6 +15178,7 @@
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -14897,6 +15241,7 @@
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14963,6 +15308,7 @@
       </c>
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -15025,6 +15371,11 @@
       </c>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 47</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -15058,7 +15409,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Deal enormous damage to one enemy that possesses life. Low chance of instakill.</t>
+          <t>Deal enormous damage to one enemy that possesses life. Low chance of instakill (12%).</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15087,6 +15438,11 @@
       </c>
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>no damage word: carries effects that are not understood: 87</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -15149,6 +15505,7 @@
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
       <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -15203,6 +15560,7 @@
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -15257,6 +15615,7 @@
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -15311,6 +15670,7 @@
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -15365,6 +15725,7 @@
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -15419,6 +15780,7 @@
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -15482,6 +15844,7 @@
 Heroine: Melvy</t>
         </is>
       </c>
+      <c r="Q242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -15543,6 +15906,7 @@
 Scales off weapon base ATK (not total character ATK)</t>
         </is>
       </c>
+      <c r="Q243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -15604,6 +15968,7 @@
 Scales off weapon base ATK</t>
         </is>
       </c>
+      <c r="Q244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -15665,6 +16030,7 @@
 Scales off weapon base ATK</t>
         </is>
       </c>
+      <c r="Q245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -15726,6 +16092,7 @@
 Scales off weapon base ATK</t>
         </is>
       </c>
+      <c r="Q246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -15787,6 +16154,7 @@
 Scales off weapon base ATK</t>
         </is>
       </c>
+      <c r="Q247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -15848,6 +16216,7 @@
 Scales off weapon base ATK</t>
         </is>
       </c>
+      <c r="Q248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -15909,6 +16278,7 @@
 Scales off weapon base ATK</t>
         </is>
       </c>
+      <c r="Q249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -15970,6 +16340,7 @@
 Scales off weapon base ATK</t>
         </is>
       </c>
+      <c r="Q250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -16031,6 +16402,7 @@
 Scales off weapon base ATK</t>
         </is>
       </c>
+      <c r="Q251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -16092,6 +16464,7 @@
 Scales off weapon base ATK</t>
         </is>
       </c>
+      <c r="Q252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -16153,6 +16526,7 @@
 Universal weapon scaling</t>
         </is>
       </c>
+      <c r="Q253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -16214,6 +16588,7 @@
 Applies to all offensive spell damage</t>
         </is>
       </c>
+      <c r="Q254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -16283,6 +16658,7 @@
 Also raises baseline healing cap on Heal and Circle Heal</t>
         </is>
       </c>
+      <c r="Q255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -16344,6 +16720,7 @@
 Triggers at start of user's action in combat</t>
         </is>
       </c>
+      <c r="Q256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -16405,6 +16782,7 @@
 Triggers at start of user's action in combat</t>
         </is>
       </c>
+      <c r="Q257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -16466,6 +16844,7 @@
 Active on user turn in battle</t>
         </is>
       </c>
+      <c r="Q258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -16527,6 +16906,7 @@
 Triggers on user turn in combat</t>
         </is>
       </c>
+      <c r="Q259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -16588,6 +16968,7 @@
 Applies to Fire, Water, Lightning, Wind, and Earth</t>
         </is>
       </c>
+      <c r="Q260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -16649,6 +17030,7 @@
 Note: Short-range retaliations will trigger enemy Dark Aura</t>
         </is>
       </c>
+      <c r="Q261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -16710,6 +17092,7 @@
 Nullifies incoming attack and strikes back</t>
         </is>
       </c>
+      <c r="Q262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -16771,6 +17154,7 @@
 Can stack with Triple Attack (up to 5 strikes total)</t>
         </is>
       </c>
+      <c r="Q263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -16832,6 +17216,7 @@
 Stacks with Double Attack</t>
         </is>
       </c>
+      <c r="Q264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -16884,6 +17269,7 @@
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr"/>
       <c r="P265" t="inlineStr"/>
+      <c r="Q265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -16936,6 +17322,7 @@
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -16997,6 +17384,7 @@
 Prevents death when hit by lethal blows</t>
         </is>
       </c>
+      <c r="Q267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -17058,6 +17446,7 @@
 Halves incoming damage when triggered</t>
         </is>
       </c>
+      <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -17119,6 +17508,7 @@
 Main hand weapon deals 100% ATK</t>
         </is>
       </c>
+      <c r="Q269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -17171,6 +17561,7 @@
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr"/>
       <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -17223,6 +17614,7 @@
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr"/>
       <c r="P271" t="inlineStr"/>
+      <c r="Q271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -17275,6 +17667,7 @@
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr"/>
       <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -17327,6 +17720,7 @@
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -17379,6 +17773,7 @@
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr"/>
       <c r="P274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -17431,6 +17826,7 @@
       <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr"/>
       <c r="P275" t="inlineStr"/>
+      <c r="Q275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -17483,6 +17879,7 @@
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr"/>
       <c r="P276" t="inlineStr"/>
+      <c r="Q276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -17527,6 +17924,7 @@
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr"/>
       <c r="P277" t="inlineStr"/>
+      <c r="Q277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -17571,6 +17969,7 @@
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr"/>
       <c r="P278" t="inlineStr"/>
+      <c r="Q278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -17623,6 +18022,7 @@
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="inlineStr"/>
       <c r="P279" t="inlineStr"/>
+      <c r="Q279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -17684,6 +18084,7 @@
 Completely negates incoming physical attacks when triggered</t>
         </is>
       </c>
+      <c r="Q280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -17749,6 +18150,7 @@
 Triggers automatically at start of user's combat turn</t>
         </is>
       </c>
+      <c r="Q281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -17810,6 +18212,7 @@
 Immediate combat stat trigger</t>
         </is>
       </c>
+      <c r="Q282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -17870,6 +18273,7 @@
           <t>Interruption Resist: +20% -&gt; +50% (+7.5%/Lv) | 80% Crit Interrupt Res at Lv 5</t>
         </is>
       </c>
+      <c r="Q283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -17931,6 +18335,7 @@
 Accelerates offensive and healing magic activation</t>
         </is>
       </c>
+      <c r="Q284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -17992,6 +18397,7 @@
 Lowers cost of all techniques and spells</t>
         </is>
       </c>
+      <c r="Q285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -18053,6 +18459,7 @@
 Significantly reduces spell evasion by high RES targets</t>
         </is>
       </c>
+      <c r="Q286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -18114,6 +18521,7 @@
 Protects party from surprise enemy encounters</t>
         </is>
       </c>
+      <c r="Q287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -18175,6 +18583,7 @@
 Grants free initial turn before enemies act</t>
         </is>
       </c>
+      <c r="Q288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -18236,6 +18645,7 @@
 Does not apply to scripted boss battles</t>
         </is>
       </c>
+      <c r="Q289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -18297,6 +18707,7 @@
 Boosts party equipment and material acquisition</t>
         </is>
       </c>
+      <c r="Q290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -18358,6 +18769,7 @@
 Earn bonus currency after every battle</t>
         </is>
       </c>
+      <c r="Q291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -18419,6 +18831,7 @@
 Finds consumables and crafting materials while walking</t>
         </is>
       </c>
+      <c r="Q292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -18488,6 +18901,7 @@
 Restores whole party after combat conclusion</t>
         </is>
       </c>
+      <c r="Q293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -18549,6 +18963,7 @@
 Item is not consumed from inventory when triggered</t>
         </is>
       </c>
+      <c r="Q294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -18610,6 +19025,7 @@
 Applies to all consumable recovery items used in combat</t>
         </is>
       </c>
+      <c r="Q295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -18671,6 +19087,7 @@
 Allows maintaining 2 active Bard songs at once</t>
         </is>
       </c>
+      <c r="Q296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -18732,6 +19149,7 @@
 Allows maintaining 2 active Dancer dances at once</t>
         </is>
       </c>
+      <c r="Q297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -18793,6 +19211,7 @@
 Maintains 2 active summoned dolls simultaneously</t>
         </is>
       </c>
+      <c r="Q298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -18854,6 +19273,7 @@
 Levels: L1-5</t>
         </is>
       </c>
+      <c r="Q299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -18915,6 +19335,7 @@
 Empowers First Aid, Cook, and Clean</t>
         </is>
       </c>
+      <c r="Q300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -18976,6 +19397,7 @@
 Empowers Bard songs and regeneration rates</t>
         </is>
       </c>
+      <c r="Q301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -19037,6 +19459,7 @@
 Empowers Dancer dances and status effects</t>
         </is>
       </c>
+      <c r="Q302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -19098,6 +19521,7 @@
 Increases damage, healing, and durability of summoned dolls</t>
         </is>
       </c>
+      <c r="Q303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -19159,6 +19583,7 @@
 Normal attack trigger</t>
         </is>
       </c>
+      <c r="Q304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -19220,6 +19645,7 @@
 Accelerates Bard song activation</t>
         </is>
       </c>
+      <c r="Q305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -19281,6 +19707,7 @@
 Lowers gold cost for item purchases and item identification</t>
         </is>
       </c>
+      <c r="Q306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -19342,6 +19769,7 @@
 Enemy skips turn when mesmerized</t>
         </is>
       </c>
+      <c r="Q307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -19395,6 +19823,7 @@
 Fixed passive (Level 1)</t>
         </is>
       </c>
+      <c r="Q308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -19448,6 +19877,7 @@
 Fixed passive (Level 1)</t>
         </is>
       </c>
+      <c r="Q309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -19492,6 +19922,7 @@
       <c r="N310" t="inlineStr"/>
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="inlineStr"/>
+      <c r="Q310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -19536,6 +19967,7 @@
       <c r="N311" t="inlineStr"/>
       <c r="O311" t="inlineStr"/>
       <c r="P311" t="inlineStr"/>
+      <c r="Q311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -19589,6 +20021,7 @@
 Spell criticals deal 1.50x normal magic damage</t>
         </is>
       </c>
+      <c r="Q312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -19642,6 +20075,7 @@
 Fixed passive (Level 1)</t>
         </is>
       </c>
+      <c r="Q313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -19693,6 +20127,7 @@
         </is>
       </c>
       <c r="P314" t="inlineStr"/>
+      <c r="Q314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -19744,6 +20179,7 @@
         </is>
       </c>
       <c r="P315" t="inlineStr"/>
+      <c r="Q315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -19795,6 +20231,7 @@
         </is>
       </c>
       <c r="P316" t="inlineStr"/>
+      <c r="Q316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -19846,6 +20283,7 @@
         </is>
       </c>
       <c r="P317" t="inlineStr"/>
+      <c r="Q317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -19897,6 +20335,7 @@
         </is>
       </c>
       <c r="P318" t="inlineStr"/>
+      <c r="Q318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -19948,6 +20387,7 @@
         </is>
       </c>
       <c r="P319" t="inlineStr"/>
+      <c r="Q319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -19999,6 +20439,7 @@
         </is>
       </c>
       <c r="P320" t="inlineStr"/>
+      <c r="Q320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -20050,6 +20491,7 @@
         </is>
       </c>
       <c r="P321" t="inlineStr"/>
+      <c r="Q321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -20101,6 +20543,7 @@
         </is>
       </c>
       <c r="P322" t="inlineStr"/>
+      <c r="Q322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -20152,6 +20595,7 @@
         </is>
       </c>
       <c r="P323" t="inlineStr"/>
+      <c r="Q323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -20203,6 +20647,7 @@
         </is>
       </c>
       <c r="P324" t="inlineStr"/>
+      <c r="Q324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -20254,6 +20699,7 @@
         </is>
       </c>
       <c r="P325" t="inlineStr"/>
+      <c r="Q325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -20305,6 +20751,7 @@
         </is>
       </c>
       <c r="P326" t="inlineStr"/>
+      <c r="Q326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -20356,6 +20803,7 @@
         </is>
       </c>
       <c r="P327" t="inlineStr"/>
+      <c r="Q327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -20407,6 +20855,7 @@
         </is>
       </c>
       <c r="P328" t="inlineStr"/>
+      <c r="Q328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -20458,6 +20907,7 @@
         </is>
       </c>
       <c r="P329" t="inlineStr"/>
+      <c r="Q329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -20509,6 +20959,7 @@
         </is>
       </c>
       <c r="P330" t="inlineStr"/>
+      <c r="Q330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -20560,6 +21011,7 @@
         </is>
       </c>
       <c r="P331" t="inlineStr"/>
+      <c r="Q331" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20714,7 +21166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -20796,34 +21248,58 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Notation</t>
+          <t>Line 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ATK: 125% -&gt; 134 -&gt; ... -&gt; 200%  |  ATK: 130% (+8%/Lv) -&gt; 202% (L10 Max)  |  Speed: 0.8x -&gt; 0.9x</t>
+          <t>The line shown in battle, where the level is unknown. One word for damage, chosen from the average of the real values (negligible below 80%, minor, moderate, major, severe; tremendous beyond the scale), and the ailment chance as (25%) when it never changes, (30%+) when it rises by 10 points or less, (20-50%) otherwise. No tilde: the game font has none. The build rejects what the binary does not give.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Line1_Notes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Averages such as "(avg +3.33%/Lv)". A step is written only when it is the same at every level.</t>
+          <t>Why a skill got no word: it carries an effect that is not understood, or the sentence would not fit.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Notation</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ATK: 125% -&gt; 134 -&gt; ... -&gt; 200%  |  ATK: 130% (+8%/Lv) -&gt; 202% (L10 Max)  |  Speed: 0.8x -&gt; 0.9x</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Averages such as "(avg +3.33%/Lv)". A step is written only when it is the same at every level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Previous_Mod_*</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Wording of the earlier mod, for reference only. Its numbers were not taken from the binary.</t>
         </is>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -443,10 +443,10 @@
     <col width="87" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="76" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="47" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="84" customWidth="1" min="15" max="15"/>
     <col width="86" customWidth="1" min="16" max="16"/>
     <col width="90" customWidth="1" min="17" max="17"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Short-range skill. Attack one enemy. May cancel enemy buffs.</t>
+          <t>Short-range skill. Attack one enemy. May cancel enemy buffs (68-85%).</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1196,26 +1196,18 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Critical rate UP | Enemy critical rate UP
-Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max) | TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
+          <t>Critical rate: 5% (+2.5%/Lv) -&gt; 15% (L5 Max) | Enemy critical rate: 4% (+2%/Lv)
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Critical rate UP; Enemy critical rate UP</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>effect_1, effect_2</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
@@ -1267,7 +1259,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Katana skill. Deal slash damage to an enemy row. May instakill (10%+).</t>
+          <t>Katana skill. Deal minor slash damage to an enemy row. May instakill (10%+).</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1301,11 +1293,7 @@
 TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 136</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1339,7 +1327,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Katana skill. Deal defense-piercing damage and DEF down to one enemy.</t>
+          <t>Katana skill. Deal minor defense-piercing damage and DEF down to one enemy.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1369,11 +1357,7 @@
 TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 | Bypasses enemy armor</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 69</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1475,7 +1459,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Katana skill. Deal slash damage 3 times to one enemy. Living targets only.</t>
+          <t>Katana skill. Deal moderate slash damage 3 times to one enemy. Living targets only.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1509,11 +1493,7 @@
 TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 | Target must be living (not undead)</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 31, 87, 90</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2035,7 +2015,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sword/lance skill. Attack one enemy (effective vs. unholy monsters).</t>
+          <t>Sword/lance skill. Deal severe damage to one enemy (effective vs. unholy monsters).</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2069,11 +2049,7 @@
 TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 88</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2383,7 +2359,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lance skill. 3-5 hits on random enemies. Stronger with a Heavy Lance.</t>
+          <t>Lance skill. 3-5 moderate hits on random enemies. Stronger with a Heavy Lance.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2417,11 +2393,7 @@
 TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 | Heavy Lance bonus: +20% dmg</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 96, 111</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2528,26 +2500,18 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Damage UP
+          <t>Damage: 1.05x -&gt; 1.1x -&gt; 1.16x -&gt; 1.22x -&gt; 1.3x (L1-5 Max)
 Turns: 2 | TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 | Speed: 0.84x -&gt; 0.9x</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Damage UP</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>effect_1</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
@@ -2721,7 +2685,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dagger skill. Inflict a critical hit with stab damage.</t>
+          <t>Dagger skill. Inflict a critical hit with minor stab damage.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2751,11 +2715,7 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 70</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2789,7 +2749,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dagger skill. Inflict stab damage relative to enemy's total buffs and debuffs.</t>
+          <t>Dagger skill. Inflict severe stab damage relative to enemy's total buffs and debuffs.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2819,11 +2779,7 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 71</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2941,11 +2897,7 @@
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>effect_1</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
@@ -3134,32 +3086,24 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Evasion increases UP
-Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max) | TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
+          <t>Physical evasion: +15% (+2-3%/Lv) -&gt; +25% | Magic evasion: +10% (+2-3%/Lv) -&gt; +20%
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Evasion increases UP</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>effect_1, effect_2</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Physical evasion, Magic evasion</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>Increase own physical evasion and magic evasion.</t>
@@ -3415,7 +3359,7 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>Number of attacks: 3 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 | ATK: 104% -&gt; 148%
-Power: -25% -&gt; -14% | TP Cost: 30 (+4-6/Lv) -&gt; 72 | Speed: 0.75x -&gt; 0.85x</t>
+Power decrease: 25% -&gt; 14% | TP Cost: 30 (+4-6/Lv) -&gt; 72 | Speed: 0.75x -&gt; 0.85x</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -3428,7 +3372,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>ATK, Power, TP Cost</t>
+          <t>ATK, Power decrease, TP Cost</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -3445,7 +3389,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>no damage word: carries effects that are not understood: 93, 125, 136</t>
+          <t>damage is minor but the sentence would be 87 characters</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3425,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bow/gun skill. Fire a single shot certain to hit one enemy.</t>
+          <t>Bow/gun skill. Fire a single shot certain to hit one enemy for minor damage.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3511,11 +3455,7 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 72</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4037,13 +3977,13 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bow skill. Deal stab damage to one enemy and pierce to the back row.</t>
+          <t>Bow skill. Deal severe stab damage to one enemy and pierce to the back row.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>ATK: 130% -&gt; 144 -&gt; 158 -&gt; 171 -&gt; 184 -&gt; 196 -&gt; 207 -&gt; 217 -&gt; 226 -&gt; 234% (L10)
-Critical rate: 5 (+1-3/Lv) -&gt; 25 | TP Cost: 24 (+3-4/Lv) -&gt; 55 | Speed: 0.7x</t>
+Critical rate: 5% (+1-3%/Lv) -&gt; 25% | TP Cost: 24 (+3-4/Lv) -&gt; 55 | Speed: 0.7x</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -4071,11 +4011,7 @@
 TP Cost: 18 -&gt; 22 -&gt; 26 -&gt; 30 -&gt; 34 | Hits both front and back target</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 31</t>
-        </is>
-      </c>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4109,13 +4045,13 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Projectile skill. Attack and decrease speed for an enemy row.</t>
+          <t>Projectile skill. Deal minor damage and decrease speed for an enemy row.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>ATK: 94% -&gt; 97 -&gt; 100 -&gt; 103 -&gt; 106 -&gt; 110 -&gt; 114 -&gt; 119 -&gt; 124 -&gt; 130% (L10)
-Turns: 4 | TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50</t>
+Speed decrease chance: 30% (+5%/Lv) | Turns: 4 | TP Cost: 24 (+2-3/Lv) -&gt; 50</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -4125,12 +4061,12 @@
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>effect_4</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>TP Cost</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>Speed</t>
@@ -4138,11 +4074,7 @@
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 79, 168</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4781,7 +4713,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tome skill. RES-based bash damage to one enemy. May freeze/silence (20-50%).</t>
+          <t>Tome skill. Severe RES-based bash damage to one enemy. May freeze/silence (20-50%).</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4806,11 +4738,7 @@
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 47</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5496,28 +5424,24 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Damage UP | Total damage cap UP
-Speed: 0.5x</t>
+          <t>Max HP damage: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)
+Total damage cap: 250 -&gt; 275 -&gt; 300 -&gt; 325 -&gt; 350 -&gt; 375 -&gt; 400 -&gt; 430 -&gt; 460 -&gt; 500</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Damage UP; Total damage cap UP</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>effect_1, effect_2</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
@@ -5662,7 +5586,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Whip skill. Deal bash damage to an enemy row from mid-range.</t>
+          <t>Whip skill. Deal moderate bash damage to an enemy row from mid-range.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5696,11 +5620,7 @@
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 (L1-5)</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 136</t>
-        </is>
-      </c>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5734,7 +5654,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Whip skill. Attack one enemy 1-5 times from mid-range.</t>
+          <t>Whip skill. Deal minor damage to one enemy 1-5 times from mid-range.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5755,11 +5675,7 @@
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 95</t>
-        </is>
-      </c>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5793,7 +5709,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Whip skill. Deal bash damage to one enemy twice. May silence/paralyze.</t>
+          <t>Whip skill. Deal moderate bash damage to one enemy twice. May silence/paralyze.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5820,7 +5736,7 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>no damage word: carries effects that are not understood: 93; chance not stated: the ailments of this sentence have different chances, or one always happens</t>
+          <t>chance not stated: the ailments of this sentence have different chances, or one always happens</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5772,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Attack 0-4 times on random targets.</t>
+          <t>Deal minor damage 0-4 times on random targets.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5890,11 +5806,7 @@
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 | Boosted by Trump / High Risk</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 94</t>
-        </is>
-      </c>
+      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6395,7 +6307,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fan skill. Deal severe bashing damage to one enemy. May delay enemy turn.</t>
+          <t>Fan skill. Deal severe bashing damage to one enemy. May delay enemy turn (25-43%).</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6576,7 +6488,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Short-range skill. Attack one enemy and reduce target's max HP.</t>
+          <t>Short-range skill. Deal minor damage to one enemy and reduce target's max HP.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6601,11 +6513,7 @@
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 133</t>
-        </is>
-      </c>
+      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6779,7 +6687,7 @@
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>no damage word: carries effects that are not understood: 99, 110</t>
+          <t>damage is moderate but the sentence would be 93 characters</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6728,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>ATK UP | Duration UP
+          <t>ATK UP | Duration: 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 5 -&gt; 6
 TP Cost: 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42</t>
         </is>
       </c>
@@ -6832,12 +6740,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>ATK UP; Duration UP</t>
+          <t>ATK UP</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>effect_1, effect_3</t>
+          <t>effect_1</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -6896,7 +6804,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ATK UP | Duration UP | Paralysis rate UP
+          <t>ATK UP | Duration: 3 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 | Paralysis rate UP
 TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 44 -&gt; 46 -&gt; 48 | Speed: 0.9x</t>
         </is>
       </c>
@@ -6908,12 +6816,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>ATK UP; Duration UP; Paralysis rate UP</t>
+          <t>ATK UP; Paralysis rate UP</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>effect_1, effect_3</t>
+          <t>effect_1</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -6959,8 +6867,8 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>HP recovery UP | Duration UP
-TP Cost: 30 -&gt; 33 -&gt; 37 -&gt; 42 -&gt; 48 (L1-5 Max) | Speed: 0.9x</t>
+          <t>HP recovery UP | Duration: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5 (L1-5 Max)
+TP Cost: 30 -&gt; 33 -&gt; 37 -&gt; 42 -&gt; 48 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -6971,12 +6879,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>HP recovery UP; Duration UP</t>
+          <t>HP recovery UP</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>effect_1, effect_3</t>
+          <t>effect_1</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -7031,7 +6939,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>ATK UP | Duration UP
+          <t>ATK UP | Duration: 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4
 TP Cost: 42 -&gt; 44 -&gt; 46 -&gt; 48 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 60 -&gt; 64 -&gt; 70 | Speed: 0.75x</t>
         </is>
       </c>
@@ -7043,12 +6951,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>ATK UP; Duration UP</t>
+          <t>ATK UP</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>effect_1, effect_3</t>
+          <t>effect_1</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -7105,11 +7013,7 @@
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>effect_1</t>
-        </is>
-      </c>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
@@ -11918,7 +11822,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Deal non-elemental damage to all enemies (effective vs. unholy monsters).</t>
+          <t>Deal major non-elemental damage to all enemies (effective vs. unholy monsters).</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11947,11 +11851,7 @@
       </c>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 88</t>
-        </is>
-      </c>
+      <c r="Q180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12731,11 +12631,7 @@
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>effect_1</t>
-        </is>
-      </c>
+      <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr">
@@ -12799,11 +12695,7 @@
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>effect_1</t>
-        </is>
-      </c>
+      <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
@@ -12856,7 +12748,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Amount of HP on revival: 40% -&gt; 52% -&gt; 64% -&gt; 76% -&gt; 88% (L1-5 Max)
+          <t>HP on revival: 40% -&gt; 52% -&gt; 64% -&gt; 76% -&gt; 88% (L1-5 Max)
 TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 | Speed: 1.25x | Chant: 1.3x -&gt; 1.5x</t>
         </is>
       </c>
@@ -13339,11 +13231,7 @@
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>effect_1</t>
-        </is>
-      </c>
+      <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr">
@@ -13818,7 +13706,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Critical rate: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 (L10)
+          <t>Critical rate: 10% -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28% (L10)
 Speed: 1.35x | Chant: 1.4x -&gt; 2x</t>
         </is>
       </c>
@@ -14510,30 +14398,26 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | ATK: -4% (-1%/Lv)
-Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x</t>
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max) | Accuracy: 64% (+4%/Lv)
+ATK: -4% (-1%/Lv) | Damage cap: 250 -&gt; 500 | Turns: 3 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>Damage UP; Damage cap UP</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>effect_1, effect_3</t>
-        </is>
-      </c>
-      <c r="M221" t="inlineStr"/>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Damage cap</t>
+        </is>
+      </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>Chant</t>
+          <t>Speed, Chant</t>
         </is>
       </c>
       <c r="O221" t="inlineStr"/>
@@ -14577,34 +14461,26 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% (+4%/Lv) -&gt; 80% (L5 Max) | Magic defense: -7% -&gt; -18%
-Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x</t>
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max) | Accuracy: 64% (+4%/Lv)
+Magic defense: -7% -&gt; -18% | Damage cap: 250 -&gt; 500 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>Damage UP; Damage cap UP</t>
-        </is>
-      </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>effect_1, effect_3</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Magic defense</t>
+          <t>Magic defense, Damage cap</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>Chant</t>
+          <t>Turns, Speed, Chant</t>
         </is>
       </c>
       <c r="O222" t="inlineStr"/>
@@ -14648,30 +14524,26 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% (+4%/Lv) -&gt; 80% (L5 Max) | Speed decrease: 4% (+1%/Lv)
-Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x</t>
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max) | Accuracy: 64% (+4%/Lv)
+Speed decrease: 4% (+1%/Lv) | Damage cap: 250 -&gt; 500 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>Damage UP; Damage cap UP</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>effect_1, effect_3</t>
-        </is>
-      </c>
-      <c r="M223" t="inlineStr"/>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>Damage cap</t>
+        </is>
+      </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>Chant</t>
+          <t>Turns, Speed, Chant</t>
         </is>
       </c>
       <c r="O223" t="inlineStr"/>
@@ -14715,30 +14587,26 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% (+4%/Lv) -&gt; 80% (L5 Max) | Evasion: -7% (-2%/Lv)
-Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x</t>
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max) | Accuracy: 64% (+4%/Lv)
+Evasion: -7% (-2%/Lv) | Damage cap: 250 -&gt; 500 | Turns: 3 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>Damage UP; Damage cap UP</t>
-        </is>
-      </c>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>effect_1, effect_3</t>
-        </is>
-      </c>
-      <c r="M224" t="inlineStr"/>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>Damage cap</t>
+        </is>
+      </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>Chant</t>
+          <t>Speed, Chant</t>
         </is>
       </c>
       <c r="O224" t="inlineStr"/>
@@ -14782,30 +14650,26 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: 64% -&gt; 68% -&gt; 72% -&gt; 76% -&gt; 80% (L1-5 Max) | DEF: -4% (-1%/Lv)
-Damage cap UP | Turns: 3 | TP Cost: 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 | Speed: 0.9x</t>
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max) | Accuracy: 64% (+4%/Lv)
+DEF: -4% (-1%/Lv) | Damage cap: 250 -&gt; 500 | Turns: 3 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>Damage UP; Damage cap UP</t>
-        </is>
-      </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>effect_1, effect_3</t>
-        </is>
-      </c>
-      <c r="M225" t="inlineStr"/>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Damage cap</t>
+        </is>
+      </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>Chant</t>
+          <t>Speed, Chant</t>
         </is>
       </c>
       <c r="O225" t="inlineStr"/>
@@ -15217,8 +15081,8 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>HP recovery UP | Recoverable status ailments UP | Amount of HP on revival UP
-Chant: 2.5x</t>
+          <t>HP recovery UP | Recoverable status ailments UP
+HP on revival: 10% -&gt; 15 -&gt; 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 50% | Chant: 2.5x</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -15229,12 +15093,12 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>HP recovery UP; Recoverable status ailments UP; Amount of HP on revival UP</t>
+          <t>HP recovery UP; Recoverable status ailments UP</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>effect_1, effect_2, effect_3</t>
+          <t>effect_1, effect_2</t>
         </is>
       </c>
       <c r="M232" t="inlineStr"/>
@@ -15280,30 +15144,26 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Defense decrease UP | Accuracy: 80% -&gt; 83% -&gt; 86% -&gt; 88% -&gt; 90% (L1-5 Max)
-HP recovery DOWN | Turns: 3 | TP Cost: 18 -&gt; 22 -&gt; 24 -&gt; 28 -&gt; 32 | Speed: 0.85x</t>
+          <t>DEF: -5% -&gt; -6% -&gt; -7% -&gt; -8% -&gt; -10% (L1-5 Max) | Magic defense: -10% -&gt; -15%
+Accuracy: 80% -&gt; 90% | HP recovery: 35 -&gt; 25 | Turns: 3 | TP Cost: 18 (+2-4/Lv) -&gt; 32</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>Defense decrease UP; HP recovery DOWN</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>effect_1, effect_2, effect_3</t>
-        </is>
-      </c>
-      <c r="M233" t="inlineStr"/>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Magic defense, Accuracy, HP recovery, TP Cost</t>
+        </is>
+      </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>Chant</t>
+          <t>Speed, Chant</t>
         </is>
       </c>
       <c r="O233" t="inlineStr"/>
@@ -15342,7 +15202,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Pierce to the back row with a raw magic attack and RES-based extra damage.</t>
+          <t>Pierce to the back row with a moderate raw magic attack and RES-based extra damage.</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15371,11 +15231,7 @@
       </c>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 47</t>
-        </is>
-      </c>
+      <c r="Q234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -15409,7 +15265,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Deal enormous damage to one enemy that possesses life. Low chance of instakill (12%).</t>
+          <t>Deal severe damage to one enemy that possesses life. Low chance of instakill (12%).</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15438,11 +15294,7 @@
       </c>
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr"/>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 87</t>
-        </is>
-      </c>
+      <c r="Q235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -18869,25 +18721,18 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>LvUp: Post-battle HP &amp; TP recovery UP</t>
+          <t>Post-battle HP: 6% -&gt; 7% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)
+Post-battle TP: 3% -&gt; 4% -&gt; 5% -&gt; 7% -&gt; 9%</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Unchanged</t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>Post-battle HP &amp; TP recovery UP</t>
-        </is>
-      </c>
-      <c r="L293" t="inlineStr">
-        <is>
-          <t>effect_1, effect_2</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr"/>
       <c r="N293" t="inlineStr"/>
       <c r="O293" t="inlineStr">
@@ -21074,19 +20919,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C2" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
         <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
@@ -21096,10 +20941,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -21108,7 +20953,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -21146,13 +20991,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -443,7 +443,7 @@
     <col width="87" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="47" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
@@ -699,7 +699,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Raise the party's ATK.</t>
+          <t>Raise the party's ATK (8%+).</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Increase own ATK at the price of lowering own DEF.</t>
+          <t>Increase own ATK at the price of lowering own DEF (ATK 20-50%, DEF 11-25%).</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Increase own DEF at the price of lowering own ATK.</t>
+          <t>Increase own DEF at the price of lowering own ATK (DEF 20-50%, ATK 11-25%).</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1225,7 +1225,11 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 114 characters</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1265,7 +1269,7 @@
       <c r="H12" t="inlineStr">
         <is>
           <t>ATK: 80% -&gt; 83 -&gt; 86 -&gt; 89 -&gt; 91 -&gt; 94 -&gt; 97 -&gt; 100 -&gt; 105 -&gt; 110% (L10)
-Instakill: 10% (+1-2%/Lv) -&gt; 20% | TP Cost: 38 (+4/Lv) -&gt; 74 | Speed: 0.65x -&gt; 0.75x</t>
+Instakill: 10% (+1-2%/Lv) -&gt; 20% | Power decrease: 10% | TP Cost: 38 (+4/Lv) -&gt; 74</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1281,7 +1285,11 @@
           <t>Instakill</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>Katana skill. Deal slash damage to an enemy row. May instakill.</t>
@@ -1465,7 +1473,7 @@
       <c r="H15" t="inlineStr">
         <is>
           <t>ATK: 118% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 146 -&gt; 152 -&gt; 158% (L10)
-TP Cost: 36 -&gt; 38 -&gt; 40 -&gt; 43 -&gt; 46 -&gt; 49 -&gt; 52 -&gt; 55 -&gt; 58 -&gt; 61</t>
+Critical rate: 10% | TP Cost: 36 (+2-3/Lv) -&gt; 61 | Speed: 0.7x -&gt; 0.8x</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1476,12 +1484,12 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>TP Cost</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>Katana skill. Strike 3 times against one living enemy.</t>
@@ -1669,7 +1677,7 @@
       <c r="H18" t="inlineStr">
         <is>
           <t>ATK: 130% -&gt; 144 -&gt; 157 -&gt; 170 -&gt; 182 -&gt; 194 -&gt; 204 -&gt; 212 -&gt; 220 -&gt; 228% (L10)
-Freeze: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 9 (+3/Lv) -&gt; 36 | Speed: 0.75x -&gt; 0.85x</t>
+Freeze: 20% (+3-4%/Lv) -&gt; 50% | Accuracy: +14% | TP Cost: 9 (+3/Lv) -&gt; 36</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1685,7 +1693,11 @@
           <t>Freeze</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>Short-range strike dealing mid-range water damage. May freeze.</t>
@@ -1740,8 +1752,8 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ATK: 135% -&gt; 149 -&gt; 163 -&gt; 176 -&gt; 189 -&gt; 201 -&gt; 213 -&gt; 225 -&gt; 236 -&gt; 247% (L10)
-Petrify: 20% (+1-2%/Lv) -&gt; 35% | TP Cost: 9 (+3-5/Lv) -&gt; 42 | Speed: 0.85x -&gt; 0.95x</t>
+          <t>ATK: 135% (+11-14%/Lv) -&gt; 247% | Petrify: 20% (+1-2%/Lv) -&gt; 35% | Accuracy: +10%
+TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 37 -&gt; 42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1754,10 +1766,14 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Petrify, TP Cost</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>ATK, Petrify</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>Axe skill. Strike one enemy with earth damage. May petrify.</t>
@@ -2021,7 +2037,7 @@
       <c r="H23" t="inlineStr">
         <is>
           <t>ATK: 130% -&gt; 140 -&gt; 150 -&gt; 160 -&gt; 170 -&gt; 180 -&gt; 190 -&gt; 200 -&gt; 211 -&gt; 222% (L10)
-Accuracy: +6% (+1-2%/Lv) -&gt; +20% | TP Cost: 12 (+3/Lv) -&gt; 39 | Speed: 0.8x -&gt; 0.9x</t>
+Accuracy: +6% -&gt; +20% | Damage vs. unholy: +65% | TP Cost: 12 (+3/Lv) -&gt; 39</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2037,7 +2053,11 @@
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>Sword and lance skill. Strike one enemy. Effective vs. Unholy foes.</t>
@@ -2083,7 +2103,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Shield skill. Reduce physical damage taken by the party once.</t>
+          <t>Shield skill. Reduce physical damage taken by the party once (12-30%).</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2151,7 +2171,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Shield skill. Reduce magic damage taken by the party once.</t>
+          <t>Shield skill. Reduce magic damage taken by the party once (12-30%).</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2297,7 +2317,7 @@
       <c r="H27" t="inlineStr">
         <is>
           <t>ATK: 135% -&gt; 149 -&gt; 163 -&gt; 176 -&gt; 189 -&gt; 201 -&gt; 213 -&gt; 223 -&gt; 234 -&gt; 245% (L10)
-Silence: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 7 (+3/Lv) -&gt; 34 | Speed: 0.85x -&gt; 0.95x</t>
+Silence: 20% (+3-4%/Lv) -&gt; 50% | Accuracy: +15% | TP Cost: 7 (+3/Lv) -&gt; 34</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -2313,7 +2333,11 @@
           <t>Silence</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>Lance skill. Strike one enemy with wind damage. May silence.</t>
@@ -2365,7 +2389,7 @@
       <c r="H28" t="inlineStr">
         <is>
           <t>ATK: 116% -&gt; 118 -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 146 -&gt; 152% (L10)
-TP Cost: 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 51 -&gt; 55 -&gt; 59 -&gt; 65 -&gt; 71</t>
+Heavy Lance bonus: +20% | TP Cost: 36 (+3-6/Lv) -&gt; 71 | Speed: 0.7x -&gt; 0.8x</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -2376,12 +2400,12 @@
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>TP Cost</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>Lance skill. Rapidly strike random enemies 3 to 5 times.</t>
@@ -2495,7 +2519,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Deal increased physical damage next turn.</t>
+          <t>Deal increased physical damage next turn (1.05-1.3x).</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2558,7 +2582,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Steal pocket money from an enemy.</t>
+          <t>Steal pocket money from an enemy (Steal success 40-64%).</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2621,7 +2645,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Steal an item from an enemy.</t>
+          <t>Steal an item from an enemy (Steal success 30-50%).</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2813,7 +2837,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Increase own physical evasion rate.</t>
+          <t>Increase own physical evasion rate (10%+).</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2945,7 +2969,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Increase own accuracy.</t>
+          <t>Increase own accuracy (15-30%).</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3017,7 +3041,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Increase own speed.</t>
+          <t>Increase own speed (10%+).</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3115,7 +3139,11 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 104 characters</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3494,26 +3522,18 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Damage UP
-TP Cost: 42 -&gt; 50 -&gt; 57 -&gt; 63 -&gt; 68 (L1-5 Max) | Speed: 0.4x</t>
+          <t>Damage: 3.3x -&gt; 3.45x -&gt; 3.6x -&gt; 3.8x -&gt; 4x (L1-5 Max) | ATK: 88%
+TP Cost: 42 -&gt; 50 -&gt; 57 -&gt; 63 -&gt; 68 | Speed: 0.4x</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Damage UP</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>effect_2</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4050,8 +4070,8 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ATK: 94% -&gt; 97 -&gt; 100 -&gt; 103 -&gt; 106 -&gt; 110 -&gt; 114 -&gt; 119 -&gt; 124 -&gt; 130% (L10)
-Speed decrease chance: 30% (+5%/Lv) | Turns: 4 | TP Cost: 24 (+2-3/Lv) -&gt; 50</t>
+          <t>ATK: 94% (+3-6%/Lv) -&gt; 130% | Speed decrease chance: 30% -&gt; 75% | Speed decrease: 10%
+Turns: 4 | TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -4064,7 +4084,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>TP Cost</t>
+          <t>ATK, Speed decrease chance</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4179,7 +4199,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Identify unknown items.</t>
+          <t>Identify unknown items (Identification success rate 32-80%).</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4268,7 +4288,11 @@
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 100 characters</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4307,32 +4331,28 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Damage UP | Accuracy: +10% (+2-4%/Lv) -&gt; +30%
-TP Cost: 28 -&gt; 32 -&gt; 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 56 -&gt; 60 -&gt; 64 | Speed: 0.75x</t>
+          <t>Damage: 2x -&gt; 2.2 -&gt; 2.4 -&gt; 2.6 -&gt; 2.8 -&gt; 3 -&gt; 3.25 -&gt; 3.5 -&gt; 3.75 -&gt; 4x (L10)
+Accuracy: +10% (+2-4%/Lv) -&gt; +30% | ATK: 82% | TP Cost: 28 (+4/Lv) -&gt; 64</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Damage UP</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>effect_3</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>Mace skill. Heavy bash strike with boosted accuracy.</t>
@@ -4387,7 +4407,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ATK: 135% -&gt; 147 -&gt; 159 -&gt; 171 -&gt; 183 -&gt; 193 -&gt; 203 -&gt; 213 -&gt; 220 -&gt; 225% (L10)
+          <t>ATK: 135% -&gt; 147 -&gt; 159 -&gt; 171 -&gt; 183 -&gt; 193 -&gt; 203 -&gt; 213 -&gt; 220 -&gt; 225% | DEF: -10%
 Turns: 4 | TP Cost: 25 -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 48 -&gt; 51 -&gt; 54 -&gt; 57</t>
         </is>
       </c>
@@ -4518,7 +4538,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Reduce magic damage taken for the party.</t>
+          <t>Reduce magic damage taken for the party (18-36%).</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4581,7 +4601,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Transform to increase own overall stats.</t>
+          <t>Transform to increase own overall stats (20-32%).</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4871,7 +4891,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Heal an ally's HP.</t>
+          <t>Heal an ally's HP (HP recovery 12-25%).</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4933,7 +4953,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Heal an ally's TP.</t>
+          <t>Heal an ally's TP (TP recovery 10%+).</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4996,7 +5016,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Distribute all of one's TP to the target.</t>
+          <t>Distribute all of one's TP to the target (TP transfer bonus 100-140%).</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5058,7 +5078,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Clean one's surroundings in order to increase mobility.</t>
+          <t>Clean one's surroundings in order to increase mobility (Speed increase 12%+).</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5121,7 +5141,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Recover some TP.</t>
+          <t>Recover some TP (16%+).</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5184,7 +5204,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dance skill. Lower all enemies' ATK while dance lasts.</t>
+          <t>Dance skill. Lower all enemies' ATK while dance lasts (4-16%).</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5247,7 +5267,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dance skill. Lower all enemies' DEF while dance lasts.</t>
+          <t>Dance skill. Lower all enemies' DEF while dance lasts (5-23%).</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5310,7 +5330,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dance skill. Lower all enemies' accuracy while dance lasts.</t>
+          <t>Dance skill. Lower all enemies' accuracy while dance lasts (4%+).</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5364,7 +5384,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dance skill. Lower all enemies' evasion while dance lasts.</t>
+          <t>Dance skill. Lower all enemies' evasion while dance lasts (5-23%).</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5444,7 +5464,11 @@
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 124 characters</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5477,7 +5501,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dance skill. Lower all enemies' speed while dance lasts.</t>
+          <t>Dance skill. Lower all enemies' speed while dance lasts (5%+).</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5531,7 +5555,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dance skill. Lower all enemies' elemental resistances while dance lasts.</t>
+          <t>Dance skill. Lower all enemies' elemental resistances while dance lasts (7-25%).</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5592,7 +5616,7 @@
       <c r="H78" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 145 -&gt; 150 -&gt; 155 -&gt; 160% (L10)
-TP Cost: 22 -&gt; 25 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 46 -&gt; 50</t>
+Power decrease: 10% | TP Cost: 22 (+3-4/Lv) -&gt; 50 | Speed: 0.75x -&gt; 0.85x</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -5603,12 +5627,12 @@
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>TP Cost</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>Whip skill. Deal bash damage to an enemy row from mid-range.</t>
@@ -5778,7 +5802,7 @@
       <c r="H81" t="inlineStr">
         <is>
           <t>ATK: 104% -&gt; 108 -&gt; 112 -&gt; 116 -&gt; 120 -&gt; 124 -&gt; 127 -&gt; 130 -&gt; 133 -&gt; 136% (L10)
-TP Cost: 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 56 -&gt; 60</t>
+Accuracy: +20% | TP Cost: 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 56 -&gt; 60</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -5840,7 +5864,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Take a break to heal own HP and raise Pep.</t>
+          <t>Take a break to heal own HP and raise Pep (HP recovery 20-40%).</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6076,7 +6100,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Increase own ATK at the price of lowering own DEF.</t>
+          <t>Increase own ATK at the price of lowering own DEF (ATK 15-35%, DEF 11-25%).</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6210,7 +6234,11 @@
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 94 characters</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6547,7 +6575,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Convert current DEF to bonus ATK (DEF becomes 0).</t>
+          <t>Convert current DEF to bonus ATK (DEF becomes 0) (60-150%).</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6723,7 +6751,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Summon Spartan for short-range bash damage.</t>
+          <t>Summon Spartan for short-range bash damage (Duration 3-6).</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6799,7 +6827,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Summon Oracles for mid-range INT-based damage and possible paralysis.</t>
+          <t>Summon Oracles for mid-range INT-based damage and possible paralysis (Duration 3-5).</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6862,7 +6890,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Summon Catalina to heal allies' HP.</t>
+          <t>Summon Catalina to heal allies' HP (Duration 3-5).</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6934,7 +6962,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Summon Mercidarian for random long-range stab damage to all foes.</t>
+          <t>Summon Mercidarian for random long-range stab damage to all foes (Duration 2-4).</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10849,7 +10877,7 @@
       <c r="H165" t="inlineStr">
         <is>
           <t>Pwr: 60 -&gt; 95 -&gt; 130 -&gt; 165 -&gt; 200 -&gt; 230 -&gt; 260 -&gt; 290 -&gt; 320 -&gt; 350 (L10)
-Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 9 (+1/Lv) -&gt; 18 | Speed: 2x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90% | HP Absorb: 100% | TP Cost: 9 (+1/Lv) -&gt; 18</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -10867,7 +10895,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>Chant</t>
+          <t>Speed, Chant</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -10921,7 +10949,7 @@
       <c r="H166" t="inlineStr">
         <is>
           <t>Pwr: 22 -&gt; 30 -&gt; 38 -&gt; 46 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 78 -&gt; 82 | Accuracy: 80% -&gt; 90%
-TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 | Speed: 1.75x</t>
+TP Absorb: 100% | TP Cost: 6 (+1/Lv) -&gt; 15 | Speed: 1.75x | Chant: 1.25x -&gt; 1.07x</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -10937,11 +10965,7 @@
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>Chant</t>
-        </is>
-      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr">
         <is>
           <t>Neutral magic strike to one enemy. Absorb damage dealt as TP.</t>
@@ -10987,7 +11011,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Raise max HP.</t>
+          <t>Raise max HP (20-50%).</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11060,8 +11084,8 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Pwr: 75 -&gt; 120 -&gt; 165 -&gt; 210 -&gt; 255 -&gt; 295 -&gt; 335 -&gt; 375 -&gt; 415 -&gt; 450 (L10)
-Accuracy: 65% (+2-3%/Lv) -&gt; 87% | TP Cost: 18 (+3-4/Lv) -&gt; 50 | Speed: 1.5x</t>
+          <t>Pwr: 75 (+35-45/Lv) -&gt; 450 | Accuracy: 65% (+2-3%/Lv) -&gt; 87% | HP Absorb: 100%
+TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 | Speed: 1.5x</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -11074,7 +11098,7 @@
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Accuracy, TP Cost</t>
+          <t>Pwr, Accuracy</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -11767,12 +11791,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Negate buffs for all enemies.</t>
+          <t>Negate buffs for all enemies (Accuracy 55-95%, Buff cancel rate 100%).</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Accuracy: 55% -&gt; 65% -&gt; 75% -&gt; 85% -&gt; 95% (L1-5 Max)
+          <t>Accuracy: 55% -&gt; 65% -&gt; 75% -&gt; 85% -&gt; 95% (L1-5 Max) | Buff cancel rate: 100%
 TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 18 -&gt; 22 | Speed: 1.25x | Chant: 1.25x -&gt; 1.45x</t>
         </is>
       </c>
@@ -11827,8 +11851,8 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Pwr: 250 -&gt; 300 -&gt; 350 -&gt; 400 -&gt; 440 -&gt; 480 -&gt; 520 -&gt; 560 -&gt; 600 -&gt; 640 (L10)
-Accuracy: 60% (+1-2%/Lv) -&gt; 70% | TP Cost: 45 (+4-8/Lv) -&gt; 100 | Speed: 1.75x</t>
+          <t>Pwr: 250 (+40-50/Lv) -&gt; 640 | Accuracy: 60% -&gt; 70% | Damage vs. unholy: +100%
+TP Cost: 45 -&gt; 52 -&gt; 59 -&gt; 66 -&gt; 74 -&gt; 80 -&gt; 86 -&gt; 90 -&gt; 95 -&gt; 100 | Speed: 1.75x</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -11841,7 +11865,7 @@
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Accuracy, TP Cost</t>
+          <t>Pwr, Accuracy</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -12205,7 +12229,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Raise one row of allies' resistance to stab damage.</t>
+          <t>Raise one row of allies' resistance to stab damage (20-36%).</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12273,7 +12297,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Raise one row of allies' resistance to slash damage.</t>
+          <t>Raise one row of allies' resistance to slash damage (18-36%).</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12341,7 +12365,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Raise one row of allies' resistance to bash damage.</t>
+          <t>Raise one row of allies' resistance to bash damage (18-36%).</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12409,7 +12433,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Heal an ally's HP.</t>
+          <t>Heal an ally's HP (HP recovery 8-26, Heal Cap 100-800).</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12481,7 +12505,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Heal the party's HP.</t>
+          <t>Heal the party's HP (HP recovery 5-14, Heal Cap 80-600).</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12743,7 +12767,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Revive a dead ally.</t>
+          <t>Revive a dead ally (HP on revival 40-88%).</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12807,7 +12831,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Raise an ally's ATK.</t>
+          <t>Raise an ally's ATK (10-22%).</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12875,7 +12899,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Raise an ally's DEF.</t>
+          <t>Raise an ally's DEF (10-25%).</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12943,7 +12967,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Raise the party's magic defense.</t>
+          <t>Raise the party's magic defense (10%+).</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13011,7 +13035,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Raise the party's resistance to fire, water, lightning, wind, and earth.</t>
+          <t>Raise the party's resistance to fire, water, lightning, wind, and earth (5-25%).</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13079,7 +13103,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Raise an ally's speed.</t>
+          <t>Raise an ally's speed (8%+).</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13147,7 +13171,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Raise an ally's max HP.</t>
+          <t>Raise an ally's max HP (20-47%).</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13343,7 +13367,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Reduce incoming physical damage by a certain amount.</t>
+          <t>Reduce incoming physical damage by a certain amount (30-45%).</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13407,7 +13431,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>While active, immediately revive upon death.</t>
+          <t>While active, immediately revive upon death (Amount of HP on revival 10-50%).</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13701,7 +13725,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Raise the party's critical rate while song lasts.</t>
+          <t>Raise the party's critical rate while song lasts (10-28%).</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13755,7 +13779,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Raise the party's magic attack power while song lasts.</t>
+          <t>Raise the party's magic attack power while song lasts (10%+).</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13809,7 +13833,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Raise the party's magic defense power while song lasts.</t>
+          <t>Raise the party's magic defense power while song lasts (10%+).</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13863,7 +13887,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Decrease the party's chant time while song lasts.</t>
+          <t>Decrease the party's chant time while song lasts (10%+).</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13917,7 +13941,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Gradually heal the party's HP while song lasts.</t>
+          <t>Gradually heal the party's HP while song lasts (HP recovery 20-250).</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13980,7 +14004,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Gradually heal the party's TP while song lasts.</t>
+          <t>Gradually heal the party's TP while song lasts (TP recovery 4-30).</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -14043,7 +14067,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Raise the party's speed while song lasts.</t>
+          <t>Raise the party's speed while song lasts (6%+).</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14106,7 +14130,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Raise the party's acquired EXP while song lasts.</t>
+          <t>Raise the party's acquired EXP while song lasts (16%+).</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14169,7 +14193,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Raise the party's magic accuracy while song lasts.</t>
+          <t>Raise the party's magic accuracy while song lasts (6%+).</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14224,7 +14248,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Dodge enemy attacks by creating a shadow clone.</t>
+          <t>Dodge enemy attacks by creating a shadow clone (Number of dodges 1-5).</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14304,7 +14328,11 @@
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 95 characters</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -14338,7 +14366,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lower all enemies' accuracy.</t>
+          <t>Lower all enemies' accuracy (10%+).</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14422,7 +14450,11 @@
       </c>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 137 characters</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -14485,7 +14517,11 @@
       </c>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 157 characters</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -14548,7 +14584,11 @@
       </c>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 155 characters</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -14611,7 +14651,11 @@
       </c>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 145 characters</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -14674,7 +14718,11 @@
       </c>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 138 characters</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -14830,7 +14878,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Raise the party's ATK.</t>
+          <t>Raise the party's ATK (8%+).</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14898,7 +14946,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Raise the party's DEF.</t>
+          <t>Raise the party's DEF (8%+).</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14966,7 +15014,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Create a field that reduces damage for both sides for a time.</t>
+          <t>Create a field that reduces damage for both sides for a time (25%+).</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -15081,31 +15129,35 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>HP recovery UP | Recoverable status ailments UP
-HP on revival: 10% -&gt; 15 -&gt; 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 50% | Chant: 2.5x</t>
+          <t>HP recovery: 22 -&gt; 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 (L8)
+Recoverable status ailments: 1 (+1/Lv) | HP on revival: 10% (+5-10%/Lv) -&gt; 50%</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>HP recovery UP; Recoverable status ailments UP</t>
-        </is>
-      </c>
-      <c r="L232" t="inlineStr">
-        <is>
-          <t>effect_1, effect_2</t>
-        </is>
-      </c>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>HP on revival</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Chant</t>
+        </is>
+      </c>
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 164 characters</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -15168,7 +15220,11 @@
       </c>
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 126 characters</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -15729,7 +15785,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>ATK bonus with sword equipped.</t>
+          <t>ATK bonus with sword equipped (3-15%).</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15791,7 +15847,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>ATK bonus with axe equipped.</t>
+          <t>ATK bonus with axe equipped (3-15%).</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15853,7 +15909,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>ATK bonus with dagger equipped.</t>
+          <t>ATK bonus with dagger equipped (3-17%).</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15915,7 +15971,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>ATK bonus with mace equipped.</t>
+          <t>ATK bonus with mace equipped (3-15%).</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15977,7 +16033,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>ATK bonus with lance equipped.</t>
+          <t>ATK bonus with lance equipped (3-15%).</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16039,7 +16095,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>ATK bonus with bow equipped.</t>
+          <t>ATK bonus with bow equipped (3-15%).</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16101,7 +16157,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>ATK bonus with katana equipped.</t>
+          <t>ATK bonus with katana equipped (3-15%).</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16163,7 +16219,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>ATK bonus with projectile weapon equipped.</t>
+          <t>ATK bonus with projectile weapon equipped (5-20%).</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16225,7 +16281,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>ATK bonus with whip equipped.</t>
+          <t>ATK bonus with whip equipped (3-17%).</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16287,7 +16343,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>ATK bonus with fan equipped.</t>
+          <t>ATK bonus with fan equipped (5-20%).</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16349,7 +16405,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>ATK bonus for all weapons.</t>
+          <t>ATK bonus for all weapons (2%+).</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16411,7 +16467,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Magic attack power bonus.</t>
+          <t>Magic attack power bonus (6%+).</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16473,30 +16529,23 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Healing magic bonus. Raises healing cap.</t>
+          <t>Healing magic bonus. Raises healing cap (HP recovery bonus 8-26%, Heal Cap 10-100%).</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>LvUp: HP recovery bonus UP Recovery cap UP</t>
+          <t>HP recovery bonus: 8% -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26% (L10)
+Heal Cap: +10% -&gt; +20 -&gt; +30 -&gt; +40 -&gt; +50 -&gt; +60 -&gt; +70 -&gt; +80 -&gt; +90 -&gt; +100%</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Unchanged</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>HP recovery bonus UP; Recovery cap UP</t>
-        </is>
-      </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t>effect_1, effect_2</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
       <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr">
@@ -16543,7 +16592,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Recover HP every turn during battle.</t>
+          <t>Recover HP every turn during battle (2%+).</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16605,7 +16654,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Slightly recover HP every turn during battle.</t>
+          <t>Slightly recover HP every turn during battle (1%+).</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16667,7 +16716,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Recover TP every turn during battle.</t>
+          <t>Recover TP every turn during battle (3-16).</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16729,7 +16778,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Slightly recover TP every turn during battle.</t>
+          <t>Slightly recover TP every turn during battle (1-9).</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16791,7 +16840,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Raise resistance to all elements.</t>
+          <t>Raise resistance to all elements (6%+).</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16853,7 +16902,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Occasionally counterattack after receiving physical damage.</t>
+          <t>Occasionally counterattack after receiving physical damage (6-18%).</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16915,7 +16964,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Occasionally parry and counterattack when targeted by an enemy.</t>
+          <t>Occasionally parry and counterattack when targeted by an enemy (Activation rate 4%+).</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16977,7 +17026,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Occasionally attack twice when attacking normally.</t>
+          <t>Occasionally attack twice when attacking normally (Double attack rate 9-21%).</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17039,7 +17088,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Occasionally attack thrice when attacking normally.</t>
+          <t>Occasionally attack thrice when attacking normally (Triple attack rate 5-17%).</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17101,7 +17150,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Increase evasion rate against stab attacks.</t>
+          <t>Increase evasion rate against stab attacks (20-36%).</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17154,7 +17203,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Occasionally parry when receiving long-range attacks.</t>
+          <t>Occasionally parry when receiving long-range attacks (Activation rate 10-30%).</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17207,7 +17256,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Occasionally survive at 1 HP after being dealt fatal damage.</t>
+          <t>Occasionally survive at 1 HP after being dealt fatal damage (10-30%).</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17269,7 +17318,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Occasionally Defend automatically when receiving physical attacks.</t>
+          <t>Occasionally Defend automatically when receiving physical attacks (4%+).</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17331,7 +17380,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Can equip two one-handed weapons at the same time.</t>
+          <t>Can equip two one-handed weapons at the same time (Sub-weapon ATK 30-72%).</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17393,7 +17442,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Convert some received damage to TP.</t>
+          <t>Convert some received damage to TP (4-20%).</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17446,7 +17495,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Occasionally instakill when inflicting a critical hit.</t>
+          <t>Occasionally instakill when inflicting a critical hit (Activation rate 8-20%).</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17499,7 +17548,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>With bow equipped, occasionally halt an enemy's action.</t>
+          <t>With bow equipped, occasionally halt an enemy's action (Activation rate 2%+).</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17572,7 +17621,11 @@
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr"/>
-      <c r="Q273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 90 characters</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -17605,7 +17658,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Gain increased speed based on missing HP.</t>
+          <t>Gain increased speed based on missing HP (15%+).</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17658,7 +17711,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Debuff an enemy when they inflict short-range damage.</t>
+          <t>Debuff an enemy when they inflict short-range damage (1-6).</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17711,7 +17764,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Increase ATK while inflicted with status ailments.</t>
+          <t>Increase ATK while inflicted with status ailments (15-27%).</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17854,7 +17907,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Decrease physical damage to the back row when using a shield in the front row.</t>
+          <t>Decrease physical damage to the back row when using a shield in the front row (6%+).</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17907,7 +17960,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Occasionally nullify physical damage.</t>
+          <t>Occasionally nullify physical damage (Activation rate 8%+).</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17984,11 +18037,7 @@
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>effect_1</t>
-        </is>
-      </c>
+      <c r="L281" t="inlineStr"/>
       <c r="M281" t="inlineStr"/>
       <c r="N281" t="inlineStr"/>
       <c r="O281" t="inlineStr">
@@ -18035,7 +18084,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Briefly increase ATK and DEX when HP drops below 50%.</t>
+          <t>Briefly increase ATK and DEX when HP drops below 50% (10%+).</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18097,7 +18146,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Make it harder for chants, songs, and dances to be interrupted.</t>
+          <t>Make it harder for chants, songs, and dances to be interrupted (10-50%).</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18158,7 +18207,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Reduce chant time.</t>
+          <t>Reduce chant time (8-20%).</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18220,7 +18269,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Reduce TP Cost in battle.</t>
+          <t>Reduce TP Cost in battle (10-30%).</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18282,7 +18331,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Heighten magic accuracy.</t>
+          <t>Heighten magic accuracy (3%+).</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18344,7 +18393,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Limit enemies' preemptive attacks.</t>
+          <t>Limit enemies' preemptive attacks (Enemy preemptive attack rate 20-50%).</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18406,7 +18455,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Increase party's preemptive attack rate.</t>
+          <t>Increase party's preemptive attack rate (8-20%).</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18468,7 +18517,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>May escape from battle more easily.</t>
+          <t>May escape from battle more easily (20-40%).</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18530,7 +18579,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Increase the enemies' item drop rate.</t>
+          <t>Increase the enemies' item drop rate (4%+).</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18592,7 +18641,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Increase the amount of money the enemies drop.</t>
+          <t>Increase the amount of money the enemies drop (Gold drop rate 25-125%).</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18654,7 +18703,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Sometimes pick up items while moving around the dungeons.</t>
+          <t>Sometimes pick up items while moving around the dungeons (Found item quality 1-5).</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18746,7 +18795,11 @@
 Restores whole party after combat conclusion</t>
         </is>
       </c>
-      <c r="Q293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>values left out: the sentence would be 95 characters</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -18779,7 +18832,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Occasionally keep disposable items after using them in battle.</t>
+          <t>Occasionally keep disposable items after using them in battle (25%+).</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18841,7 +18894,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Increase the effects of HP and TP recovery items during battle.</t>
+          <t>Increase the effects of HP and TP recovery items during battle (10-100%).</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18903,7 +18956,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Become capable of performing two songs at once.</t>
+          <t>Become capable of performing two songs at once (Speed 6-18%).</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18965,7 +19018,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Become capable of performing two dances at once.</t>
+          <t>Become capable of performing two dances at once (Speed 6-18%).</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19027,7 +19080,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Become capable of controlling two dolls at once.</t>
+          <t>Become capable of controlling two dolls at once (Speed 6-18%).</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19089,7 +19142,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Increase doll power with the strength of the equipped Sealbook.</t>
+          <t>Increase doll power with the strength of the equipped Sealbook (15-27%).</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19151,7 +19204,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Increased effects for all maid skills.</t>
+          <t>Increased effects for all maid skills (1%+).</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19213,7 +19266,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Increased effects for all songs.</t>
+          <t>Increased effects for all songs (Singing skill bonus 3%+).</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19275,7 +19328,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Increased effects for all dances.</t>
+          <t>Increased effects for all dances (Dancing skill bonus 3%+).</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -19337,7 +19390,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Increased effects for all doll skills.</t>
+          <t>Increased effects for all doll skills (3%+).</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -19399,7 +19452,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Occasionally attack twice when attacking normally.</t>
+          <t>Occasionally attack twice when attacking normally (Double attack rate 20-32%).</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19461,7 +19514,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Reduce chant time for songs.</t>
+          <t>Reduce chant time for songs (10%+).</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19523,7 +19576,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Reduce purchase and identification prices at shops.</t>
+          <t>Reduce purchase and identification prices at shops (Negotiation rate 10-25%).</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19585,7 +19638,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Mesmerize enemies, causing them to occasionally do nothing.</t>
+          <t>Mesmerize enemies, causing them to occasionally do nothing (Occurrence rate 3%+).</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20919,19 +20972,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E2" t="n">
         <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3">
@@ -20941,10 +20994,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -20953,7 +21006,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -20991,13 +21044,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -449,7 +449,7 @@
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="84" customWidth="1" min="15" max="15"/>
     <col width="86" customWidth="1" min="16" max="16"/>
-    <col width="90" customWidth="1" min="17" max="17"/>
+    <col width="67" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Raise own critical rate, but also own vulnerability to critical hits.</t>
+          <t>Raise own critical rate (5%+), but also own vulnerability to critical hits (4%+).</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1225,11 +1225,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 114 characters</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1671,7 +1667,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Short-range skill. Deal severe mid-range water damage to one enemy. May freeze.</t>
+          <t>Short-range skill. Severe mid-range water damage to one enemy. May freeze (20-50%).</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1709,11 +1705,7 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>chance left out: the sentence would be 88 characters</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1819,7 +1811,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Axe skill. Attack an enemy, then the next immediate enemy in the turn order.</t>
+          <t>Axe skill. Deal major damage to an enemy, then the next one in the turn order.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1857,11 +1849,7 @@
 TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28 | Hits 2 sequential turn targets</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>damage is major but the sentence would be 90 characters</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2239,7 +2227,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Short-range skill. Deal minor lightning damage to an enemy row. May paralyze.</t>
+          <t>Short-range skill. Minor lightning damage to an enemy row. May paralyze (20-40%).</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2273,11 +2261,7 @@
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>chance left out: the sentence would be 86 characters</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3105,7 +3089,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Increase own physical evasion rate and magical evasion rate.</t>
+          <t>Increase own physical evasion rate (15%+) and magical evasion rate (10%+).</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3139,11 +3123,7 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 104 characters</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3381,7 +3361,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bow/gun skill. Attack one enemy multiple times with escalating crit rate.</t>
+          <t>Bow/gun skill. Deal minor damage to one enemy multiple times with rising crit rate.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3415,11 +3395,7 @@
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>damage is minor but the sentence would be 87 characters</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3517,7 +3493,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bow skill. Shoot a powerful single shot at one enemy for stab damage.</t>
+          <t>Bow skill. Shoot a tremendous single shot at one enemy for stab damage.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3547,11 +3523,7 @@
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 73</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4263,7 +4235,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Briefly sacrifice magic accuracy to increase magic damage.</t>
+          <t>Briefly sacrifice magic accuracy (2%+) to increase magic damage (38-60%).</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4288,11 +4260,7 @@
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 100 characters</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4326,7 +4294,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Mace skill. Deal bash damage with an inexorable thud.</t>
+          <t>Mace skill. Deal tremendous bash damage with an inexorable thud.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4364,11 +4332,7 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 73</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5439,7 +5403,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dance skill. Damage all enemies at the start of user's turn while dance lasts.</t>
+          <t>Dance skill. Damage all enemies at the start of user's turn (max HP 3%+).</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5464,11 +5428,7 @@
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 124 characters</t>
-        </is>
-      </c>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5733,7 +5693,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Whip skill. Deal moderate bash damage to one enemy twice. May silence/paralyze.</t>
+          <t>Whip skill. Deal moderate bash damage twice. May silence (25-37%)/paralyze (20-32%).</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5758,11 +5718,7 @@
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>chance not stated: the ailments of this sentence have different chances, or one always happens</t>
-        </is>
-      </c>
+      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6213,7 +6169,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Turn a weakened enemy into food. Ineffective against some enemies.</t>
+          <t>Turn a weakened enemy into food (35-65%). Ineffective against some enemies.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6234,11 +6190,7 @@
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 94 characters</t>
-        </is>
-      </c>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6272,7 +6224,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Deal moderate non-elemental damage to all enemies with a storm of roses. May poison.</t>
+          <t>Storm of roses: moderate non-elemental damage to all enemies. May poison (50-80%).</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6297,11 +6249,7 @@
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>chance left out: the sentence would be 93 characters</t>
-        </is>
-      </c>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6453,7 +6401,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Short-range skill. Pierce through to the back row with major stab damage. May slow.</t>
+          <t>Short-range skill. Pierce to the back row with major stab damage. May slow (25-45%).</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6478,11 +6426,7 @@
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>chance left out: the sentence would be 92 characters</t>
-        </is>
-      </c>
+      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6684,7 +6628,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Whip skill. Attack one enemy 1-3 times from mid-range. Crits against Beasts.</t>
+          <t>Whip skill. Deal moderate damage to one enemy 1-3 times, mid-range. Crits on Beasts.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6713,11 +6657,7 @@
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>damage is moderate but the sentence would be 93 characters</t>
-        </is>
-      </c>
+      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -14307,7 +14247,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Disable skill usage for an enemy row. Level must exceed the target's.</t>
+          <t>Disable skill usage for an enemy row (30%+). Level must exceed the target's.</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14328,11 +14268,7 @@
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 95 characters</t>
-        </is>
-      </c>
+      <c r="Q219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -14421,7 +14357,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Deal fire damage based on enemy's max HP and lower ATK to an enemy row.</t>
+          <t>Deal fire damage based on enemy's max HP (4%+) and lower ATK (4%+) to an enemy row.</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14450,11 +14386,7 @@
       </c>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 137 characters</t>
-        </is>
-      </c>
+      <c r="Q221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -14488,7 +14420,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Deal water damage based on enemy's max HP and lower magic def. to an enemy row.</t>
+          <t>Water damage by max HP (4%+) and lower magic def. (7-18%) to an enemy row.</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14517,11 +14449,7 @@
       </c>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 157 characters</t>
-        </is>
-      </c>
+      <c r="Q222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -14555,7 +14483,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Deal lightning damage based on enemy's max HP and lower speed to an enemy row.</t>
+          <t>Lightning damage by max HP (4%+) and lower speed (4%+) to an enemy row.</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14584,11 +14512,7 @@
       </c>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 155 characters</t>
-        </is>
-      </c>
+      <c r="Q223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -14622,7 +14546,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Deal wind damage based on enemy's max HP and lower evasion to an enemy row.</t>
+          <t>Deal wind damage based on enemy's max HP (4%+) and lower evasion (7%+) to a row.</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14651,11 +14575,7 @@
       </c>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 145 characters</t>
-        </is>
-      </c>
+      <c r="Q224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -14689,7 +14609,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Deal earth damage based on enemy's max HP and lower DEF to an enemy row.</t>
+          <t>Deal earth damage based on enemy's max HP (4%+) and lower DEF (4%+) to an enemy row.</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14718,11 +14638,7 @@
       </c>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 138 characters</t>
-        </is>
-      </c>
+      <c r="Q225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -15124,7 +15040,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Sacrifice yourself to revive, heal, and recover status effects for the rest of the party.</t>
+          <t>Sacrifice yourself to revive (HP 10-50%), heal, and cure the rest of the party.</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15153,11 +15069,7 @@
       </c>
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 164 characters</t>
-        </is>
-      </c>
+      <c r="Q232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -15191,7 +15103,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Heal an enemy's HP to decrease its physical and magic defense.</t>
+          <t>Heal an enemy's HP to decrease its physical (5%+) and magic defense (10%+).</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15220,11 +15132,7 @@
       </c>
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 126 characters</t>
-        </is>
-      </c>
+      <c r="Q233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -17601,7 +17509,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>With bow equipped, occasionally attack again after an ally's attack.</t>
+          <t>With bow equipped, occasionally (4%+) attack again after an ally's attack.</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17621,11 +17529,7 @@
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr"/>
-      <c r="Q273" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 90 characters</t>
-        </is>
-      </c>
+      <c r="Q273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -18765,7 +18669,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Party's HP and TP is restored slightly after a battle.</t>
+          <t>Party's HP (6%+) and TP (3%+) is restored slightly after a battle.</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18795,11 +18699,7 @@
 Restores whole party after combat conclusion</t>
         </is>
       </c>
-      <c r="Q293" t="inlineStr">
-        <is>
-          <t>values left out: the sentence would be 95 characters</t>
-        </is>
-      </c>
+      <c r="Q293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Raise the party's ATK (8%+).</t>
+          <t>Raise the party's ATK.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Increase own ATK at the price of lowering own DEF (ATK 20-50%, DEF 11-25%).</t>
+          <t>Increase own ATK at the price of lowering own DEF.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Increase own DEF at the price of lowering own ATK (DEF 20-50%, ATK 11-25%).</t>
+          <t>Increase own DEF at the price of lowering own ATK.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Katana skill. Deal moderate bash damage to one enemy. May paralyze (20-50%).</t>
+          <t>Katana skill. Moderate bash damage to an enemy. May paralyze (20-50%).</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Raise own critical rate (5%+), but also own vulnerability to critical hits (4%+).</t>
+          <t>Raise own critical rate, but also own vulnerability to critical hits.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Katana skill. Deal minor slash damage to an enemy row. May instakill (10%+).</t>
+          <t>Katana skill. Minor slash damage to a row. May instakill (10%+).</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Katana skill. Deal minor defense-piercing damage and DEF down to one enemy.</t>
+          <t>Katana skill. Minor defense-piercing damage and DEF down to one enemy.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Katana skill. Deal moderate slash damage 3 times to one enemy. Living targets only.</t>
+          <t>Katana skill. Moderate slash damage 3 times to a living enemy.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Short-range skill. Severe mid-range water damage to one enemy. May freeze (20-50%).</t>
+          <t>Short-range skill. Severe mid-range water damage. May freeze (20-50%).</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Axe skill. Deal severe earth damage to one enemy. May petrify (20-35%).</t>
+          <t>Axe skill. Severe earth damage to an enemy. May petrify (20-35%).</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Axe skill. Deal major damage to an enemy, then the next one in the turn order.</t>
+          <t>Axe skill. Deal major damage to an enemy, then the next in turn order.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sword/lance skill. Deal severe damage to one enemy (effective vs. unholy monsters).</t>
+          <t>Sword/lance skill. Deal severe damage to an enemy (strong vs. unholy).</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Shield skill. Reduce physical damage taken by the party once (12-30%).</t>
+          <t>Shield skill. Reduce physical damage taken by the party once.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Shield skill. Reduce magic damage taken by the party once (12-30%).</t>
+          <t>Shield skill. Reduce magic damage taken by the party once.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Short-range skill. Minor lightning damage to an enemy row. May paralyze (20-40%).</t>
+          <t>Short-range. Minor lightning damage to a row. May paralyze (20-40%).</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lance skill. Deal severe wind damage to one enemy. May silence (20-50%).</t>
+          <t>Lance skill. Severe wind damage to an enemy. May silence (20-50%).</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lance skill. 3-5 moderate hits on random enemies. Stronger with a Heavy Lance.</t>
+          <t>Lance skill. 3-5 moderate hits on random enemies. Heavy Lance bonus.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Deal increased physical damage next turn (1.05-1.3x).</t>
+          <t>Deal increased physical damage next turn.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Steal pocket money from an enemy (Steal success 40-64%).</t>
+          <t>Steal pocket money from an enemy.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Steal an item from an enemy (Steal success 30-50%).</t>
+          <t>Steal an item from an enemy.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dagger skill. Inflict severe stab damage relative to enemy's total buffs and debuffs.</t>
+          <t>Dagger skill. Severe stab damage based on enemy buffs and debuffs.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Increase own physical evasion rate (10%+).</t>
+          <t>Increase own physical evasion rate.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Increase own accuracy (15-30%).</t>
+          <t>Increase own accuracy.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Increase own speed (10%+).</t>
+          <t>Increase own speed.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Increase own physical evasion rate (15%+) and magical evasion rate (10%+).</t>
+          <t>Increase own physical evasion rate and magical evasion rate.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Short-range skill. Deal moderate damage to one enemy. May cause sleep (20-50%).</t>
+          <t>Short-range: moderate damage to an enemy. May cause sleep (20-50%).</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Short-range skill. Deal moderate damage to one enemy. May silence (20-50%).</t>
+          <t>Short-range: moderate damage to an enemy. May silence (20-50%).</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Short-range skill. Deal moderate damage to one enemy. May stun (20-50%).</t>
+          <t>Short-range: moderate damage to an enemy. May stun (20-50%).</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bow/gun skill. Deal minor damage to one enemy multiple times with rising crit rate.</t>
+          <t>Bow/gun skill. Multiple minor hits on an enemy, crit rate rising.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bow/gun skill. Fire a single shot certain to hit one enemy for minor damage.</t>
+          <t>Bow/gun skill. A single minor shot certain to hit one enemy.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bow skill. Shoot a tremendous single shot at one enemy for stab damage.</t>
+          <t>Bow skill. Shoot a tremendous single shot at an enemy for stab damage.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bow skill. Deal moderate stab damage to one enemy. May freeze (20-50%).</t>
+          <t>Bow skill. Moderate stab damage to an enemy. May freeze (20-50%).</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bow skill. Deal moderate stab damage to one enemy. May paralyze (20-50%).</t>
+          <t>Bow skill. Moderate stab damage to an enemy. May paralyze (20-50%).</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bow skill. Shoot a barrage of arrows that rains minor damage upon all enemies.</t>
+          <t>Bow skill. A barrage of arrows rains minor damage upon all enemies.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bow skill. Deal severe stab damage to one enemy and pierce to the back row.</t>
+          <t>Bow skill. Severe stab damage to an enemy, piercing to the back row.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Projectile skill. Deal minor damage and decrease speed for an enemy row.</t>
+          <t>Projectile skill. Deal minor damage and lower speed for an enemy row.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Identify unknown items (Identification success rate 32-80%).</t>
+          <t>Identify unknown items.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Briefly sacrifice magic accuracy (2%+) to increase magic damage (38-60%).</t>
+          <t>Briefly sacrifice magic accuracy to increase magic damage.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Reduce magic damage taken for the party (18-36%).</t>
+          <t>Reduce magic damage taken for the party.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Transform to increase own overall stats (20-32%).</t>
+          <t>Transform to increase own overall stats.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tome skill. Severe RES-based bash damage to one enemy. May freeze/silence (20-50%).</t>
+          <t>Tome skill. Severe RES-based bash damage. May freeze/silence (20-50%).</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4806,7 +4806,7 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Detect how many unopened treasure chests are left on the current floor.</t>
+          <t>Detect how many unopened treasure chests are left on this floor.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Heal an ally's HP (HP recovery 12-25%).</t>
+          <t>Heal an ally's HP.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Heal an ally's TP (TP recovery 10%+).</t>
+          <t>Heal an ally's TP.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Distribute all of one's TP to the target (TP transfer bonus 100-140%).</t>
+          <t>Distribute all of one's TP to the target.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Clean one's surroundings in order to increase mobility (Speed increase 12%+).</t>
+          <t>Clean one's surroundings in order to increase mobility.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Recover some TP (16%+).</t>
+          <t>Recover some TP.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dance skill. Lower all enemies' ATK while dance lasts (4-16%).</t>
+          <t>Dance skill. Lower all enemies' ATK while dance lasts.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dance skill. Lower all enemies' DEF while dance lasts (5-23%).</t>
+          <t>Dance skill. Lower all enemies' DEF while dance lasts.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dance skill. Lower all enemies' accuracy while dance lasts (4%+).</t>
+          <t>Dance skill. Lower all enemies' accuracy while dance lasts.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dance skill. Lower all enemies' evasion while dance lasts (5-23%).</t>
+          <t>Dance skill. Lower all enemies' evasion while dance lasts.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dance skill. Damage all enemies at the start of user's turn (max HP 3%+).</t>
+          <t>Dance skill. Damage all enemies at the start of each of your turns.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dance skill. Lower all enemies' speed while dance lasts (5%+).</t>
+          <t>Dance skill. Lower all enemies' speed while dance lasts.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dance skill. Lower all enemies' elemental resistances while dance lasts (7-25%).</t>
+          <t>Dance skill. Lower all enemies' elemental resistances while dancing.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Whip skill. Deal moderate bash damage twice. May silence (25-37%)/paralyze (20-32%).</t>
+          <t>Whip: moderate bash damage twice. Silence (25-37%), paralyze (20-32%).</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Take a break to heal own HP and raise Pep (HP recovery 20-40%).</t>
+          <t>Take a break to heal own HP and raise Pep.</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>50/50 chance of minor non-elemental damage to each enemy. May stun (40-70%).</t>
+          <t>50/50: minor non-elemental damage to each enemy. May stun (40-70%).</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Increase own ATK at the price of lowering own DEF (ATK 15-35%, DEF 11-25%).</t>
+          <t>Increase own ATK at the price of lowering own DEF.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Turn a weakened enemy into food (35-65%). Ineffective against some enemies.</t>
+          <t>Turn a weakened enemy into food. Ineffective against some enemies.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Storm of roses: moderate non-elemental damage to all enemies. May poison (50-80%).</t>
+          <t>Rose storm: moderate non-elemental damage to all. May poison (50-80%).</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fan skill. Deal severe bashing damage to one enemy. May delay enemy turn (25-43%).</t>
+          <t>Fan skill. Severe bashing damage. May delay enemy turn (25-43%).</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6346,7 +6346,7 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fan skill. With increased ATK, deal minor long-range damage to one enemy.</t>
+          <t>Fan skill. With raised ATK, deal minor long-range damage to an enemy.</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Short-range skill. Pierce to the back row with major stab damage. May slow (25-45%).</t>
+          <t>Short-range. Major stab damage through to back row. May slow (25-45%).</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Short-range skill. Deal minor damage to one enemy and reduce target's max HP.</t>
+          <t>Short-range. Deal minor damage to an enemy and reduce its max HP.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Convert current DEF to bonus ATK (DEF becomes 0) (60-150%).</t>
+          <t>Convert current DEF to bonus ATK (DEF becomes 0).</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Whip skill. Deal moderate damage to one enemy 1-3 times, mid-range. Crits on Beasts.</t>
+          <t>Whip skill. 1-3 moderate hits on an enemy, mid-range. Crits on Beasts.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Summon Spartan for short-range bash damage (Duration 3-6).</t>
+          <t>Summon Spartan for short-range bash damage.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Summon Oracles for mid-range INT-based damage and possible paralysis (Duration 3-5).</t>
+          <t>Summon Oracles for mid-range INT-based damage and possible paralysis.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Summon Catalina to heal allies' HP (Duration 3-5).</t>
+          <t>Summon Catalina to heal allies' HP.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Summon Mercidarian for random long-range stab damage to all foes (Duration 2-4).</t>
+          <t>Summon Mercidarian for random long-range stab damage to all foes.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Raise max HP (20-50%).</t>
+          <t>Raise max HP.</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Negate buffs for all enemies (Accuracy 55-95%, Buff cancel rate 100%).</t>
+          <t>Negate buffs for all enemies.</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Deal major non-elemental damage to all enemies (effective vs. unholy monsters).</t>
+          <t>Major non-elemental damage to all enemies (strong vs. unholy).</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Raise one row of allies' resistance to stab damage (20-36%).</t>
+          <t>Raise one row of allies' resistance to stab damage.</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Raise one row of allies' resistance to slash damage (18-36%).</t>
+          <t>Raise one row of allies' resistance to slash damage.</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Raise one row of allies' resistance to bash damage (18-36%).</t>
+          <t>Raise one row of allies' resistance to bash damage.</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Heal an ally's HP (HP recovery 8-26, Heal Cap 100-800).</t>
+          <t>Heal an ally's HP.</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Heal the party's HP (HP recovery 5-14, Heal Cap 80-600).</t>
+          <t>Heal the party's HP.</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Revive a dead ally (HP on revival 40-88%).</t>
+          <t>Revive a dead ally.</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Raise an ally's ATK (10-22%).</t>
+          <t>Raise an ally's ATK.</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Raise an ally's DEF (10-25%).</t>
+          <t>Raise an ally's DEF.</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12907,7 +12907,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Raise the party's magic defense (10%+).</t>
+          <t>Raise the party's magic defense.</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Raise the party's resistance to fire, water, lightning, wind, and earth (5-25%).</t>
+          <t>Raise party resistance to fire, water, lightning, wind, and earth.</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Raise an ally's speed (8%+).</t>
+          <t>Raise an ally's speed.</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Raise an ally's max HP (20-47%).</t>
+          <t>Raise an ally's max HP.</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Reduce incoming physical damage by a certain amount (30-45%).</t>
+          <t>Reduce incoming physical damage by a certain amount.</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>While active, immediately revive upon death (Amount of HP on revival 10-50%).</t>
+          <t>While active, immediately revive upon death.</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Raise the party's critical rate while song lasts (10-28%).</t>
+          <t>Raise the party's critical rate while song lasts.</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Raise the party's magic attack power while song lasts (10%+).</t>
+          <t>Raise the party's magic attack power while song lasts.</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Raise the party's magic defense power while song lasts (10%+).</t>
+          <t>Raise the party's magic defense power while song lasts.</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Decrease the party's chant time while song lasts (10%+).</t>
+          <t>Decrease the party's chant time while song lasts.</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13881,7 +13881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Gradually heal the party's HP while song lasts (HP recovery 20-250).</t>
+          <t>Gradually heal the party's HP while song lasts.</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Gradually heal the party's TP while song lasts (TP recovery 4-30).</t>
+          <t>Gradually heal the party's TP while song lasts.</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Raise the party's speed while song lasts (6%+).</t>
+          <t>Raise the party's speed while song lasts.</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Raise the party's acquired EXP while song lasts (16%+).</t>
+          <t>Raise the party's acquired EXP while song lasts.</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Raise the party's magic accuracy while song lasts (6%+).</t>
+          <t>Raise the party's magic accuracy while song lasts.</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Dodge enemy attacks by creating a shadow clone (Number of dodges 1-5).</t>
+          <t>Dodge enemy attacks by creating a shadow clone.</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Disable skill usage for an enemy row (30%+). Level must exceed the target's.</t>
+          <t>Disable skill usage for an enemy row. Level must exceed the target's.</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lower all enemies' accuracy (10%+).</t>
+          <t>Lower all enemies' accuracy.</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Deal fire damage based on enemy's max HP (4%+) and lower ATK (4%+) to an enemy row.</t>
+          <t>Fire damage by enemy max HP and lower ATK to an enemy row.</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Water damage by max HP (4%+) and lower magic def. (7-18%) to an enemy row.</t>
+          <t>Water damage by enemy max HP and lower magic def. to an enemy row.</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Lightning damage by max HP (4%+) and lower speed (4%+) to an enemy row.</t>
+          <t>Lightning damage by enemy max HP and lower speed to an enemy row.</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Deal wind damage based on enemy's max HP (4%+) and lower evasion (7%+) to a row.</t>
+          <t>Wind damage by enemy max HP and lower evasion to an enemy row.</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Deal earth damage based on enemy's max HP (4%+) and lower DEF (4%+) to an enemy row.</t>
+          <t>Earth damage by enemy max HP and lower DEF to an enemy row.</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Raise the party's ATK (8%+).</t>
+          <t>Raise the party's ATK.</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Raise the party's DEF (8%+).</t>
+          <t>Raise the party's DEF.</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Create a field that reduces damage for both sides for a time (25%+).</t>
+          <t>Create a field that reduces damage for both sides for a time.</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Sacrifice yourself to revive (HP 10-50%), heal, and cure the rest of the party.</t>
+          <t>Sacrifice yourself to revive, heal, and cure the rest of the party.</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Heal an enemy's HP to decrease its physical (5%+) and magic defense (10%+).</t>
+          <t>Heal an enemy's HP to decrease its physical and magic defense.</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Pierce to the back row with a moderate raw magic attack and RES-based extra damage.</t>
+          <t>Hit both rows with a moderate raw magic attack plus RES-based damage.</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Deal severe damage to one enemy that possesses life. Low chance of instakill (12%).</t>
+          <t>Deal severe damage to a living enemy. Low chance of instakill (12%).</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>ATK bonus with sword equipped (3-15%).</t>
+          <t>ATK bonus with sword equipped.</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15755,7 +15755,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>ATK bonus with axe equipped (3-15%).</t>
+          <t>ATK bonus with axe equipped.</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15817,7 +15817,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>ATK bonus with dagger equipped (3-17%).</t>
+          <t>ATK bonus with dagger equipped.</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>ATK bonus with mace equipped (3-15%).</t>
+          <t>ATK bonus with mace equipped.</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>ATK bonus with lance equipped (3-15%).</t>
+          <t>ATK bonus with lance equipped.</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16003,7 +16003,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>ATK bonus with bow equipped (3-15%).</t>
+          <t>ATK bonus with bow equipped.</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16065,7 +16065,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>ATK bonus with katana equipped (3-15%).</t>
+          <t>ATK bonus with katana equipped.</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>ATK bonus with projectile weapon equipped (5-20%).</t>
+          <t>ATK bonus with projectile weapon equipped.</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>ATK bonus with whip equipped (3-17%).</t>
+          <t>ATK bonus with whip equipped.</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>ATK bonus with fan equipped (5-20%).</t>
+          <t>ATK bonus with fan equipped.</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>ATK bonus for all weapons (2%+).</t>
+          <t>ATK bonus for all weapons.</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Magic attack power bonus (6%+).</t>
+          <t>Magic attack power bonus.</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16437,7 +16437,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Healing magic bonus. Raises healing cap (HP recovery bonus 8-26%, Heal Cap 10-100%).</t>
+          <t>Healing magic bonus. Raises healing cap.</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Recover HP every turn during battle (2%+).</t>
+          <t>Recover HP every turn during battle.</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Slightly recover HP every turn during battle (1%+).</t>
+          <t>Slightly recover HP every turn during battle.</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16624,7 +16624,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Recover TP every turn during battle (3-16).</t>
+          <t>Recover TP every turn during battle.</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16686,7 +16686,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Slightly recover TP every turn during battle (1-9).</t>
+          <t>Slightly recover TP every turn during battle.</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16748,7 +16748,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Raise resistance to all elements (6%+).</t>
+          <t>Raise resistance to all elements.</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16810,7 +16810,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Occasionally counterattack after receiving physical damage (6-18%).</t>
+          <t>Occasionally counterattack after receiving physical damage.</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Occasionally parry and counterattack when targeted by an enemy (Activation rate 4%+).</t>
+          <t>Occasionally parry and counterattack when targeted by an enemy.</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Occasionally attack twice when attacking normally (Double attack rate 9-21%).</t>
+          <t>Occasionally attack twice when attacking normally.</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16996,7 +16996,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Occasionally attack thrice when attacking normally (Triple attack rate 5-17%).</t>
+          <t>Occasionally attack thrice when attacking normally.</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Increase evasion rate against stab attacks (20-36%).</t>
+          <t>Increase evasion rate against stab attacks.</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Occasionally parry when receiving long-range attacks (Activation rate 10-30%).</t>
+          <t>Occasionally parry when receiving long-range attacks.</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Occasionally survive at 1 HP after being dealt fatal damage (10-30%).</t>
+          <t>Occasionally survive at 1 HP after being dealt fatal damage.</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Occasionally Defend automatically when receiving physical attacks (4%+).</t>
+          <t>Occasionally Defend automatically when receiving physical attacks.</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Can equip two one-handed weapons at the same time (Sub-weapon ATK 30-72%).</t>
+          <t>Can equip two one-handed weapons at the same time.</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Convert some received damage to TP (4-20%).</t>
+          <t>Convert some received damage to TP.</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Occasionally instakill when inflicting a critical hit (Activation rate 8-20%).</t>
+          <t>Occasionally instakill when inflicting a critical hit.</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17456,7 +17456,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>With bow equipped, occasionally halt an enemy's action (Activation rate 2%+).</t>
+          <t>With bow equipped, occasionally halt an enemy's action.</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17509,7 +17509,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>With bow equipped, occasionally (4%+) attack again after an ally's attack.</t>
+          <t>With bow equipped, occasionally attack again after an ally's attack.</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Gain increased speed based on missing HP (15%+).</t>
+          <t>Gain increased speed based on missing HP.</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17615,7 +17615,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Debuff an enemy when they inflict short-range damage (1-6).</t>
+          <t>Debuff an enemy when they inflict short-range damage.</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17668,7 +17668,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Increase ATK while inflicted with status ailments (15-27%).</t>
+          <t>Increase ATK while inflicted with status ailments.</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Decrease physical damage to the back row when using a shield in the front row (6%+).</t>
+          <t>Decrease physical damage to the back row when using a shield in the front row.</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Occasionally nullify physical damage (Activation rate 8%+).</t>
+          <t>Occasionally nullify physical damage.</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17988,7 +17988,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Briefly increase ATK and DEX when HP drops below 50% (10%+).</t>
+          <t>Briefly increase ATK and DEX when HP drops below 50%.</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18050,7 +18050,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Make it harder for chants, songs, and dances to be interrupted (10-50%).</t>
+          <t>Make it harder for chants, songs, and dances to be interrupted.</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18111,7 +18111,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Reduce chant time (8-20%).</t>
+          <t>Reduce chant time.</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Reduce TP Cost in battle (10-30%).</t>
+          <t>Reduce TP Cost in battle.</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Heighten magic accuracy (3%+).</t>
+          <t>Heighten magic accuracy.</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18297,7 +18297,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Limit enemies' preemptive attacks (Enemy preemptive attack rate 20-50%).</t>
+          <t>Limit enemies' preemptive attacks.</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18359,7 +18359,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Increase party's preemptive attack rate (8-20%).</t>
+          <t>Increase party's preemptive attack rate.</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18421,7 +18421,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>May escape from battle more easily (20-40%).</t>
+          <t>May escape from battle more easily.</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Increase the enemies' item drop rate (4%+).</t>
+          <t>Increase the enemies' item drop rate.</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18545,7 +18545,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Increase the amount of money the enemies drop (Gold drop rate 25-125%).</t>
+          <t>Increase the amount of money the enemies drop.</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18607,7 +18607,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Sometimes pick up items while moving around the dungeons (Found item quality 1-5).</t>
+          <t>Sometimes pick up items while moving around the dungeons.</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Party's HP (6%+) and TP (3%+) is restored slightly after a battle.</t>
+          <t>Party's HP and TP is restored slightly after a battle.</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Occasionally keep disposable items after using them in battle (25%+).</t>
+          <t>Occasionally keep disposable items after using them in battle.</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18794,7 +18794,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Increase the effects of HP and TP recovery items during battle (10-100%).</t>
+          <t>Increase the effects of HP and TP recovery items during battle.</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Become capable of performing two songs at once (Speed 6-18%).</t>
+          <t>Become capable of performing two songs at once.</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Become capable of performing two dances at once (Speed 6-18%).</t>
+          <t>Become capable of performing two dances at once.</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Become capable of controlling two dolls at once (Speed 6-18%).</t>
+          <t>Become capable of controlling two dolls at once.</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19042,7 +19042,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Increase doll power with the strength of the equipped Sealbook (15-27%).</t>
+          <t>Increase doll power with the strength of the equipped Sealbook.</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Increased effects for all maid skills (1%+).</t>
+          <t>Increased effects for all maid skills.</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Increased effects for all songs (Singing skill bonus 3%+).</t>
+          <t>Increased effects for all songs.</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19228,7 +19228,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Increased effects for all dances (Dancing skill bonus 3%+).</t>
+          <t>Increased effects for all dances.</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -19290,7 +19290,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Increased effects for all doll skills (3%+).</t>
+          <t>Increased effects for all doll skills.</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -19352,7 +19352,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Occasionally attack twice when attacking normally (Double attack rate 20-32%).</t>
+          <t>Occasionally attack twice when attacking normally.</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Reduce chant time for songs (10%+).</t>
+          <t>Reduce chant time for songs.</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19476,7 +19476,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Reduce purchase and identification prices at shops (Negotiation rate 10-25%).</t>
+          <t>Reduce purchase and identification prices at shops.</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19538,7 +19538,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Mesmerize enemies, causing them to occasionally do nothing (Occurrence rate 3%+).</t>
+          <t>Mesmerize enemies, causing them to occasionally do nothing.</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20683,7 +20683,8 @@
       <c r="G329" t="inlineStr">
         <is>
           <t>Occasionally reflects a percentage of damage taken as fixed damage.
-Lv1-9: 50% -&gt; 55 -&gt; 60 -&gt; 65 -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 90 -&gt; 100% | Crown EX: 200%</t>
+Lv1-9: 50% -&gt; 55 -&gt; 60 -&gt; 65 -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 90 -&gt; 100% | Crown EX: 200%
+Activation rate: about 15% (player guide; the game data holds no figure)</t>
         </is>
       </c>
       <c r="H329" t="inlineStr"/>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -20684,7 +20684,7 @@
         <is>
           <t>Occasionally reflects a percentage of damage taken as fixed damage.
 Lv1-9: 50% -&gt; 55 -&gt; 60 -&gt; 65 -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 90 -&gt; 100% | Crown EX: 200%
-Activation rate: about 15% (player guide; the game data holds no figure)</t>
+Activation rate: about 15%</t>
         </is>
       </c>
       <c r="H329" t="inlineStr"/>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -19955,7 +19955,7 @@
       <c r="G315" t="inlineStr">
         <is>
           <t>Occasionally inflict enemies with status ailments or Dispel at random.
-Lv1-9: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 25%</t>
+Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 25%</t>
         </is>
       </c>
       <c r="H315" t="inlineStr"/>
@@ -20007,7 +20007,7 @@
       <c r="G316" t="inlineStr">
         <is>
           <t>May counter short-range attacks with Slow and a Speed decrease.
-Lv1-9: 16% -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38% | Crown EX: 50%</t>
+Activation rate: 16% -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38% | Crown EX: 50%</t>
         </is>
       </c>
       <c r="H316" t="inlineStr"/>
@@ -20059,7 +20059,7 @@
       <c r="G317" t="inlineStr">
         <is>
           <t>Increase weapon modifier when attacking with weapon-based skills.
-Lv1-9: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18% | Crown EX: 25%</t>
+Weapon modifier: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18% | Crown EX: 25%</t>
         </is>
       </c>
       <c r="H317" t="inlineStr"/>
@@ -20111,7 +20111,7 @@
       <c r="G318" t="inlineStr">
         <is>
           <t>May guarantee a hit and bypass DEF with physical attacks or skills.
-Lv1-9: 12% -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% | Crown EX: 30%</t>
+Activation rate: 12% -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% | Crown EX: 30%</t>
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
@@ -20163,7 +20163,7 @@
       <c r="G319" t="inlineStr">
         <is>
           <t>Occasionally nullify all damage received from enemies.
-Lv1-9: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
+Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
         </is>
       </c>
       <c r="H319" t="inlineStr"/>
@@ -20215,7 +20215,7 @@
       <c r="G320" t="inlineStr">
         <is>
           <t>Before acting, may erase enemy puppets, familiars, shikigami, or slaves.
-Lv1-9: 25% -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 49 -&gt; 53 -&gt; 57% | Crown EX: 75%</t>
+Activation rate: 25% -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 49 -&gt; 53 -&gt; 57% | Crown EX: 75%</t>
         </is>
       </c>
       <c r="H320" t="inlineStr"/>
@@ -20267,7 +20267,7 @@
       <c r="G321" t="inlineStr">
         <is>
           <t>Before acting, may use an item from her own personal stock.
-Lv1-9: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18% | Crown EX: 25%</t>
+Activation rate: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18% | Crown EX: 25%</t>
         </is>
       </c>
       <c r="H321" t="inlineStr"/>
@@ -20319,7 +20319,7 @@
       <c r="G322" t="inlineStr">
         <is>
           <t>Decrease turn delay after using skills or magic.
-Lv1-9: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
+Turn delay: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
         </is>
       </c>
       <c r="H322" t="inlineStr"/>
@@ -20371,7 +20371,7 @@
       <c r="G323" t="inlineStr">
         <is>
           <t>Increased effects for all maid skills.
-Lv1-9: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 10% | Crown EX: 13%</t>
+Maid skill effects: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 10% | Crown EX: 13%</t>
         </is>
       </c>
       <c r="H323" t="inlineStr"/>
@@ -20423,7 +20423,7 @@
       <c r="G324" t="inlineStr">
         <is>
           <t>May occasionally act twice in one turn.
-Lv1-9: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
+Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
         </is>
       </c>
       <c r="H324" t="inlineStr"/>
@@ -20579,7 +20579,7 @@
       <c r="G327" t="inlineStr">
         <is>
           <t>May lower all enemies' ATK and INT with heart-penetrating vocals.
-Lv1-9: 7% -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13% | Crown EX: 20%</t>
+Activation rate: 7% -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13% | Crown EX: 20%</t>
         </is>
       </c>
       <c r="H327" t="inlineStr"/>
@@ -20631,7 +20631,7 @@
       <c r="G328" t="inlineStr">
         <is>
           <t>Magic will occasionally activate immediately without the need to chant.
-Lv1-9: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
+Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
         </is>
       </c>
       <c r="H328" t="inlineStr"/>
@@ -20683,8 +20683,8 @@
       <c r="G329" t="inlineStr">
         <is>
           <t>Occasionally reflects a percentage of damage taken as fixed damage.
-Lv1-9: 50% -&gt; 55 -&gt; 60 -&gt; 65 -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 90 -&gt; 100% | Crown EX: 200%
-Activation rate: about 15%</t>
+Reflected: 50% -&gt; 55 -&gt; 60 -&gt; 65 -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 90 -&gt; 100% | Crown EX: 200%
+Activation rate: 15%</t>
         </is>
       </c>
       <c r="H329" t="inlineStr"/>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -576,8 +576,8 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max) | TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5
-Speed: 1.5x -&gt; 2x</t>
+          <t>Enmity: 250
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 | Speed: 1.5x -&gt; 2x</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -640,8 +640,8 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max) | TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8
-Speed: 1.25x -&gt; 1.77x</t>
+          <t>Enmity: 150
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | Speed: 1.25x -&gt; 1.77x</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -447,8 +447,8 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="47" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="84" customWidth="1" min="15" max="15"/>
-    <col width="86" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
     <col width="67" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
@@ -590,17 +590,8 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Attract single-target attacks. | Fast turn recovery.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | Speed: +50% -&gt; +100% (+12.5%/Lv)
-TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -654,17 +645,8 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Attract all enemies' attacks to user with high speed turn recovery.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | Speed: +40% -&gt; +80% (+10%/Lv)
-TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 11</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -722,17 +704,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Raise party physical ATK &amp; cleanse debuffs. Usable out of battle.</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>ATK: +8% -&gt; +10% -&gt; +12% -&gt; +14% -&gt; +18% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -790,17 +763,8 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Short-range strike. | Hit Rate: +20% -&gt; +38% (+2%/Lv)</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>ATK (L1-10): 125% -&gt; 133 -&gt; 141 -&gt; 150 -&gt; 158 -&gt; 166 -&gt; 175 -&gt; 183 -&gt; 191 -&gt; 200%
-TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28  (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -858,17 +822,8 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Short-range strike to one enemy. May cancel enemy active buffs.</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Dispel Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -930,17 +885,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Greatly boost own physical ATK at the cost of lowering own DEF.</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>ATK: +25% -&gt; +65% (+10%/Lv) | DEF: -15% -&gt; -35% (-5%/Lv)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1002,17 +948,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Increase own DEF at the cost of ATK (ATK debuff can be cleansed).</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>DEF: +20% -&gt; +27% -&gt; +35% -&gt; +42% -&gt; +50% (L1-5 Max)
-ATK: -11% -&gt; -25% (-3.5%/Lv) | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1074,17 +1011,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Shield skill. Deal bash damage to one enemy. May stun.</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>ATK: 110% -&gt; 150% (+10%/Lv) | Stun: 20% -&gt; 40% (+5%/Lv)
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 | Requires equipped shield</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1146,17 +1074,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Katana skill. Deal bash damage to one enemy. May paralyze.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>ATK: 120% -&gt; 180% (+15%/Lv) | Paralysis: 25% -&gt; 50% (+6.25%/Lv)
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1214,17 +1133,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Greatly boost own critical rate, but increase vulnerability to crits.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Crit Rate: +25% -&gt; +55% (+7.5%/Lv) | Enemy Crit: +15% -&gt; +25%
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1286,17 +1196,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Katana skill. Deal slash damage to an enemy row. May instakill.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>ATK: 115% -&gt; 175% (+15%/Lv) | Instakill: 10% -&gt; 25% (+3.75%/Lv)
-TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28</t>
-        </is>
-      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1350,17 +1251,8 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Katana skill. Deal defense-piercing damage and lower target DEF.</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>ATK: 120% -&gt; 180% (+15%/Lv) | DEF Debuff: -15% -&gt; -30% (-3.75%/Lv)
-TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 | Bypasses enemy armor</t>
-        </is>
-      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1418,17 +1310,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Katana skill. Strike an enemy row with fierce slashing blades.</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>ATK: 130% -&gt; 145% -&gt; 160% -&gt; 175% -&gt; 190% (L1-5)
-TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1486,17 +1369,8 @@
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Katana skill. Strike 3 times against one living enemy.</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>ATK: 70% -&gt; 80% -&gt; 90% -&gt; 100% -&gt; 110% per hit (3 hits total)
-TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 | Target must be living (not undead)</t>
-        </is>
-      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1554,17 +1428,8 @@
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Short-range strike to one enemy. Absorb a portion of damage as HP.</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)
-HP Absorb: 20% -&gt; 30% -&gt; 40% -&gt; 50% -&gt; 60% | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1622,17 +1487,8 @@
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Short-range strike to one enemy. Absorb a portion of damage as TP.</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>ATK: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% (L1-5)
-TP Absorb: 5% -&gt; 8% -&gt; 11% -&gt; 14% -&gt; 18% | TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8</t>
-        </is>
-      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1694,17 +1550,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Short-range strike dealing mid-range water damage. May freeze.</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>ATK: 120% -&gt; 180% (+15%/Lv) | Freeze: 20% -&gt; 40% (+5%/Lv)
-TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
-        </is>
-      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1766,17 +1613,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Axe skill. Strike one enemy with earth damage. May petrify.</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>ATK: 130% -&gt; 210% (+20%/Lv) | Petrify: 15% -&gt; 30% (+3.75%/Lv)
-TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
-        </is>
-      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1838,17 +1676,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Axe skill. Strike target and the next immediate enemy in turn order.</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>ATK: 140% -&gt; 160% -&gt; 180% -&gt; 200% -&gt; 220% (L1-5)
-TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28 | Hits 2 sequential turn targets</t>
-        </is>
-      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1906,17 +1735,8 @@
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Step forward to intercept physical attacks aimed at allies.</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Guard: 30% -&gt; 60% (+7.5%/Lv)
-TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24 | Requires 1H weapon &amp; shield</t>
-        </is>
-      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1974,17 +1794,8 @@
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Short-range skill. Block physical attacks with equipped weapon.</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | Recovery Speed: 1.30x
-TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22 | May break on repeat blocks</t>
-        </is>
-      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -2046,17 +1857,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Sword and lance skill. Strike one enemy. Effective vs. Unholy foes.</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>ATK: 140% -&gt; 155% -&gt; 170% -&gt; 185% -&gt; 200% (L1-5) | Unholy Bonus: 1.50x
-TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
-        </is>
-      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -2114,17 +1916,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Shield skill. Erect a physical barrier mitigating party damage once.</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Damage Reduction: -30% -&gt; -50% (-5%/Lv) | Levels: L1-5
-TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 | Requires shield</t>
-        </is>
-      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2182,17 +1975,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Shield skill. Erect a magic barrier mitigating party magic damage once.</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Magic Reduction: -30% -&gt; -50% (-5%/Lv) | Levels: L1-5
-TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 | Requires shield</t>
-        </is>
-      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2250,17 +2034,8 @@
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Short-range skill. Deal lightning damage to an enemy row. May paralyze.</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>ATK: 110% -&gt; 170% (+15%/Lv) | Paralysis: 20% -&gt; 40% (+5%/Lv)
-TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
-        </is>
-      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2322,17 +2097,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Lance skill. Strike one enemy with wind damage. May silence.</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>ATK: 125% -&gt; 185% (+15%/Lv) | Silence: 20% -&gt; 40% (+5%/Lv)
-TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
-        </is>
-      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2390,17 +2156,8 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Lance skill. Rapidly strike random enemies 3 to 5 times.</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>ATK: 65% -&gt; 75% -&gt; 85% -&gt; 95% -&gt; 105% per hit (L1-5)
-TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 | Heavy Lance bonus: +20% dmg</t>
-        </is>
-      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2458,17 +2215,8 @@
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Sword and lance skill. Pierces through to the back row.</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>ATK: 135% -&gt; 195% (+15%/Lv) | Hits front and back target
-TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
-        </is>
-      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2522,17 +2270,8 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Concentrate strength to deal massive physical damage next turn.</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Next Physical Hit: +80% -&gt; +110% -&gt; +140% -&gt; +170% -&gt; +200% (L1-5)
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 | Applies to next physical action</t>
-        </is>
-      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2585,17 +2324,8 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Attempt to pilfer pocket money from an enemy.</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Success Rate: 40% -&gt; 70% (+7.5%/Lv) | Gold: 1.0x -&gt; 2.5x (+0.375x/Lv)
-TP Cost: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2648,17 +2378,8 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Attempt to steal an item from an enemy.</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Success Rate: 25% -&gt; 55% (+7.5%/Lv) | Levels: L1-5
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2712,17 +2433,8 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Dagger skill. Strike for guaranteed critical stab damage.</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>ATK: 130% -&gt; 145% -&gt; 160% -&gt; 175% -&gt; 190% (L1-5) | 100% Critical Hit
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2776,17 +2488,8 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Dagger skill. Damage scales higher per buff and debuff on the target.</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Base ATK: 120% -&gt; 160% (+10%/Lv) | +25% dmg per active buff/debuff
-TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
-        </is>
-      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2844,17 +2547,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Increase own physical evasion rate.</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>EVA: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
-        </is>
-      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2908,17 +2602,8 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Cure status ailments for a single ally.</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep
-TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 11 (L1-5)</t>
-        </is>
-      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2980,17 +2665,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Concentrate to boost own accuracy and critical hit rate.</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Accuracy: +20% -&gt; +35% (+3.75%/Lv) | Crit: +10% -&gt; +20% (+2.5%/Lv)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
-        </is>
-      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -3044,17 +2720,8 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Enhance own movement and agility for increased turn speed.</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Speed: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -3112,17 +2779,8 @@
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Increase own physical evasion and magic evasion.</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Physical &amp; Magic EVA: +12% -&gt; +28% (+4%/Lv) | Levels: L1-5
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -3180,17 +2838,8 @@
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Short-range strike to one enemy. May inflict Sleep.</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>ATK: 110% -&gt; 170% (+15%/Lv) | Sleep: 30% -&gt; 60% (+7.5%/Lv)
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -3248,17 +2897,8 @@
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Short-range strike to one enemy. May inflict Silence.</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>ATK: 110% -&gt; 170% (+15%/Lv) | Silence: 30% -&gt; 60% (+7.5%/Lv)
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -3316,17 +2956,8 @@
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Short-range strike to one enemy. May inflict Stun.</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>ATK: 110% -&gt; 170% (+15%/Lv) | Stun: 25% -&gt; 50% (+6.25%/Lv)
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -3384,17 +3015,8 @@
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Bow and gun skill. Rapid fire multiple shots with escalating crit rate.</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Hits: 2 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 | ATK: 65% -&gt; 85% per hit (+5%/Lv)
-TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25</t>
-        </is>
-      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -3448,17 +3070,8 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Bow and gun skill. Fire a precision shot guaranteed to never miss.</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>ATK: 125% -&gt; 140% -&gt; 155% -&gt; 170% -&gt; 185% (L1-5) | 100% Accuracy
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3512,17 +3125,8 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Bow skill. Unleash a piercing arrow with boosted critical strike rate.</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>ATK: 150% -&gt; 170% -&gt; 190% -&gt; 210% -&gt; 230% (L1-5) | Crit Rate: +30%
-TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
-        </is>
-      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -3580,17 +3184,8 @@
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Bow and gun skill. Attack one enemy with a toxic shot. May poison.</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>ATK: 110% -&gt; 170% (+15%/Lv) | Poison: 30% -&gt; 60% (+7.5%/Lv)
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -3648,17 +3243,8 @@
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Bow skill. Attack one enemy with a chilling shot. May freeze.</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>ATK: 115% -&gt; 175% (+15%/Lv) | Freeze: 25% -&gt; 50% (+6.25%/Lv)
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3716,17 +3302,8 @@
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Bow skill. Attack one enemy with an electric shot. May paralyze.</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>ATK: 115% -&gt; 175% (+15%/Lv) | Paralysis: 25% -&gt; 50% (+6.25%/Lv)
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -3784,17 +3361,8 @@
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Bow skill. Deal stab damage to one enemy. May slow.</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>ATK: 115% -&gt; 175% (+15%/Lv) | Slow: 25% -&gt; 50% (+6.25%/Lv)
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -3848,17 +3416,8 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Bow skill. Fire an arrow volley striking all enemies on screen.</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>ATK: 95% -&gt; 110% -&gt; 125% -&gt; 140% -&gt; 155% (L1-5 Max)
-TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28</t>
-        </is>
-      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -3920,17 +3479,8 @@
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Bow skill. Shower random enemies with arrows over multiple turns.</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Hits: 3-5 arrows per wave | ATK: 70% -&gt; 95% per arrow (+6.25%/Lv)
-Duration: 2 -&gt; 3 turns | TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
-        </is>
-      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
           <t>no damage word: carries effects that are not understood: 146, 147</t>
@@ -3992,17 +3542,8 @@
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Bow skill. Massive piercing shot that penetrates through to the back row.</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>ATK: 175% -&gt; 200% -&gt; 225% -&gt; 250% -&gt; 280% (L1-5 Max)
-TP Cost: 18 -&gt; 22 -&gt; 26 -&gt; 30 -&gt; 34 | Hits both front and back target</t>
-        </is>
-      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -4127,17 +3668,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Deal bash damage to one enemy. May stun.</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>ATK: 130% -&gt; 190% (+15%/Lv) | Stun: 30% -&gt; 60% (+7.5%/Lv)
-TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
-        </is>
-      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -4190,17 +3722,8 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Identify unknown dungeon loot items.</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Success Rate: 70% -&gt; 98% (+7%/Lv) | Levels: L1-5
-TP Cost: 5 -&gt; 4 -&gt; 3 -&gt; 2 -&gt; 1 (Max)</t>
-        </is>
-      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -4321,17 +3844,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Mace skill. Heavy bash strike with boosted accuracy.</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>ATK: 140% -&gt; 200% (+15%/Lv) | Accuracy: +25% -&gt; +45% (+5%/Lv)
-TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
-        </is>
-      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -4389,17 +3903,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Mace skill. Strike target and reduce enemy physical DEF by 10%.</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>ATK: 125% -&gt; 185% (+15%/Lv) | Inflicts -10% DEF debuff
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 | Fast turn recovery (0.85x delay)</t>
-        </is>
-      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -4457,17 +3962,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Sword skill. Deal slash damage to all enemies on screen.</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>ATK: 120% -&gt; 160% (+10%/Lv, L1-5) | Hits all foes
-TP Cost: 36 -&gt; 46 -&gt; 57 -&gt; 68 -&gt; 79 | Action delay: 0.80x -&gt; 0.98x</t>
-        </is>
-      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -4584,17 +4080,8 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Transform into Magical Princess, raising all stats.</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>All Stats: +15% -&gt; +35% (+5%/Lv) | Levels: L1-5
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32</t>
-        </is>
-      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -4652,17 +4139,8 @@
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Short-range strike dealing heavy lightning damage to one enemy.</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>ATK: 136% -&gt; 216% (+20%/Lv, L1-5) | Lightning element
-TP Cost: 13 -&gt; 20 -&gt; 28 -&gt; 36 -&gt; 45</t>
-        </is>
-      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -4873,17 +4351,8 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Heal one ally's HP.</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Heal: 12% -&gt; 15% -&gt; 18% -&gt; 21% -&gt; 25% Max HP (L1-5 Max)
-TP Cost: 2 -&gt; 4 -&gt; 6 -&gt; 8 -&gt; 10 | Affected by Maid Mastery (+10% cap)</t>
-        </is>
-      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -4936,17 +4405,8 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Prepare a snack to restore one ally's TP.</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>TP Heal: 10% -&gt; 11% -&gt; 12% -&gt; 13% -&gt; 15% Max TP (L1-5)
-Action delay: 0.85x | TP Cost: 0 (Costs no TP to use)</t>
-        </is>
-      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -4998,17 +4458,8 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Sacrifice all user TP to transfer a magnified amount to an ally.</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>TP Transferred: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% of user's TP (L1-5)
-Leaves user at 0 TP | Fast recovery</t>
-        </is>
-      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -5061,17 +4512,8 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Clean up battle area to grant party action speed boost.</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Speed: +12% -&gt; +14% -&gt; +16% -&gt; +18% -&gt; +20% (L1-5)
-Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
-        </is>
-      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -5124,17 +4566,8 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>Focus divine power to restore own TP.</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>TP Restore: 16% -&gt; 25% Max TP (+2.25%/Lv) | Levels: L1-5
-TP Cost: 0 | Action delay: 1.00x</t>
-        </is>
-      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -5187,17 +4620,8 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Dance skill. Lower all enemies' physical ATK while dance lasts.</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Enemy ATK: -12% -&gt; -24% (-3%/Lv) | Levels: L1-5
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -5250,17 +4674,8 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>Dance skill. Lower all enemies' physical DEF while dance lasts.</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Enemy DEF: -12% -&gt; -24% (-3%/Lv) | Levels: L1-5
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -5520,7 +4935,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Resistance decrease: 7% -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25% (L10)
+          <t>Resistance decrease: 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 (L10)
 Speed: 0.75x</t>
         </is>
       </c>
@@ -5593,17 +5008,8 @@
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>Whip skill. Deal bash damage to an enemy row from mid-range.</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>ATK: 120% -&gt; 180% (+15%/Lv) | Row bash attack
-TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 (L1-5)</t>
-        </is>
-      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
@@ -5775,17 +5181,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>High risk gamble. Unleash 0 to 4 strikes on random enemies.</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>ATK per hit: 90% -&gt; 110% -&gt; 130% -&gt; 150% -&gt; 180% (L1-5)
-TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 | Boosted by Trump / High Risk</t>
-        </is>
-      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -5839,17 +5236,8 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Take a rest to restore own HP and raise Pep. Fast turn recovery.</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Heal: 20% -&gt; 25% -&gt; 30% -&gt; 35% -&gt; 40% Max HP (L1-5 Max)
-TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Action delay: 1.50x (fast)</t>
-        </is>
-      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
@@ -5952,17 +5340,8 @@
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>Attack one enemy. May instakill.</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>ATK: 140% -&gt; 200% (+15%/Lv) | Instakill Chance: 15% -&gt; 35% (+5%/Lv)
-TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28 (L1-5)</t>
-        </is>
-      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -6079,17 +5458,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>Greatly boost own physical ATK at the cost of reducing DEF to 0.</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>ATK: +40% -&gt; +80% (+10%/Lv) | User DEF reduced to 0
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
-        </is>
-      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
@@ -6306,17 +5676,8 @@
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>Fan skill. Deal bash damage to one enemy and delay target turn.</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>ATK: 120% -&gt; 180% (+15%/Lv) | Action Delay: -20% -&gt; -40%
-TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
-        </is>
-      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
@@ -6538,17 +5899,8 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>Convert current DEF to bonus ATK (user DEF becomes 0).</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>ATK Bonus: 100% -&gt; 150% of converted DEF value (+12.5%/Lv)
-Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
-        </is>
-      </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
@@ -6722,17 +6074,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>Summon puppet Spartan to attack enemies with short-range bash strikes.</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Puppet Power: 100% -&gt; 160% (+15%/Lv) | Duration: 4 -&gt; 6 turns
-TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 (L1-5)</t>
-        </is>
-      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
@@ -6857,17 +6200,8 @@
       </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>Summon puppet Catalina to heal party members' HP.</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Heal Potency: 20% -&gt; 40% Max HP (+5%/Lv) | Duration: 4 -&gt; 6 turns
-TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 (L1-5)</t>
-        </is>
-      </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
@@ -6984,17 +6318,8 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>Summon puppet Perdurabo to cure allies' status ailments.</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Cures status ailments for 2 allies per turn | Duration: 4 -&gt; 6 turns
-TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 (L1-5)</t>
-        </is>
-      </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
@@ -7056,17 +6381,8 @@
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>Summon puppet Musiy to cast immediate single-target attack spells.</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Spell Pwr: 120 -&gt; 240 (+30/Lv) | Duration: 4 -&gt; 6 turns
-TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 (L1-5)</t>
-        </is>
-      </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
@@ -9438,17 +8754,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>Deal fire damage to one enemy.</t>
-        </is>
-      </c>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
-TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
@@ -9510,17 +8817,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>Deal fire damage to an enemy row.</t>
-        </is>
-      </c>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
-TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
@@ -9582,17 +8880,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>Deal fire damage to all enemies.</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
-TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
@@ -9646,17 +8935,8 @@
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Unleash devastating master fire magic on one enemy. Pierces 50 Elemental Res.</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
-TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
@@ -9718,17 +8998,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>Deal water damage to one enemy.</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
-TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
@@ -9790,17 +9061,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>Deal water damage to an enemy row.</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
-TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
@@ -9862,17 +9124,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>Deal water damage to all enemies.</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
-TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
@@ -9926,17 +9179,8 @@
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>Unleash devastating master water magic on one enemy. Pierces 50 Elemental Res.</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
-TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
@@ -9998,17 +9242,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>Deal lightning damage to one enemy.</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
-TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
@@ -10070,17 +9305,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>Deal lightning damage to an enemy row.</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
-TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
@@ -10142,17 +9368,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>Deal lightning damage to all enemies.</t>
-        </is>
-      </c>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
-TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
@@ -10206,17 +9423,8 @@
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>Unleash devastating master lightning magic on one enemy. Pierces 50 Elemental Res.</t>
-        </is>
-      </c>
-      <c r="P156" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
-TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
@@ -10278,17 +9486,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>Deal wind damage to one enemy.</t>
-        </is>
-      </c>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
-TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
     </row>
     <row r="158">
@@ -10350,17 +9549,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>Deal wind damage to an enemy row.</t>
-        </is>
-      </c>
-      <c r="P158" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
-TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
@@ -10422,17 +9612,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>Deal wind damage to all enemies.</t>
-        </is>
-      </c>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
-TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
@@ -10486,17 +9667,8 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>Unleash devastating master wind magic on one enemy. Pierces 50 Elemental Res.</t>
-        </is>
-      </c>
-      <c r="P160" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
-TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
@@ -10558,17 +9730,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>Deal earth damage to one enemy.</t>
-        </is>
-      </c>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
-TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
     </row>
     <row r="162">
@@ -10630,17 +9793,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>Deal earth damage to an enemy row.</t>
-        </is>
-      </c>
-      <c r="P162" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
-TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
@@ -10702,17 +9856,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>Deal earth damage to all enemies.</t>
-        </is>
-      </c>
-      <c r="P163" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
-TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
     </row>
     <row r="164">
@@ -10766,17 +9911,8 @@
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>Unleash devastating master earth magic on one enemy. Pierces 50 Elemental Res.</t>
-        </is>
-      </c>
-      <c r="P164" t="inlineStr">
-        <is>
-          <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
-TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
     </row>
     <row r="165">
@@ -10838,17 +9974,8 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>Neutral magic strike to one enemy. Absorb damage dealt as HP.</t>
-        </is>
-      </c>
-      <c r="P165" t="inlineStr">
-        <is>
-          <t>Pwr: 60 -&gt; 120 -&gt; 180 -&gt; 260 -&gt; 350 (L1-5) | Bypasses elemental resists
-TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 18</t>
-        </is>
-      </c>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
     </row>
     <row r="166">
@@ -10906,17 +10033,8 @@
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>Neutral magic strike to one enemy. Absorb damage dealt as TP.</t>
-        </is>
-      </c>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>Pwr: 22 -&gt; 35 -&gt; 50 -&gt; 65 -&gt; 82 (L1-5) | Restores TP equal to damage dealt
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 15</t>
-        </is>
-      </c>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
     </row>
     <row r="167">
@@ -10974,17 +10092,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>Boost own magic attack power at the cost of consuming HP.</t>
-        </is>
-      </c>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>Magic ATK: +20% -&gt; +40% (+5%/Lv) | HP Cost: 10% Max HP
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
-        </is>
-      </c>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
     </row>
     <row r="168">
@@ -11046,17 +10155,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>Transfer a portion of user HP to restore an ally's HP.</t>
-        </is>
-      </c>
-      <c r="P168" t="inlineStr">
-        <is>
-          <t>Heal: 30% -&gt; 60% (+7.5%/Lv) of target Max HP | Consumes 20% user HP
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 (L1-5)</t>
-        </is>
-      </c>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
     </row>
     <row r="169">
@@ -11110,17 +10210,8 @@
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>Deal magic damage to one enemy. May stun.</t>
-        </is>
-      </c>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>Stun Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
@@ -11174,17 +10265,8 @@
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>Poison all enemies (5% Max HP damage per enemy turn, cap 250).</t>
-        </is>
-      </c>
-      <c r="P170" t="inlineStr">
-        <is>
-          <t>Accuracy: +15% -&gt; +35% (+5%/Lv) | Chant: 1.20x -&gt; 1.40x
-TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5)</t>
-        </is>
-      </c>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
     </row>
     <row r="171">
@@ -11238,17 +10320,8 @@
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>Deal water magic damage to one enemy. May freeze.</t>
-        </is>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>Freeze Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
     </row>
     <row r="172">
@@ -11302,17 +10375,8 @@
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>Deal lightning magic damage to one enemy. May paralyze.</t>
-        </is>
-      </c>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>Paralysis Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
     </row>
     <row r="173">
@@ -11366,17 +10430,8 @@
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>Put an enemy to sleep with magic.</t>
-        </is>
-      </c>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>Sleep Chance: 40% -&gt; 70% (+7.5%/Lv) | Levels: L1-5
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
     </row>
     <row r="174">
@@ -11430,17 +10485,8 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>Silence an enemy to prevent spell casting.</t>
-        </is>
-      </c>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>Silence Chance: 40% -&gt; 70% (+7.5%/Lv) | Levels: L1-5
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
     </row>
     <row r="175">
@@ -11494,17 +10540,8 @@
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr">
-        <is>
-          <t>Turn one enemy to stone with earth magic.</t>
-        </is>
-      </c>
-      <c r="P175" t="inlineStr">
-        <is>
-          <t>Petrify Chance: 20% -&gt; 40% (+5%/Lv) | Levels: L1-5
-TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
-        </is>
-      </c>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
     </row>
     <row r="176">
@@ -11558,17 +10595,8 @@
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr">
-        <is>
-          <t>Attempt to instantly slay one living enemy.</t>
-        </is>
-      </c>
-      <c r="P176" t="inlineStr">
-        <is>
-          <t>Instakill Chance: 15% -&gt; 35% (+5%/Lv) | Levels: L1-5
-TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28</t>
-        </is>
-      </c>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
     </row>
     <row r="177">
@@ -11622,17 +10650,8 @@
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>Inflict Slow on an enemy row, cutting action speed by -50%.</t>
-        </is>
-      </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>Slow Chance: 35% -&gt; 65% (+7.5%/Lv) | Inflicts -50% Speed
-TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 (L1-5)</t>
-        </is>
-      </c>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
     </row>
     <row r="178">
@@ -11686,17 +10705,8 @@
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>Terrify an enemy with dark magic to inflict Stun.</t>
-        </is>
-      </c>
-      <c r="P178" t="inlineStr">
-        <is>
-          <t>Stun Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
     </row>
     <row r="179">
@@ -11868,17 +10878,8 @@
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr">
-        <is>
-          <t>Imbue an ally's weapon with Fire element.</t>
-        </is>
-      </c>
-      <c r="P181" t="inlineStr">
-        <is>
-          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Fire damage to weapon strikes
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr"/>
     </row>
     <row r="182">
@@ -11932,17 +10933,8 @@
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>Imbue an ally's weapon with Water element.</t>
-        </is>
-      </c>
-      <c r="P182" t="inlineStr">
-        <is>
-          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Water damage to weapon strikes
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
     </row>
     <row r="183">
@@ -11996,17 +10988,8 @@
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>Imbue an ally's weapon with Lightning element.</t>
-        </is>
-      </c>
-      <c r="P183" t="inlineStr">
-        <is>
-          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Lightning damage to weapon strikes
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr"/>
     </row>
     <row r="184">
@@ -12060,17 +11043,8 @@
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>Imbue an ally's weapon with Wind element.</t>
-        </is>
-      </c>
-      <c r="P184" t="inlineStr">
-        <is>
-          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Wind damage to weapon strikes
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr"/>
     </row>
     <row r="185">
@@ -12124,17 +11098,8 @@
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr">
-        <is>
-          <t>Imbue an ally's weapon with Earth element.</t>
-        </is>
-      </c>
-      <c r="P185" t="inlineStr">
-        <is>
-          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Earth damage to weapon strikes
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr"/>
     </row>
     <row r="186">
@@ -12174,7 +11139,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Resistance: 20% -&gt; 24% -&gt; 28% -&gt; 32% -&gt; 36% (L1-5 Max)
+          <t>Resistance: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
@@ -12192,17 +11157,8 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>Raise one row of allies' resistance to stab damage.</t>
-        </is>
-      </c>
-      <c r="P186" t="inlineStr">
-        <is>
-          <t>Stab Resistance: +15 -&gt; +35 (+5/Lv) | Levels: L1-5
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
-        </is>
-      </c>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
     </row>
     <row r="187">
@@ -12242,7 +11198,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Resistance: 18% -&gt; 24% -&gt; 28% -&gt; 32% -&gt; 36% (L1-5 Max)
+          <t>Resistance: 18 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
@@ -12260,17 +11216,8 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O187" t="inlineStr">
-        <is>
-          <t>Raise one row of allies' resistance to slash damage.</t>
-        </is>
-      </c>
-      <c r="P187" t="inlineStr">
-        <is>
-          <t>Slash Resistance: +15 -&gt; +35 (+5/Lv) | Levels: L1-5
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
-        </is>
-      </c>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
     </row>
     <row r="188">
@@ -12310,7 +11257,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Resistance: 18% -&gt; 24% -&gt; 28% -&gt; 32% -&gt; 36% (L1-5 Max)
+          <t>Resistance: 18 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
@@ -12328,17 +11275,8 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O188" t="inlineStr">
-        <is>
-          <t>Raise one row of allies' resistance to bash damage.</t>
-        </is>
-      </c>
-      <c r="P188" t="inlineStr">
-        <is>
-          <t>Bash Resistance: +15 -&gt; +35 (+5/Lv) | Levels: L1-5
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
-        </is>
-      </c>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
     </row>
     <row r="189">
@@ -12400,17 +11338,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O189" t="inlineStr">
-        <is>
-          <t>Heal an ally's HP.</t>
-        </is>
-      </c>
-      <c r="P189" t="inlineStr">
-        <is>
-          <t>Heal Cap (L1-10): 100 -&gt; 150 -&gt; 200 -&gt; 270 -&gt; 350 -&gt; 440 -&gt; 540 -&gt; 650 -&gt; 720 -&gt; 800
-TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26  (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
     </row>
     <row r="190">
@@ -12472,17 +11401,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O190" t="inlineStr">
-        <is>
-          <t>Heal the entire party's HP.</t>
-        </is>
-      </c>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>Heal Cap (L1-10): 80 -&gt; 120 -&gt; 160 -&gt; 210 -&gt; 270 -&gt; 340 -&gt; 420 -&gt; 510 -&gt; 600 -&gt; 700
-TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 21 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 46  (Lv1 to Max)</t>
-        </is>
-      </c>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
       <c r="Q190" t="inlineStr"/>
     </row>
     <row r="191">
@@ -12534,17 +11454,8 @@
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>Fully restore one ally's HP to maximum.</t>
-        </is>
-      </c>
-      <c r="P191" t="inlineStr">
-        <is>
-          <t>Heals 100% Max HP (9,999 HP cap) | Chant: 2 turns -&gt; 1 turn
-TP Cost: 35 -&gt; 30 -&gt; 25 -&gt; 20 -&gt; 16 (L1-5)</t>
-        </is>
-      </c>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr"/>
     </row>
     <row r="192">
@@ -12598,17 +11509,8 @@
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>Cure status ailments for a single ally.</t>
-        </is>
-      </c>
-      <c r="P192" t="inlineStr">
-        <is>
-          <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep -&gt; Petrify -&gt; Slow
-TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 (L1-7)</t>
-        </is>
-      </c>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr"/>
     </row>
     <row r="193">
@@ -12662,17 +11564,8 @@
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>Cure status ailments for the entire party.</t>
-        </is>
-      </c>
-      <c r="P193" t="inlineStr">
-        <is>
-          <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep -&gt; Petrify -&gt; Slow
-TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 (L1-7)</t>
-        </is>
-      </c>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
       <c r="Q193" t="inlineStr"/>
     </row>
     <row r="194">
@@ -12726,17 +11619,8 @@
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>Revive a fallen ally.</t>
-        </is>
-      </c>
-      <c r="P194" t="inlineStr">
-        <is>
-          <t>Revival HP: 20% -&gt; 35% -&gt; 50% -&gt; 70% -&gt; 100% Max HP (L1-5)
-Chant time decreases per level | TP Cost: 18 -&gt; 22 -&gt; 26 -&gt; 30 -&gt; 35</t>
-        </is>
-      </c>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
     </row>
     <row r="195">
@@ -12794,17 +11678,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>Raise an ally's physical ATK.</t>
-        </is>
-      </c>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>ATK: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
       <c r="Q195" t="inlineStr"/>
     </row>
     <row r="196">
@@ -12862,17 +11737,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>Raise an ally's physical DEF.</t>
-        </is>
-      </c>
-      <c r="P196" t="inlineStr">
-        <is>
-          <t>DEF: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
       <c r="Q196" t="inlineStr"/>
     </row>
     <row r="197">
@@ -12930,17 +11796,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>Raise the party's magical defense against incoming spells.</t>
-        </is>
-      </c>
-      <c r="P197" t="inlineStr">
-        <is>
-          <t>Magic DEF: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
-        </is>
-      </c>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr"/>
     </row>
     <row r="198">
@@ -12980,7 +11837,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Elemental resistance increase: 5% -&gt; 10% -&gt; 15% -&gt; 20% -&gt; 25% (L1-5 Max)
+          <t>Elemental resistance increase: 5 -&gt; 10 -&gt; 15 -&gt; 20 -&gt; 25 (L1-5 Max)
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Chant: 1.25x</t>
         </is>
       </c>
@@ -12998,17 +11855,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>Raise party resistance to Fire, Water, Lightning, Wind, and Earth.</t>
-        </is>
-      </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>Resist: +15 -&gt; +20 -&gt; +25 -&gt; +30 -&gt; +35 all elements (L1-5)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
-        </is>
-      </c>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr"/>
     </row>
     <row r="199">
@@ -13066,17 +11914,8 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>Raise an ally's action speed.</t>
-        </is>
-      </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>Speed: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
-Chant time decreases per level | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
     </row>
     <row r="200">
@@ -13134,17 +11973,8 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O200" t="inlineStr">
-        <is>
-          <t>Temporarily raise an ally's maximum HP cap.</t>
-        </is>
-      </c>
-      <c r="P200" t="inlineStr">
-        <is>
-          <t>Max HP: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
-        </is>
-      </c>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
     </row>
     <row r="201">
@@ -13198,17 +12028,8 @@
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr">
-        <is>
-          <t>Cure status ailments for one row of allies.</t>
-        </is>
-      </c>
-      <c r="P201" t="inlineStr">
-        <is>
-          <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep -&gt; Petrify -&gt; Slow
-TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24 -&gt; 28 (L1-7)</t>
-        </is>
-      </c>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr"/>
     </row>
     <row r="202">
@@ -13262,17 +12083,8 @@
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr">
-        <is>
-          <t>Create magical afterimages that let user dodge incoming attacks.</t>
-        </is>
-      </c>
-      <c r="P202" t="inlineStr">
-        <is>
-          <t>Dodges: 2 guaranteed physical attacks avoided
-Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
-        </is>
-      </c>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr"/>
     </row>
     <row r="203">
@@ -13326,17 +12138,8 @@
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>Enchant self with a barrier reducing incoming physical damage.</t>
-        </is>
-      </c>
-      <c r="P203" t="inlineStr">
-        <is>
-          <t>Physical Damage Reduction: -20% -&gt; -35% (-3.75%/Lv) | Levels: L1-5
-TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
-        </is>
-      </c>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
     </row>
     <row r="204">
@@ -13447,17 +12250,8 @@
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr">
-        <is>
-          <t>Illuminate dark dungeons to reveal secret passages and hidden doors.</t>
-        </is>
-      </c>
-      <c r="P205" t="inlineStr">
-        <is>
-          <t>Duration: 50 -&gt; 100 -&gt; 150 -&gt; 200 -&gt; 300 steps (L1-5)
-TP Cost: 4 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 4</t>
-        </is>
-      </c>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
       <c r="Q205" t="inlineStr"/>
     </row>
     <row r="206">
@@ -13509,17 +12303,8 @@
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr">
-        <is>
-          <t>Immediately teleport the party safely out of the dungeon.</t>
-        </is>
-      </c>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>TP Cost: 20 -&gt; 15 -&gt; 10 -&gt; 6 -&gt; 2 (L1-5 Max)
-Works identical to an Emergency Exit item</t>
-        </is>
-      </c>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
       <c r="Q206" t="inlineStr"/>
     </row>
     <row r="207">
@@ -13572,17 +12357,8 @@
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr">
-        <is>
-          <t>Sing a soothing lullaby. May put target enemy to sleep.</t>
-        </is>
-      </c>
-      <c r="P207" t="inlineStr">
-        <is>
-          <t>Sleep Chance: 40% -&gt; 70% (+7.5%/Lv) | Levels: L1-5
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
-        </is>
-      </c>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr"/>
     </row>
     <row r="208">
@@ -13900,17 +12676,8 @@
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr">
-        <is>
-          <t>Perform a song that regenerates party HP every turn while singing.</t>
-        </is>
-      </c>
-      <c r="P213" t="inlineStr">
-        <is>
-          <t>HP Regen: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% Max HP per turn (L1-5)
-Chant Time: 2 turns -&gt; 1 turn | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
-        </is>
-      </c>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
       <c r="Q213" t="inlineStr"/>
     </row>
     <row r="214">
@@ -13963,17 +12730,8 @@
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr">
-        <is>
-          <t>Perform a song that regenerates party TP every turn while singing.</t>
-        </is>
-      </c>
-      <c r="P214" t="inlineStr">
-        <is>
-          <t>TP Regen: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 12 TP per turn (L1-5)
-Chant Time: 2 turns -&gt; 1 turn | TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
-        </is>
-      </c>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
       <c r="Q214" t="inlineStr"/>
     </row>
     <row r="215">
@@ -14026,17 +12784,8 @@
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr">
-        <is>
-          <t>Perform a lively march boosting party action speed while singing.</t>
-        </is>
-      </c>
-      <c r="P215" t="inlineStr">
-        <is>
-          <t>Party Speed: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
-TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
-        </is>
-      </c>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
     </row>
     <row r="216">
@@ -14089,17 +12838,8 @@
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>Perform a song that increases combat EXP gained by the party.</t>
-        </is>
-      </c>
-      <c r="P216" t="inlineStr">
-        <is>
-          <t>EXP Bonus: +10% -&gt; +15% -&gt; +20% -&gt; +25% -&gt; +30% (L1-5)
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
-        </is>
-      </c>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
       <c r="Q216" t="inlineStr"/>
     </row>
     <row r="217">
@@ -14817,17 +13557,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O228" t="inlineStr">
-        <is>
-          <t>Raise the entire party's physical ATK.</t>
-        </is>
-      </c>
-      <c r="P228" t="inlineStr">
-        <is>
-          <t>Party ATK: +10% -&gt; +13% -&gt; +16% -&gt; +20% -&gt; +25% (L1-5)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30</t>
-        </is>
-      </c>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
       <c r="Q228" t="inlineStr"/>
     </row>
     <row r="229">
@@ -14885,17 +13616,8 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O229" t="inlineStr">
-        <is>
-          <t>Raise the entire party's physical DEF.</t>
-        </is>
-      </c>
-      <c r="P229" t="inlineStr">
-        <is>
-          <t>Party DEF: +10% -&gt; +13% -&gt; +16% -&gt; +20% -&gt; +25% (L1-5)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30</t>
-        </is>
-      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
       <c r="Q229" t="inlineStr"/>
     </row>
     <row r="230">
@@ -15649,17 +14371,8 @@
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr">
-        <is>
-          <t>Occasionally reflects incoming damage back as fixed neutral damage.</t>
-        </is>
-      </c>
-      <c r="P242" t="inlineStr">
-        <is>
-          <t>Reflect Rate: 20% chance to reflect 30% of received damage to attacker
-Heroine: Melvy</t>
-        </is>
-      </c>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
       <c r="Q242" t="inlineStr"/>
     </row>
     <row r="243">
@@ -15711,17 +14424,8 @@
       <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr">
-        <is>
-          <t>Increases equipped sword base ATK.</t>
-        </is>
-      </c>
-      <c r="P243" t="inlineStr">
-        <is>
-          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
-Scales off weapon base ATK (not total character ATK)</t>
-        </is>
-      </c>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
       <c r="Q243" t="inlineStr"/>
     </row>
     <row r="244">
@@ -15773,17 +14477,8 @@
       <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr">
-        <is>
-          <t>Increases equipped axe base ATK.</t>
-        </is>
-      </c>
-      <c r="P244" t="inlineStr">
-        <is>
-          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
-Scales off weapon base ATK</t>
-        </is>
-      </c>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
       <c r="Q244" t="inlineStr"/>
     </row>
     <row r="245">
@@ -15835,17 +14530,8 @@
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr"/>
-      <c r="O245" t="inlineStr">
-        <is>
-          <t>Increases equipped dagger base ATK.</t>
-        </is>
-      </c>
-      <c r="P245" t="inlineStr">
-        <is>
-          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
-Scales off weapon base ATK</t>
-        </is>
-      </c>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
       <c r="Q245" t="inlineStr"/>
     </row>
     <row r="246">
@@ -15897,17 +14583,8 @@
       <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr">
-        <is>
-          <t>Increases equipped mace base ATK.</t>
-        </is>
-      </c>
-      <c r="P246" t="inlineStr">
-        <is>
-          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
-Scales off weapon base ATK</t>
-        </is>
-      </c>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
       <c r="Q246" t="inlineStr"/>
     </row>
     <row r="247">
@@ -15959,17 +14636,8 @@
       <c r="L247" t="inlineStr"/>
       <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr">
-        <is>
-          <t>Increases equipped lance base ATK.</t>
-        </is>
-      </c>
-      <c r="P247" t="inlineStr">
-        <is>
-          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
-Scales off weapon base ATK</t>
-        </is>
-      </c>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr"/>
       <c r="Q247" t="inlineStr"/>
     </row>
     <row r="248">
@@ -16021,17 +14689,8 @@
       <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr"/>
-      <c r="O248" t="inlineStr">
-        <is>
-          <t>Increases equipped bow base ATK.</t>
-        </is>
-      </c>
-      <c r="P248" t="inlineStr">
-        <is>
-          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
-Scales off weapon base ATK</t>
-        </is>
-      </c>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr"/>
       <c r="Q248" t="inlineStr"/>
     </row>
     <row r="249">
@@ -16083,17 +14742,8 @@
       <c r="L249" t="inlineStr"/>
       <c r="M249" t="inlineStr"/>
       <c r="N249" t="inlineStr"/>
-      <c r="O249" t="inlineStr">
-        <is>
-          <t>Increases equipped katana base ATK.</t>
-        </is>
-      </c>
-      <c r="P249" t="inlineStr">
-        <is>
-          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
-Scales off weapon base ATK</t>
-        </is>
-      </c>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr"/>
       <c r="Q249" t="inlineStr"/>
     </row>
     <row r="250">
@@ -16145,17 +14795,8 @@
       <c r="L250" t="inlineStr"/>
       <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr"/>
-      <c r="O250" t="inlineStr">
-        <is>
-          <t>Increases equipped projectile weapon base ATK.</t>
-        </is>
-      </c>
-      <c r="P250" t="inlineStr">
-        <is>
-          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
-Scales off weapon base ATK</t>
-        </is>
-      </c>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr"/>
       <c r="Q250" t="inlineStr"/>
     </row>
     <row r="251">
@@ -16207,17 +14848,8 @@
       <c r="L251" t="inlineStr"/>
       <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr"/>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>Increases equipped whip base ATK.</t>
-        </is>
-      </c>
-      <c r="P251" t="inlineStr">
-        <is>
-          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
-Scales off weapon base ATK</t>
-        </is>
-      </c>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
       <c r="Q251" t="inlineStr"/>
     </row>
     <row r="252">
@@ -16269,17 +14901,8 @@
       <c r="L252" t="inlineStr"/>
       <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr"/>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>Increases equipped fan base ATK.</t>
-        </is>
-      </c>
-      <c r="P252" t="inlineStr">
-        <is>
-          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
-Scales off weapon base ATK</t>
-        </is>
-      </c>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
       <c r="Q252" t="inlineStr"/>
     </row>
     <row r="253">
@@ -16331,17 +14954,8 @@
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr"/>
-      <c r="O253" t="inlineStr">
-        <is>
-          <t>Increases equipped base ATK for all weapon types.</t>
-        </is>
-      </c>
-      <c r="P253" t="inlineStr">
-        <is>
-          <t>ATK (L1-10): +2% -&gt; +3% -&gt; +4% -&gt; +5% -&gt; +6% -&gt; +7% -&gt; +8% -&gt; +9% -&gt; +10% -&gt; +12%
-Universal weapon scaling</t>
-        </is>
-      </c>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
       <c r="Q253" t="inlineStr"/>
     </row>
     <row r="254">
@@ -16393,17 +15007,8 @@
       <c r="L254" t="inlineStr"/>
       <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr"/>
-      <c r="O254" t="inlineStr">
-        <is>
-          <t>Increase magic attack power bonus for all spells.</t>
-        </is>
-      </c>
-      <c r="P254" t="inlineStr">
-        <is>
-          <t>Magic Power (L1-10): +6% (L1) -&gt; +15% (L10 Max) | Step: +1%/Lv (+6% base)
-Applies to all offensive spell damage</t>
-        </is>
-      </c>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr"/>
       <c r="Q254" t="inlineStr"/>
     </row>
     <row r="255">
@@ -16456,17 +15061,8 @@
       <c r="L255" t="inlineStr"/>
       <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr"/>
-      <c r="O255" t="inlineStr">
-        <is>
-          <t>Boost potency and maximum HP healing cap of healing magic.</t>
-        </is>
-      </c>
-      <c r="P255" t="inlineStr">
-        <is>
-          <t>Healing Bonus: +10% -&gt; +30% (+2%/Lv up to L5, then +3%/Lv, Max +30%)
-Also raises baseline healing cap on Heal and Circle Heal</t>
-        </is>
-      </c>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr"/>
       <c r="Q255" t="inlineStr"/>
     </row>
     <row r="256">
@@ -16518,17 +15114,8 @@
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr"/>
-      <c r="O256" t="inlineStr">
-        <is>
-          <t>Recover HP every turn during battle.</t>
-        </is>
-      </c>
-      <c r="P256" t="inlineStr">
-        <is>
-          <t>HP Regen: 10 -&gt; 20 -&gt; 30 -&gt; 40 -&gt; 50 HP per turn (L1-5)
-Triggers at start of user's action in combat</t>
-        </is>
-      </c>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr"/>
       <c r="Q256" t="inlineStr"/>
     </row>
     <row r="257">
@@ -16580,17 +15167,8 @@
       <c r="L257" t="inlineStr"/>
       <c r="M257" t="inlineStr"/>
       <c r="N257" t="inlineStr"/>
-      <c r="O257" t="inlineStr">
-        <is>
-          <t>Slightly recover HP every turn during battle.</t>
-        </is>
-      </c>
-      <c r="P257" t="inlineStr">
-        <is>
-          <t>HP Regen (L1-5): 1% -&gt; 2% -&gt; 3% -&gt; 4% -&gt; 5% (+1%/Lv)
-Triggers at start of user's action in combat</t>
-        </is>
-      </c>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr"/>
       <c r="Q257" t="inlineStr"/>
     </row>
     <row r="258">
@@ -16642,17 +15220,8 @@
       <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr"/>
-      <c r="O258" t="inlineStr">
-        <is>
-          <t>Recover TP every turn during battle.</t>
-        </is>
-      </c>
-      <c r="P258" t="inlineStr">
-        <is>
-          <t>TP Regen (L1-10): 2 -&gt; 3 -&gt; 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 TP per turn
-Active on user turn in battle</t>
-        </is>
-      </c>
+      <c r="O258" t="inlineStr"/>
+      <c r="P258" t="inlineStr"/>
       <c r="Q258" t="inlineStr"/>
     </row>
     <row r="259">
@@ -16704,17 +15273,8 @@
       <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr"/>
-      <c r="O259" t="inlineStr">
-        <is>
-          <t>Slightly recover TP every turn during battle.</t>
-        </is>
-      </c>
-      <c r="P259" t="inlineStr">
-        <is>
-          <t>TP Regen: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 TP per turn (L1-8)
-Triggers on user turn in combat</t>
-        </is>
-      </c>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr"/>
       <c r="Q259" t="inlineStr"/>
     </row>
     <row r="260">
@@ -16753,7 +15313,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Elemental resistance: 6% -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
+          <t>Elemental resistance: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 (L10)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -16766,17 +15326,8 @@
       <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr">
-        <is>
-          <t>Raise innate resistance to all elements.</t>
-        </is>
-      </c>
-      <c r="P260" t="inlineStr">
-        <is>
-          <t>Elemental Resist: +5 -&gt; +10 -&gt; +15 -&gt; +20 -&gt; +25 all elements (L1-5)
-Applies to Fire, Water, Lightning, Wind, and Earth</t>
-        </is>
-      </c>
+      <c r="O260" t="inlineStr"/>
+      <c r="P260" t="inlineStr"/>
       <c r="Q260" t="inlineStr"/>
     </row>
     <row r="261">
@@ -16828,17 +15379,8 @@
       <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr"/>
       <c r="N261" t="inlineStr"/>
-      <c r="O261" t="inlineStr">
-        <is>
-          <t>Counterattack short/medium physical hits with equipped weapon.</t>
-        </is>
-      </c>
-      <c r="P261" t="inlineStr">
-        <is>
-          <t>Counter Rate: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5) | Step: +3%/Lv
-Note: Short-range retaliations will trigger enemy Dark Aura</t>
-        </is>
-      </c>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="inlineStr"/>
       <c r="Q261" t="inlineStr"/>
     </row>
     <row r="262">
@@ -16890,17 +15432,8 @@
       <c r="L262" t="inlineStr"/>
       <c r="M262" t="inlineStr"/>
       <c r="N262" t="inlineStr"/>
-      <c r="O262" t="inlineStr">
-        <is>
-          <t>Occasionally parry and counterattack when targeted by an enemy.</t>
-        </is>
-      </c>
-      <c r="P262" t="inlineStr">
-        <is>
-          <t>Parry &amp; Counter: 10% -&gt; 25% (+3.75%/Lv) | Levels: L1-5
-Nullifies incoming attack and strikes back</t>
-        </is>
-      </c>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr"/>
       <c r="Q262" t="inlineStr"/>
     </row>
     <row r="263">
@@ -16952,17 +15485,8 @@
       <c r="L263" t="inlineStr"/>
       <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr"/>
-      <c r="O263" t="inlineStr">
-        <is>
-          <t>Chance to attack twice when using normal attacks.</t>
-        </is>
-      </c>
-      <c r="P263" t="inlineStr">
-        <is>
-          <t>Trigger Rate: 9% -&gt; 12% -&gt; 15% -&gt; 18% -&gt; 21% (L1-5) | Step: +3%/Lv
-Can stack with Triple Attack (up to 5 strikes total)</t>
-        </is>
-      </c>
+      <c r="O263" t="inlineStr"/>
+      <c r="P263" t="inlineStr"/>
       <c r="Q263" t="inlineStr"/>
     </row>
     <row r="264">
@@ -17014,17 +15538,8 @@
       <c r="L264" t="inlineStr"/>
       <c r="M264" t="inlineStr"/>
       <c r="N264" t="inlineStr"/>
-      <c r="O264" t="inlineStr">
-        <is>
-          <t>Chance to attack thrice when using normal attacks.</t>
-        </is>
-      </c>
-      <c r="P264" t="inlineStr">
-        <is>
-          <t>Trigger Rate: 5% -&gt; 7.5% -&gt; 10% -&gt; 12.5% -&gt; 15% (L1-5) | Step: +2.5%/Lv
-Stacks with Double Attack</t>
-        </is>
-      </c>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr"/>
       <c r="Q264" t="inlineStr"/>
     </row>
     <row r="265">
@@ -17182,17 +15697,8 @@
       <c r="L267" t="inlineStr"/>
       <c r="M267" t="inlineStr"/>
       <c r="N267" t="inlineStr"/>
-      <c r="O267" t="inlineStr">
-        <is>
-          <t>Occasionally survive at 1 HP after receiving fatal damage.</t>
-        </is>
-      </c>
-      <c r="P267" t="inlineStr">
-        <is>
-          <t>Survival Rate: 20% -&gt; 30% -&gt; 40% -&gt; 50% -&gt; 60% (L1-5) | Step: +10%/Lv
-Prevents death when hit by lethal blows</t>
-        </is>
-      </c>
+      <c r="O267" t="inlineStr"/>
+      <c r="P267" t="inlineStr"/>
       <c r="Q267" t="inlineStr"/>
     </row>
     <row r="268">
@@ -17244,17 +15750,8 @@
       <c r="L268" t="inlineStr"/>
       <c r="M268" t="inlineStr"/>
       <c r="N268" t="inlineStr"/>
-      <c r="O268" t="inlineStr">
-        <is>
-          <t>Occasionally Defend automatically when receiving physical attacks.</t>
-        </is>
-      </c>
-      <c r="P268" t="inlineStr">
-        <is>
-          <t>Auto-Guard Rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5) | Step: +5%/Lv
-Halves incoming damage when triggered</t>
-        </is>
-      </c>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
       <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
@@ -17306,17 +15803,8 @@
       <c r="L269" t="inlineStr"/>
       <c r="M269" t="inlineStr"/>
       <c r="N269" t="inlineStr"/>
-      <c r="O269" t="inlineStr">
-        <is>
-          <t>Equip two one-handed weapons simultaneously.</t>
-        </is>
-      </c>
-      <c r="P269" t="inlineStr">
-        <is>
-          <t>Off-Hand ATK: 50% -&gt; 57.5% -&gt; 65% -&gt; 72.5% -&gt; 80% (L1-5) | Step: +7.5%/Lv
-Main hand weapon deals 100% ATK</t>
-        </is>
-      </c>
+      <c r="O269" t="inlineStr"/>
+      <c r="P269" t="inlineStr"/>
       <c r="Q269" t="inlineStr"/>
     </row>
     <row r="270">
@@ -17882,17 +16370,8 @@
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr"/>
       <c r="N280" t="inlineStr"/>
-      <c r="O280" t="inlineStr">
-        <is>
-          <t>Occasionally nullify physical damage.</t>
-        </is>
-      </c>
-      <c r="P280" t="inlineStr">
-        <is>
-          <t>Nullify Rate: 8% -&gt; 20% (+3%/Lv) | Levels: L1-5
-Completely negates incoming physical attacks when triggered</t>
-        </is>
-      </c>
+      <c r="O280" t="inlineStr"/>
+      <c r="P280" t="inlineStr"/>
       <c r="Q280" t="inlineStr"/>
     </row>
     <row r="281">
@@ -17944,17 +16423,8 @@
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="inlineStr"/>
       <c r="N281" t="inlineStr"/>
-      <c r="O281" t="inlineStr">
-        <is>
-          <t>Automatically cure own status ailments at start of turn.</t>
-        </is>
-      </c>
-      <c r="P281" t="inlineStr">
-        <is>
-          <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep -&gt; Slow
-Triggers automatically at start of user's combat turn</t>
-        </is>
-      </c>
+      <c r="O281" t="inlineStr"/>
+      <c r="P281" t="inlineStr"/>
       <c r="Q281" t="inlineStr"/>
     </row>
     <row r="282">
@@ -18006,17 +16476,8 @@
       <c r="L282" t="inlineStr"/>
       <c r="M282" t="inlineStr"/>
       <c r="N282" t="inlineStr"/>
-      <c r="O282" t="inlineStr">
-        <is>
-          <t>Boost physical ATK and DEX when HP drops below 50%.</t>
-        </is>
-      </c>
-      <c r="P282" t="inlineStr">
-        <is>
-          <t>ATK &amp; DEX: +20% -&gt; +40% (+5%/Lv) when HP &lt; 50% | Levels: L1-5
-Immediate combat stat trigger</t>
-        </is>
-      </c>
+      <c r="O282" t="inlineStr"/>
+      <c r="P282" t="inlineStr"/>
       <c r="Q282" t="inlineStr"/>
     </row>
     <row r="283">
@@ -18068,16 +16529,8 @@
       <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr"/>
       <c r="N283" t="inlineStr"/>
-      <c r="O283" t="inlineStr">
-        <is>
-          <t>Make it harder for chants, songs, and dances to be interrupted.</t>
-        </is>
-      </c>
-      <c r="P283" t="inlineStr">
-        <is>
-          <t>Interruption Resist: +20% -&gt; +50% (+7.5%/Lv) | 80% Crit Interrupt Res at Lv 5</t>
-        </is>
-      </c>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="inlineStr"/>
       <c r="Q283" t="inlineStr"/>
     </row>
     <row r="284">
@@ -18129,17 +16582,8 @@
       <c r="L284" t="inlineStr"/>
       <c r="M284" t="inlineStr"/>
       <c r="N284" t="inlineStr"/>
-      <c r="O284" t="inlineStr">
-        <is>
-          <t>Reduce chant time required to cast spells.</t>
-        </is>
-      </c>
-      <c r="P284" t="inlineStr">
-        <is>
-          <t>Chant Time Reduction: -10% -&gt; -30% (-5%/Lv) | Levels: L1-5
-Accelerates offensive and healing magic activation</t>
-        </is>
-      </c>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="inlineStr"/>
       <c r="Q284" t="inlineStr"/>
     </row>
     <row r="285">
@@ -18191,17 +16635,8 @@
       <c r="L285" t="inlineStr"/>
       <c r="M285" t="inlineStr"/>
       <c r="N285" t="inlineStr"/>
-      <c r="O285" t="inlineStr">
-        <is>
-          <t>Reduce TP consumption in battle.</t>
-        </is>
-      </c>
-      <c r="P285" t="inlineStr">
-        <is>
-          <t>TP Cost Reduction: -10% -&gt; -15% -&gt; -20% -&gt; -25% -&gt; -30% (L1-5)
-Lowers cost of all techniques and spells</t>
-        </is>
-      </c>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="inlineStr"/>
       <c r="Q285" t="inlineStr"/>
     </row>
     <row r="286">
@@ -18253,17 +16688,8 @@
       <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr"/>
       <c r="N286" t="inlineStr"/>
-      <c r="O286" t="inlineStr">
-        <is>
-          <t>Heighten magic accuracy for all cast spells.</t>
-        </is>
-      </c>
-      <c r="P286" t="inlineStr">
-        <is>
-          <t>Magic Accuracy: +15% -&gt; +35% (+5%/Lv) | Levels: L1-5
-Significantly reduces spell evasion by high RES targets</t>
-        </is>
-      </c>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="inlineStr"/>
       <c r="Q286" t="inlineStr"/>
     </row>
     <row r="287">
@@ -18315,17 +16741,8 @@
       <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr"/>
       <c r="N287" t="inlineStr"/>
-      <c r="O287" t="inlineStr">
-        <is>
-          <t>Reduce enemy preemptive strike rate in dungeons.</t>
-        </is>
-      </c>
-      <c r="P287" t="inlineStr">
-        <is>
-          <t>Preemptive Reduction: -20% -&gt; -60% (-10%/Lv) | Levels: L1-5
-Protects party from surprise enemy encounters</t>
-        </is>
-      </c>
+      <c r="O287" t="inlineStr"/>
+      <c r="P287" t="inlineStr"/>
       <c r="Q287" t="inlineStr"/>
     </row>
     <row r="288">
@@ -18377,17 +16794,8 @@
       <c r="L288" t="inlineStr"/>
       <c r="M288" t="inlineStr"/>
       <c r="N288" t="inlineStr"/>
-      <c r="O288" t="inlineStr">
-        <is>
-          <t>Increase party's preemptive strike rate against foes.</t>
-        </is>
-      </c>
-      <c r="P288" t="inlineStr">
-        <is>
-          <t>Party Preemptive Rate: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
-Grants free initial turn before enemies act</t>
-        </is>
-      </c>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="inlineStr"/>
       <c r="Q288" t="inlineStr"/>
     </row>
     <row r="289">
@@ -18439,17 +16847,8 @@
       <c r="L289" t="inlineStr"/>
       <c r="M289" t="inlineStr"/>
       <c r="N289" t="inlineStr"/>
-      <c r="O289" t="inlineStr">
-        <is>
-          <t>Increase success rate when attempting to flee from battle.</t>
-        </is>
-      </c>
-      <c r="P289" t="inlineStr">
-        <is>
-          <t>Escape Success: +20% -&gt; +50% (+7.5%/Lv) | Levels: L1-5
-Does not apply to scripted boss battles</t>
-        </is>
-      </c>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
       <c r="Q289" t="inlineStr"/>
     </row>
     <row r="290">
@@ -18501,17 +16900,8 @@
       <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr"/>
       <c r="N290" t="inlineStr"/>
-      <c r="O290" t="inlineStr">
-        <is>
-          <t>Increase enemies' item drop rate after battle.</t>
-        </is>
-      </c>
-      <c r="P290" t="inlineStr">
-        <is>
-          <t>Item Drop Rate: +10% -&gt; +15% -&gt; +20% -&gt; +25% -&gt; +30% (L1-5)
-Boosts party equipment and material acquisition</t>
-        </is>
-      </c>
+      <c r="O290" t="inlineStr"/>
+      <c r="P290" t="inlineStr"/>
       <c r="Q290" t="inlineStr"/>
     </row>
     <row r="291">
@@ -18563,17 +16953,8 @@
       <c r="L291" t="inlineStr"/>
       <c r="M291" t="inlineStr"/>
       <c r="N291" t="inlineStr"/>
-      <c r="O291" t="inlineStr">
-        <is>
-          <t>Increase amount of gold dropped by defeated enemies.</t>
-        </is>
-      </c>
-      <c r="P291" t="inlineStr">
-        <is>
-          <t>Gold Gain: +15% -&gt; +23% -&gt; +32% -&gt; +41% -&gt; +50% (L1-5)
-Earn bonus currency after every battle</t>
-        </is>
-      </c>
+      <c r="O291" t="inlineStr"/>
+      <c r="P291" t="inlineStr"/>
       <c r="Q291" t="inlineStr"/>
     </row>
     <row r="292">
@@ -18625,17 +17006,8 @@
       <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr"/>
       <c r="N292" t="inlineStr"/>
-      <c r="O292" t="inlineStr">
-        <is>
-          <t>Occasionally discover items while exploring dungeons.</t>
-        </is>
-      </c>
-      <c r="P292" t="inlineStr">
-        <is>
-          <t>Item Find Rate: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
-Finds consumables and crafting materials while walking</t>
-        </is>
-      </c>
+      <c r="O292" t="inlineStr"/>
+      <c r="P292" t="inlineStr"/>
       <c r="Q292" t="inlineStr"/>
     </row>
     <row r="293">
@@ -18688,17 +17060,8 @@
       <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr"/>
       <c r="N293" t="inlineStr"/>
-      <c r="O293" t="inlineStr">
-        <is>
-          <t>Restore party HP and TP slightly after winning a battle.</t>
-        </is>
-      </c>
-      <c r="P293" t="inlineStr">
-        <is>
-          <t>Post-Battle Recovery: 5% -&gt; 15% HP &amp; TP (+2.5%/Lv) | Levels: L1-5
-Restores whole party after combat conclusion</t>
-        </is>
-      </c>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr"/>
       <c r="Q293" t="inlineStr"/>
     </row>
     <row r="294">
@@ -18750,17 +17113,8 @@
       <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr"/>
       <c r="N294" t="inlineStr"/>
-      <c r="O294" t="inlineStr">
-        <is>
-          <t>Occasionally retain disposable items after using them in combat.</t>
-        </is>
-      </c>
-      <c r="P294" t="inlineStr">
-        <is>
-          <t>Item Retain Chance: 15% -&gt; 35% (+5%/Lv) | Levels: L1-5
-Item is not consumed from inventory when triggered</t>
-        </is>
-      </c>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="inlineStr"/>
       <c r="Q294" t="inlineStr"/>
     </row>
     <row r="295">
@@ -18812,17 +17166,8 @@
       <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr"/>
       <c r="N295" t="inlineStr"/>
-      <c r="O295" t="inlineStr">
-        <is>
-          <t>Increase effects of HP and TP recovery items during battle.</t>
-        </is>
-      </c>
-      <c r="P295" t="inlineStr">
-        <is>
-          <t>Item Potency: +20% -&gt; +30% -&gt; +40% -&gt; +50% -&gt; +60% (L1-5)
-Applies to all consumable recovery items used in combat</t>
-        </is>
-      </c>
+      <c r="O295" t="inlineStr"/>
+      <c r="P295" t="inlineStr"/>
       <c r="Q295" t="inlineStr"/>
     </row>
     <row r="296">
@@ -18874,17 +17219,8 @@
       <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr"/>
       <c r="N296" t="inlineStr"/>
-      <c r="O296" t="inlineStr">
-        <is>
-          <t>Become capable of performing two songs simultaneously.</t>
-        </is>
-      </c>
-      <c r="P296" t="inlineStr">
-        <is>
-          <t>Singing Speed: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
-Allows maintaining 2 active Bard songs at once</t>
-        </is>
-      </c>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
       <c r="Q296" t="inlineStr"/>
     </row>
     <row r="297">
@@ -18936,17 +17272,8 @@
       <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr"/>
       <c r="N297" t="inlineStr"/>
-      <c r="O297" t="inlineStr">
-        <is>
-          <t>Become capable of performing two dances simultaneously.</t>
-        </is>
-      </c>
-      <c r="P297" t="inlineStr">
-        <is>
-          <t>Dancing Speed: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
-Allows maintaining 2 active Dancer dances at once</t>
-        </is>
-      </c>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="inlineStr"/>
       <c r="Q297" t="inlineStr"/>
     </row>
     <row r="298">
@@ -18998,17 +17325,8 @@
       <c r="L298" t="inlineStr"/>
       <c r="M298" t="inlineStr"/>
       <c r="N298" t="inlineStr"/>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>Become capable of controlling two summoned dolls at once. Dolls gain Guts.</t>
-        </is>
-      </c>
-      <c r="P298" t="inlineStr">
-        <is>
-          <t>Doll Control Speed: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
-Maintains 2 active summoned dolls simultaneously</t>
-        </is>
-      </c>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="inlineStr"/>
       <c r="Q298" t="inlineStr"/>
     </row>
     <row r="299">
@@ -19060,17 +17378,8 @@
       <c r="L299" t="inlineStr"/>
       <c r="M299" t="inlineStr"/>
       <c r="N299" t="inlineStr"/>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>Increase doll power with strength of equipped Sealbook.</t>
-        </is>
-      </c>
-      <c r="P299" t="inlineStr">
-        <is>
-          <t>Doll Power Bonus: +10% -&gt; +30% (+5%/Lv) based on Sealbook level
-Levels: L1-5</t>
-        </is>
-      </c>
+      <c r="O299" t="inlineStr"/>
+      <c r="P299" t="inlineStr"/>
       <c r="Q299" t="inlineStr"/>
     </row>
     <row r="300">
@@ -19122,17 +17431,8 @@
       <c r="L300" t="inlineStr"/>
       <c r="M300" t="inlineStr"/>
       <c r="N300" t="inlineStr"/>
-      <c r="O300" t="inlineStr">
-        <is>
-          <t>Increased potency and effectiveness for all maid skills.</t>
-        </is>
-      </c>
-      <c r="P300" t="inlineStr">
-        <is>
-          <t>Maid Skill Bonus: +2% -&gt; +4% -&gt; +6% -&gt; +8% -&gt; +10% (L1-5)
-Empowers First Aid, Cook, and Clean</t>
-        </is>
-      </c>
+      <c r="O300" t="inlineStr"/>
+      <c r="P300" t="inlineStr"/>
       <c r="Q300" t="inlineStr"/>
     </row>
     <row r="301">
@@ -19184,17 +17484,8 @@
       <c r="L301" t="inlineStr"/>
       <c r="M301" t="inlineStr"/>
       <c r="N301" t="inlineStr"/>
-      <c r="O301" t="inlineStr">
-        <is>
-          <t>Increased potency and effectiveness for all songs.</t>
-        </is>
-      </c>
-      <c r="P301" t="inlineStr">
-        <is>
-          <t>Song Potency: +3% -&gt; +6% -&gt; +9% -&gt; +12% -&gt; +15% (L1-5)
-Empowers Bard songs and regeneration rates</t>
-        </is>
-      </c>
+      <c r="O301" t="inlineStr"/>
+      <c r="P301" t="inlineStr"/>
       <c r="Q301" t="inlineStr"/>
     </row>
     <row r="302">
@@ -19246,17 +17537,8 @@
       <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr"/>
       <c r="N302" t="inlineStr"/>
-      <c r="O302" t="inlineStr">
-        <is>
-          <t>Increased potency and effectiveness for all dances.</t>
-        </is>
-      </c>
-      <c r="P302" t="inlineStr">
-        <is>
-          <t>Dance Potency: +3% -&gt; +6% -&gt; +9% -&gt; +12% -&gt; +15% (L1-5)
-Empowers Dancer dances and status effects</t>
-        </is>
-      </c>
+      <c r="O302" t="inlineStr"/>
+      <c r="P302" t="inlineStr"/>
       <c r="Q302" t="inlineStr"/>
     </row>
     <row r="303">
@@ -19308,17 +17590,8 @@
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr"/>
       <c r="N303" t="inlineStr"/>
-      <c r="O303" t="inlineStr">
-        <is>
-          <t>Increased potency and effectiveness for all doll skills.</t>
-        </is>
-      </c>
-      <c r="P303" t="inlineStr">
-        <is>
-          <t>Doll Stat Bonus: +3% -&gt; +15% (+3%/Lv) | Levels: L1-5
-Increases damage, healing, and durability of summoned dolls</t>
-        </is>
-      </c>
+      <c r="O303" t="inlineStr"/>
+      <c r="P303" t="inlineStr"/>
       <c r="Q303" t="inlineStr"/>
     </row>
     <row r="304">
@@ -19370,17 +17643,8 @@
       <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr"/>
       <c r="N304" t="inlineStr"/>
-      <c r="O304" t="inlineStr">
-        <is>
-          <t>Occasionally attack twice when performing normal attacks.</t>
-        </is>
-      </c>
-      <c r="P304" t="inlineStr">
-        <is>
-          <t>Double Attack Rate: 8% -&gt; 20% (+3%/Lv) | Levels: L1-5
-Normal attack trigger</t>
-        </is>
-      </c>
+      <c r="O304" t="inlineStr"/>
+      <c r="P304" t="inlineStr"/>
       <c r="Q304" t="inlineStr"/>
     </row>
     <row r="305">
@@ -19432,17 +17696,8 @@
       <c r="L305" t="inlineStr"/>
       <c r="M305" t="inlineStr"/>
       <c r="N305" t="inlineStr"/>
-      <c r="O305" t="inlineStr">
-        <is>
-          <t>Reduce chant time required to start songs.</t>
-        </is>
-      </c>
-      <c r="P305" t="inlineStr">
-        <is>
-          <t>Song Chant Reduction: -10% -&gt; -30% (-5%/Lv) | Levels: L1-5
-Accelerates Bard song activation</t>
-        </is>
-      </c>
+      <c r="O305" t="inlineStr"/>
+      <c r="P305" t="inlineStr"/>
       <c r="Q305" t="inlineStr"/>
     </row>
     <row r="306">
@@ -19494,17 +17749,8 @@
       <c r="L306" t="inlineStr"/>
       <c r="M306" t="inlineStr"/>
       <c r="N306" t="inlineStr"/>
-      <c r="O306" t="inlineStr">
-        <is>
-          <t>Reduce purchase and identification prices at shops.</t>
-        </is>
-      </c>
-      <c r="P306" t="inlineStr">
-        <is>
-          <t>Shop Discount: -5% -&gt; -25% (-5%/Lv) | Levels: L1-5
-Lowers gold cost for item purchases and item identification</t>
-        </is>
-      </c>
+      <c r="O306" t="inlineStr"/>
+      <c r="P306" t="inlineStr"/>
       <c r="Q306" t="inlineStr"/>
     </row>
     <row r="307">
@@ -19556,17 +17802,8 @@
       <c r="L307" t="inlineStr"/>
       <c r="M307" t="inlineStr"/>
       <c r="N307" t="inlineStr"/>
-      <c r="O307" t="inlineStr">
-        <is>
-          <t>Mesmerize enemies with dance steps, causing them to lose turns.</t>
-        </is>
-      </c>
-      <c r="P307" t="inlineStr">
-        <is>
-          <t>Mesmerize Rate: 5% -&gt; 15% (+2.5%/Lv) | Levels: L1-5
-Enemy skips turn when mesmerized</t>
-        </is>
-      </c>
+      <c r="O307" t="inlineStr"/>
+      <c r="P307" t="inlineStr"/>
       <c r="Q307" t="inlineStr"/>
     </row>
     <row r="308">
@@ -19610,17 +17847,8 @@
       <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr"/>
       <c r="N308" t="inlineStr"/>
-      <c r="O308" t="inlineStr">
-        <is>
-          <t>Nullify first hit of battle against user.</t>
-        </is>
-      </c>
-      <c r="P308" t="inlineStr">
-        <is>
-          <t>100% nullification of the very first physical attack received
-Fixed passive (Level 1)</t>
-        </is>
-      </c>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="inlineStr"/>
       <c r="Q308" t="inlineStr"/>
     </row>
     <row r="309">
@@ -19664,17 +17892,8 @@
       <c r="L309" t="inlineStr"/>
       <c r="M309" t="inlineStr"/>
       <c r="N309" t="inlineStr"/>
-      <c r="O309" t="inlineStr">
-        <is>
-          <t>Heighten probability of beneficial results for random skills.</t>
-        </is>
-      </c>
-      <c r="P309" t="inlineStr">
-        <is>
-          <t>Drastically increases odds of favorable outcomes on Gamble skills
-Fixed passive (Level 1)</t>
-        </is>
-      </c>
+      <c r="O309" t="inlineStr"/>
+      <c r="P309" t="inlineStr"/>
       <c r="Q309" t="inlineStr"/>
     </row>
     <row r="310">
@@ -19808,17 +18027,8 @@
       <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr"/>
       <c r="N312" t="inlineStr"/>
-      <c r="O312" t="inlineStr">
-        <is>
-          <t>Occasionally land critical hits with offensive spells.</t>
-        </is>
-      </c>
-      <c r="P312" t="inlineStr">
-        <is>
-          <t>Spell Crit Rate: +10% -&gt; +13.75% -&gt; +17.5% -&gt; +21.25% -&gt; +25% (L1-5)
-Spell criticals deal 1.50x normal magic damage</t>
-        </is>
-      </c>
+      <c r="O312" t="inlineStr"/>
+      <c r="P312" t="inlineStr"/>
       <c r="Q312" t="inlineStr"/>
     </row>
     <row r="313">
@@ -19862,17 +18072,8 @@
       <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr"/>
       <c r="N313" t="inlineStr"/>
-      <c r="O313" t="inlineStr">
-        <is>
-          <t>Increase doll summon duration on battlefield.</t>
-        </is>
-      </c>
-      <c r="P313" t="inlineStr">
-        <is>
-          <t>Doll Summon Duration: +1 turn (Summons persist longer in battle)
-Fixed passive (Level 1)</t>
-        </is>
-      </c>
+      <c r="O313" t="inlineStr"/>
+      <c r="P313" t="inlineStr"/>
       <c r="Q313" t="inlineStr"/>
     </row>
     <row r="314">
@@ -19917,13 +18118,7 @@
       <c r="L314" t="inlineStr"/>
       <c r="M314" t="inlineStr"/>
       <c r="N314" t="inlineStr"/>
-      <c r="O314" t="inlineStr">
-        <is>
-          <t>Heroine: Luco | Damage scales with Pep.
-Effect: +1% damage per Pep point (up to +100% damage at Max Pep).
-[Crown EX]: Scales up to +150% damage bonus at Max Pep.</t>
-        </is>
-      </c>
+      <c r="O314" t="inlineStr"/>
       <c r="P314" t="inlineStr"/>
       <c r="Q314" t="inlineStr"/>
     </row>
@@ -19969,13 +18164,7 @@
       <c r="L315" t="inlineStr"/>
       <c r="M315" t="inlineStr"/>
       <c r="N315" t="inlineStr"/>
-      <c r="O315" t="inlineStr">
-        <is>
-          <t>Heroine: Mefmera | 15% trigger chance on enemy action.
-Inflicts Poison, Paralyze, Silence, or cancels enemy buffs.
-[Crown EX]: Trigger chance increases to 25% on any enemy action.</t>
-        </is>
-      </c>
+      <c r="O315" t="inlineStr"/>
       <c r="P315" t="inlineStr"/>
       <c r="Q315" t="inlineStr"/>
     </row>
@@ -20021,13 +18210,7 @@
       <c r="L316" t="inlineStr"/>
       <c r="M316" t="inlineStr"/>
       <c r="N316" t="inlineStr"/>
-      <c r="O316" t="inlineStr">
-        <is>
-          <t>Heroine: Souffle | 25% counter chance on physical contact.
-Inflicts Slow and -30% Speed on attacker.
-[Crown EX]: Counter chance increases to 40% on physical contact.</t>
-        </is>
-      </c>
+      <c r="O316" t="inlineStr"/>
       <c r="P316" t="inlineStr"/>
       <c r="Q316" t="inlineStr"/>
     </row>
@@ -20073,13 +18256,7 @@
       <c r="L317" t="inlineStr"/>
       <c r="M317" t="inlineStr"/>
       <c r="N317" t="inlineStr"/>
-      <c r="O317" t="inlineStr">
-        <is>
-          <t>Heroine: Grishna | Weapon Scaling Bonus.
-Grants +25% extra damage to all weapon-based techniques.
-[Crown EX]: Weapon technique damage bonus increases to +40%.</t>
-        </is>
-      </c>
+      <c r="O317" t="inlineStr"/>
       <c r="P317" t="inlineStr"/>
       <c r="Q317" t="inlineStr"/>
     </row>
@@ -20125,13 +18302,7 @@
       <c r="L318" t="inlineStr"/>
       <c r="M318" t="inlineStr"/>
       <c r="N318" t="inlineStr"/>
-      <c r="O318" t="inlineStr">
-        <is>
-          <t>Heroine: Yae | 20% activation rate on physical attacks.
-Guarantees 100% hit rate and completely ignores target DEF.
-[Crown EX]: Activation rate increases to 30% (ignores target DEF).</t>
-        </is>
-      </c>
+      <c r="O318" t="inlineStr"/>
       <c r="P318" t="inlineStr"/>
       <c r="Q318" t="inlineStr"/>
     </row>
@@ -20177,13 +18348,7 @@
       <c r="L319" t="inlineStr"/>
       <c r="M319" t="inlineStr"/>
       <c r="N319" t="inlineStr"/>
-      <c r="O319" t="inlineStr">
-        <is>
-          <t>Heroine: Lize | 10% nullification rate.
-Chance to completely negate all incoming damage.
-[Crown EX]: Total damage nullification rate increases to 15%.</t>
-        </is>
-      </c>
+      <c r="O319" t="inlineStr"/>
       <c r="P319" t="inlineStr"/>
       <c r="Q319" t="inlineStr"/>
     </row>
@@ -20229,13 +18394,7 @@
       <c r="L320" t="inlineStr"/>
       <c r="M320" t="inlineStr"/>
       <c r="N320" t="inlineStr"/>
-      <c r="O320" t="inlineStr">
-        <is>
-          <t>Heroine: Lilian | 25% banish rate before acting.
-Instantly eliminates enemy summon entities, puppets, and familiars.
-[Crown EX]: Enemy summon and minion banish rate increases to 40%.</t>
-        </is>
-      </c>
+      <c r="O320" t="inlineStr"/>
       <c r="P320" t="inlineStr"/>
       <c r="Q320" t="inlineStr"/>
     </row>
@@ -20281,13 +18440,7 @@
       <c r="L321" t="inlineStr"/>
       <c r="M321" t="inlineStr"/>
       <c r="N321" t="inlineStr"/>
-      <c r="O321" t="inlineStr">
-        <is>
-          <t>Heroine: Monica | 20% trigger rate at start of turn.
-Uses a free recovery item from personal stock without turn cost.
-[Crown EX]: Free item trigger rate increases to 30% without turn cost.</t>
-        </is>
-      </c>
+      <c r="O321" t="inlineStr"/>
       <c r="P321" t="inlineStr"/>
       <c r="Q321" t="inlineStr"/>
     </row>
@@ -20333,13 +18486,7 @@
       <c r="L322" t="inlineStr"/>
       <c r="M322" t="inlineStr"/>
       <c r="N322" t="inlineStr"/>
-      <c r="O322" t="inlineStr">
-        <is>
-          <t>Heroine: Alisia | Action Recovery Acceleration.
-Decreases action recovery delay by 20% after using skills or magic.
-[Crown EX]: Action recovery delay reduction increases to 30%.</t>
-        </is>
-      </c>
+      <c r="O322" t="inlineStr"/>
       <c r="P322" t="inlineStr"/>
       <c r="Q322" t="inlineStr"/>
     </row>
@@ -20385,13 +18532,7 @@
       <c r="L323" t="inlineStr"/>
       <c r="M323" t="inlineStr"/>
       <c r="N323" t="inlineStr"/>
-      <c r="O323" t="inlineStr">
-        <is>
-          <t>Heroine: Conette | Maid Mastery Booster.
-Increases potency and effectiveness of all Maid skills by +15%.
-[Crown EX]: Maid skill effectiveness bonus increases to +25%.</t>
-        </is>
-      </c>
+      <c r="O323" t="inlineStr"/>
       <c r="P323" t="inlineStr"/>
       <c r="Q323" t="inlineStr"/>
     </row>
@@ -20437,13 +18578,7 @@
       <c r="L324" t="inlineStr"/>
       <c r="M324" t="inlineStr"/>
       <c r="N324" t="inlineStr"/>
-      <c r="O324" t="inlineStr">
-        <is>
-          <t>Heroine: Yuni | 15% double action chance.
-Grants an immediate second action in the same turn.
-[Crown EX]: Immediate second action trigger rate increases to 25%.</t>
-        </is>
-      </c>
+      <c r="O324" t="inlineStr"/>
       <c r="P324" t="inlineStr"/>
       <c r="Q324" t="inlineStr"/>
     </row>
@@ -20489,13 +18624,7 @@
       <c r="L325" t="inlineStr"/>
       <c r="M325" t="inlineStr"/>
       <c r="N325" t="inlineStr"/>
-      <c r="O325" t="inlineStr">
-        <is>
-          <t>Heroine: Gina | Auto-Resurrection.
-Resurrects with 50% Max HP 3 turns after falling in combat.
-[Crown EX]: Resurrects with 100% Max HP after 2 turns.</t>
-        </is>
-      </c>
+      <c r="O325" t="inlineStr"/>
       <c r="P325" t="inlineStr"/>
       <c r="Q325" t="inlineStr"/>
     </row>
@@ -20541,13 +18670,7 @@
       <c r="L326" t="inlineStr"/>
       <c r="M326" t="inlineStr"/>
       <c r="N326" t="inlineStr"/>
-      <c r="O326" t="inlineStr">
-        <is>
-          <t>Heroine: Ist | Row Protection Barrier.
-Reduces incoming damage from Demons, Undead, and Apparitions by 20%.
-[Crown EX]: Damage reduction from Demons/Undead/Apparitions to 30%.</t>
-        </is>
-      </c>
+      <c r="O326" t="inlineStr"/>
       <c r="P326" t="inlineStr"/>
       <c r="Q326" t="inlineStr"/>
     </row>
@@ -20593,13 +18716,7 @@
       <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr"/>
       <c r="N327" t="inlineStr"/>
-      <c r="O327" t="inlineStr">
-        <is>
-          <t>Heroine: Fiora | 15% trigger rate at start of turn.
-Inflicts -20% ATK and -20% INT on all enemies.
-[Crown EX]: Turn-start debuff trigger rate increases to 25%.</t>
-        </is>
-      </c>
+      <c r="O327" t="inlineStr"/>
       <c r="P327" t="inlineStr"/>
       <c r="Q327" t="inlineStr"/>
     </row>
@@ -20645,13 +18762,7 @@
       <c r="L328" t="inlineStr"/>
       <c r="M328" t="inlineStr"/>
       <c r="N328" t="inlineStr"/>
-      <c r="O328" t="inlineStr">
-        <is>
-          <t>Heroine: Eltricia | 15% instant cast chance.
-Offensive and support spells activate immediately with 0 chant time.
-[Crown EX]: Instant cast (0 chant delay) rate increases to 25%.</t>
-        </is>
-      </c>
+      <c r="O328" t="inlineStr"/>
       <c r="P328" t="inlineStr"/>
       <c r="Q328" t="inlineStr"/>
     </row>
@@ -20698,13 +18809,7 @@
       <c r="L329" t="inlineStr"/>
       <c r="M329" t="inlineStr"/>
       <c r="N329" t="inlineStr"/>
-      <c r="O329" t="inlineStr">
-        <is>
-          <t>Heroine: Melvy | 20% damage reflect rate.
-Reflects 30% of received damage back to attacker as neutral damage.
-[Crown EX]: Damage reflect rate increases to 30% with 45% reflected.</t>
-        </is>
-      </c>
+      <c r="O329" t="inlineStr"/>
       <c r="P329" t="inlineStr"/>
       <c r="Q329" t="inlineStr"/>
     </row>
@@ -20750,13 +18855,7 @@
       <c r="L330" t="inlineStr"/>
       <c r="M330" t="inlineStr"/>
       <c r="N330" t="inlineStr"/>
-      <c r="O330" t="inlineStr">
-        <is>
-          <t>Heroine: Tsurara | Shadow Clone Follow-up.
-Normal attacks trigger an extra strike dealing 75% damage.
-[Crown EX]: Shadow strike follow-up deals 100% full attack damage.</t>
-        </is>
-      </c>
+      <c r="O330" t="inlineStr"/>
       <c r="P330" t="inlineStr"/>
       <c r="Q330" t="inlineStr"/>
     </row>
@@ -20802,13 +18901,7 @@
       <c r="L331" t="inlineStr"/>
       <c r="M331" t="inlineStr"/>
       <c r="N331" t="inlineStr"/>
-      <c r="O331" t="inlineStr">
-        <is>
-          <t>Heroine: Siena | Class Mastery Booster.
-Increases all class stat bonuses and weapon masteries by +10%.
-[Crown EX]: Class and weapon mastery bonuses increase to +15%.</t>
-        </is>
-      </c>
+      <c r="O331" t="inlineStr"/>
       <c r="P331" t="inlineStr"/>
       <c r="Q331" t="inlineStr"/>
     </row>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -444,7 +444,7 @@
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="46" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="47" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
@@ -1717,8 +1717,8 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5 Max) | TP Cost: 10 -&gt; 14 -&gt; 18 -&gt; 21 -&gt; 24
-Speed: 0.9x -&gt; 0.95x</t>
+          <t>Cover ends per hit: 70% -&gt; 62% -&gt; 54% -&gt; 46% -&gt; 40% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 14 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>effect_1</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -1776,8 +1776,8 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max) | TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26
-Speed: 0.9x -&gt; 0.95x</t>
+          <t>Parry ends per block: 80% -&gt; 72% -&gt; 64% -&gt; 58% -&gt; 52% (L1-5 Max)
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>effect_1</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Damage UP
+          <t>Damage UP | Turns on field: 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 3
 TP Cost: 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 59 -&gt; 62 | Speed: 0.82x</t>
         </is>
       </c>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>effect_2, effect_3</t>
+          <t>effect_2</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -6305,7 +6305,7 @@
       <c r="H101" t="inlineStr">
         <is>
           <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
-TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 38 | Speed: 1.15x</t>
+Turns on field: 5 | TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 38</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -6317,7 +6317,11 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
@@ -6359,7 +6363,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Doll magic damage UP | Doll magic accuracy UP
+          <t>Doll magic damage UP | Doll magic accuracy UP | Turns on field: 4
 TP Cost: 38 -&gt; 42 -&gt; 46 -&gt; 51 -&gt; 56 -&gt; 62 -&gt; 68 | Speed: 0.82x -&gt; 0.92x</t>
         </is>
       </c>
@@ -18104,7 +18108,7 @@
       <c r="G314" t="inlineStr">
         <is>
           <t>Significantly increase damage according to Pep.
-Lv1-9: 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3 -&gt; 2 | Crown EX: 1</t>
+Pep over 100 per +1% damage: 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3 -&gt; 2 | Crown EX: 1</t>
         </is>
       </c>
       <c r="H314" t="inlineStr"/>
@@ -18610,7 +18614,7 @@
       <c r="G325" t="inlineStr">
         <is>
           <t>If killed, revive after a certain number of turns.
-Lv1-9: 8% -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24% | Crown EX: 30%</t>
+Activation rate: 8% -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24% | Crown EX: 30%</t>
         </is>
       </c>
       <c r="H325" t="inlineStr"/>
@@ -18841,7 +18845,7 @@
       <c r="G330" t="inlineStr">
         <is>
           <t>Summons another self from the shadows to attack.
-Lv1-9: 4% -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% | Crown EX: 20%</t>
+Activation rate: 4% -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% | Crown EX: 20%</t>
         </is>
       </c>
       <c r="H330" t="inlineStr"/>
@@ -18887,7 +18891,7 @@
       <c r="G331" t="inlineStr">
         <is>
           <t>Increased effects for all class modifiers.
-Lv1-9: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Crown EX: 15</t>
+Class modifiers (%): 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Crown EX: 15</t>
         </is>
       </c>
       <c r="H331" t="inlineStr"/>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -3457,7 +3457,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Damage UP | Turns on field: 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 3
+          <t>Damage UP | Duration: 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 3
 TP Cost: 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 59 -&gt; 62 | Speed: 0.82x</t>
         </is>
       </c>
@@ -6305,7 +6305,7 @@
       <c r="H101" t="inlineStr">
         <is>
           <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
-Turns on field: 5 | TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 38</t>
+Duration: 5 | TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 38 | Speed: 1.15x</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -6317,11 +6317,7 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
@@ -6363,7 +6359,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Doll magic damage UP | Doll magic accuracy UP | Turns on field: 4
+          <t>Doll magic damage UP | Doll magic accuracy UP | Duration: 4
 TP Cost: 38 -&gt; 42 -&gt; 46 -&gt; 51 -&gt; 56 -&gt; 62 -&gt; 68 | Speed: 0.82x -&gt; 0.92x</t>
         </is>
       </c>
@@ -18660,7 +18656,7 @@
       <c r="G326" t="inlineStr">
         <is>
           <t>Whole row takes less damage from Demons, Undead, and Apparitions.
-Lv1-9: -12% -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -19 -&gt; -20% | Crown EX: -25%</t>
+Taken: -12% -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -19 -&gt; -20% | Crown EX: -25%</t>
         </is>
       </c>
       <c r="H326" t="inlineStr"/>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -440,7 +440,7 @@
     <col width="90" customWidth="1" min="5" max="5"/>
     <col width="74" customWidth="1" min="6" max="6"/>
     <col width="90" customWidth="1" min="7" max="7"/>
-    <col width="87" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="46" customWidth="1" min="11" max="11"/>
@@ -577,7 +577,7 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Enmity: 250
-Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 | Speed: 1.5x -&gt; 2x</t>
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5   |   Speed: 1.5x -&gt; 2x</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -687,7 +687,7 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>ATK: +8% -&gt; +10% -&gt; +12% -&gt; +15% -&gt; +18% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -746,7 +746,7 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>ATK: 125% -&gt; 134 -&gt; 143 -&gt; 152 -&gt; 161 -&gt; 170 -&gt; 178 -&gt; 186 -&gt; 193 -&gt; 200% (L10)
-Accuracy: +20% (+2%/Lv) | TP Cost: 5 (+2-3/Lv) -&gt; 28 | Speed: 0.8x -&gt; 0.9x</t>
+Accuracy: +20% (+2%/Lv)   |   TP Cost: 5 (+2-3/Lv) -&gt; 28   |   Speed: 0.8x -&gt; 0.9x</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -805,7 +805,7 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>Accuracy: +20% -&gt; +22 -&gt; +24 -&gt; +26 -&gt; +28 -&gt; +30 -&gt; +31 -&gt; +32 -&gt; +33 -&gt; +35% (L10)
-Buff cancel rate: 68% (+1-2%/Lv) -&gt; 85% | TP Cost: 5 (+1-2/Lv) -&gt; 18 | Speed: 0.9x</t>
+Buff cancel rate: 68% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 5 (+1-2/Lv) -&gt; 18   |   Speed: 0.9x</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -864,7 +864,7 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>ATK: +20% -&gt; +30% -&gt; +40% -&gt; +45% -&gt; +50% (L1-5 Max)
-DEF: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25% | Turns: 4 -&gt; 8 | TP Cost: 8 (+2/Lv) -&gt; 16</t>
+DEF: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%   |   Turns: 4 -&gt; 8   |   TP Cost: 8 (+2/Lv) -&gt; 16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -927,7 +927,7 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>DEF: +20% -&gt; +30% -&gt; +40% -&gt; +45% -&gt; +50% (L1-5 Max)
-ATK: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25% | Turns: 4 -&gt; 8 | TP Cost: 8 (+2/Lv) -&gt; 16</t>
+ATK: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%   |   Turns: 4 -&gt; 8   |   TP Cost: 8 (+2/Lv) -&gt; 16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -989,8 +989,8 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ATK: 85% -&gt; 90% -&gt; 94% -&gt; 98% -&gt; 102% (L1-5 Max) | Accuracy: +6% (+3-4%/Lv) -&gt; +20%
-Stun: 30% -&gt; 32% -&gt; 34% -&gt; 36% -&gt; 38% | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+          <t>ATK: 85% -&gt; 90% -&gt; 94% -&gt; 98% -&gt; 102% (L1-5 Max)   |   Accuracy: +6% (+3-4%/Lv) -&gt; +20%
+Stun: 30% -&gt; 32% -&gt; 34% -&gt; 36% -&gt; 38%   |   TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>ATK: 106% -&gt; 112 -&gt; 118 -&gt; 124 -&gt; 130 -&gt; 134 -&gt; 138 -&gt; 142 -&gt; 146 -&gt; 150% (L10)
-Accuracy: +5% (+2-3%/Lv) -&gt; +28% | Paralysis: 20% -&gt; 50% | TP Cost: 6 (+2/Lv) -&gt; 24</t>
+Accuracy: +5% (+2-3%/Lv) -&gt; +28%   |   Paralysis: 20% -&gt; 50%   |   TP Cost: 6 (+2/Lv) -&gt; 24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1115,8 +1115,8 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Critical rate: 5% (+2.5%/Lv) -&gt; 15% (L5 Max) | Enemy critical rate: 4% (+2%/Lv)
-Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
+          <t>Critical rate: 5% (+2.5%/Lv) -&gt; 15% (L5 Max)   |   Enemy critical rate: 4% (+2%/Lv)
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1175,7 +1175,7 @@
       <c r="H12" t="inlineStr">
         <is>
           <t>ATK: 80% -&gt; 83 -&gt; 86 -&gt; 89 -&gt; 91 -&gt; 94 -&gt; 97 -&gt; 100 -&gt; 105 -&gt; 110% (L10)
-Instakill: 10% (+1-2%/Lv) -&gt; 20% | Power decrease: 10% | TP Cost: 38 (+4/Lv) -&gt; 74</t>
+Instakill: 10% (+1-2%/Lv) -&gt; 20%   |   Power decrease: 10%   |   TP Cost: 38 (+4/Lv) -&gt; 74</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1238,7 +1238,7 @@
       <c r="H13" t="inlineStr">
         <is>
           <t>ATK: 84% -&gt; 88 -&gt; 92 -&gt; 96 -&gt; 100 -&gt; 104 -&gt; 108 -&gt; 112 -&gt; 116 -&gt; 120% (L10)
-Enemy DEF: -16% (-1%/Lv) | Turns: 4 | TP Cost: 14 (+2/Lv) -&gt; 32 | Speed: 0.8x</t>
+Enemy DEF: -16% (-1%/Lv)   |   Turns: 4   |   TP Cost: 14 (+2/Lv) -&gt; 32   |   Speed: 0.8x</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
       <c r="H15" t="inlineStr">
         <is>
           <t>ATK: 118% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 146 -&gt; 152 -&gt; 158% (L10)
-Critical rate: 10% | TP Cost: 36 (+2-3/Lv) -&gt; 61 | Speed: 0.7x -&gt; 0.8x</t>
+Critical rate: 10%   |   TP Cost: 36 (+2-3/Lv) -&gt; 61   |   Speed: 0.7x -&gt; 0.8x</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1410,8 +1410,8 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ATK: 74% (+4%/Lv) -&gt; 110% (L10 Max) | HP Absorb: 15% (+1-2%/Lv) -&gt; 25%
-TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36 | Speed: 0.9x</t>
+          <t>ATK: 74% (+4%/Lv) -&gt; 110% (L10 Max)   |   HP Absorb: 15% (+1-2%/Lv) -&gt; 25%
+TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36   |   Speed: 0.9x</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1470,7 +1470,7 @@
       <c r="H17" t="inlineStr">
         <is>
           <t>ATK: 65% -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 84 -&gt; 88 -&gt; 91 -&gt; 94 -&gt; 97 -&gt; 100% (L10)
-TP Absorb: 10% (+1-2%/Lv) -&gt; 20% | TP Cost: 6 (+2/Lv) -&gt; 24 | Speed: 0.9x</t>
+TP Absorb: 10% (+1-2%/Lv) -&gt; 20%   |   TP Cost: 6 (+2/Lv) -&gt; 24   |   Speed: 0.9x</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1529,7 +1529,7 @@
       <c r="H18" t="inlineStr">
         <is>
           <t>ATK: 130% -&gt; 144 -&gt; 157 -&gt; 170 -&gt; 182 -&gt; 194 -&gt; 204 -&gt; 212 -&gt; 220 -&gt; 228% (L10)
-Freeze: 20% (+3-4%/Lv) -&gt; 50% | Accuracy: +14% | TP Cost: 9 (+3/Lv) -&gt; 36</t>
+Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   Accuracy: +14%   |   TP Cost: 9 (+3/Lv) -&gt; 36</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ATK: 135% (+11-14%/Lv) -&gt; 247% | Petrify: 20% (+1-2%/Lv) -&gt; 35% | Accuracy: +10%
+          <t>ATK: 135% (+11-14%/Lv) -&gt; 247%   |   Petrify: 20% (+1-2%/Lv) -&gt; 35%   |   Accuracy: +10%
 TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 37 -&gt; 42</t>
         </is>
       </c>
@@ -1655,7 +1655,7 @@
       <c r="H20" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 130 -&gt; 140 -&gt; 148 -&gt; 156 -&gt; 164 -&gt; 170 -&gt; 176 -&gt; 180 -&gt; 184% (L10)
-Targets: 2 -&gt; 2 -&gt; 2 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 | TP Cost: 26 (+4-6/Lv) -&gt; 68</t>
+Targets: 2 -&gt; 2 -&gt; 2 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5   |   TP Cost: 26 (+4-6/Lv) -&gt; 68</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1718,7 +1718,7 @@
       <c r="H21" t="inlineStr">
         <is>
           <t>Cover ends per hit: 70% -&gt; 62% -&gt; 54% -&gt; 46% -&gt; 40% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 14 -&gt; 18 -&gt; 21 -&gt; 24</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 10 -&gt; 14 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1777,7 +1777,7 @@
       <c r="H22" t="inlineStr">
         <is>
           <t>Parry ends per block: 80% -&gt; 72% -&gt; 64% -&gt; 58% -&gt; 52% (L1-5 Max)
-Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1836,7 +1836,7 @@
       <c r="H23" t="inlineStr">
         <is>
           <t>ATK: 130% -&gt; 140 -&gt; 150 -&gt; 160 -&gt; 170 -&gt; 180 -&gt; 190 -&gt; 200 -&gt; 211 -&gt; 222% (L10)
-Accuracy: +6% -&gt; +20% | Damage vs. unholy: +65% | TP Cost: 12 (+3/Lv) -&gt; 39</t>
+Accuracy: +6% -&gt; +20%   |   Damage vs. unholy: +65%   |   TP Cost: 12 (+3/Lv) -&gt; 39</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1899,7 +1899,7 @@
       <c r="H24" t="inlineStr">
         <is>
           <t>Damage reduction rate: 12% -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30%
-Turns: 5 | TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
+Turns: 5   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1958,7 +1958,7 @@
       <c r="H25" t="inlineStr">
         <is>
           <t>Damage reduction rate: 12% -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30%
-Turns: 5 | TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
+Turns: 5   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2017,7 +2017,7 @@
       <c r="H26" t="inlineStr">
         <is>
           <t>ATK: 96% -&gt; 100 -&gt; 104 -&gt; 108 -&gt; 113 -&gt; 118 -&gt; 123 -&gt; 128 -&gt; 133 -&gt; 138% (L10)
-Paralysis: 20% (+2-3%/Lv) -&gt; 40% | TP Cost: 26 (+4-5/Lv) -&gt; 64 | Speed: 0.8x</t>
+Paralysis: 20% (+2-3%/Lv) -&gt; 40%   |   TP Cost: 26 (+4-5/Lv) -&gt; 64   |   Speed: 0.8x</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -2076,7 +2076,7 @@
       <c r="H27" t="inlineStr">
         <is>
           <t>ATK: 135% -&gt; 149 -&gt; 163 -&gt; 176 -&gt; 189 -&gt; 201 -&gt; 213 -&gt; 223 -&gt; 234 -&gt; 245% (L10)
-Silence: 20% (+3-4%/Lv) -&gt; 50% | Accuracy: +15% | TP Cost: 7 (+3/Lv) -&gt; 34</t>
+Silence: 20% (+3-4%/Lv) -&gt; 50%   |   Accuracy: +15%   |   TP Cost: 7 (+3/Lv) -&gt; 34</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
       <c r="H28" t="inlineStr">
         <is>
           <t>ATK: 116% -&gt; 118 -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 146 -&gt; 152% (L10)
-Heavy Lance bonus: +20% | TP Cost: 36 (+3-6/Lv) -&gt; 71 | Speed: 0.7x -&gt; 0.8x</t>
+Heavy Lance bonus: +20%   |   TP Cost: 36 (+3-6/Lv) -&gt; 71   |   Speed: 0.7x -&gt; 0.8x</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -2198,7 +2198,7 @@
       <c r="H29" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 130 -&gt; 142 -&gt; 154 -&gt; 165 -&gt; 176 -&gt; 186 -&gt; 196 -&gt; 204 -&gt; 212% (L10)
-Accuracy: +5% (+1-2%/Lv) -&gt; +15% | TP Cost: 32 (+3/Lv) -&gt; 59 | Speed: 0.8x</t>
+Accuracy: +5% (+1-2%/Lv) -&gt; +15%   |   TP Cost: 32 (+3/Lv) -&gt; 59   |   Speed: 0.8x</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -2257,7 +2257,7 @@
       <c r="H30" t="inlineStr">
         <is>
           <t>Damage: 1.05x -&gt; 1.1x -&gt; 1.16x -&gt; 1.22x -&gt; 1.3x (L1-5 Max)
-Turns: 2 | TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 | Speed: 0.84x -&gt; 0.9x</t>
+Turns: 2   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Speed: 0.84x -&gt; 0.9x</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -2420,7 +2420,7 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>ATK: 105% -&gt; 109 -&gt; 113 -&gt; 116 -&gt; 119 -&gt; 121 -&gt; 123 -&gt; 125 -&gt; 127 -&gt; 129% (L10)
-TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 -&gt; 28 -&gt; 30 | Speed: 0.9x</t>
+TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 -&gt; 28 -&gt; 30   |   Speed: 0.9x</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>ATK: 170% -&gt; 182% -&gt; 194% -&gt; 204% -&gt; 212% (L1-5 Max)
-TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 35 -&gt; 38 | Speed: 0.85x</t>
+TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 35 -&gt; 38   |   Speed: 0.85x</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -2530,7 +2530,7 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>Evasion: +10% -&gt; +13% -&gt; +16% -&gt; +18% -&gt; +20% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>Accuracy: +15% -&gt; +17 -&gt; +19 -&gt; +21 -&gt; +23 -&gt; +25 -&gt; +26 -&gt; +27 -&gt; +28 -&gt; +30% (L10)
-Turns: 5 -&gt; 9 | TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28</t>
+Turns: 5 -&gt; 9   |   TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>Speed increase: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 20% (L10)
-Turns: 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 5 -&gt; 6 | TP Cost: 14 (+2/Lv) -&gt; 32</t>
+Turns: 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 5 -&gt; 6   |   TP Cost: 14 (+2/Lv) -&gt; 32</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2761,8 +2761,8 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Physical evasion: +15% (+2-3%/Lv) -&gt; +25% | Magic evasion: +10% (+2-3%/Lv) -&gt; +20%
-Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 | Speed: 0.9x</t>
+          <t>Physical evasion: +15% (+2-3%/Lv) -&gt; +25%   |   Magic evasion: +10% (+2-3%/Lv) -&gt; +20%
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20   |   Speed: 0.9x</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2821,7 +2821,7 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>ATK: 116% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150 -&gt; 156% (L10)
-Sleep: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 7 (+2/Lv) -&gt; 25 | Speed: 0.9x</t>
+Sleep: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
       <c r="H41" t="inlineStr">
         <is>
           <t>ATK: 116% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150 -&gt; 156% (L10)
-Silence: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 7 (+2/Lv) -&gt; 25 | Speed: 0.9x</t>
+Silence: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2939,7 +2939,7 @@
       <c r="H42" t="inlineStr">
         <is>
           <t>ATK: 112% -&gt; 116 -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150% (L10)
-Stun: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 7 (+2/Lv) -&gt; 25 | Speed: 0.9x</t>
+Stun: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2997,8 +2997,8 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Number of attacks: 3 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 | ATK: 104% -&gt; 148%
-Power decrease: 25% -&gt; 14% | TP Cost: 30 (+4-6/Lv) -&gt; 72 | Speed: 0.75x -&gt; 0.85x</t>
+          <t>Number of attacks: 3 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5   |   ATK: 104% -&gt; 148%
+Power decrease: 25% -&gt; 14%   |   TP Cost: 30 (+4-6/Lv) -&gt; 72   |   Speed: 0.75x -&gt; 0.85x</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -3057,7 +3057,7 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>ATK: 114% -&gt; 118% -&gt; 122% -&gt; 126% -&gt; 130% (L1-5 Max)
-TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 | Speed: 1x -&gt; 1.12x</t>
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16   |   Speed: 1x -&gt; 1.12x</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -3111,8 +3111,8 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Damage: 3.3x -&gt; 3.45x -&gt; 3.6x -&gt; 3.8x -&gt; 4x (L1-5 Max) | ATK: 88%
-TP Cost: 42 -&gt; 50 -&gt; 57 -&gt; 63 -&gt; 68 | Speed: 0.4x</t>
+          <t>Damage: 3.3x -&gt; 3.45x -&gt; 3.6x -&gt; 3.8x -&gt; 4x (L1-5 Max)   |   ATK: 88%
+TP Cost: 42 -&gt; 50 -&gt; 57 -&gt; 63 -&gt; 68   |   Speed: 0.4x</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -3167,7 +3167,7 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170% (L10)
-Poison: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 7 (+2/Lv) -&gt; 25</t>
+Poison: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -3226,7 +3226,7 @@
       <c r="H47" t="inlineStr">
         <is>
           <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170% (L10)
-Freeze: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 8 (+2/Lv) -&gt; 26</t>
+Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 8 (+2/Lv) -&gt; 26</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -3285,7 +3285,7 @@
       <c r="H48" t="inlineStr">
         <is>
           <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170% (L10)
-Paralysis: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 8 (+2/Lv) -&gt; 26</t>
+Paralysis: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 8 (+2/Lv) -&gt; 26</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
       <c r="H49" t="inlineStr">
         <is>
           <t>ATK: 116% -&gt; 122 -&gt; 128 -&gt; 134 -&gt; 140 -&gt; 145 -&gt; 150 -&gt; 155 -&gt; 160 -&gt; 165% (L10)
-Slow: 20% (+3-4%/Lv) -&gt; 50% | TP Cost: 9 (+2/Lv) -&gt; 27 | Speed: 0.95x</t>
+Slow: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 9 (+2/Lv) -&gt; 27   |   Speed: 0.95x</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -3403,7 +3403,7 @@
       <c r="H50" t="inlineStr">
         <is>
           <t>ATK: 84% -&gt; 88 -&gt; 92 -&gt; 96 -&gt; 100 -&gt; 103 -&gt; 106 -&gt; 109 -&gt; 112 -&gt; 115% (L10)
-TP Cost: 20 -&gt; 23 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 | Speed: 0.65x</t>
+TP Cost: 20 -&gt; 23 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48   |   Speed: 0.65x</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -3457,8 +3457,8 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Damage UP | Duration: 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 3
-TP Cost: 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 59 -&gt; 62 | Speed: 0.82x</t>
+          <t>Damage UP   |   Duration: 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 3
+TP Cost: 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 59 -&gt; 62   |   Speed: 0.82x</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -3525,7 +3525,7 @@
       <c r="H52" t="inlineStr">
         <is>
           <t>ATK: 130% -&gt; 144 -&gt; 158 -&gt; 171 -&gt; 184 -&gt; 196 -&gt; 207 -&gt; 217 -&gt; 226 -&gt; 234% (L10)
-Critical rate: 5% (+1-3%/Lv) -&gt; 25% | TP Cost: 24 (+3-4/Lv) -&gt; 55 | Speed: 0.7x</t>
+Critical rate: 5% (+1-3%/Lv) -&gt; 25%   |   TP Cost: 24 (+3-4/Lv) -&gt; 55   |   Speed: 0.7x</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -3584,7 +3584,7 @@
       <c r="H53" t="inlineStr">
         <is>
           <t>ATK: 94% (+3-6%/Lv) -&gt; 130% | Speed decrease chance: 30% -&gt; 75% | Speed decrease: 10%
-Turns: 4 | TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50</t>
+Turns: 4   |   TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -3647,7 +3647,7 @@
       <c r="H54" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 126 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 154 -&gt; 162 -&gt; 170 -&gt; 180 -&gt; 192% (L10)
-Stun: 10% -&gt; 20% | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36</t>
+Stun: 10% -&gt; 20%   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3764,7 +3764,7 @@
       <c r="H56" t="inlineStr">
         <is>
           <t>Magic damage: +38% -&gt; +42% -&gt; +47% -&gt; +53% -&gt; +60% (L1-5 Max)
-Magic accuracy: -2% (-2%/Lv) | Turns: 6 | TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 32</t>
+Magic accuracy: -2% (-2%/Lv)   |   Turns: 6   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 32</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -3823,7 +3823,7 @@
       <c r="H57" t="inlineStr">
         <is>
           <t>Damage: 2x -&gt; 2.2 -&gt; 2.4 -&gt; 2.6 -&gt; 2.8 -&gt; 3 -&gt; 3.25 -&gt; 3.5 -&gt; 3.75 -&gt; 4x (L10)
-Accuracy: +10% (+2-4%/Lv) -&gt; +30% | ATK: 82% | TP Cost: 28 (+4/Lv) -&gt; 64</t>
+Accuracy: +10% (+2-4%/Lv) -&gt; +30%   |   ATK: 82%   |   TP Cost: 28 (+4/Lv) -&gt; 64</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3885,8 +3885,8 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ATK: 135% -&gt; 147 -&gt; 159 -&gt; 171 -&gt; 183 -&gt; 193 -&gt; 203 -&gt; 213 -&gt; 220 -&gt; 225% | DEF: -10%
-Turns: 4 | TP Cost: 25 -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 48 -&gt; 51 -&gt; 54 -&gt; 57</t>
+          <t>ATK: 135% -&gt; 147 -&gt; 159 -&gt; 171 -&gt; 183 -&gt; 193 -&gt; 203 -&gt; 213 -&gt; 220 -&gt; 225%   |   DEF: -10%
+Turns: 4   |   TP Cost: 25 -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 48 -&gt; 51 -&gt; 54 -&gt; 57</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -4004,7 +4004,7 @@
       <c r="H60" t="inlineStr">
         <is>
           <t>Damage reduction: 18% -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36% (L10)
-Turns: 4 -&gt; 7 | TP Cost: 22 -&gt; 25 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 56</t>
+Turns: 4 -&gt; 7   |   TP Cost: 22 -&gt; 25 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 56</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -4067,7 +4067,7 @@
       <c r="H61" t="inlineStr">
         <is>
           <t>Stat: +20% -&gt; +23% -&gt; +26% -&gt; +29% -&gt; +32% (L1-5 Max)
-Turns: 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 6 | TP Cost: 52 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 92 | Speed: 1.25x</t>
+Turns: 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 6   |   TP Cost: 52 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 92   |   Speed: 1.25x</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -4122,7 +4122,7 @@
       <c r="H62" t="inlineStr">
         <is>
           <t>ATK: 136% -&gt; 142 -&gt; 148 -&gt; 155 -&gt; 162 -&gt; 172 -&gt; 182 -&gt; 193 -&gt; 204 -&gt; 216% (L10)
-Accuracy: +10% (+1-2%/Lv) -&gt; +20% | TP Cost: 13 (+3-4/Lv) -&gt; 45 | Speed: 0.9x -&gt; 1x</t>
+Accuracy: +10% (+1-2%/Lv) -&gt; +20%   |   TP Cost: 13 (+3-4/Lv) -&gt; 45   |   Speed: 0.9x -&gt; 1x</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -4181,7 +4181,7 @@
       <c r="H63" t="inlineStr">
         <is>
           <t>ATK: 150% -&gt; 162 -&gt; 174 -&gt; 186 -&gt; 198 -&gt; 208 -&gt; 218 -&gt; 228 -&gt; 236 -&gt; 244% (L10)
-Freeze: 20% (+3-4%/Lv) -&gt; 50% | Silence: 20% -&gt; 50% | TP Cost: 9 (+3/Lv) -&gt; 36</t>
+Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   Silence: 20% -&gt; 50%   |   TP Cost: 9 (+3/Lv) -&gt; 36</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -4991,7 +4991,7 @@
       <c r="H78" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 145 -&gt; 150 -&gt; 155 -&gt; 160% (L10)
-Power decrease: 10% | TP Cost: 22 (+3-4/Lv) -&gt; 50 | Speed: 0.75x -&gt; 0.85x</t>
+Power decrease: 10%   |   TP Cost: 22 (+3-4/Lv) -&gt; 50   |   Speed: 0.75x -&gt; 0.85x</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -5050,7 +5050,7 @@
       <c r="H79" t="inlineStr">
         <is>
           <t>ATK: 107% -&gt; 114% -&gt; 121% -&gt; 128% -&gt; 136% (L1-5 Max)
-TP Cost: 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 | Speed: 0.75x -&gt; 0.8x</t>
+TP Cost: 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46   |   Speed: 0.75x -&gt; 0.8x</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -5104,8 +5104,8 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ATK: 135% -&gt; 142% -&gt; 149% -&gt; 157% -&gt; 165% (L1-5 Max) | Silence: 25% (+3%/Lv)
-Paralysis: 20% -&gt; 23% -&gt; 26% -&gt; 29% -&gt; 32% | TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
+          <t>ATK: 135% -&gt; 142% -&gt; 149% -&gt; 157% -&gt; 165% (L1-5 Max)   |   Silence: 25% (+3%/Lv)
+Paralysis: 20% -&gt; 23% -&gt; 26% -&gt; 29% -&gt; 32%   |   TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -5164,7 +5164,7 @@
       <c r="H81" t="inlineStr">
         <is>
           <t>ATK: 104% -&gt; 108 -&gt; 112 -&gt; 116 -&gt; 120 -&gt; 124 -&gt; 127 -&gt; 130 -&gt; 133 -&gt; 136% (L10)
-Accuracy: +20% | TP Cost: 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 56 -&gt; 60</t>
+Accuracy: +20%   |   TP Cost: 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 56 -&gt; 60</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -5223,7 +5223,7 @@
       <c r="H82" t="inlineStr">
         <is>
           <t>HP recovery: 20% -&gt; 25% -&gt; 30% -&gt; 35% -&gt; 40% (L1-5 Max)
-TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Speed: 1.5x</t>
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -5323,7 +5323,7 @@
       <c r="H84" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 126 -&gt; 132 -&gt; 138 -&gt; 142 -&gt; 150 -&gt; 158 -&gt; 168 -&gt; 178 -&gt; 190% (L10)
-Instakill: 15% (+1-2%/Lv) -&gt; 25% | TP Cost: 17 (+2/Lv) -&gt; 35 | Speed: 0.88x</t>
+Instakill: 15% (+1-2%/Lv) -&gt; 25%   |   TP Cost: 17 (+2/Lv) -&gt; 35   |   Speed: 0.88x</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -5382,7 +5382,7 @@
       <c r="H85" t="inlineStr">
         <is>
           <t>ATK: 95% -&gt; 99 -&gt; 103 -&gt; 107 -&gt; 111 -&gt; 115 -&gt; 119 -&gt; 123 -&gt; 127 -&gt; 131% (L10)
-Stun: 40% (+3-4%/Lv) -&gt; 70% | TP Cost: 32 (+2/Lv) -&gt; 50 | Speed: 0.65x</t>
+Stun: 40% (+3-4%/Lv) -&gt; 70%   |   TP Cost: 32 (+2/Lv) -&gt; 50   |   Speed: 0.65x</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -5440,8 +5440,8 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ATK: 15% (+5%/Lv) -&gt; 35% (L5 Max) | DEF: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+          <t>ATK: 15% (+5%/Lv) -&gt; 35% (L5 Max)   |   DEF: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -5545,7 +5545,7 @@
       <c r="H88" t="inlineStr">
         <is>
           <t>Conversion success: 35% -&gt; 42% -&gt; 49% -&gt; 57% -&gt; 65% (L1-5 Max)
-TP Cost: 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 | Speed: 0.85x</t>
+TP Cost: 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32   |   Speed: 0.85x</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -5600,7 +5600,7 @@
       <c r="H89" t="inlineStr">
         <is>
           <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 164 -&gt; 170 -&gt; 176% (L10)
-Poison: 50% (+3-4%/Lv) -&gt; 80% | TP Cost: 22 (+4/Lv) -&gt; 58 | Speed: 0.6x -&gt; 0.7x</t>
+Poison: 50% (+3-4%/Lv) -&gt; 80%   |   TP Cost: 22 (+4/Lv) -&gt; 58   |   Speed: 0.6x -&gt; 0.7x</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -5659,7 +5659,7 @@
       <c r="H90" t="inlineStr">
         <is>
           <t>ATK: 150% -&gt; 162 -&gt; 174 -&gt; 186 -&gt; 198 -&gt; 208 -&gt; 218 -&gt; 228 -&gt; 240 -&gt; 256% (L10)
-Turn delay rate: 25% (+2%/Lv) | TP Cost: 10 (+2-3/Lv) -&gt; 32 | Speed: 0.95x</t>
+Turn delay rate: 25% (+2%/Lv)   |   TP Cost: 10 (+2-3/Lv) -&gt; 32   |   Speed: 0.95x</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -5767,8 +5767,8 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ATK: 130% (+8%/Lv) -&gt; 202% (L10 Max) | Slow: 25% -&gt; 45% | Accuracy: -5% (+2%/Lv)
-TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50 | Speed: 0.75x</t>
+          <t>ATK: 130% (+8%/Lv) -&gt; 202% (L10 Max)   |   Slow: 25% -&gt; 45%   |   Accuracy: -5% (+2%/Lv)
+TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50   |   Speed: 0.75x</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -5826,8 +5826,8 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>ATK: 88% -&gt; 92% -&gt; 97% -&gt; 103% -&gt; 110% (L1-5 Max) | Max HP reduction: 50% -&gt; 100%
-Turns: 6 | TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 23 -&gt; 25 | Speed: 0.85x</t>
+          <t>ATK: 88% -&gt; 92% -&gt; 97% -&gt; 103% -&gt; 110% (L1-5 Max)   |   Max HP reduction: 50% -&gt; 100%
+Turns: 6   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 23 -&gt; 25   |   Speed: 0.85x</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -5886,7 +5886,7 @@
       <c r="H94" t="inlineStr">
         <is>
           <t>DEF conversion bonus: 60% -&gt; 80% -&gt; 100% -&gt; 125% -&gt; 150% (L1-5 Max)
-Turns: 2 | TP Cost: 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 | Speed: 1.15x</t>
+Turns: 2   |   TP Cost: 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50   |   Speed: 1.15x</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -5986,7 +5986,7 @@
       <c r="H96" t="inlineStr">
         <is>
           <t>ATK: 118% -&gt; 122 -&gt; 126 -&gt; 130 -&gt; 134 -&gt; 138 -&gt; 142 -&gt; 145 -&gt; 148 -&gt; 151% (L10)
-Accuracy UP | TP Cost: 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40</t>
+Accuracy UP   |   TP Cost: 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>ATK UP | Duration: 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 5 -&gt; 6
+          <t>ATK UP   |   Duration: 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 5 -&gt; 6
 TP Cost: 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42</t>
         </is>
       </c>
@@ -6116,7 +6116,7 @@
       <c r="H98" t="inlineStr">
         <is>
           <t>ATK UP | Duration: 3 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 | Paralysis rate UP
-TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 44 -&gt; 46 -&gt; 48 | Speed: 0.9x</t>
+TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 44 -&gt; 46 -&gt; 48   |   Speed: 0.9x</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -6178,8 +6178,8 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>HP recovery UP | Duration: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5 (L1-5 Max)
-TP Cost: 30 -&gt; 33 -&gt; 37 -&gt; 42 -&gt; 48 | Speed: 0.9x</t>
+          <t>HP recovery UP   |   Duration: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5 (L1-5 Max)
+TP Cost: 30 -&gt; 33 -&gt; 37 -&gt; 42 -&gt; 48   |   Speed: 0.9x</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -6241,8 +6241,8 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>ATK UP | Duration: 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4
-TP Cost: 42 -&gt; 44 -&gt; 46 -&gt; 48 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 60 -&gt; 64 -&gt; 70 | Speed: 0.75x</t>
+          <t>ATK UP   |   Duration: 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4
+TP Cost: 42 -&gt; 44 -&gt; 46 -&gt; 48 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 60 -&gt; 64 -&gt; 70   |   Speed: 0.75x</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -6305,7 +6305,7 @@
       <c r="H101" t="inlineStr">
         <is>
           <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
-Duration: 5 | TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 38 | Speed: 1.15x</t>
+Duration: 5   |   TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 38   |   Speed: 1.15x</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -6359,8 +6359,8 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Doll magic damage UP | Doll magic accuracy UP | Duration: 4
-TP Cost: 38 -&gt; 42 -&gt; 46 -&gt; 51 -&gt; 56 -&gt; 62 -&gt; 68 | Speed: 0.82x -&gt; 0.92x</t>
+          <t>Doll magic damage UP   |   Doll magic accuracy UP   |   Duration: 4
+TP Cost: 38 -&gt; 42 -&gt; 46 -&gt; 51 -&gt; 56 -&gt; 62 -&gt; 68   |   Speed: 0.82x -&gt; 0.92x</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -8733,7 +8733,7 @@
       <c r="H145" t="inlineStr">
         <is>
           <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
-Accuracy: 86% (+1%/Lv) | TP Cost: 5 (+2-4/Lv) -&gt; 32 | Speed: 2.25x</t>
+Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -8796,7 +8796,7 @@
       <c r="H146" t="inlineStr">
         <is>
           <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
-Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 15 (+4-6/Lv) -&gt; 60 | Speed: 1.7x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -8859,7 +8859,7 @@
       <c r="H147" t="inlineStr">
         <is>
           <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
-Accuracy: 75% (+1-2%/Lv) -&gt; 85% | TP Cost: 42 (+6-10/Lv) -&gt; 120 | Speed: 1.3x</t>
+Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -8921,8 +8921,8 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max) | Accuracy: 82% (+2%/Lv)
-TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84 | Speed: 1.5x | Chant: 0.75x -&gt; 0.7x</t>
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max)   |   Accuracy: 82% (+2%/Lv)
+TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -8977,7 +8977,7 @@
       <c r="H149" t="inlineStr">
         <is>
           <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
-Accuracy: 86% (+1%/Lv) | TP Cost: 5 (+2-4/Lv) -&gt; 32 | Speed: 2.25x</t>
+Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -9040,7 +9040,7 @@
       <c r="H150" t="inlineStr">
         <is>
           <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
-Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 15 (+4-6/Lv) -&gt; 60 | Speed: 1.7x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -9103,7 +9103,7 @@
       <c r="H151" t="inlineStr">
         <is>
           <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
-Accuracy: 75% (+1-2%/Lv) -&gt; 85% | TP Cost: 42 (+6-10/Lv) -&gt; 120 | Speed: 1.3x</t>
+Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -9165,8 +9165,8 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max) | Accuracy: 82% (+2%/Lv)
-TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84 | Speed: 1.5x | Chant: 0.75x -&gt; 0.7x</t>
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max)   |   Accuracy: 82% (+2%/Lv)
+TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -9221,7 +9221,7 @@
       <c r="H153" t="inlineStr">
         <is>
           <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
-Accuracy: 86% (+1%/Lv) | TP Cost: 5 (+2-4/Lv) -&gt; 32 | Speed: 2.25x</t>
+Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -9284,7 +9284,7 @@
       <c r="H154" t="inlineStr">
         <is>
           <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
-Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 15 (+4-6/Lv) -&gt; 60 | Speed: 1.7x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -9347,7 +9347,7 @@
       <c r="H155" t="inlineStr">
         <is>
           <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
-Accuracy: 75% (+1-2%/Lv) -&gt; 85% | TP Cost: 42 (+6-10/Lv) -&gt; 120 | Speed: 1.3x</t>
+Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -9409,8 +9409,8 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max) | Accuracy: 82% (+2%/Lv)
-TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84 | Speed: 1.5x | Chant: 0.75x -&gt; 0.7x</t>
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max)   |   Accuracy: 82% (+2%/Lv)
+TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -9465,7 +9465,7 @@
       <c r="H157" t="inlineStr">
         <is>
           <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
-Accuracy: 86% (+1%/Lv) | TP Cost: 5 (+2-4/Lv) -&gt; 32 | Speed: 2.25x</t>
+Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -9528,7 +9528,7 @@
       <c r="H158" t="inlineStr">
         <is>
           <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
-Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 15 (+4-6/Lv) -&gt; 60 | Speed: 1.7x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -9591,7 +9591,7 @@
       <c r="H159" t="inlineStr">
         <is>
           <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
-Accuracy: 75% (+1-2%/Lv) -&gt; 85% | TP Cost: 42 (+6-10/Lv) -&gt; 120 | Speed: 1.3x</t>
+Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -9653,8 +9653,8 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max) | Accuracy: 82% (+2%/Lv)
-TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84 | Speed: 1.5x | Chant: 0.75x -&gt; 0.7x</t>
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max)   |   Accuracy: 82% (+2%/Lv)
+TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -9709,7 +9709,7 @@
       <c r="H161" t="inlineStr">
         <is>
           <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
-Accuracy: 86% (+1%/Lv) | TP Cost: 5 (+2-4/Lv) -&gt; 32 | Speed: 2.25x</t>
+Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -9772,7 +9772,7 @@
       <c r="H162" t="inlineStr">
         <is>
           <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
-Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 15 (+4-6/Lv) -&gt; 60 | Speed: 1.7x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -9835,7 +9835,7 @@
       <c r="H163" t="inlineStr">
         <is>
           <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
-Accuracy: 75% (+1-2%/Lv) -&gt; 85% | TP Cost: 42 (+6-10/Lv) -&gt; 120 | Speed: 1.3x</t>
+Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -9897,8 +9897,8 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max) | Accuracy: 82% (+2%/Lv)
-TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84 | Speed: 1.5x | Chant: 0.75x -&gt; 0.7x</t>
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max)   |   Accuracy: 82% (+2%/Lv)
+TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -9953,7 +9953,7 @@
       <c r="H165" t="inlineStr">
         <is>
           <t>Pwr: 60 -&gt; 95 -&gt; 130 -&gt; 165 -&gt; 200 -&gt; 230 -&gt; 260 -&gt; 290 -&gt; 320 -&gt; 350 (L10)
-Accuracy: 80% (+1-2%/Lv) -&gt; 90% | HP Absorb: 100% | TP Cost: 9 (+1/Lv) -&gt; 18</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   HP Absorb: 100%   |   TP Cost: 9 (+1/Lv) -&gt; 18</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Pwr: 22 -&gt; 30 -&gt; 38 -&gt; 46 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 78 -&gt; 82 | Accuracy: 80% -&gt; 90%
+          <t>Pwr: 22 -&gt; 30 -&gt; 38 -&gt; 46 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 78 -&gt; 82   |   Accuracy: 80% -&gt; 90%
 TP Absorb: 100% | TP Cost: 6 (+1/Lv) -&gt; 15 | Speed: 1.75x | Chant: 1.25x -&gt; 1.07x</t>
         </is>
       </c>
@@ -10075,7 +10075,7 @@
       <c r="H167" t="inlineStr">
         <is>
           <t>Max HP increase rate: 20% -&gt; 28% -&gt; 36% -&gt; 45% -&gt; 50% (L1-5 Max)
-Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 27 -&gt; 31 -&gt; 35 -&gt; 39 -&gt; 43 | Speed: 1.5x</t>
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 27 -&gt; 31 -&gt; 35 -&gt; 39 -&gt; 43   |   Speed: 1.5x</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -10133,8 +10133,8 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Pwr: 75 (+35-45/Lv) -&gt; 450 | Accuracy: 65% (+2-3%/Lv) -&gt; 87% | HP Absorb: 100%
-TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 | Speed: 1.5x</t>
+          <t>Pwr: 75 (+35-45/Lv) -&gt; 450   |   Accuracy: 65% (+2-3%/Lv) -&gt; 87%   |   HP Absorb: 100%
+TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50   |   Speed: 1.5x</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -10197,7 +10197,7 @@
       <c r="H169" t="inlineStr">
         <is>
           <t>Accuracy: 65% -&gt; 68% -&gt; 71% -&gt; 73% -&gt; 75% (L1-5 Max)
-TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 | Speed: 0.8x -&gt; 0.92x | Chant: 1.25x</t>
+TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18   |   Speed: 0.8x -&gt; 0.92x   |   Chant: 1.25x</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -10252,7 +10252,7 @@
       <c r="H170" t="inlineStr">
         <is>
           <t>Accuracy: 75% -&gt; 78% -&gt; 81% -&gt; 83% -&gt; 85% (L1-5 Max)
-TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | Speed: 2.15x | Chant: 1.2x -&gt; 1.4x</t>
+TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   Speed: 2.15x   |   Chant: 1.2x -&gt; 1.4x</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -10307,7 +10307,7 @@
       <c r="H171" t="inlineStr">
         <is>
           <t>Accuracy: 70% -&gt; 72% -&gt; 74% -&gt; 76% -&gt; 78% (L1-5 Max)
-TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Speed: 1.5x | Chant: 1.5x -&gt; 1.66x</t>
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -10362,7 +10362,7 @@
       <c r="H172" t="inlineStr">
         <is>
           <t>Accuracy: 65% -&gt; 68% -&gt; 71% -&gt; 73% -&gt; 75% (L1-5 Max)
-TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Speed: 1.5x | Chant: 1x -&gt; 1.2x</t>
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1x -&gt; 1.2x</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -10417,7 +10417,7 @@
       <c r="H173" t="inlineStr">
         <is>
           <t>Accuracy: 65% -&gt; 68% -&gt; 71% -&gt; 73% -&gt; 75% (L1-5 Max)
-TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 | Chant: 0.75x -&gt; 0.87x</t>
+TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -10472,7 +10472,7 @@
       <c r="H174" t="inlineStr">
         <is>
           <t>Accuracy: 70% -&gt; 72% -&gt; 74% -&gt; 76% -&gt; 78% (L1-5 Max)
-TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Speed: 1.5x | Chant: 1.5x -&gt; 1.66x</t>
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -10527,7 +10527,7 @@
       <c r="H175" t="inlineStr">
         <is>
           <t>Accuracy: 70% -&gt; 72% -&gt; 74% -&gt; 76% -&gt; 78% (L1-5 Max)
-TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 | Chant: 0.75x -&gt; 0.87x</t>
+TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -10582,7 +10582,7 @@
       <c r="H176" t="inlineStr">
         <is>
           <t>Accuracy: 50% -&gt; 52% -&gt; 55% -&gt; 58% -&gt; 60% (L1-5 Max)
-TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 | Chant: 0.75x -&gt; 0.87x</t>
+TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -10637,7 +10637,7 @@
       <c r="H177" t="inlineStr">
         <is>
           <t>Accuracy: 50% -&gt; 55% -&gt; 60% -&gt; 64% -&gt; 68% (L1-5 Max)
-TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 | Chant: 1x -&gt; 1.12x</t>
+TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23   |   Chant: 1x -&gt; 1.12x</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -10692,7 +10692,7 @@
       <c r="H178" t="inlineStr">
         <is>
           <t>Accuracy: 54% -&gt; 58% -&gt; 62% -&gt; 66% -&gt; 70% (L1-5 Max)
-TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 | Speed: 0.4x -&gt; 0.5x | Chant: 1.25x</t>
+TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30   |   Speed: 0.4x -&gt; 0.5x   |   Chant: 1.25x</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -10746,8 +10746,8 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Accuracy: 55% -&gt; 65% -&gt; 75% -&gt; 85% -&gt; 95% (L1-5 Max) | Buff cancel rate: 100%
-TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 18 -&gt; 22 | Speed: 1.25x | Chant: 1.25x -&gt; 1.45x</t>
+          <t>Accuracy: 55% -&gt; 65% -&gt; 75% -&gt; 85% -&gt; 95% (L1-5 Max)   |   Buff cancel rate: 100%
+TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 18 -&gt; 22   |   Speed: 1.25x   |   Chant: 1.25x -&gt; 1.45x</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -10801,8 +10801,8 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Pwr: 250 (+40-50/Lv) -&gt; 640 | Accuracy: 60% -&gt; 70% | Damage vs. unholy: +100%
-TP Cost: 45 -&gt; 52 -&gt; 59 -&gt; 66 -&gt; 74 -&gt; 80 -&gt; 86 -&gt; 90 -&gt; 95 -&gt; 100 | Speed: 1.75x</t>
+          <t>Pwr: 250 (+40-50/Lv) -&gt; 640   |   Accuracy: 60% -&gt; 70%   |   Damage vs. unholy: +100%
+TP Cost: 45 -&gt; 52 -&gt; 59 -&gt; 66 -&gt; 74 -&gt; 80 -&gt; 86 -&gt; 90 -&gt; 95 -&gt; 100   |   Speed: 1.75x</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -10864,8 +10864,8 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
-Speed: 1.5x -&gt; 1.7x | Chant: 1.75x -&gt; 2.25x</t>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max)   |   TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -10919,8 +10919,8 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
-Speed: 1.5x -&gt; 1.7x | Chant: 1.75x -&gt; 2.25x</t>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max)   |   TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -10974,8 +10974,8 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
-Speed: 1.5x -&gt; 1.7x | Chant: 1.75x -&gt; 2.25x</t>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max)   |   TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -11029,8 +11029,8 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
-Speed: 1.5x -&gt; 1.7x | Chant: 1.75x -&gt; 2.25x</t>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max)   |   TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -11084,8 +11084,8 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max) | TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
-Speed: 1.5x -&gt; 1.7x | Chant: 1.75x -&gt; 2.25x</t>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max)   |   TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -11140,7 +11140,7 @@
       <c r="H186" t="inlineStr">
         <is>
           <t>Resistance: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -11199,7 +11199,7 @@
       <c r="H187" t="inlineStr">
         <is>
           <t>Resistance: 18 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -11258,7 +11258,7 @@
       <c r="H188" t="inlineStr">
         <is>
           <t>Resistance: 18 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -11316,8 +11316,8 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>HP recovery: 8 (+2/Lv) -&gt; 26 (L10 Max) | Heal Cap: 100 (+60-80/Lv) -&gt; 800
-TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 | Speed: 1.75x</t>
+          <t>Heals RES: 4x (+1x/Lv) -&gt; 13x (L10 Max)   |   Heal Cap: 100 (+60-80/Lv) -&gt; 800
+TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26   |   Speed: 1.75x</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -11379,8 +11379,8 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>HP recovery: 5 (+1/Lv) -&gt; 14 (L10 Max) | Heal Cap: 80 (+50-60/Lv) -&gt; 600
-TP Cost: 15 -&gt; 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 46 -&gt; 52 -&gt; 58 -&gt; 64 | Speed: 1.35x</t>
+          <t>Heals RES: 2.5x (+0.5x/Lv) -&gt; 7x (L10 Max)   |   Heal Cap: 80 (+50-60/Lv) -&gt; 600
+TP Cost: 15 -&gt; 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 46 -&gt; 52 -&gt; 58 -&gt; 64   |   Speed: 1.35x</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>TP Cost: 48 -&gt; 45 -&gt; 42 -&gt; 39 -&gt; 36 (L1-5 Max) | Speed: 1.15x | Chant: 1.5x -&gt; 1.75x</t>
+          <t>TP Cost: 48 -&gt; 45 -&gt; 42 -&gt; 39 -&gt; 36 (L1-5 Max)   |   Speed: 1.15x   |   Chant: 1.5x -&gt; 1.75x</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -11496,7 +11496,7 @@
       <c r="H192" t="inlineStr">
         <is>
           <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
-TP Cost: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 | Speed: 2.25x | Chant: 2.75x</t>
+TP Cost: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   Speed: 2.25x   |   Chant: 2.75x</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -11551,7 +11551,7 @@
       <c r="H193" t="inlineStr">
         <is>
           <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
-TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25 -&gt; 30 -&gt; 36 | Speed: 1.5x | Chant: 2x</t>
+TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25 -&gt; 30 -&gt; 36   |   Speed: 1.5x   |   Chant: 2x</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       <c r="H194" t="inlineStr">
         <is>
           <t>HP on revival: 40% -&gt; 52% -&gt; 64% -&gt; 76% -&gt; 88% (L1-5 Max)
-TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 | Speed: 1.25x | Chant: 1.3x -&gt; 1.5x</t>
+TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42   |   Speed: 1.25x   |   Chant: 1.3x -&gt; 1.5x</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -11661,7 +11661,7 @@
       <c r="H195" t="inlineStr">
         <is>
           <t>ATK: +10% -&gt; +13% -&gt; +16% -&gt; +19% -&gt; +22% (L1-5 Max)
-Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 | TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 | Chant: 1.25x</t>
+Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17   |   Chant: 1.25x</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -11720,7 +11720,7 @@
       <c r="H196" t="inlineStr">
         <is>
           <t>DEF: +10% -&gt; +14% -&gt; +18% -&gt; +22% -&gt; +25% (L1-5 Max)
-Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 | TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 | Chant: 1.25x</t>
+Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17   |   Chant: 1.25x</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -11779,7 +11779,7 @@
       <c r="H197" t="inlineStr">
         <is>
           <t>Magic defense: +10% -&gt; +12% -&gt; +14% -&gt; +16% -&gt; +18% (L1-5 Max)
-Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Chant: 1.25x</t>
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32   |   Chant: 1.25x</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -11838,7 +11838,7 @@
       <c r="H198" t="inlineStr">
         <is>
           <t>Elemental resistance increase: 5 -&gt; 10 -&gt; 15 -&gt; 20 -&gt; 25 (L1-5 Max)
-Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 | Chant: 1.25x</t>
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32   |   Chant: 1.25x</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -11897,7 +11897,7 @@
       <c r="H199" t="inlineStr">
         <is>
           <t>Speed increase: 8% -&gt; 9% -&gt; 10% -&gt; 11% -&gt; 12% (L1-5 Max)
-Turns: 3 | TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 | Speed: 1.25x -&gt; 1.41x</t>
+Turns: 3   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Speed: 1.25x -&gt; 1.41x</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -11956,7 +11956,7 @@
       <c r="H200" t="inlineStr">
         <is>
           <t>Max HP: +20% -&gt; +23 -&gt; +26 -&gt; +29 -&gt; +32 -&gt; +35 -&gt; +38 -&gt; +41 -&gt; +44 -&gt; +47% (L10)
-Turns: 5 -&gt; 5 -&gt; 6 -&gt; 6 -&gt; 7 -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 18 (+3/Lv) -&gt; 45</t>
+Turns: 5 -&gt; 5 -&gt; 6 -&gt; 6 -&gt; 7 -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 18 (+3/Lv) -&gt; 45</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -12015,7 +12015,7 @@
       <c r="H201" t="inlineStr">
         <is>
           <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
-TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 21 -&gt; 24 -&gt; 28 | Speed: 1.75x | Chant: 2.25x</t>
+TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 21 -&gt; 24 -&gt; 28   |   Speed: 1.75x   |   Chant: 2.25x</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 (L1-3 Max) | TP Cost: 30 -&gt; 38 -&gt; 46 | Speed: 0.85x
+          <t>Turns: 3 -&gt; 4 -&gt; 5 (L1-3 Max)   |   TP Cost: 30 -&gt; 38 -&gt; 46   |   Speed: 0.85x
 Chant: 0.75x -&gt; 0.65x</t>
         </is>
       </c>
@@ -12125,7 +12125,7 @@
       <c r="H203" t="inlineStr">
         <is>
           <t>Amount of damage reduced: 30% -&gt; 33% -&gt; 37% -&gt; 41% -&gt; 45% (L1-5 Max)
-Turns: 4 | TP Cost: 24 -&gt; 28 -&gt; 33 -&gt; 37 -&gt; 42 | Speed: 1.5x | Chant: 0.75x</t>
+Turns: 4   |   TP Cost: 24 -&gt; 28 -&gt; 33 -&gt; 37 -&gt; 42   |   Speed: 1.5x   |   Chant: 0.75x</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -12180,7 +12180,7 @@
       <c r="H204" t="inlineStr">
         <is>
           <t>Amount of HP on revival: 10% -&gt; 20% -&gt; 30% -&gt; 40% -&gt; 50% (L1-5 Max)
-Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 45 | Speed: 1.5x</t>
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 45   |   Speed: 1.5x</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -12344,7 +12344,7 @@
       <c r="H207" t="inlineStr">
         <is>
           <t>Accuracy: 70% -&gt; 73% -&gt; 76% -&gt; 79% -&gt; 82% (L1-5 Max)
-Speed: 1.5x | Chant: 1.5x -&gt; 1.66x</t>
+Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Speed: 1.35x | Chant: 1.4x</t>
+          <t>Speed: 1.35x   |   Chant: 1.4x</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -12447,7 +12447,7 @@
       <c r="H209" t="inlineStr">
         <is>
           <t>Critical rate: 10% -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28% (L10)
-Speed: 1.35x | Chant: 1.4x -&gt; 2x</t>
+Speed: 1.35x   |   Chant: 1.4x -&gt; 2x</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -12501,7 +12501,7 @@
       <c r="H210" t="inlineStr">
         <is>
           <t>Magic attack: +10% -&gt; +11 -&gt; +12 -&gt; +13 -&gt; +14 -&gt; +15 -&gt; +16 -&gt; +17 -&gt; +18 -&gt; +20%
-Speed: 1.35x | Chant: 1.25x -&gt; 1.7x</t>
+Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -12555,7 +12555,7 @@
       <c r="H211" t="inlineStr">
         <is>
           <t>Magic defense: +10% -&gt; +11 -&gt; +12 -&gt; +13 -&gt; +14 -&gt; +15 -&gt; +16 -&gt; +17 -&gt; +18 -&gt; +20%
-Speed: 1.35x | Chant: 1.25x -&gt; 1.7x</t>
+Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -12609,7 +12609,7 @@
       <c r="H212" t="inlineStr">
         <is>
           <t>Chant time: -10% -&gt; -11 -&gt; -12 -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -20%
-Speed: 1.35x | Chant: 1.4x -&gt; 2x</t>
+Speed: 1.35x   |   Chant: 1.4x -&gt; 2x</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -12663,7 +12663,7 @@
       <c r="H213" t="inlineStr">
         <is>
           <t>HP recovery: 20 -&gt; 35 -&gt; 50 -&gt; 65 -&gt; 80 -&gt; 100 -&gt; 130 -&gt; 170 -&gt; 210 -&gt; 250 (L10)
-Speed: 1.35x | Chant: 1.25x -&gt; 1.7x</t>
+Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -12717,7 +12717,7 @@
       <c r="H214" t="inlineStr">
         <is>
           <t>TP recovery: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30 (L10)
-Speed: 1.35x | Chant: 1.1x -&gt; 1.5x</t>
+Speed: 1.35x   |   Chant: 1.1x -&gt; 1.5x</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -12771,7 +12771,7 @@
       <c r="H215" t="inlineStr">
         <is>
           <t>Speed increase: 6% -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)
-Speed: 1.35x | Chant: 1.1x -&gt; 1.5x</t>
+Speed: 1.35x   |   Chant: 1.1x -&gt; 1.5x</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -12825,7 +12825,7 @@
       <c r="H216" t="inlineStr">
         <is>
           <t>EXP: +16% -&gt; +17 -&gt; +18 -&gt; +19 -&gt; +20 -&gt; +21 -&gt; +22 -&gt; +23 -&gt; +24 -&gt; +25% (L10)
-Speed: 1.35x | Chant: 1.25x -&gt; 1.7x</t>
+Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -12879,7 +12879,7 @@
       <c r="H217" t="inlineStr">
         <is>
           <t>Magic accuracy: +6% -&gt; +7 -&gt; +8 -&gt; +9 -&gt; +10 -&gt; +11 -&gt; +12 -&gt; +13 -&gt; +14 -&gt; +15%
-Speed: 1.35x | Chant: 1.25x -&gt; 1.7x</t>
+Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -12934,7 +12934,7 @@
       <c r="H218" t="inlineStr">
         <is>
           <t>Number of dodges: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 (L1-5 Max)
-Turns: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5 | TP Cost: 23 -&gt; 27 -&gt; 32 -&gt; 38 -&gt; 45 | Speed: 0.85x</t>
+Turns: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5   |   TP Cost: 23 -&gt; 27 -&gt; 32 -&gt; 38 -&gt; 45   |   Speed: 0.85x</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -13048,7 +13048,7 @@
       <c r="H220" t="inlineStr">
         <is>
           <t>Accuracy: -10% -&gt; -12% -&gt; -14% -&gt; -16% -&gt; -18% (L1-5 Max)
-Turns: 3 | TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 | Chant: 1.15x -&gt; 1.3x</t>
+Turns: 3   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Chant: 1.15x -&gt; 1.3x</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max) | Accuracy: 64% (+4%/Lv)
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
 ATK: -4% (-1%/Lv) | Damage cap: 250 -&gt; 500 | Turns: 3 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
@@ -13165,8 +13165,8 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max) | Accuracy: 64% (+4%/Lv)
-Magic defense: -7% -&gt; -18% | Damage cap: 250 -&gt; 500 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
+Magic defense: -7% -&gt; -18%   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -13228,8 +13228,8 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max) | Accuracy: 64% (+4%/Lv)
-Speed decrease: 4% (+1%/Lv) | Damage cap: 250 -&gt; 500 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
+Speed decrease: 4% (+1%/Lv)   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max) | Accuracy: 64% (+4%/Lv)
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
 Evasion: -7% (-2%/Lv) | Damage cap: 250 -&gt; 500 | Turns: 3 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max) | Accuracy: 64% (+4%/Lv)
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
 DEF: -4% (-1%/Lv) | Damage cap: 250 -&gt; 500 | Turns: 3 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
@@ -13418,7 +13418,7 @@
       <c r="H226" t="inlineStr">
         <is>
           <t>Pwr: 350 -&gt; 390 -&gt; 430 -&gt; 470 -&gt; 510 -&gt; 550 -&gt; 590 -&gt; 630 -&gt; 680 -&gt; 720 (L10)
-Accuracy: 86% (+1%/Lv) | TP Cost: 22 (+4-6/Lv) -&gt; 66 | Speed: 1.3x</t>
+Accuracy: 86% (+1%/Lv)   |   TP Cost: 22 (+4-6/Lv) -&gt; 66   |   Speed: 1.3x</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -13480,8 +13480,8 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Pwr: 240 (+40/Lv) -&gt; 600 (L10 Max) | Accuracy: 76% (+1%/Lv) | Stun: 25%
-TP Cost: 36 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 80 -&gt; 88 -&gt; 96 | Speed: 1.5x</t>
+          <t>Pwr: 240 (+40/Lv) -&gt; 600 (L10 Max)   |   Accuracy: 76% (+1%/Lv)   |   Stun: 25%
+TP Cost: 36 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 80 -&gt; 88 -&gt; 96   |   Speed: 1.5x</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -13540,7 +13540,7 @@
       <c r="H228" t="inlineStr">
         <is>
           <t>ATK: +8% -&gt; +10% -&gt; +12% -&gt; +14% -&gt; +16% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22 | Chant: 1.15x</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22   |   Chant: 1.15x</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -13599,7 +13599,7 @@
       <c r="H229" t="inlineStr">
         <is>
           <t>DEF: +8% -&gt; +10% -&gt; +12% -&gt; +14% -&gt; +16% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22 | Chant: 1.15x</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22   |   Chant: 1.15x</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -13658,7 +13658,7 @@
       <c r="H230" t="inlineStr">
         <is>
           <t>Damage reduction: 25% -&gt; 27% -&gt; 29% -&gt; 32% -&gt; 35% (L1-5 Max)
-Turns: 3 | TP Cost: 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 | Speed: 0.75x | Chant: 1.75x</t>
+Turns: 3   |   TP Cost: 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40   |   Speed: 0.75x   |   Chant: 1.75x</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -13767,8 +13767,8 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>HP recovery: 22 -&gt; 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 (L8)
-Recoverable status ailments: 1 (+1/Lv) | HP on revival: 10% (+5-10%/Lv) -&gt; 50%</t>
+          <t>Heals RES: 11x -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25x (L8)
+Recoverable status ailments: 1 (+1/Lv)   |   HP on revival: 10% (+5-10%/Lv) -&gt; 50%</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>DEF: -5% -&gt; -6% -&gt; -7% -&gt; -8% -&gt; -10% (L1-5 Max) | Magic defense: -10% -&gt; -15%
+          <t>DEF: -5% -&gt; -6% -&gt; -7% -&gt; -8% -&gt; -10% (L1-5 Max)   |   Magic defense: -10% -&gt; -15%
 Accuracy: 80% -&gt; 90% | HP recovery: 35 -&gt; 25 | Turns: 3 | TP Cost: 18 (+2-4/Lv) -&gt; 32</t>
         </is>
       </c>
@@ -13894,7 +13894,7 @@
       <c r="H234" t="inlineStr">
         <is>
           <t>Pwr: 100 -&gt; 130 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 280 -&gt; 320 -&gt; 370 -&gt; 420 -&gt; 480 (L10)
-Accuracy: 80% (+1-2%/Lv) -&gt; 90% | TP Cost: 30 (+4/Lv) -&gt; 66 | Speed: 0.85x</t>
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 30 (+4/Lv) -&gt; 66   |   Speed: 0.85x</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -13956,8 +13956,8 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Pwr: 360 (+40-50/Lv) -&gt; 740 | Accuracy: 76% (+1%/Lv) | Instakill: 12%
-TP Cost: 32 -&gt; 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 52 -&gt; 54 -&gt; 56 | Speed: 1.2x</t>
+          <t>Pwr: 360 (+40-50/Lv) -&gt; 740   |   Accuracy: 76% (+1%/Lv)   |   Instakill: 12%
+TP Cost: 32 -&gt; 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 52 -&gt; 54 -&gt; 56   |   Speed: 1.2x</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -14019,8 +14019,8 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Maximum damage UP | Maximum heal UP
-TP Cost: 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 (L1-5 Max) | Speed: 1.5x | Chant: 0.84x -&gt; 0.8x</t>
+          <t>Maximum damage UP   |   Maximum heal UP
+TP Cost: 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 (L1-5 Max)   |   Speed: 1.5x   |   Chant: 0.84x -&gt; 0.8x</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -18104,7 +18104,7 @@
       <c r="G314" t="inlineStr">
         <is>
           <t>Significantly increase damage according to Pep.
-Pep over 100 per +1% damage: 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3 -&gt; 2 | Crown EX: 1</t>
+Pep over 100 per +1% damage: 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3 -&gt; 2   |   Crown EX: 1</t>
         </is>
       </c>
       <c r="H314" t="inlineStr"/>
@@ -18150,7 +18150,7 @@
       <c r="G315" t="inlineStr">
         <is>
           <t>Occasionally inflict enemies with status ailments or Dispel at random.
-Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 25%</t>
+Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 25%</t>
         </is>
       </c>
       <c r="H315" t="inlineStr"/>
@@ -18196,7 +18196,7 @@
       <c r="G316" t="inlineStr">
         <is>
           <t>May counter short-range attacks with Slow and a Speed decrease.
-Activation rate: 16% -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38% | Crown EX: 50%</t>
+Activation rate: 16% -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38%   |   Crown EX: 50%</t>
         </is>
       </c>
       <c r="H316" t="inlineStr"/>
@@ -18242,7 +18242,7 @@
       <c r="G317" t="inlineStr">
         <is>
           <t>Increase weapon modifier when attacking with weapon-based skills.
-Weapon modifier: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18% | Crown EX: 25%</t>
+Weapon modifier: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18%   |   Crown EX: 25%</t>
         </is>
       </c>
       <c r="H317" t="inlineStr"/>
@@ -18288,7 +18288,7 @@
       <c r="G318" t="inlineStr">
         <is>
           <t>May guarantee a hit and bypass DEF with physical attacks or skills.
-Activation rate: 12% -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% | Crown EX: 30%</t>
+Activation rate: 12% -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20%   |   Crown EX: 30%</t>
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
@@ -18334,7 +18334,7 @@
       <c r="G319" t="inlineStr">
         <is>
           <t>Occasionally nullify all damage received from enemies.
-Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
+Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
       <c r="H319" t="inlineStr"/>
@@ -18380,7 +18380,7 @@
       <c r="G320" t="inlineStr">
         <is>
           <t>Before acting, may erase enemy puppets, familiars, shikigami, or slaves.
-Activation rate: 25% -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 49 -&gt; 53 -&gt; 57% | Crown EX: 75%</t>
+Activation rate: 25% -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 49 -&gt; 53 -&gt; 57%   |   Crown EX: 75%</t>
         </is>
       </c>
       <c r="H320" t="inlineStr"/>
@@ -18426,7 +18426,7 @@
       <c r="G321" t="inlineStr">
         <is>
           <t>Before acting, may use an item from her own personal stock.
-Activation rate: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18% | Crown EX: 25%</t>
+Activation rate: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18%   |   Crown EX: 25%</t>
         </is>
       </c>
       <c r="H321" t="inlineStr"/>
@@ -18472,7 +18472,7 @@
       <c r="G322" t="inlineStr">
         <is>
           <t>Decrease turn delay after using skills or magic.
-Turn delay: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
+Turn delay: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
       <c r="H322" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       <c r="G323" t="inlineStr">
         <is>
           <t>Increased effects for all maid skills.
-Maid skill effects: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 10% | Crown EX: 13%</t>
+Maid skill effects: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 10%   |   Crown EX: 13%</t>
         </is>
       </c>
       <c r="H323" t="inlineStr"/>
@@ -18564,7 +18564,7 @@
       <c r="G324" t="inlineStr">
         <is>
           <t>May occasionally act twice in one turn.
-Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
+Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
       <c r="H324" t="inlineStr"/>
@@ -18610,7 +18610,7 @@
       <c r="G325" t="inlineStr">
         <is>
           <t>If killed, revive after a certain number of turns.
-Activation rate: 8% -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24% | Crown EX: 30%</t>
+Activation rate: 8% -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24%   |   Crown EX: 30%</t>
         </is>
       </c>
       <c r="H325" t="inlineStr"/>
@@ -18656,7 +18656,7 @@
       <c r="G326" t="inlineStr">
         <is>
           <t>Whole row takes less damage from Demons, Undead, and Apparitions.
-Taken: -12% -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -19 -&gt; -20% | Crown EX: -25%</t>
+Taken: -12% -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -19 -&gt; -20%   |   Crown EX: -25%</t>
         </is>
       </c>
       <c r="H326" t="inlineStr"/>
@@ -18702,7 +18702,7 @@
       <c r="G327" t="inlineStr">
         <is>
           <t>May lower all enemies' ATK and INT with heart-penetrating vocals.
-Activation rate: 7% -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13% | Crown EX: 20%</t>
+Activation rate: 7% -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13%   |   Crown EX: 20%</t>
         </is>
       </c>
       <c r="H327" t="inlineStr"/>
@@ -18748,7 +18748,7 @@
       <c r="G328" t="inlineStr">
         <is>
           <t>Magic will occasionally activate immediately without the need to chant.
-Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% | Crown EX: 20%</t>
+Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
       <c r="H328" t="inlineStr"/>
@@ -18794,7 +18794,7 @@
       <c r="G329" t="inlineStr">
         <is>
           <t>Occasionally reflects a percentage of damage taken as fixed damage.
-Reflected: 50% -&gt; 55 -&gt; 60 -&gt; 65 -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 90 -&gt; 100% | Crown EX: 200%
+Reflected: 50% -&gt; 55 -&gt; 60 -&gt; 65 -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 90 -&gt; 100%   |   Crown EX: 200%
 Activation rate: 15%</t>
         </is>
       </c>
@@ -18841,7 +18841,7 @@
       <c r="G330" t="inlineStr">
         <is>
           <t>Summons another self from the shadows to attack.
-Activation rate: 4% -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% | Crown EX: 20%</t>
+Activation rate: 4% -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12%   |   Crown EX: 20%</t>
         </is>
       </c>
       <c r="H330" t="inlineStr"/>
@@ -18887,7 +18887,7 @@
       <c r="G331" t="inlineStr">
         <is>
           <t>Increased effects for all class modifiers.
-Class modifiers (%): 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Crown EX: 15</t>
+Class modifiers (%): 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Crown EX: 15</t>
         </is>
       </c>
       <c r="H331" t="inlineStr"/>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -580,19 +580,11 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5   |   Speed: 1.5x -&gt; 2x</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -635,19 +627,11 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | Speed: 1.25x -&gt; 1.77x</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -690,23 +674,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -749,23 +726,16 @@
 Accuracy: +20% (+2%/Lv)   |   TP Cost: 5 (+2-3/Lv) -&gt; 28   |   Speed: 0.8x -&gt; 0.9x</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -808,23 +778,16 @@
 Buff cancel rate: 68% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 5 (+1-2/Lv) -&gt; 18   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Buff cancel rate, TP Cost</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -867,14 +830,11 @@
 DEF: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%   |   Turns: 4 -&gt; 8   |   TP Cost: 8 (+2/Lv) -&gt; 16</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -885,9 +845,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -930,14 +887,11 @@
 ATK: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%   |   Turns: 4 -&gt; 8   |   TP Cost: 8 (+2/Lv) -&gt; 16</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -948,9 +902,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -993,14 +944,11 @@
 Stun: 30% -&gt; 32% -&gt; 34% -&gt; 36% -&gt; 38%   |   TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -1011,9 +959,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1056,14 +1001,11 @@
 Accuracy: +5% (+2-3%/Lv) -&gt; +28%   |   Paralysis: 20% -&gt; 50%   |   TP Cost: 6 (+2/Lv) -&gt; 24</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Accuracy, Paralysis</t>
@@ -1074,9 +1016,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1119,23 +1058,16 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1178,14 +1110,11 @@
 Instakill: 10% (+1-2%/Lv) -&gt; 20%   |   Power decrease: 10%   |   TP Cost: 38 (+4/Lv) -&gt; 74</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Instakill</t>
@@ -1196,9 +1125,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1241,19 +1167,11 @@
 Enemy DEF: -16% (-1%/Lv)   |   Turns: 4   |   TP Cost: 14 (+2/Lv) -&gt; 32   |   Speed: 0.8x</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1296,23 +1214,16 @@
 TP Cost: 22 -&gt; 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1355,23 +1266,16 @@
 Critical rate: 10%   |   TP Cost: 36 (+2-3/Lv) -&gt; 61   |   Speed: 0.7x -&gt; 0.8x</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1414,23 +1318,16 @@
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>HP Absorb</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1473,23 +1370,16 @@
 TP Absorb: 10% (+1-2%/Lv) -&gt; 20%   |   TP Cost: 6 (+2/Lv) -&gt; 24   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>TP Absorb</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1532,14 +1422,11 @@
 Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   Accuracy: +14%   |   TP Cost: 9 (+3/Lv) -&gt; 36</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Freeze</t>
@@ -1550,9 +1437,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1595,14 +1479,11 @@
 TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 37 -&gt; 42</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>ATK, Petrify</t>
@@ -1613,9 +1494,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1658,14 +1536,11 @@
 Targets: 2 -&gt; 2 -&gt; 2 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5   |   TP Cost: 26 (+4-6/Lv) -&gt; 68</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -1676,9 +1551,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1721,23 +1593,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 10 -&gt; 14 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1780,23 +1645,16 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1839,14 +1697,11 @@
 Accuracy: +6% -&gt; +20%   |   Damage vs. unholy: +65%   |   TP Cost: 12 (+3/Lv) -&gt; 39</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -1857,9 +1712,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1902,23 +1754,16 @@
 Turns: 5   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1961,23 +1806,16 @@
 Turns: 5   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2020,23 +1858,16 @@
 Paralysis: 20% (+2-3%/Lv) -&gt; 40%   |   TP Cost: 26 (+4-5/Lv) -&gt; 64   |   Speed: 0.8x</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Paralysis, TP Cost</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2079,14 +1910,11 @@
 Silence: 20% (+3-4%/Lv) -&gt; 50%   |   Accuracy: +15%   |   TP Cost: 7 (+3/Lv) -&gt; 34</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Silence</t>
@@ -2097,9 +1925,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2142,23 +1967,16 @@
 Heavy Lance bonus: +20%   |   TP Cost: 36 (+3-6/Lv) -&gt; 71   |   Speed: 0.7x -&gt; 0.8x</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2201,23 +2019,16 @@
 Accuracy: +5% (+1-2%/Lv) -&gt; +15%   |   TP Cost: 32 (+3/Lv) -&gt; 59   |   Speed: 0.8x</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2260,19 +2071,11 @@
 Turns: 2   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Speed: 0.84x -&gt; 0.9x</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2314,19 +2117,11 @@
 Speed: 1x -&gt; 1.5x</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2368,19 +2163,11 @@
 Speed: 0.6x -&gt; 0.8x</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2423,19 +2210,11 @@
 TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 -&gt; 28 -&gt; 30   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2478,19 +2257,11 @@
 TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 35 -&gt; 38   |   Speed: 0.85x</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2533,23 +2304,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2592,19 +2356,11 @@
 TP Cost: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2647,14 +2403,11 @@
 Turns: 5 -&gt; 9   |   TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -2665,9 +2418,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2710,19 +2460,11 @@
 Turns: 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 5 -&gt; 6   |   TP Cost: 14 (+2/Lv) -&gt; 32</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2765,23 +2507,16 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>Physical evasion, Magic evasion</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2815,7 +2550,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Short-range: moderate damage to an enemy. May cause sleep (20-50%).</t>
+          <t>Short-range/Projectile: moderate damage. May cause sleep (20-50%).</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2824,23 +2559,16 @@
 Sleep: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>Sleep</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2874,7 +2602,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Short-range: moderate damage to an enemy. May silence (20-50%).</t>
+          <t>Short-range/Projectile: moderate damage. May silence (20-50%).</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2883,23 +2611,16 @@
 Silence: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>Silence</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2933,7 +2654,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Short-range: moderate damage to an enemy. May stun (20-50%).</t>
+          <t>Short-range/Projectile: moderate damage. May stun (20-50%).</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2942,23 +2663,16 @@
 Stun: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>Stun</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3001,23 +2715,16 @@
 Power decrease: 25% -&gt; 14%   |   TP Cost: 30 (+4-6/Lv) -&gt; 72   |   Speed: 0.75x -&gt; 0.85x</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>ATK, Power decrease, TP Cost</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3060,19 +2767,11 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16   |   Speed: 1x -&gt; 1.12x</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3115,19 +2814,11 @@
 TP Cost: 42 -&gt; 50 -&gt; 57 -&gt; 63 -&gt; 68   |   Speed: 0.4x</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3170,23 +2861,16 @@
 Poison: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>Poison</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3229,23 +2913,16 @@
 Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 8 (+2/Lv) -&gt; 26</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>Freeze</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3288,23 +2965,16 @@
 Paralysis: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 8 (+2/Lv) -&gt; 26</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>Paralysis</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3347,23 +3017,16 @@
 Slow: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 9 (+2/Lv) -&gt; 27   |   Speed: 0.95x</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>Slow</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3406,19 +3069,11 @@
 TP Cost: 20 -&gt; 23 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48   |   Speed: 0.65x</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3461,7 +3116,6 @@
 TP Cost: 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 59 -&gt; 62   |   Speed: 0.82x</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -3477,10 +3131,6 @@
           <t>effect_2</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
           <t>no damage word: carries effects that are not understood: 146, 147</t>
@@ -3528,23 +3178,16 @@
 Critical rate: 5% (+1-3%/Lv) -&gt; 25%   |   TP Cost: 24 (+3-4/Lv) -&gt; 55   |   Speed: 0.7x</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>Critical rate, TP Cost</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3578,7 +3221,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Projectile skill. Deal minor damage and lower speed for an enemy row.</t>
+          <t>Short-range/Projectile: minor damage, lower speed for an enemy row.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3587,14 +3230,11 @@
 Turns: 4   |   TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>ATK, Speed decrease chance</t>
@@ -3605,9 +3245,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3650,14 +3287,11 @@
 Stun: 10% -&gt; 20%   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>Stun</t>
@@ -3668,9 +3302,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3712,19 +3343,11 @@
 TP Cost: 10 -&gt; 8 -&gt; 6 -&gt; 4 -&gt; 2</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3767,23 +3390,16 @@
 Magic accuracy: -2% (-2%/Lv)   |   Turns: 6   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 32</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3826,14 +3442,11 @@
 Accuracy: +10% (+2-4%/Lv) -&gt; +30%   |   ATK: 82%   |   TP Cost: 28 (+4/Lv) -&gt; 64</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -3844,9 +3457,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3889,23 +3499,16 @@
 Turns: 4   |   TP Cost: 25 -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 48 -&gt; 51 -&gt; 54 -&gt; 57</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3948,23 +3551,16 @@
 TP Cost: 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 57 -&gt; 62 -&gt; 67 -&gt; 73 -&gt; 79</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4007,14 +3603,11 @@
 Turns: 4 -&gt; 7   |   TP Cost: 22 -&gt; 25 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 56</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -4025,9 +3618,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4070,19 +3660,11 @@
 Turns: 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 6   |   TP Cost: 52 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 92   |   Speed: 1.25x</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4125,23 +3707,16 @@
 Accuracy: +10% (+1-2%/Lv) -&gt; +20%   |   TP Cost: 13 (+3-4/Lv) -&gt; 45   |   Speed: 0.9x -&gt; 1x</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4184,23 +3759,16 @@
 Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   Silence: 20% -&gt; 50%   |   TP Cost: 9 (+3/Lv) -&gt; 36</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>Freeze, Silence</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4243,19 +3811,11 @@
 TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 36 -&gt; 40 -&gt; 43 -&gt; 46 -&gt; 49 -&gt; 52 -&gt; 55</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4281,26 +3841,16 @@
           <t>Detect how many unopened treasure chests are left on the current floor.</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>Detect how many unopened treasure chests are left on this floor.</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4341,19 +3891,11 @@
           <t>HP recovery: 12% -&gt; 15% -&gt; 18% -&gt; 21% -&gt; 25% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4395,19 +3937,11 @@
 Speed: 0.85x</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4448,19 +3982,11 @@
           <t>TP transfer bonus: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4502,19 +4028,11 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4556,19 +4074,11 @@
 Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4610,19 +4120,11 @@
 Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4664,19 +4166,11 @@
 Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4718,19 +4212,11 @@
 Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4772,19 +4258,11 @@
 Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4827,23 +4305,16 @@
 Total damage cap: 250 -&gt; 275 -&gt; 300 -&gt; 325 -&gt; 350 -&gt; 375 -&gt; 400 -&gt; 430 -&gt; 460 -&gt; 500</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4885,19 +4356,11 @@
 Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4939,19 +4402,11 @@
 Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4994,23 +4449,16 @@
 Power decrease: 10%   |   TP Cost: 22 (+3-4/Lv) -&gt; 50   |   Speed: 0.75x -&gt; 0.85x</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5053,19 +4501,11 @@
 TP Cost: 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46   |   Speed: 0.75x -&gt; 0.8x</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5108,23 +4548,16 @@
 Paralysis: 20% -&gt; 23% -&gt; 26% -&gt; 29% -&gt; 32%   |   TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5167,23 +4600,16 @@
 Accuracy: +20%   |   TP Cost: 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 56 -&gt; 60</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5226,19 +4652,11 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5264,26 +4682,16 @@
           <t>Spin the magic roulette. Nobody knows what will happen.</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>Spin the magic roulette. Nobody knows what will happen.</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5326,23 +4734,16 @@
 Instakill: 15% (+1-2%/Lv) -&gt; 25%   |   TP Cost: 17 (+2/Lv) -&gt; 35   |   Speed: 0.88x</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
           <t>Instakill</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5385,23 +4786,16 @@
 Stun: 40% (+3-4%/Lv) -&gt; 70%   |   TP Cost: 32 (+2/Lv) -&gt; 50   |   Speed: 0.65x</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
           <t>Stun</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5444,23 +4838,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5486,26 +4873,16 @@
           <t>Open a magic box. Nobody knows what will happen.</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>Open a magic box. Nobody knows what will happen.</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5548,19 +4925,11 @@
 TP Cost: 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32   |   Speed: 0.85x</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5603,23 +4972,16 @@
 Poison: 50% (+3-4%/Lv) -&gt; 80%   |   TP Cost: 22 (+4/Lv) -&gt; 58   |   Speed: 0.6x -&gt; 0.7x</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>Poison</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5662,23 +5024,16 @@
 Turn delay rate: 25% (+2%/Lv)   |   TP Cost: 10 (+2-3/Lv) -&gt; 32   |   Speed: 0.95x</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5704,7 +5059,6 @@
           <t>Fan skill. With increased ATK, deal long-range damage to one enemy.</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>Fan skill. With raised ATK, deal minor long-range damage to an enemy.</t>
@@ -5716,19 +5070,11 @@
 Speed: 1.15x</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5771,23 +5117,16 @@
 TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50   |   Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>Slow</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5830,23 +5169,16 @@
 Turns: 6   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 23 -&gt; 25   |   Speed: 0.85x</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>Max HP reduction</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5889,19 +5221,11 @@
 Turns: 2   |   TP Cost: 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50   |   Speed: 1.15x</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5927,26 +5251,16 @@
           <t>Something emerges from the shadows. Nobody knows what will happen.</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>Something emerges from the shadows. Nobody knows what will happen.</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5989,7 +5303,6 @@
 Accuracy UP   |   TP Cost: 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -6000,16 +5313,11 @@
           <t>Accuracy UP</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6052,7 +5360,6 @@
 TP Cost: 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -6068,15 +5375,11 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6119,7 +5422,6 @@
 TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 44 -&gt; 46 -&gt; 48   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -6135,11 +5437,6 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6182,7 +5479,6 @@
 TP Cost: 30 -&gt; 33 -&gt; 37 -&gt; 42 -&gt; 48   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -6198,11 +5494,6 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6245,7 +5536,6 @@
 TP Cost: 42 -&gt; 44 -&gt; 46 -&gt; 48 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 60 -&gt; 64 -&gt; 70   |   Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -6261,11 +5551,6 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6308,19 +5593,11 @@
 Duration: 5   |   TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 38   |   Speed: 1.15x</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6363,7 +5640,6 @@
 TP Cost: 38 -&gt; 42 -&gt; 46 -&gt; 51 -&gt; 56 -&gt; 62 -&gt; 68   |   Speed: 0.82x -&gt; 0.92x</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -6379,11 +5655,6 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6426,19 +5697,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6481,19 +5744,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6536,19 +5791,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6591,19 +5838,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6646,19 +5885,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6701,19 +5932,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6756,19 +5979,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6811,19 +6026,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6866,19 +6073,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6921,19 +6120,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6976,19 +6167,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7031,19 +6214,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7086,19 +6261,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7141,19 +6308,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7196,19 +6355,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7251,19 +6402,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7306,19 +6449,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7361,19 +6496,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7416,19 +6543,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7471,19 +6590,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7526,19 +6637,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7581,19 +6684,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7636,19 +6731,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7691,19 +6778,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7746,19 +6825,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7801,19 +6872,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7856,19 +6919,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7911,19 +6966,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7966,19 +7013,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8021,19 +7060,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8076,19 +7107,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8131,19 +7154,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8186,19 +7201,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8241,19 +7248,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8296,19 +7295,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8351,19 +7342,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8406,19 +7389,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8461,19 +7436,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8516,19 +7483,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8571,19 +7530,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8626,19 +7577,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8681,19 +7624,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8736,14 +7671,11 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -8754,9 +7686,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8799,14 +7728,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8817,9 +7743,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8862,14 +7785,11 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8880,9 +7800,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8925,19 +7842,11 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8980,14 +7889,11 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -8998,9 +7904,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9043,14 +7946,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9061,9 +7961,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9106,14 +8003,11 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9124,9 +8018,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9169,19 +8060,11 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9224,14 +8107,11 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -9242,9 +8122,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9287,14 +8164,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9305,9 +8179,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9350,14 +8221,11 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9368,9 +8236,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9413,19 +8278,11 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9468,14 +8325,11 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -9486,9 +8340,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9531,14 +8382,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9549,9 +8397,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9594,14 +8439,11 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9612,9 +8454,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9657,19 +8496,11 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9712,14 +8543,11 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -9730,9 +8558,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9775,14 +8600,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9793,9 +8615,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9838,14 +8657,11 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9856,9 +8672,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9901,19 +8714,11 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9956,14 +8761,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   HP Absorb: 100%   |   TP Cost: 9 (+1/Lv) -&gt; 18</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -9974,9 +8776,6 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O165" t="inlineStr"/>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10019,23 +8818,16 @@
 TP Absorb: 100% | TP Cost: 6 (+1/Lv) -&gt; 15 | Speed: 1.75x | Chant: 1.25x -&gt; 1.07x</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10078,23 +8870,16 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 27 -&gt; 31 -&gt; 35 -&gt; 39 -&gt; 43   |   Speed: 1.5x</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10137,14 +8922,11 @@
 TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50   |   Speed: 1.5x</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
           <t>Pwr, Accuracy</t>
@@ -10155,9 +8937,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10200,19 +8979,11 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18   |   Speed: 0.8x -&gt; 0.92x   |   Chant: 1.25x</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10255,19 +9026,11 @@
 TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   Speed: 2.15x   |   Chant: 1.2x -&gt; 1.4x</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10310,19 +9073,11 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10365,19 +9120,11 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1x -&gt; 1.2x</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10420,19 +9167,11 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10475,19 +9214,11 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10530,19 +9261,11 @@
 TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10585,19 +9308,11 @@
 TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10640,19 +9355,11 @@
 TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23   |   Chant: 1x -&gt; 1.12x</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10695,19 +9402,11 @@
 TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30   |   Speed: 0.4x -&gt; 0.5x   |   Chant: 1.25x</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10750,19 +9449,11 @@
 TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 18 -&gt; 22   |   Speed: 1.25x   |   Chant: 1.25x -&gt; 1.45x</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10805,14 +9496,11 @@
 TP Cost: 45 -&gt; 52 -&gt; 59 -&gt; 66 -&gt; 74 -&gt; 80 -&gt; 86 -&gt; 90 -&gt; 95 -&gt; 100   |   Speed: 1.75x</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
           <t>Pwr, Accuracy</t>
@@ -10823,9 +9511,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10868,19 +9553,11 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10923,19 +9600,11 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10978,19 +9647,11 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11033,19 +9694,11 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11088,19 +9741,11 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11143,23 +9788,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O186" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11202,23 +9840,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11261,23 +9892,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11320,14 +9944,11 @@
 TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26   |   Speed: 1.75x</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
           <t>Heal Cap</t>
@@ -11338,9 +9959,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11383,14 +10001,11 @@
 TP Cost: 15 -&gt; 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 46 -&gt; 52 -&gt; 58 -&gt; 64   |   Speed: 1.35x</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr">
         <is>
           <t>Heal Cap</t>
@@ -11401,9 +10016,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11444,19 +10056,11 @@
           <t>TP Cost: 48 -&gt; 45 -&gt; 42 -&gt; 39 -&gt; 36 (L1-5 Max)   |   Speed: 1.15x   |   Chant: 1.5x -&gt; 1.75x</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11499,19 +10103,11 @@
 TP Cost: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   Speed: 2.25x   |   Chant: 2.75x</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11554,19 +10150,11 @@
 TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25 -&gt; 30 -&gt; 36   |   Speed: 1.5x   |   Chant: 2x</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11609,19 +10197,11 @@
 TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42   |   Speed: 1.25x   |   Chant: 1.3x -&gt; 1.5x</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11664,23 +10244,16 @@
 Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17   |   Chant: 1.25x</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11723,23 +10296,16 @@
 Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17   |   Chant: 1.25x</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11782,23 +10348,16 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32   |   Chant: 1.25x</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11841,23 +10400,16 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32   |   Chant: 1.25x</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -11900,23 +10452,16 @@
 Turns: 3   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Speed: 1.25x -&gt; 1.41x</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
-      <c r="O199" t="inlineStr"/>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -11959,23 +10504,16 @@
 Turns: 5 -&gt; 5 -&gt; 6 -&gt; 6 -&gt; 7 -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 18 (+3/Lv) -&gt; 45</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12018,19 +10556,11 @@
 TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 21 -&gt; 24 -&gt; 28   |   Speed: 1.75x   |   Chant: 2.25x</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12073,19 +10603,11 @@
 Chant: 0.75x -&gt; 0.65x</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12128,19 +10650,11 @@
 Turns: 4   |   TP Cost: 24 -&gt; 28 -&gt; 33 -&gt; 37 -&gt; 42   |   Speed: 1.5x   |   Chant: 0.75x</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12183,23 +10697,16 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 45   |   Speed: 1.5x</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
-      <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12240,19 +10747,11 @@
           <t>Turns: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12293,19 +10792,11 @@
           <t>TP Cost: 28 -&gt; 21 -&gt; 14 -&gt; 7 -&gt; 1 (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12347,19 +10838,11 @@
 Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12385,7 +10868,6 @@
           <t>Raise the party's chance of doing multiple strikes while song lasts.</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
           <t>Raise the party's chance of doing multiple strikes while song lasts.</t>
@@ -12396,19 +10878,11 @@
           <t>Speed: 1.35x   |   Chant: 1.4x</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12450,19 +10924,11 @@
 Speed: 1.35x   |   Chant: 1.4x -&gt; 2x</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12504,19 +10970,11 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12558,19 +11016,11 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr"/>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12612,19 +11062,11 @@
 Speed: 1.35x   |   Chant: 1.4x -&gt; 2x</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12666,19 +11108,11 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12720,19 +11154,11 @@
 Speed: 1.35x   |   Chant: 1.1x -&gt; 1.5x</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12774,19 +11200,11 @@
 Speed: 1.35x   |   Chant: 1.1x -&gt; 1.5x</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12828,19 +11246,11 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12882,19 +11292,11 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12937,23 +11339,16 @@
 Turns: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5   |   TP Cost: 23 -&gt; 27 -&gt; 32 -&gt; 38 -&gt; 45   |   Speed: 0.85x</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
-      <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12996,19 +11391,11 @@
 Turns: 3 | TP Cost: 36 -&gt; 39 -&gt; 43 -&gt; 47 -&gt; 52 | Speed: 0.8x | Chant: 0.8x -&gt; 0.88x</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13051,19 +11438,11 @@
 Turns: 3   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Chant: 1.15x -&gt; 1.3x</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
-      <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13106,14 +11485,11 @@
 ATK: -4% (-1%/Lv) | Damage cap: 250 -&gt; 500 | Turns: 3 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -13124,9 +11500,6 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13169,14 +11542,11 @@
 Magic defense: -7% -&gt; -18%   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
           <t>Magic defense, Damage cap</t>
@@ -13187,9 +11557,6 @@
           <t>Turns, Speed, Chant</t>
         </is>
       </c>
-      <c r="O222" t="inlineStr"/>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13232,14 +11599,11 @@
 Speed decrease: 4% (+1%/Lv)   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -13250,9 +11614,6 @@
           <t>Turns, Speed, Chant</t>
         </is>
       </c>
-      <c r="O223" t="inlineStr"/>
-      <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13295,14 +11656,11 @@
 Evasion: -7% (-2%/Lv) | Damage cap: 250 -&gt; 500 | Turns: 3 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -13313,9 +11671,6 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O224" t="inlineStr"/>
-      <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13358,14 +11713,11 @@
 DEF: -4% (-1%/Lv) | Damage cap: 250 -&gt; 500 | Turns: 3 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -13376,9 +11728,6 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13421,14 +11770,11 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 22 (+4-6/Lv) -&gt; 66   |   Speed: 1.3x</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -13439,9 +11785,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13484,23 +11827,16 @@
 TP Cost: 36 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 80 -&gt; 88 -&gt; 96   |   Speed: 1.5x</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13543,23 +11879,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22   |   Chant: 1.15x</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13602,23 +11931,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22   |   Chant: 1.15x</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O229" t="inlineStr"/>
-      <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13661,19 +11983,11 @@
 Turns: 3   |   TP Cost: 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40   |   Speed: 0.75x   |   Chant: 1.75x</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
-      <c r="O230" t="inlineStr"/>
-      <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13716,19 +12030,11 @@
 TP Cost: 12 -&gt; 11 -&gt; 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13771,14 +12077,11 @@
 Recoverable status ailments: 1 (+1/Lv)   |   HP on revival: 10% (+5-10%/Lv) -&gt; 50%</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
           <t>HP on revival</t>
@@ -13789,9 +12092,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13834,14 +12134,11 @@
 Accuracy: 80% -&gt; 90% | HP recovery: 35 -&gt; 25 | Turns: 3 | TP Cost: 18 (+2-4/Lv) -&gt; 32</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
         <is>
           <t>Magic defense, Accuracy, HP recovery, TP Cost</t>
@@ -13852,9 +12149,6 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O233" t="inlineStr"/>
-      <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13897,14 +12191,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 30 (+4/Lv) -&gt; 66   |   Speed: 0.85x</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -13915,9 +12206,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O234" t="inlineStr"/>
-      <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13960,14 +12248,11 @@
 TP Cost: 32 -&gt; 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 52 -&gt; 54 -&gt; 56   |   Speed: 1.2x</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
           <t>Pwr</t>
@@ -13978,9 +12263,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr"/>
-      <c r="Q235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14023,7 +12305,6 @@
 TP Cost: 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 (L1-5 Max)   |   Speed: 1.5x   |   Chant: 0.84x -&gt; 0.8x</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -14039,11 +12320,6 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr"/>
-      <c r="Q236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14086,19 +12362,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr"/>
-      <c r="P237" t="inlineStr"/>
-      <c r="Q237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14141,19 +12409,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
-      <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14196,19 +12456,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr"/>
-      <c r="P239" t="inlineStr"/>
-      <c r="Q239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14251,19 +12503,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr"/>
-      <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14306,19 +12550,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
-      <c r="O241" t="inlineStr"/>
-      <c r="P241" t="inlineStr"/>
-      <c r="Q241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14361,19 +12597,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr"/>
-      <c r="P242" t="inlineStr"/>
-      <c r="Q242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14414,19 +12642,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr"/>
-      <c r="P243" t="inlineStr"/>
-      <c r="Q243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14467,19 +12687,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
-      <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14520,19 +12732,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17% (L10)</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
-      <c r="O245" t="inlineStr"/>
-      <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14573,19 +12777,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr"/>
-      <c r="P246" t="inlineStr"/>
-      <c r="Q246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14626,19 +12822,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr"/>
-      <c r="P247" t="inlineStr"/>
-      <c r="Q247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14679,19 +12867,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
-      <c r="O248" t="inlineStr"/>
-      <c r="P248" t="inlineStr"/>
-      <c r="Q248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14732,19 +12912,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
-      <c r="O249" t="inlineStr"/>
-      <c r="P249" t="inlineStr"/>
-      <c r="Q249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -14785,19 +12957,11 @@
           <t>ATK bonus: 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% (L10)</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr"/>
-      <c r="N250" t="inlineStr"/>
-      <c r="O250" t="inlineStr"/>
-      <c r="P250" t="inlineStr"/>
-      <c r="Q250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14838,19 +13002,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17% (L10)</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr"/>
-      <c r="N251" t="inlineStr"/>
-      <c r="O251" t="inlineStr"/>
-      <c r="P251" t="inlineStr"/>
-      <c r="Q251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -14891,19 +13047,11 @@
           <t>ATK bonus: 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% (L10)</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
-      <c r="M252" t="inlineStr"/>
-      <c r="N252" t="inlineStr"/>
-      <c r="O252" t="inlineStr"/>
-      <c r="P252" t="inlineStr"/>
-      <c r="Q252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -14944,19 +13092,11 @@
           <t>ATK bonus: 2% -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 12% (L10)</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr"/>
-      <c r="N253" t="inlineStr"/>
-      <c r="O253" t="inlineStr"/>
-      <c r="P253" t="inlineStr"/>
-      <c r="Q253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -14997,19 +13137,11 @@
           <t>Magic attack bonus: 6% -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
-      <c r="O254" t="inlineStr"/>
-      <c r="P254" t="inlineStr"/>
-      <c r="Q254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -15051,19 +13183,11 @@
 Heal Cap: +10% -&gt; +20 -&gt; +30 -&gt; +40 -&gt; +50 -&gt; +60 -&gt; +70 -&gt; +80 -&gt; +90 -&gt; +100%</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
-      <c r="O255" t="inlineStr"/>
-      <c r="P255" t="inlineStr"/>
-      <c r="Q255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15104,19 +13228,11 @@
           <t>HP recovery: 2% -&gt; 4% -&gt; 6% -&gt; 8% -&gt; 10% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
-      <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
-      <c r="O256" t="inlineStr"/>
-      <c r="P256" t="inlineStr"/>
-      <c r="Q256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -15157,19 +13273,11 @@
           <t>HP recovery: 1% -&gt; 2% -&gt; 3% -&gt; 4% -&gt; 5% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr"/>
-      <c r="N257" t="inlineStr"/>
-      <c r="O257" t="inlineStr"/>
-      <c r="P257" t="inlineStr"/>
-      <c r="Q257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -15210,19 +13318,11 @@
           <t>TP recovery: 3 -&gt; 6 -&gt; 9 -&gt; 12 -&gt; 16 (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
-      <c r="O258" t="inlineStr"/>
-      <c r="P258" t="inlineStr"/>
-      <c r="Q258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -15263,19 +13363,11 @@
           <t>TP recovery: 1 -&gt; 3 -&gt; 5 -&gt; 7 -&gt; 9 (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
-      <c r="O259" t="inlineStr"/>
-      <c r="P259" t="inlineStr"/>
-      <c r="Q259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -15316,19 +13408,11 @@
           <t>Elemental resistance: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 (L10)</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr"/>
-      <c r="P260" t="inlineStr"/>
-      <c r="Q260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15369,19 +13453,11 @@
           <t>Counterattack rate: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
-      <c r="O261" t="inlineStr"/>
-      <c r="P261" t="inlineStr"/>
-      <c r="Q261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -15422,19 +13498,11 @@
           <t>Activation rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
-      <c r="O262" t="inlineStr"/>
-      <c r="P262" t="inlineStr"/>
-      <c r="Q262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15475,19 +13543,11 @@
           <t>Double attack rate: 9% -&gt; 12% -&gt; 15% -&gt; 18% -&gt; 21% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
-      <c r="O263" t="inlineStr"/>
-      <c r="P263" t="inlineStr"/>
-      <c r="Q263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -15528,19 +13588,11 @@
           <t>Triple attack rate: 5% -&gt; 8% -&gt; 11% -&gt; 14% -&gt; 17% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr"/>
-      <c r="N264" t="inlineStr"/>
-      <c r="O264" t="inlineStr"/>
-      <c r="P264" t="inlineStr"/>
-      <c r="Q264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -15581,19 +13633,11 @@
           <t>Evasion rate: 20% -&gt; 24% -&gt; 28% -&gt; 32% -&gt; 36% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-      <c r="M265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
-      <c r="O265" t="inlineStr"/>
-      <c r="P265" t="inlineStr"/>
-      <c r="Q265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15634,19 +13678,11 @@
           <t>Activation rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
-      <c r="O266" t="inlineStr"/>
-      <c r="P266" t="inlineStr"/>
-      <c r="Q266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -15687,19 +13723,11 @@
           <t>Survival rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr"/>
-      <c r="N267" t="inlineStr"/>
-      <c r="O267" t="inlineStr"/>
-      <c r="P267" t="inlineStr"/>
-      <c r="Q267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -15740,19 +13768,11 @@
           <t>Auto-guard rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr"/>
-      <c r="N268" t="inlineStr"/>
-      <c r="O268" t="inlineStr"/>
-      <c r="P268" t="inlineStr"/>
-      <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -15793,19 +13813,11 @@
           <t>Sub-weapon ATK: 30% -&gt; 35 -&gt; 40 -&gt; 45 -&gt; 50 -&gt; 54 -&gt; 58 -&gt; 62 -&gt; 68 -&gt; 72% (L10)</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
-      <c r="M269" t="inlineStr"/>
-      <c r="N269" t="inlineStr"/>
-      <c r="O269" t="inlineStr"/>
-      <c r="P269" t="inlineStr"/>
-      <c r="Q269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -15846,19 +13858,11 @@
           <t>TP conversion: 4% -&gt; 8% -&gt; 12% -&gt; 16% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
-      <c r="O270" t="inlineStr"/>
-      <c r="P270" t="inlineStr"/>
-      <c r="Q270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -15899,19 +13903,11 @@
           <t>Activation rate: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
-      <c r="O271" t="inlineStr"/>
-      <c r="P271" t="inlineStr"/>
-      <c r="Q271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -15952,19 +13948,11 @@
           <t>Activation rate: 2% -&gt; 3% -&gt; 4% -&gt; 5% -&gt; 6% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr"/>
-      <c r="N272" t="inlineStr"/>
-      <c r="O272" t="inlineStr"/>
-      <c r="P272" t="inlineStr"/>
-      <c r="Q272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -16005,19 +13993,11 @@
           <t>Activation rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr"/>
-      <c r="N273" t="inlineStr"/>
-      <c r="O273" t="inlineStr"/>
-      <c r="P273" t="inlineStr"/>
-      <c r="Q273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16058,19 +14038,11 @@
           <t>Speed increase: 15% -&gt; 16% -&gt; 17% -&gt; 18% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr"/>
-      <c r="N274" t="inlineStr"/>
-      <c r="O274" t="inlineStr"/>
-      <c r="P274" t="inlineStr"/>
-      <c r="Q274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -16111,19 +14083,11 @@
           <t>Number of possible debuffs: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 (L6)</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr"/>
-      <c r="N275" t="inlineStr"/>
-      <c r="O275" t="inlineStr"/>
-      <c r="P275" t="inlineStr"/>
-      <c r="Q275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -16164,19 +14128,11 @@
           <t>ATK: +15% -&gt; +18% -&gt; +21% -&gt; +24% -&gt; +27% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr"/>
-      <c r="N276" t="inlineStr"/>
-      <c r="O276" t="inlineStr"/>
-      <c r="P276" t="inlineStr"/>
-      <c r="Q276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -16202,26 +14158,16 @@
           <t>Nullify the effects of enemy Dark Auras.</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
           <t>Nullify the effects of enemy Dark Auras.</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
-      <c r="O277" t="inlineStr"/>
-      <c r="P277" t="inlineStr"/>
-      <c r="Q277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -16247,26 +14193,16 @@
           <t>No longer suffer counterattacks from enemies.</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
           <t>No longer suffer counterattacks from enemies.</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr"/>
-      <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr"/>
-      <c r="N278" t="inlineStr"/>
-      <c r="O278" t="inlineStr"/>
-      <c r="P278" t="inlineStr"/>
-      <c r="Q278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -16307,19 +14243,11 @@
           <t>Physical damage: -6% -&gt; -7% -&gt; -8% -&gt; -9% -&gt; -10% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
-      <c r="P279" t="inlineStr"/>
-      <c r="Q279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -16360,19 +14288,11 @@
           <t>Activation rate: 8% -&gt; 9% -&gt; 10% -&gt; 11% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="inlineStr"/>
-      <c r="N280" t="inlineStr"/>
-      <c r="O280" t="inlineStr"/>
-      <c r="P280" t="inlineStr"/>
-      <c r="Q280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -16413,19 +14333,11 @@
           <t>LvUp: Can cure poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; slow</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr"/>
-      <c r="N281" t="inlineStr"/>
-      <c r="O281" t="inlineStr"/>
-      <c r="P281" t="inlineStr"/>
-      <c r="Q281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -16466,19 +14378,11 @@
           <t>ATK/DEX: +10% -&gt; +11% -&gt; +12% -&gt; +13% -&gt; +15% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
-      <c r="M282" t="inlineStr"/>
-      <c r="N282" t="inlineStr"/>
-      <c r="O282" t="inlineStr"/>
-      <c r="P282" t="inlineStr"/>
-      <c r="Q282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -16519,19 +14423,11 @@
           <t>Interruption rate: -10% -&gt; -20% -&gt; -30% -&gt; -40% -&gt; -50% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr"/>
-      <c r="N283" t="inlineStr"/>
-      <c r="O283" t="inlineStr"/>
-      <c r="P283" t="inlineStr"/>
-      <c r="Q283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -16572,19 +14468,11 @@
           <t>Chant time: -8% -&gt; -11% -&gt; -14% -&gt; -17% -&gt; -20% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr"/>
-      <c r="O284" t="inlineStr"/>
-      <c r="P284" t="inlineStr"/>
-      <c r="Q284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -16625,19 +14513,11 @@
           <t>TP Cost reduction: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr"/>
-      <c r="N285" t="inlineStr"/>
-      <c r="O285" t="inlineStr"/>
-      <c r="P285" t="inlineStr"/>
-      <c r="Q285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -16678,19 +14558,11 @@
           <t>Accuracy: 3% -&gt; 5% -&gt; 7% -&gt; 9% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr"/>
-      <c r="N286" t="inlineStr"/>
-      <c r="O286" t="inlineStr"/>
-      <c r="P286" t="inlineStr"/>
-      <c r="Q286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -16731,19 +14603,11 @@
           <t>Enemy preemptive attack rate: -20% -&gt; -28% -&gt; -36% -&gt; -44% -&gt; -50% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
-      <c r="M287" t="inlineStr"/>
-      <c r="N287" t="inlineStr"/>
-      <c r="O287" t="inlineStr"/>
-      <c r="P287" t="inlineStr"/>
-      <c r="Q287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -16784,19 +14648,11 @@
           <t>Preemptive attack rate: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr"/>
-      <c r="N288" t="inlineStr"/>
-      <c r="O288" t="inlineStr"/>
-      <c r="P288" t="inlineStr"/>
-      <c r="Q288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -16837,19 +14693,11 @@
           <t>Battle escape rate: 20% -&gt; 25% -&gt; 30% -&gt; 35% -&gt; 40% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
-      <c r="M289" t="inlineStr"/>
-      <c r="N289" t="inlineStr"/>
-      <c r="O289" t="inlineStr"/>
-      <c r="P289" t="inlineStr"/>
-      <c r="Q289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -16890,19 +14738,11 @@
           <t>Item drop rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
-      <c r="M290" t="inlineStr"/>
-      <c r="N290" t="inlineStr"/>
-      <c r="O290" t="inlineStr"/>
-      <c r="P290" t="inlineStr"/>
-      <c r="Q290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -16943,19 +14783,11 @@
           <t>Gold drop rate: 25% -&gt; 50% -&gt; 75% -&gt; 100% -&gt; 125% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
-      <c r="M291" t="inlineStr"/>
-      <c r="N291" t="inlineStr"/>
-      <c r="O291" t="inlineStr"/>
-      <c r="P291" t="inlineStr"/>
-      <c r="Q291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -16996,19 +14828,11 @@
           <t>Found item quality: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr"/>
-      <c r="N292" t="inlineStr"/>
-      <c r="O292" t="inlineStr"/>
-      <c r="P292" t="inlineStr"/>
-      <c r="Q292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -17050,19 +14874,11 @@
 Post-battle TP: 3% -&gt; 4% -&gt; 5% -&gt; 7% -&gt; 9%</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" t="inlineStr"/>
-      <c r="N293" t="inlineStr"/>
-      <c r="O293" t="inlineStr"/>
-      <c r="P293" t="inlineStr"/>
-      <c r="Q293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -17103,19 +14919,11 @@
           <t>Item keep rate: 25% -&gt; 27% -&gt; 29% -&gt; 32% -&gt; 35% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
-      <c r="M294" t="inlineStr"/>
-      <c r="N294" t="inlineStr"/>
-      <c r="O294" t="inlineStr"/>
-      <c r="P294" t="inlineStr"/>
-      <c r="Q294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -17156,19 +14964,11 @@
           <t>Item effects: 10% -&gt; 20 -&gt; 30 -&gt; 40 -&gt; 50 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 90 -&gt; 100% (L10)</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr"/>
-      <c r="N295" t="inlineStr"/>
-      <c r="O295" t="inlineStr"/>
-      <c r="P295" t="inlineStr"/>
-      <c r="Q295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -17209,19 +15009,11 @@
           <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr"/>
-      <c r="O296" t="inlineStr"/>
-      <c r="P296" t="inlineStr"/>
-      <c r="Q296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -17262,19 +15054,11 @@
           <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
-      <c r="M297" t="inlineStr"/>
-      <c r="N297" t="inlineStr"/>
-      <c r="O297" t="inlineStr"/>
-      <c r="P297" t="inlineStr"/>
-      <c r="Q297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -17315,19 +15099,11 @@
           <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
-      <c r="M298" t="inlineStr"/>
-      <c r="N298" t="inlineStr"/>
-      <c r="O298" t="inlineStr"/>
-      <c r="P298" t="inlineStr"/>
-      <c r="Q298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -17368,19 +15144,11 @@
           <t>Sealbook ability: +15% -&gt; +18% -&gt; +21% -&gt; +24% -&gt; +27% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
-      <c r="L299" t="inlineStr"/>
-      <c r="M299" t="inlineStr"/>
-      <c r="N299" t="inlineStr"/>
-      <c r="O299" t="inlineStr"/>
-      <c r="P299" t="inlineStr"/>
-      <c r="Q299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -17421,19 +15189,11 @@
           <t>Maid skill bonus: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10% (L10)</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
-      <c r="L300" t="inlineStr"/>
-      <c r="M300" t="inlineStr"/>
-      <c r="N300" t="inlineStr"/>
-      <c r="O300" t="inlineStr"/>
-      <c r="P300" t="inlineStr"/>
-      <c r="Q300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -17474,19 +15234,11 @@
           <t>Singing skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
-      <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
-      <c r="L301" t="inlineStr"/>
-      <c r="M301" t="inlineStr"/>
-      <c r="N301" t="inlineStr"/>
-      <c r="O301" t="inlineStr"/>
-      <c r="P301" t="inlineStr"/>
-      <c r="Q301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -17527,19 +15279,11 @@
           <t>Dancing skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
-      <c r="L302" t="inlineStr"/>
-      <c r="M302" t="inlineStr"/>
-      <c r="N302" t="inlineStr"/>
-      <c r="O302" t="inlineStr"/>
-      <c r="P302" t="inlineStr"/>
-      <c r="Q302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -17580,19 +15324,11 @@
           <t>Doll skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
-      <c r="L303" t="inlineStr"/>
-      <c r="M303" t="inlineStr"/>
-      <c r="N303" t="inlineStr"/>
-      <c r="O303" t="inlineStr"/>
-      <c r="P303" t="inlineStr"/>
-      <c r="Q303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -17633,19 +15369,11 @@
           <t>Double attack rate: 20% -&gt; 21 -&gt; 22 -&gt; 23 -&gt; 24 -&gt; 25 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32% (L10)</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
-      <c r="L304" t="inlineStr"/>
-      <c r="M304" t="inlineStr"/>
-      <c r="N304" t="inlineStr"/>
-      <c r="O304" t="inlineStr"/>
-      <c r="P304" t="inlineStr"/>
-      <c r="Q304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -17686,19 +15414,11 @@
           <t>Song chant time: -10% -&gt; -11 -&gt; -12 -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -20%</t>
         </is>
       </c>
-      <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
-      <c r="L305" t="inlineStr"/>
-      <c r="M305" t="inlineStr"/>
-      <c r="N305" t="inlineStr"/>
-      <c r="O305" t="inlineStr"/>
-      <c r="P305" t="inlineStr"/>
-      <c r="Q305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -17739,19 +15459,11 @@
           <t>Negotiation rate: 10% -&gt; 14% -&gt; 18% -&gt; 22% -&gt; 25% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
-      <c r="L306" t="inlineStr"/>
-      <c r="M306" t="inlineStr"/>
-      <c r="N306" t="inlineStr"/>
-      <c r="O306" t="inlineStr"/>
-      <c r="P306" t="inlineStr"/>
-      <c r="Q306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -17792,19 +15504,11 @@
           <t>Occurrence rate: 3% -&gt; 4% -&gt; 5% -&gt; 6% -&gt; 7% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
-      <c r="L307" t="inlineStr"/>
-      <c r="M307" t="inlineStr"/>
-      <c r="N307" t="inlineStr"/>
-      <c r="O307" t="inlineStr"/>
-      <c r="P307" t="inlineStr"/>
-      <c r="Q307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -17830,26 +15534,16 @@
           <t>Nullify first hit of battle against user (does not work for status ailments).</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
           <t>Nullify first hit of battle against user (does not work for status ailments).</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr"/>
-      <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
-      <c r="L308" t="inlineStr"/>
-      <c r="M308" t="inlineStr"/>
-      <c r="N308" t="inlineStr"/>
-      <c r="O308" t="inlineStr"/>
-      <c r="P308" t="inlineStr"/>
-      <c r="Q308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -17875,26 +15569,16 @@
           <t>Heighten the probability of beneficial results for random effect skills.</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr">
         <is>
           <t>Heighten the probability of beneficial results for random effect skills.</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr"/>
-      <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
-      <c r="L309" t="inlineStr"/>
-      <c r="M309" t="inlineStr"/>
-      <c r="N309" t="inlineStr"/>
-      <c r="O309" t="inlineStr"/>
-      <c r="P309" t="inlineStr"/>
-      <c r="Q309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -17920,26 +15604,16 @@
           <t>Whip skill. Strike back with a normal attack before a targeted attack hits you.</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr">
         <is>
           <t>Whip skill. Strike back with a normal attack before a targeted attack hits you.</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr"/>
-      <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
-      <c r="L310" t="inlineStr"/>
-      <c r="M310" t="inlineStr"/>
-      <c r="N310" t="inlineStr"/>
-      <c r="O310" t="inlineStr"/>
-      <c r="P310" t="inlineStr"/>
-      <c r="Q310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -17965,26 +15639,16 @@
           <t>Occasionally get the first action regardless of speed.</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr">
         <is>
           <t>Occasionally get the first action regardless of speed.</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr"/>
-      <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
-      <c r="L311" t="inlineStr"/>
-      <c r="M311" t="inlineStr"/>
-      <c r="N311" t="inlineStr"/>
-      <c r="O311" t="inlineStr"/>
-      <c r="P311" t="inlineStr"/>
-      <c r="Q311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -18010,26 +15674,16 @@
           <t>Occasionally land critical hits with offensive spells.</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
           <t>Occasionally land critical hits with offensive spells.</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr"/>
-      <c r="M312" t="inlineStr"/>
-      <c r="N312" t="inlineStr"/>
-      <c r="O312" t="inlineStr"/>
-      <c r="P312" t="inlineStr"/>
-      <c r="Q312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -18055,26 +15709,16 @@
           <t>Increase doll summon duration by 1 turn.</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr">
         <is>
           <t>Increase doll summon duration by 1 turn.</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
-      <c r="L313" t="inlineStr"/>
-      <c r="M313" t="inlineStr"/>
-      <c r="N313" t="inlineStr"/>
-      <c r="O313" t="inlineStr"/>
-      <c r="P313" t="inlineStr"/>
-      <c r="Q313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -18100,27 +15744,17 @@
           <t>Significantly increase damage according to Pep.</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr">
         <is>
           <t>Significantly increase damage according to Pep.
 Pep over 100 per +1% damage: 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3 -&gt; 2   |   Crown EX: 1</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr"/>
-      <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
-      <c r="L314" t="inlineStr"/>
-      <c r="M314" t="inlineStr"/>
-      <c r="N314" t="inlineStr"/>
-      <c r="O314" t="inlineStr"/>
-      <c r="P314" t="inlineStr"/>
-      <c r="Q314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -18146,27 +15780,17 @@
           <t>Occasionally inflict enemies with status ailments or Dispel at random.</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr">
         <is>
           <t>Occasionally inflict enemies with status ailments or Dispel at random.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 25%</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
-      <c r="L315" t="inlineStr"/>
-      <c r="M315" t="inlineStr"/>
-      <c r="N315" t="inlineStr"/>
-      <c r="O315" t="inlineStr"/>
-      <c r="P315" t="inlineStr"/>
-      <c r="Q315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -18192,27 +15816,17 @@
           <t>May counter short-range attacks with Slow and a Speed decrease.</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr">
         <is>
           <t>May counter short-range attacks with Slow and a Speed decrease.
 Activation rate: 16% -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38%   |   Crown EX: 50%</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
-      <c r="L316" t="inlineStr"/>
-      <c r="M316" t="inlineStr"/>
-      <c r="N316" t="inlineStr"/>
-      <c r="O316" t="inlineStr"/>
-      <c r="P316" t="inlineStr"/>
-      <c r="Q316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -18238,27 +15852,17 @@
           <t>Increase weapon modifier when attacking with weapon-based skills.</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr"/>
       <c r="G317" t="inlineStr">
         <is>
           <t>Increase weapon modifier when attacking with weapon-based skills.
 Weapon modifier: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18%   |   Crown EX: 25%</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
-      <c r="L317" t="inlineStr"/>
-      <c r="M317" t="inlineStr"/>
-      <c r="N317" t="inlineStr"/>
-      <c r="O317" t="inlineStr"/>
-      <c r="P317" t="inlineStr"/>
-      <c r="Q317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -18284,27 +15888,17 @@
           <t>May guarantee a hit and bypass DEF with physical attacks or skills.</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr">
         <is>
           <t>May guarantee a hit and bypass DEF with physical attacks or skills.
 Activation rate: 12% -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20%   |   Crown EX: 30%</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr"/>
       <c r="J318" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
-      <c r="L318" t="inlineStr"/>
-      <c r="M318" t="inlineStr"/>
-      <c r="N318" t="inlineStr"/>
-      <c r="O318" t="inlineStr"/>
-      <c r="P318" t="inlineStr"/>
-      <c r="Q318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -18330,27 +15924,17 @@
           <t>Occasionally nullify all damage received from enemies.</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr"/>
       <c r="G319" t="inlineStr">
         <is>
           <t>Occasionally nullify all damage received from enemies.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr"/>
-      <c r="M319" t="inlineStr"/>
-      <c r="N319" t="inlineStr"/>
-      <c r="O319" t="inlineStr"/>
-      <c r="P319" t="inlineStr"/>
-      <c r="Q319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -18376,27 +15960,17 @@
           <t>Before acting, may erase enemy puppets, familiars, shikigami, or slaves.</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr">
         <is>
           <t>Before acting, may erase enemy puppets, familiars, shikigami, or slaves.
 Activation rate: 25% -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 49 -&gt; 53 -&gt; 57%   |   Crown EX: 75%</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
-      <c r="L320" t="inlineStr"/>
-      <c r="M320" t="inlineStr"/>
-      <c r="N320" t="inlineStr"/>
-      <c r="O320" t="inlineStr"/>
-      <c r="P320" t="inlineStr"/>
-      <c r="Q320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -18422,27 +15996,17 @@
           <t>Before acting, may use an item from her own personal stock.</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr">
         <is>
           <t>Before acting, may use an item from her own personal stock.
 Activation rate: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18%   |   Crown EX: 25%</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
-      <c r="M321" t="inlineStr"/>
-      <c r="N321" t="inlineStr"/>
-      <c r="O321" t="inlineStr"/>
-      <c r="P321" t="inlineStr"/>
-      <c r="Q321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -18468,27 +16032,17 @@
           <t>Decrease turn delay after using skills or magic.</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr">
         <is>
           <t>Decrease turn delay after using skills or magic.
 Turn delay: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
-      <c r="L322" t="inlineStr"/>
-      <c r="M322" t="inlineStr"/>
-      <c r="N322" t="inlineStr"/>
-      <c r="O322" t="inlineStr"/>
-      <c r="P322" t="inlineStr"/>
-      <c r="Q322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -18514,27 +16068,17 @@
           <t>Increased effects for all maid skills.</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr">
         <is>
           <t>Increased effects for all maid skills.
 Maid skill effects: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 10%   |   Crown EX: 13%</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
-      <c r="L323" t="inlineStr"/>
-      <c r="M323" t="inlineStr"/>
-      <c r="N323" t="inlineStr"/>
-      <c r="O323" t="inlineStr"/>
-      <c r="P323" t="inlineStr"/>
-      <c r="Q323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -18560,27 +16104,17 @@
           <t>May occasionally act twice in one turn.</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr">
         <is>
           <t>May occasionally act twice in one turn.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
-      <c r="L324" t="inlineStr"/>
-      <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr"/>
-      <c r="O324" t="inlineStr"/>
-      <c r="P324" t="inlineStr"/>
-      <c r="Q324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -18606,27 +16140,17 @@
           <t>If killed, revive after a certain number of turns.</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr">
         <is>
           <t>If killed, revive after a certain number of turns.
 Activation rate: 8% -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24%   |   Crown EX: 30%</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
-      <c r="L325" t="inlineStr"/>
-      <c r="M325" t="inlineStr"/>
-      <c r="N325" t="inlineStr"/>
-      <c r="O325" t="inlineStr"/>
-      <c r="P325" t="inlineStr"/>
-      <c r="Q325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -18652,27 +16176,17 @@
           <t>Whole row takes less damage from Demons, Undead, and Apparitions.</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr">
         <is>
           <t>Whole row takes less damage from Demons, Undead, and Apparitions.
 Taken: -12% -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -19 -&gt; -20%   |   Crown EX: -25%</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
-      <c r="L326" t="inlineStr"/>
-      <c r="M326" t="inlineStr"/>
-      <c r="N326" t="inlineStr"/>
-      <c r="O326" t="inlineStr"/>
-      <c r="P326" t="inlineStr"/>
-      <c r="Q326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -18698,27 +16212,17 @@
           <t>May lower all enemies' ATK and INT with heart-penetrating vocals.</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr">
         <is>
           <t>May lower all enemies' ATK and INT with heart-penetrating vocals.
 Activation rate: 7% -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13%   |   Crown EX: 20%</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
-      <c r="L327" t="inlineStr"/>
-      <c r="M327" t="inlineStr"/>
-      <c r="N327" t="inlineStr"/>
-      <c r="O327" t="inlineStr"/>
-      <c r="P327" t="inlineStr"/>
-      <c r="Q327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -18744,27 +16248,17 @@
           <t>Magic will occasionally activate immediately without the need to chant.</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr">
         <is>
           <t>Magic will occasionally activate immediately without the need to chant.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr"/>
       <c r="J328" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
-      <c r="L328" t="inlineStr"/>
-      <c r="M328" t="inlineStr"/>
-      <c r="N328" t="inlineStr"/>
-      <c r="O328" t="inlineStr"/>
-      <c r="P328" t="inlineStr"/>
-      <c r="Q328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -18790,7 +16284,6 @@
           <t>Occasionally reflects a percentage of damage taken as fixed damage.</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr">
         <is>
           <t>Occasionally reflects a percentage of damage taken as fixed damage.
@@ -18798,20 +16291,11 @@
 Activation rate: 15%</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
-      <c r="L329" t="inlineStr"/>
-      <c r="M329" t="inlineStr"/>
-      <c r="N329" t="inlineStr"/>
-      <c r="O329" t="inlineStr"/>
-      <c r="P329" t="inlineStr"/>
-      <c r="Q329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -18837,27 +16321,17 @@
           <t>Summons another self from the shadows to attack.</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr">
         <is>
           <t>Summons another self from the shadows to attack.
 Activation rate: 4% -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12%   |   Crown EX: 20%</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
-      <c r="L330" t="inlineStr"/>
-      <c r="M330" t="inlineStr"/>
-      <c r="N330" t="inlineStr"/>
-      <c r="O330" t="inlineStr"/>
-      <c r="P330" t="inlineStr"/>
-      <c r="Q330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -18883,27 +16357,17 @@
           <t>Increased effects for all class modifiers.</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr">
         <is>
           <t>Increased effects for all class modifiers.
 Class modifiers (%): 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Crown EX: 15</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
-      <c r="L331" t="inlineStr"/>
-      <c r="M331" t="inlineStr"/>
-      <c r="N331" t="inlineStr"/>
-      <c r="O331" t="inlineStr"/>
-      <c r="P331" t="inlineStr"/>
-      <c r="Q331" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -3112,23 +3112,18 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Damage UP   |   Duration: 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 3
-TP Cost: 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 59 -&gt; 62   |   Speed: 0.82x</t>
+          <t>ATK: 100% -&gt; 102 -&gt; 104 -&gt; 106 -&gt; 108 -&gt; 110 -&gt; 112 -&gt; 114 -&gt; 117 -&gt; 120% (L10)
+1-3 hits   |   Duration: 2 -&gt; 3   |   TP Cost: 35 (+3/Lv) -&gt; 62   |   Speed: 0.82x</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Damage UP</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>effect_2</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -5356,23 +5351,18 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>ATK UP   |   Duration: 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 5 -&gt; 6
-TP Cost: 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42</t>
+          <t>ATK: 144% -&gt; 147 -&gt; 150 -&gt; 154 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170 -&gt; 175 -&gt; 180% (L10)
+Duration: 3 -&gt; 6   |   TP Cost: 20 (+2-3/Lv) -&gt; 42   |   Speed: 0.85x -&gt; 0.98x</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>ATK UP</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>effect_1</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -5418,23 +5408,18 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ATK UP | Duration: 3 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 | Paralysis rate UP
-TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 44 -&gt; 46 -&gt; 48   |   Speed: 0.9x</t>
+          <t>ATK: 126% (+2-5%/Lv) -&gt; 157%   |   Paralysis: 30% (+3-5%/Lv) -&gt; 64% (L10)
+Duration: 3 -&gt; 5   |   TP Cost: 24 (+2-3/Lv) -&gt; 48   |   Speed: 0.9x</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>ATK UP; Paralysis rate UP</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>effect_1</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -5475,23 +5460,18 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>HP recovery UP   |   Duration: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5 (L1-5 Max)
+          <t>Heal Power: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 (L1-5 Max)   |   Duration: 3 -&gt; 5
 TP Cost: 30 -&gt; 33 -&gt; 37 -&gt; 42 -&gt; 48   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>HP recovery UP</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>effect_1</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -5532,23 +5512,18 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>ATK UP   |   Duration: 2 -&gt; 2 -&gt; 2 -&gt; 2 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4
-TP Cost: 42 -&gt; 44 -&gt; 46 -&gt; 48 -&gt; 50 -&gt; 53 -&gt; 56 -&gt; 60 -&gt; 64 -&gt; 70   |   Speed: 0.75x</t>
+          <t>ATK: 100% -&gt; 104 -&gt; 108 -&gt; 112 -&gt; 118 -&gt; 123 -&gt; 128 -&gt; 133 -&gt; 138 -&gt; 143% (L10)
+Duration: 2 -&gt; 4   |   TP Cost: 42 (+2-6/Lv) -&gt; 70   |   Speed: 0.75x</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>ATK UP</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>effect_1</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -5636,23 +5611,18 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Doll magic damage UP   |   Doll magic accuracy UP   |   Duration: 4
-TP Cost: 38 -&gt; 42 -&gt; 46 -&gt; 51 -&gt; 56 -&gt; 62 -&gt; 68   |   Speed: 0.82x -&gt; 0.92x</t>
+          <t>Pwr: 180 -&gt; 240 -&gt; 310 -&gt; 390 -&gt; 480 -&gt; 585 -&gt; 700 (L7 Max)
+Duration: 4   |   TP Cost: 38 (+4-6/Lv) -&gt; 68   |   Speed: 0.82x -&gt; 0.92x</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Doll magic damage UP; Doll magic accuracy UP</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>effect_1</t>
+          <t>Full</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -3113,7 +3113,7 @@
       <c r="H51" t="inlineStr">
         <is>
           <t>ATK: 100% -&gt; 102 -&gt; 104 -&gt; 106 -&gt; 108 -&gt; 110 -&gt; 112 -&gt; 114 -&gt; 117 -&gt; 120% (L10)
-1-3 hits   |   Duration: 2 -&gt; 3   |   TP Cost: 35 (+3/Lv) -&gt; 62   |   Speed: 0.82x</t>
+1-3 hits   |   Turns: 2 (Lv1-9) -&gt; 3 (L10 Max)   |   TP Cost: 35 (+3/Lv) -&gt; 62</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5352,7 +5352,7 @@
       <c r="H97" t="inlineStr">
         <is>
           <t>ATK: 144% -&gt; 147 -&gt; 150 -&gt; 154 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170 -&gt; 175 -&gt; 180% (L10)
-Duration: 3 -&gt; 6   |   TP Cost: 20 (+2-3/Lv) -&gt; 42   |   Speed: 0.85x -&gt; 0.98x</t>
+Turns: 3 (Lv1-3) -&gt; 4 (Lv4-6) -&gt; 5 (Lv7-9) -&gt; 6 (L10)   |   TP Cost: 20 -&gt; 42</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5409,7 +5409,7 @@
       <c r="H98" t="inlineStr">
         <is>
           <t>ATK: 126% (+2-5%/Lv) -&gt; 157%   |   Paralysis: 30% (+3-5%/Lv) -&gt; 64% (L10)
-Duration: 3 -&gt; 5   |   TP Cost: 24 (+2-3/Lv) -&gt; 48   |   Speed: 0.9x</t>
+Turns: 3 (Lv1-4) -&gt; 4 (Lv5-8) -&gt; 5 (Lv9-10) | TP Cost: 24 -&gt; 48 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5460,8 +5460,8 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Heal Power: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 (L1-5 Max)   |   Duration: 3 -&gt; 5
-TP Cost: 30 -&gt; 33 -&gt; 37 -&gt; 42 -&gt; 48   |   Speed: 0.9x</t>
+          <t>Heal Power: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 (L1-5 Max)
+Turns: 3 (Lv1-2) -&gt; 4 (Lv3-4) -&gt; 5 (L5 Max) | TP Cost: 30 -&gt; 48 | Speed: 0.9x</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5513,7 +5513,7 @@
       <c r="H100" t="inlineStr">
         <is>
           <t>ATK: 100% -&gt; 104 -&gt; 108 -&gt; 112 -&gt; 118 -&gt; 123 -&gt; 128 -&gt; 133 -&gt; 138 -&gt; 143% (L10)
-Duration: 2 -&gt; 4   |   TP Cost: 42 (+2-6/Lv) -&gt; 70   |   Speed: 0.75x</t>
+Turns: 2 (Lv1-4) -&gt; 3 (Lv5-7) -&gt; 4 (Lv8-10) | TP Cost: 42 -&gt; 70 | Speed: 0.75x</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5612,7 +5612,7 @@
       <c r="H102" t="inlineStr">
         <is>
           <t>Pwr: 180 -&gt; 240 -&gt; 310 -&gt; 390 -&gt; 480 -&gt; 585 -&gt; 700 (L7 Max)
-Duration: 4   |   TP Cost: 38 (+4-6/Lv) -&gt; 68   |   Speed: 0.82x -&gt; 0.92x</t>
+Turns: 4   |   TP Cost: 38 (+4-6/Lv) -&gt; 68   |   Speed: 0.82x -&gt; 0.92x</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -1533,7 +1533,12 @@
       <c r="H20" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 130 -&gt; 140 -&gt; 148 -&gt; 156 -&gt; 164 -&gt; 170 -&gt; 176 -&gt; 180 -&gt; 184% (L10)
-Targets: 2 -&gt; 2 -&gt; 2 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5   |   TP Cost: 26 (+4-6/Lv) -&gt; 68</t>
+Targets: 2 (Lv1-3) -&gt; 3 (Lv4-6) -&gt; 4 (Lv7-8) -&gt; 5 (L9-10) | TP: 26 (+4-6/Lv) -&gt; 68</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2457,7 +2462,12 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>Speed increase: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 20% (L10)
-Turns: 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 5 -&gt; 6   |   TP Cost: 14 (+2/Lv) -&gt; 32</t>
+Turns: 3 (Lv1-3) -&gt; 4 (Lv4-6) -&gt; 5 (Lv7-9) -&gt; 6 (L10)  |  TP Cost: 14 (+2/Lv) -&gt; 32</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2711,8 +2721,13 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Number of attacks: 3 -&gt; 3 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 5 -&gt; 5   |   ATK: 104% -&gt; 148%
-Power decrease: 25% -&gt; 14%   |   TP Cost: 30 (+4-6/Lv) -&gt; 72   |   Speed: 0.75x -&gt; 0.85x</t>
+          <t>Number of attacks: 3 (Lv1-4) -&gt; 4 (Lv5-8) -&gt; 5 (L9-10)   |   ATK: 104% -&gt; 148%
+Power decrease: 25% -&gt; 14% | TP Cost: 30 (+4-6/Lv) -&gt; 72 | Speed: 0.75x -&gt; 0.85x</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -11452,7 +11467,12 @@
       <c r="H221" t="inlineStr">
         <is>
           <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
-ATK: -4% (-1%/Lv) | Damage cap: 250 -&gt; 500 | Turns: 3 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
+ATK: -4% (-1%/Lv) (3 Turns) | Damage cap: 250 -&gt; 500 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -11623,7 +11643,12 @@
       <c r="H224" t="inlineStr">
         <is>
           <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
-Evasion: -7% (-2%/Lv) | Damage cap: 250 -&gt; 500 | Turns: 3 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
+Evasion: -7% (-2%/Lv) (3 Turns) | Damage cap: 250 -&gt; 500 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -11680,7 +11705,12 @@
       <c r="H225" t="inlineStr">
         <is>
           <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
-DEF: -4% (-1%/Lv) | Damage cap: 250 -&gt; 500 | Turns: 3 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
+DEF: -4% (-1%/Lv) (3 Turns) | Damage cap: 250 -&gt; 500 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -12101,7 +12131,12 @@
       <c r="H233" t="inlineStr">
         <is>
           <t>DEF: -5% -&gt; -6% -&gt; -7% -&gt; -8% -&gt; -10% (L1-5 Max)   |   Magic defense: -10% -&gt; -15%
-Accuracy: 80% -&gt; 90% | HP recovery: 35 -&gt; 25 | Turns: 3 | TP Cost: 18 (+2-4/Lv) -&gt; 32</t>
+Accuracy: 80% -&gt; 90% | HP recovery: 35 -&gt; 25 | Turns: 3 | TP: 18 (+2-4/Lv) -&gt; 32</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -5367,7 +5367,7 @@
       <c r="H97" t="inlineStr">
         <is>
           <t>ATK: 144% -&gt; 147 -&gt; 150 -&gt; 154 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170 -&gt; 175 -&gt; 180% (L10)
-Turns: 3 (Lv1-3) -&gt; 4 (Lv4-6) -&gt; 5 (Lv7-9) -&gt; 6 (L10)   |   TP Cost: 20 -&gt; 42</t>
+Turns: 3 (Lv1-3) -&gt; 4 (Lv4-6) -&gt; 5 (Lv7-9) -&gt; 6 (L10)    |    TP Cost: 20 -&gt; 42</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5424,7 +5424,7 @@
       <c r="H98" t="inlineStr">
         <is>
           <t>ATK: 126% (+2-5%/Lv) -&gt; 157%   |   Paralysis: 30% (+3-5%/Lv) -&gt; 64% (L10)
-Turns: 3 (Lv1-4) -&gt; 4 (Lv5-8) -&gt; 5 (Lv9-10) | TP Cost: 24 -&gt; 48 | Speed: 0.9x</t>
+Turns: 3 (Lv1-4) -&gt; 4 (Lv5-8) -&gt; 5 (Lv9-10)  |  TP Cost: 24 -&gt; 48  |  Speed: 0.9x</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5476,7 +5476,7 @@
       <c r="H99" t="inlineStr">
         <is>
           <t>Heal Power: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 (L1-5 Max)
-Turns: 3 (Lv1-2) -&gt; 4 (Lv3-4) -&gt; 5 (L5 Max) | TP Cost: 30 -&gt; 48 | Speed: 0.9x</t>
+Turns: 3 (Lv1-2) -&gt; 4 (Lv3-4) -&gt; 5 (L5 Max)   |   TP Cost: 30 -&gt; 48   |   Speed: 0.9x</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5528,7 +5528,7 @@
       <c r="H100" t="inlineStr">
         <is>
           <t>ATK: 100% -&gt; 104 -&gt; 108 -&gt; 112 -&gt; 118 -&gt; 123 -&gt; 128 -&gt; 133 -&gt; 138 -&gt; 143% (L10)
-Turns: 2 (Lv1-4) -&gt; 3 (Lv5-7) -&gt; 4 (Lv8-10) | TP Cost: 42 -&gt; 70 | Speed: 0.75x</t>
+Turns: 2 (Lv1-4) -&gt; 3 (Lv5-7) -&gt; 4 (Lv8-10)  |  TP Cost: 42 -&gt; 70  |  Speed: 0.75x</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5627,7 +5627,7 @@
       <c r="H102" t="inlineStr">
         <is>
           <t>Pwr: 180 -&gt; 240 -&gt; 310 -&gt; 390 -&gt; 480 -&gt; 585 -&gt; 700 (L7 Max)
-Turns: 4   |   TP Cost: 38 (+4-6/Lv) -&gt; 68   |   Speed: 0.82x -&gt; 0.92x</t>
+Turns: 4    |    TP Cost: 38 (+4-6/Lv) -&gt; 68    |    Speed: 0.82x -&gt; 0.92x</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -449,7 +449,7 @@
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="67" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -580,11 +580,19 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5   |   Speed: 1.5x -&gt; 2x</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -627,11 +635,19 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | Speed: 1.25x -&gt; 1.77x</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -674,16 +690,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -726,16 +749,23 @@
 Accuracy: +20% (+2%/Lv)   |   TP Cost: 5 (+2-3/Lv) -&gt; 28   |   Speed: 0.8x -&gt; 0.9x</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -778,16 +808,23 @@
 Buff cancel rate: 68% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 5 (+1-2/Lv) -&gt; 18   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Buff cancel rate, TP Cost</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -830,11 +867,14 @@
 DEF: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%   |   Turns: 4 -&gt; 8   |   TP Cost: 8 (+2/Lv) -&gt; 16</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -845,6 +885,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -887,11 +930,14 @@
 ATK: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%   |   Turns: 4 -&gt; 8   |   TP Cost: 8 (+2/Lv) -&gt; 16</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -902,6 +948,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -944,11 +993,14 @@
 Stun: 30% -&gt; 32% -&gt; 34% -&gt; 36% -&gt; 38%   |   TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -959,6 +1011,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1001,11 +1056,14 @@
 Accuracy: +5% (+2-3%/Lv) -&gt; +28%   |   Paralysis: 20% -&gt; 50%   |   TP Cost: 6 (+2/Lv) -&gt; 24</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Accuracy, Paralysis</t>
@@ -1016,6 +1074,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1058,16 +1119,23 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1110,11 +1178,14 @@
 Instakill: 10% (+1-2%/Lv) -&gt; 20%   |   Power decrease: 10%   |   TP Cost: 38 (+4/Lv) -&gt; 74</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Instakill</t>
@@ -1125,6 +1196,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1167,11 +1241,19 @@
 Enemy DEF: -16% (-1%/Lv)   |   Turns: 4   |   TP Cost: 14 (+2/Lv) -&gt; 32   |   Speed: 0.8x</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1214,16 +1296,23 @@
 TP Cost: 22 -&gt; 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1266,16 +1355,23 @@
 Critical rate: 10%   |   TP Cost: 36 (+2-3/Lv) -&gt; 61   |   Speed: 0.7x -&gt; 0.8x</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1318,16 +1414,23 @@
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>HP Absorb</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1370,16 +1473,23 @@
 TP Absorb: 10% (+1-2%/Lv) -&gt; 20%   |   TP Cost: 6 (+2/Lv) -&gt; 24   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>TP Absorb</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1422,11 +1532,14 @@
 Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   Accuracy: +14%   |   TP Cost: 9 (+3/Lv) -&gt; 36</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Freeze</t>
@@ -1437,6 +1550,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1479,11 +1595,14 @@
 TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 37 -&gt; 42</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>ATK, Petrify</t>
@@ -1494,6 +1613,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1533,7 +1655,7 @@
       <c r="H20" t="inlineStr">
         <is>
           <t>ATK: 120% -&gt; 130 -&gt; 140 -&gt; 148 -&gt; 156 -&gt; 164 -&gt; 170 -&gt; 176 -&gt; 180 -&gt; 184% (L10)
-Targets: 2 (Lv1-3) -&gt; 3 (Lv4-6) -&gt; 4 (Lv7-8) -&gt; 5 (L9-10) | TP: 26 (+4-6/Lv) -&gt; 68</t>
+Targets: 2 (Lv1-3) -&gt; 3 (Lv4-6) -&gt; 4 (Lv7-8) -&gt; 5 (L9-10)   |   TP: 26 (+4-6/Lv) -&gt; 68</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1543,9 +1665,11 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -1556,6 +1680,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1598,16 +1725,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 10 -&gt; 14 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1650,16 +1784,23 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1702,11 +1843,14 @@
 Accuracy: +6% -&gt; +20%   |   Damage vs. unholy: +65%   |   TP Cost: 12 (+3/Lv) -&gt; 39</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -1717,6 +1861,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1759,16 +1906,23 @@
 Turns: 5   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1811,16 +1965,23 @@
 Turns: 5   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1863,16 +2024,23 @@
 Paralysis: 20% (+2-3%/Lv) -&gt; 40%   |   TP Cost: 26 (+4-5/Lv) -&gt; 64   |   Speed: 0.8x</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Paralysis, TP Cost</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1915,11 +2083,14 @@
 Silence: 20% (+3-4%/Lv) -&gt; 50%   |   Accuracy: +15%   |   TP Cost: 7 (+3/Lv) -&gt; 34</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Silence</t>
@@ -1930,6 +2101,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1972,16 +2146,23 @@
 Heavy Lance bonus: +20%   |   TP Cost: 36 (+3-6/Lv) -&gt; 71   |   Speed: 0.7x -&gt; 0.8x</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2024,16 +2205,23 @@
 Accuracy: +5% (+1-2%/Lv) -&gt; +15%   |   TP Cost: 32 (+3/Lv) -&gt; 59   |   Speed: 0.8x</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2076,11 +2264,19 @@
 Turns: 2   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Speed: 0.84x -&gt; 0.9x</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2122,11 +2318,19 @@
 Speed: 1x -&gt; 1.5x</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2168,11 +2372,19 @@
 Speed: 0.6x -&gt; 0.8x</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2215,11 +2427,19 @@
 TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 -&gt; 28 -&gt; 30   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2262,11 +2482,19 @@
 TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 35 -&gt; 38   |   Speed: 0.85x</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2309,16 +2537,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2361,11 +2596,19 @@
 TP Cost: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2408,11 +2651,14 @@
 Turns: 5 -&gt; 9   |   TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -2423,6 +2669,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2462,7 +2711,7 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>Speed increase: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 20% (L10)
-Turns: 3 (Lv1-3) -&gt; 4 (Lv4-6) -&gt; 5 (Lv7-9) -&gt; 6 (L10)  |  TP Cost: 14 (+2/Lv) -&gt; 32</t>
+Turns: 3 (Lv1-3) -&gt; 4 (Lv4-6) -&gt; 5 (Lv7-9) -&gt; 6 (L10)   |   TP Cost: 14 (+2/Lv) -&gt; 32</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2472,9 +2721,16 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2517,16 +2773,23 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>Physical evasion, Magic evasion</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2560,7 +2823,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Short-range/Projectile: moderate damage. May cause sleep (20-50%).</t>
+          <t>Short-range: moderate damage to an enemy. May cause sleep (20-50%).</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2569,16 +2832,23 @@
 Sleep: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>Sleep</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2612,7 +2882,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Short-range/Projectile: moderate damage. May silence (20-50%).</t>
+          <t>Short-range: moderate damage to an enemy. May silence (20-50%).</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2621,16 +2891,23 @@
 Silence: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>Silence</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2664,7 +2941,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Short-range/Projectile: moderate damage. May stun (20-50%).</t>
+          <t>Short-range: moderate damage to an enemy. May stun (20-50%).</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2673,16 +2950,23 @@
 Stun: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>Stun</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2722,7 +3006,7 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>Number of attacks: 3 (Lv1-4) -&gt; 4 (Lv5-8) -&gt; 5 (L9-10)   |   ATK: 104% -&gt; 148%
-Power decrease: 25% -&gt; 14% | TP Cost: 30 (+4-6/Lv) -&gt; 72 | Speed: 0.75x -&gt; 0.85x</t>
+Power decrease: 25% -&gt; 14%   |   TP Cost: 30 (+4-6/Lv) -&gt; 72   |   Speed: 0.75x -&gt; 0.85x</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2732,14 +3016,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>ATK, Power decrease, TP Cost</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2782,11 +3072,19 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16   |   Speed: 1x -&gt; 1.12x</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2829,11 +3127,19 @@
 TP Cost: 42 -&gt; 50 -&gt; 57 -&gt; 63 -&gt; 68   |   Speed: 0.4x</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2876,16 +3182,23 @@
 Poison: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>Poison</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2928,16 +3241,23 @@
 Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 8 (+2/Lv) -&gt; 26</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>Freeze</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2980,16 +3300,23 @@
 Paralysis: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 8 (+2/Lv) -&gt; 26</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>Paralysis</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3032,16 +3359,23 @@
 Slow: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 9 (+2/Lv) -&gt; 27   |   Speed: 0.95x</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>Slow</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3084,11 +3418,19 @@
 TP Cost: 20 -&gt; 23 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48   |   Speed: 0.65x</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3138,14 +3480,24 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>no damage word: carries effects that are not understood: 146, 147</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Damage UP</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>effect_2</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3188,16 +3540,23 @@
 Critical rate: 5% (+1-3%/Lv) -&gt; 25%   |   TP Cost: 24 (+3-4/Lv) -&gt; 55   |   Speed: 0.7x</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>Critical rate, TP Cost</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3231,7 +3590,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Short-range/Projectile: minor damage, lower speed for an enemy row.</t>
+          <t>Projectile skill. Deal minor damage and lower speed for an enemy row.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3240,11 +3599,14 @@
 Turns: 4   |   TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>ATK, Speed decrease chance</t>
@@ -3255,6 +3617,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3297,11 +3662,14 @@
 Stun: 10% -&gt; 20%   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>Stun</t>
@@ -3312,6 +3680,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3353,11 +3724,19 @@
 TP Cost: 10 -&gt; 8 -&gt; 6 -&gt; 4 -&gt; 2</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3400,16 +3779,23 @@
 Magic accuracy: -2% (-2%/Lv)   |   Turns: 6   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 32</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3452,11 +3838,14 @@
 Accuracy: +10% (+2-4%/Lv) -&gt; +30%   |   ATK: 82%   |   TP Cost: 28 (+4/Lv) -&gt; 64</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -3467,6 +3856,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3509,16 +3901,23 @@
 Turns: 4   |   TP Cost: 25 -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 48 -&gt; 51 -&gt; 54 -&gt; 57</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3561,16 +3960,23 @@
 TP Cost: 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 57 -&gt; 62 -&gt; 67 -&gt; 73 -&gt; 79</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3613,11 +4019,14 @@
 Turns: 4 -&gt; 7   |   TP Cost: 22 -&gt; 25 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 56</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -3628,6 +4037,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3670,11 +4082,19 @@
 Turns: 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 6   |   TP Cost: 52 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 92   |   Speed: 1.25x</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3717,16 +4137,23 @@
 Accuracy: +10% (+1-2%/Lv) -&gt; +20%   |   TP Cost: 13 (+3-4/Lv) -&gt; 45   |   Speed: 0.9x -&gt; 1x</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3769,16 +4196,23 @@
 Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   Silence: 20% -&gt; 50%   |   TP Cost: 9 (+3/Lv) -&gt; 36</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>Freeze, Silence</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3821,11 +4255,19 @@
 TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 36 -&gt; 40 -&gt; 43 -&gt; 46 -&gt; 49 -&gt; 52 -&gt; 55</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3851,16 +4293,26 @@
           <t>Detect how many unopened treasure chests are left on the current floor.</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>Detect how many unopened treasure chests are left on this floor.</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3901,11 +4353,19 @@
           <t>HP recovery: 12% -&gt; 15% -&gt; 18% -&gt; 21% -&gt; 25% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3947,11 +4407,19 @@
 Speed: 0.85x</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3992,11 +4460,19 @@
           <t>TP transfer bonus: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4038,11 +4514,19 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4084,11 +4568,19 @@
 Speed: 0.9x</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4130,11 +4622,19 @@
 Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4176,11 +4676,19 @@
 Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4222,11 +4730,19 @@
 Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4268,11 +4784,19 @@
 Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4315,16 +4839,23 @@
 Total damage cap: 250 -&gt; 275 -&gt; 300 -&gt; 325 -&gt; 350 -&gt; 375 -&gt; 400 -&gt; 430 -&gt; 460 -&gt; 500</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4366,11 +4897,19 @@
 Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4412,11 +4951,19 @@
 Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4459,16 +5006,23 @@
 Power decrease: 10%   |   TP Cost: 22 (+3-4/Lv) -&gt; 50   |   Speed: 0.75x -&gt; 0.85x</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4511,11 +5065,19 @@
 TP Cost: 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46   |   Speed: 0.75x -&gt; 0.8x</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4558,16 +5120,23 @@
 Paralysis: 20% -&gt; 23% -&gt; 26% -&gt; 29% -&gt; 32%   |   TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4610,16 +5179,23 @@
 Accuracy: +20%   |   TP Cost: 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 56 -&gt; 60</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4662,11 +5238,19 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4692,16 +5276,26 @@
           <t>Spin the magic roulette. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>Spin the magic roulette. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4744,16 +5338,23 @@
 Instakill: 15% (+1-2%/Lv) -&gt; 25%   |   TP Cost: 17 (+2/Lv) -&gt; 35   |   Speed: 0.88x</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
           <t>Instakill</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4796,16 +5397,23 @@
 Stun: 40% (+3-4%/Lv) -&gt; 70%   |   TP Cost: 32 (+2/Lv) -&gt; 50   |   Speed: 0.65x</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
           <t>Stun</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4848,16 +5456,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4883,16 +5498,26 @@
           <t>Open a magic box. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>Open a magic box. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4935,11 +5560,19 @@
 TP Cost: 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32   |   Speed: 0.85x</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4982,16 +5615,23 @@
 Poison: 50% (+3-4%/Lv) -&gt; 80%   |   TP Cost: 22 (+4/Lv) -&gt; 58   |   Speed: 0.6x -&gt; 0.7x</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>Poison</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5034,16 +5674,23 @@
 Turn delay rate: 25% (+2%/Lv)   |   TP Cost: 10 (+2-3/Lv) -&gt; 32   |   Speed: 0.95x</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5069,6 +5716,7 @@
           <t>Fan skill. With increased ATK, deal long-range damage to one enemy.</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>Fan skill. With raised ATK, deal minor long-range damage to an enemy.</t>
@@ -5080,11 +5728,19 @@
 Speed: 1.15x</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5127,16 +5783,23 @@
 TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50   |   Speed: 0.75x</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>Slow</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5179,16 +5842,23 @@
 Turns: 6   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 23 -&gt; 25   |   Speed: 0.85x</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>Max HP reduction</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5231,11 +5901,19 @@
 Turns: 2   |   TP Cost: 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50   |   Speed: 1.15x</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5261,16 +5939,26 @@
           <t>Something emerges from the shadows. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>Something emerges from the shadows. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5313,6 +6001,7 @@
 Accuracy UP   |   TP Cost: 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -5323,11 +6012,16 @@
           <t>Accuracy UP</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5367,7 +6061,7 @@
       <c r="H97" t="inlineStr">
         <is>
           <t>ATK: 144% -&gt; 147 -&gt; 150 -&gt; 154 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170 -&gt; 175 -&gt; 180% (L10)
-Turns: 3 (Lv1-3) -&gt; 4 (Lv4-6) -&gt; 5 (Lv7-9) -&gt; 6 (L10)    |    TP Cost: 20 -&gt; 42</t>
+Turns: 3 (Lv1-3) -&gt; 4 (Lv4-6) -&gt; 5 (Lv7-9) -&gt; 6 (L10)   |   TP Cost: 20 -&gt; 42</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5377,14 +6071,28 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>ATK UP</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>effect_1</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5424,7 +6132,7 @@
       <c r="H98" t="inlineStr">
         <is>
           <t>ATK: 126% (+2-5%/Lv) -&gt; 157%   |   Paralysis: 30% (+3-5%/Lv) -&gt; 64% (L10)
-Turns: 3 (Lv1-4) -&gt; 4 (Lv5-8) -&gt; 5 (Lv9-10)  |  TP Cost: 24 -&gt; 48  |  Speed: 0.9x</t>
+Turns: 3 (Lv1-4) -&gt; 4 (Lv5-8) -&gt; 5 (Lv9-10)   |   TP Cost: 24 -&gt; 48   |   Speed: 0.9x</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5434,9 +6142,24 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>ATK UP; Paralysis rate UP</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>effect_1</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5486,9 +6209,24 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>HP recovery UP</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>effect_1</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5528,7 +6266,7 @@
       <c r="H100" t="inlineStr">
         <is>
           <t>ATK: 100% -&gt; 104 -&gt; 108 -&gt; 112 -&gt; 118 -&gt; 123 -&gt; 128 -&gt; 133 -&gt; 138 -&gt; 143% (L10)
-Turns: 2 (Lv1-4) -&gt; 3 (Lv5-7) -&gt; 4 (Lv8-10)  |  TP Cost: 42 -&gt; 70  |  Speed: 0.75x</t>
+Turns: 2 (Lv1-4) -&gt; 3 (Lv5-7) -&gt; 4 (Lv8-10)   |   TP Cost: 42 -&gt; 70   |   Speed: 0.75x</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5538,9 +6276,24 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>ATK UP</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>effect_1</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5583,11 +6336,19 @@
 Duration: 5   |   TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 38   |   Speed: 1.15x</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5627,7 +6388,7 @@
       <c r="H102" t="inlineStr">
         <is>
           <t>Pwr: 180 -&gt; 240 -&gt; 310 -&gt; 390 -&gt; 480 -&gt; 585 -&gt; 700 (L7 Max)
-Turns: 4    |    TP Cost: 38 (+4-6/Lv) -&gt; 68    |    Speed: 0.82x -&gt; 0.92x</t>
+Turns: 4   |   TP Cost: 38 (+4-6/Lv) -&gt; 68   |   Speed: 0.82x -&gt; 0.92x</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5637,9 +6398,24 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Doll magic damage UP; Doll magic accuracy UP</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>effect_1</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5682,11 +6458,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5729,11 +6513,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5776,11 +6568,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5823,11 +6623,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5870,11 +6678,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5917,11 +6733,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5964,11 +6788,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6011,11 +6843,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6058,11 +6898,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6105,11 +6953,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6152,11 +7008,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6199,11 +7063,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6246,11 +7118,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6293,11 +7173,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6340,11 +7228,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6387,11 +7283,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6434,11 +7338,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6481,11 +7393,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6528,11 +7448,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6575,11 +7503,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6622,11 +7558,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6669,11 +7613,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6716,11 +7668,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6763,11 +7723,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6810,11 +7778,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6857,11 +7833,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6904,11 +7888,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6951,11 +7943,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6998,11 +7998,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7045,11 +8053,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7092,11 +8108,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7139,11 +8163,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7186,11 +8218,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7233,11 +8273,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7280,11 +8328,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7327,11 +8383,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7374,11 +8438,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7421,11 +8493,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7468,11 +8548,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7515,11 +8603,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7562,11 +8658,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7609,11 +8713,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7656,11 +8768,14 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -7671,6 +8786,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7713,11 +8831,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -7728,6 +8849,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7770,11 +8894,14 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -7785,6 +8912,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7827,11 +8957,19 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7874,11 +9012,14 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -7889,6 +9030,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7931,11 +9075,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -7946,6 +9093,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7988,11 +9138,14 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8003,6 +9156,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8045,11 +9201,19 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8092,11 +9256,14 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -8107,6 +9274,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8149,11 +9319,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8164,6 +9337,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8206,11 +9382,14 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8221,6 +9400,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8263,11 +9445,19 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8310,11 +9500,14 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -8325,6 +9518,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8367,11 +9563,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8382,6 +9581,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8424,11 +9626,14 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8439,6 +9644,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8481,11 +9689,19 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8528,11 +9744,14 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -8543,6 +9762,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8585,11 +9807,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8600,6 +9825,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8642,11 +9870,14 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8657,6 +9888,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8699,11 +9933,19 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8746,11 +9988,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   HP Absorb: 100%   |   TP Cost: 9 (+1/Lv) -&gt; 18</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -8761,6 +10006,9 @@
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8803,16 +10051,23 @@
 TP Absorb: 100% | TP Cost: 6 (+1/Lv) -&gt; 15 | Speed: 1.75x | Chant: 1.25x -&gt; 1.07x</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8855,16 +10110,23 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 27 -&gt; 31 -&gt; 35 -&gt; 39 -&gt; 43   |   Speed: 1.5x</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8907,11 +10169,14 @@
 TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50   |   Speed: 1.5x</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
           <t>Pwr, Accuracy</t>
@@ -8922,6 +10187,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8964,11 +10232,19 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18   |   Speed: 0.8x -&gt; 0.92x   |   Chant: 1.25x</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9011,11 +10287,19 @@
 TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   Speed: 2.15x   |   Chant: 1.2x -&gt; 1.4x</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9058,11 +10342,19 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9105,11 +10397,19 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1x -&gt; 1.2x</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9152,11 +10452,19 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9199,11 +10507,19 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9246,11 +10562,19 @@
 TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9293,11 +10617,19 @@
 TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9340,11 +10672,19 @@
 TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23   |   Chant: 1x -&gt; 1.12x</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9387,11 +10727,19 @@
 TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30   |   Speed: 0.4x -&gt; 0.5x   |   Chant: 1.25x</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9434,11 +10782,19 @@
 TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 18 -&gt; 22   |   Speed: 1.25x   |   Chant: 1.25x -&gt; 1.45x</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9481,11 +10837,14 @@
 TP Cost: 45 -&gt; 52 -&gt; 59 -&gt; 66 -&gt; 74 -&gt; 80 -&gt; 86 -&gt; 90 -&gt; 95 -&gt; 100   |   Speed: 1.75x</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
           <t>Pwr, Accuracy</t>
@@ -9496,6 +10855,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9538,11 +10900,19 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9585,11 +10955,19 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9632,11 +11010,19 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9679,11 +11065,19 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9726,11 +11120,19 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9773,16 +11175,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9825,16 +11234,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9877,16 +11293,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9929,11 +11352,14 @@
 TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26   |   Speed: 1.75x</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
           <t>Heal Cap</t>
@@ -9944,6 +11370,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9986,11 +11415,14 @@
 TP Cost: 15 -&gt; 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 46 -&gt; 52 -&gt; 58 -&gt; 64   |   Speed: 1.35x</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr">
         <is>
           <t>Heal Cap</t>
@@ -10001,6 +11433,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10041,11 +11476,19 @@
           <t>TP Cost: 48 -&gt; 45 -&gt; 42 -&gt; 39 -&gt; 36 (L1-5 Max)   |   Speed: 1.15x   |   Chant: 1.5x -&gt; 1.75x</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10088,11 +11531,19 @@
 TP Cost: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   Speed: 2.25x   |   Chant: 2.75x</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10135,11 +11586,19 @@
 TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25 -&gt; 30 -&gt; 36   |   Speed: 1.5x   |   Chant: 2x</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10182,11 +11641,19 @@
 TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42   |   Speed: 1.25x   |   Chant: 1.3x -&gt; 1.5x</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10229,16 +11696,23 @@
 Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17   |   Chant: 1.25x</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10281,16 +11755,23 @@
 Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17   |   Chant: 1.25x</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10333,16 +11814,23 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32   |   Chant: 1.25x</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10385,16 +11873,23 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32   |   Chant: 1.25x</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10437,16 +11932,23 @@
 Turns: 3   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Speed: 1.25x -&gt; 1.41x</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10489,16 +11991,23 @@
 Turns: 5 -&gt; 5 -&gt; 6 -&gt; 6 -&gt; 7 -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 18 (+3/Lv) -&gt; 45</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10541,11 +12050,19 @@
 TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 21 -&gt; 24 -&gt; 28   |   Speed: 1.75x   |   Chant: 2.25x</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10588,11 +12105,19 @@
 Chant: 0.75x -&gt; 0.65x</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10635,11 +12160,19 @@
 Turns: 4   |   TP Cost: 24 -&gt; 28 -&gt; 33 -&gt; 37 -&gt; 42   |   Speed: 1.5x   |   Chant: 0.75x</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10682,16 +12215,23 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 45   |   Speed: 1.5x</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10732,11 +12272,19 @@
           <t>Turns: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10777,11 +12325,19 @@
           <t>TP Cost: 28 -&gt; 21 -&gt; 14 -&gt; 7 -&gt; 1 (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10823,11 +12379,19 @@
 Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10853,6 +12417,7 @@
           <t>Raise the party's chance of doing multiple strikes while song lasts.</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
           <t>Raise the party's chance of doing multiple strikes while song lasts.</t>
@@ -10863,11 +12428,19 @@
           <t>Speed: 1.35x   |   Chant: 1.4x</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10909,11 +12482,19 @@
 Speed: 1.35x   |   Chant: 1.4x -&gt; 2x</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10955,11 +12536,19 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11001,11 +12590,19 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11047,11 +12644,19 @@
 Speed: 1.35x   |   Chant: 1.4x -&gt; 2x</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11093,11 +12698,19 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11139,11 +12752,19 @@
 Speed: 1.35x   |   Chant: 1.1x -&gt; 1.5x</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11185,11 +12806,19 @@
 Speed: 1.35x   |   Chant: 1.1x -&gt; 1.5x</t>
         </is>
       </c>
+      <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11231,11 +12860,19 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11277,11 +12914,19 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
+      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11324,16 +12969,23 @@
 Turns: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5   |   TP Cost: 23 -&gt; 27 -&gt; 32 -&gt; 38 -&gt; 45   |   Speed: 0.85x</t>
         </is>
       </c>
+      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11376,11 +13028,19 @@
 Turns: 3 | TP Cost: 36 -&gt; 39 -&gt; 43 -&gt; 47 -&gt; 52 | Speed: 0.8x | Chant: 0.8x -&gt; 0.88x</t>
         </is>
       </c>
+      <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11423,11 +13083,19 @@
 Turns: 3   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Chant: 1.15x -&gt; 1.3x</t>
         </is>
       </c>
+      <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11467,7 +13135,7 @@
       <c r="H221" t="inlineStr">
         <is>
           <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
-ATK: -4% (-1%/Lv) (3 Turns) | Damage cap: 250 -&gt; 500 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
+ATK: -4% (-1%/Lv) (3 Turns)   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -11477,9 +13145,11 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -11490,6 +13160,9 @@
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11532,11 +13205,14 @@
 Magic defense: -7% -&gt; -18%   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
+      <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
           <t>Magic defense, Damage cap</t>
@@ -11547,6 +13223,9 @@
           <t>Turns, Speed, Chant</t>
         </is>
       </c>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11589,11 +13268,14 @@
 Speed decrease: 4% (+1%/Lv)   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -11604,6 +13286,9 @@
           <t>Turns, Speed, Chant</t>
         </is>
       </c>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11643,7 +13328,7 @@
       <c r="H224" t="inlineStr">
         <is>
           <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
-Evasion: -7% (-2%/Lv) (3 Turns) | Damage cap: 250 -&gt; 500 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
+Evasion: -7% (-2%/Lv) (3 Turns)   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -11653,9 +13338,11 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -11666,6 +13353,9 @@
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11705,7 +13395,7 @@
       <c r="H225" t="inlineStr">
         <is>
           <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
-DEF: -4% (-1%/Lv) (3 Turns) | Damage cap: 250 -&gt; 500 | TP Cost: 20 (+5/Lv) -&gt; 40</t>
+DEF: -4% (-1%/Lv) (3 Turns)   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -11715,9 +13405,11 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -11728,6 +13420,9 @@
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11770,11 +13465,14 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 22 (+4-6/Lv) -&gt; 66   |   Speed: 1.3x</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -11785,6 +13483,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11827,16 +13528,23 @@
 TP Cost: 36 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 80 -&gt; 88 -&gt; 96   |   Speed: 1.5x</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11879,16 +13587,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22   |   Chant: 1.15x</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11931,16 +13646,23 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22   |   Chant: 1.15x</t>
         </is>
       </c>
+      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11983,11 +13705,19 @@
 Turns: 3   |   TP Cost: 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40   |   Speed: 0.75x   |   Chant: 1.75x</t>
         </is>
       </c>
+      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12030,11 +13760,19 @@
 TP Cost: 12 -&gt; 11 -&gt; 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3</t>
         </is>
       </c>
+      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -12077,11 +13815,14 @@
 Recoverable status ailments: 1 (+1/Lv)   |   HP on revival: 10% (+5-10%/Lv) -&gt; 50%</t>
         </is>
       </c>
+      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
           <t>HP on revival</t>
@@ -12092,6 +13833,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12131,7 +13875,7 @@
       <c r="H233" t="inlineStr">
         <is>
           <t>DEF: -5% -&gt; -6% -&gt; -7% -&gt; -8% -&gt; -10% (L1-5 Max)   |   Magic defense: -10% -&gt; -15%
-Accuracy: 80% -&gt; 90% | HP recovery: 35 -&gt; 25 | Turns: 3 | TP: 18 (+2-4/Lv) -&gt; 32</t>
+Accuracy: 80% -&gt; 90%   |   HP recovery: 35 -&gt; 25   |   Turns: 3   |   TP: 18 (+2-4/Lv) -&gt; 32</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -12141,9 +13885,11 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Full</t>
-        </is>
-      </c>
+          <t>Edited by hand</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
         <is>
           <t>Magic defense, Accuracy, HP recovery, TP Cost</t>
@@ -12154,6 +13900,9 @@
           <t>Speed, Chant</t>
         </is>
       </c>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -12196,11 +13945,14 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 30 (+4/Lv) -&gt; 66   |   Speed: 0.85x</t>
         </is>
       </c>
+      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -12211,6 +13963,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -12253,11 +14008,14 @@
 TP Cost: 32 -&gt; 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 52 -&gt; 54 -&gt; 56   |   Speed: 1.2x</t>
         </is>
       </c>
+      <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
           <t>Pwr</t>
@@ -12268,6 +14026,9 @@
           <t>Chant</t>
         </is>
       </c>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12310,6 +14071,7 @@
 TP Cost: 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 (L1-5 Max)   |   Speed: 1.5x   |   Chant: 0.84x -&gt; 0.8x</t>
         </is>
       </c>
+      <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -12325,6 +14087,11 @@
           <t>effect_1</t>
         </is>
       </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12367,11 +14134,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12414,11 +14189,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12461,11 +14244,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12508,11 +14299,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -12555,11 +14354,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -12602,11 +14409,19 @@
 dummy</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -12647,11 +14462,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -12692,11 +14515,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -12737,11 +14568,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17% (L10)</t>
         </is>
       </c>
+      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12782,11 +14621,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12827,11 +14674,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -12872,11 +14727,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr"/>
+      <c r="Q248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -12917,11 +14780,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -12962,11 +14833,19 @@
           <t>ATK bonus: 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% (L10)</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr"/>
+      <c r="Q250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13007,11 +14886,19 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17% (L10)</t>
         </is>
       </c>
+      <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13052,11 +14939,19 @@
           <t>ATK bonus: 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% (L10)</t>
         </is>
       </c>
+      <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13097,11 +14992,19 @@
           <t>ATK bonus: 2% -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 12% (L10)</t>
         </is>
       </c>
+      <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13142,11 +15045,19 @@
           <t>Magic attack bonus: 6% -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
+      <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13188,11 +15099,19 @@
 Heal Cap: +10% -&gt; +20 -&gt; +30 -&gt; +40 -&gt; +50 -&gt; +60 -&gt; +70 -&gt; +80 -&gt; +90 -&gt; +100%</t>
         </is>
       </c>
+      <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -13233,11 +15152,19 @@
           <t>HP recovery: 2% -&gt; 4% -&gt; 6% -&gt; 8% -&gt; 10% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -13278,11 +15205,19 @@
           <t>HP recovery: 1% -&gt; 2% -&gt; 3% -&gt; 4% -&gt; 5% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13323,11 +15258,19 @@
           <t>TP recovery: 3 -&gt; 6 -&gt; 9 -&gt; 12 -&gt; 16 (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr"/>
+      <c r="P258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -13368,11 +15311,19 @@
           <t>TP recovery: 1 -&gt; 3 -&gt; 5 -&gt; 7 -&gt; 9 (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -13413,11 +15364,19 @@
           <t>Elemental resistance: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 (L10)</t>
         </is>
       </c>
+      <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
+      <c r="P260" t="inlineStr"/>
+      <c r="Q260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -13458,11 +15417,19 @@
           <t>Counterattack rate: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -13503,11 +15470,19 @@
           <t>Activation rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -13548,11 +15523,19 @@
           <t>Double attack rate: 9% -&gt; 12% -&gt; 15% -&gt; 18% -&gt; 21% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr"/>
+      <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -13593,11 +15576,19 @@
           <t>Triple attack rate: 5% -&gt; 8% -&gt; 11% -&gt; 14% -&gt; 17% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -13638,11 +15629,19 @@
           <t>Evasion rate: 20% -&gt; 24% -&gt; 28% -&gt; 32% -&gt; 36% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr"/>
+      <c r="P265" t="inlineStr"/>
+      <c r="Q265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -13683,11 +15682,19 @@
           <t>Activation rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr"/>
+      <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -13728,11 +15735,19 @@
           <t>Survival rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr"/>
+      <c r="P267" t="inlineStr"/>
+      <c r="Q267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -13773,11 +15788,19 @@
           <t>Auto-guard rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -13818,11 +15841,19 @@
           <t>Sub-weapon ATK: 30% -&gt; 35 -&gt; 40 -&gt; 45 -&gt; 50 -&gt; 54 -&gt; 58 -&gt; 62 -&gt; 68 -&gt; 72% (L10)</t>
         </is>
       </c>
+      <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr"/>
+      <c r="P269" t="inlineStr"/>
+      <c r="Q269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -13863,11 +15894,19 @@
           <t>TP conversion: 4% -&gt; 8% -&gt; 12% -&gt; 16% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr"/>
+      <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -13908,11 +15947,19 @@
           <t>Activation rate: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr"/>
+      <c r="P271" t="inlineStr"/>
+      <c r="Q271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -13953,11 +16000,19 @@
           <t>Activation rate: 2% -&gt; 3% -&gt; 4% -&gt; 5% -&gt; 6% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr"/>
+      <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -13998,11 +16053,19 @@
           <t>Activation rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr"/>
+      <c r="P273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14043,11 +16106,19 @@
           <t>Speed increase: 15% -&gt; 16% -&gt; 17% -&gt; 18% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr"/>
+      <c r="P274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14088,11 +16159,19 @@
           <t>Number of possible debuffs: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 (L6)</t>
         </is>
       </c>
+      <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr"/>
+      <c r="P275" t="inlineStr"/>
+      <c r="Q275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -14133,11 +16212,19 @@
           <t>ATK: +15% -&gt; +18% -&gt; +21% -&gt; +24% -&gt; +27% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr"/>
+      <c r="P276" t="inlineStr"/>
+      <c r="Q276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14163,16 +16250,26 @@
           <t>Nullify the effects of enemy Dark Auras.</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
           <t>Nullify the effects of enemy Dark Auras.</t>
         </is>
       </c>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr"/>
+      <c r="P277" t="inlineStr"/>
+      <c r="Q277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14198,16 +16295,26 @@
           <t>No longer suffer counterattacks from enemies.</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
           <t>No longer suffer counterattacks from enemies.</t>
         </is>
       </c>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr"/>
+      <c r="P278" t="inlineStr"/>
+      <c r="Q278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14248,11 +16355,19 @@
           <t>Physical damage: -6% -&gt; -7% -&gt; -8% -&gt; -9% -&gt; -10% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
+      <c r="P279" t="inlineStr"/>
+      <c r="Q279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14293,11 +16408,19 @@
           <t>Activation rate: 8% -&gt; 9% -&gt; 10% -&gt; 11% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr"/>
+      <c r="P280" t="inlineStr"/>
+      <c r="Q280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -14338,11 +16461,19 @@
           <t>LvUp: Can cure poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; slow</t>
         </is>
       </c>
+      <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr"/>
+      <c r="P281" t="inlineStr"/>
+      <c r="Q281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -14383,11 +16514,19 @@
           <t>ATK/DEX: +10% -&gt; +11% -&gt; +12% -&gt; +13% -&gt; +15% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr"/>
+      <c r="P282" t="inlineStr"/>
+      <c r="Q282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -14428,11 +16567,19 @@
           <t>Interruption rate: -10% -&gt; -20% -&gt; -30% -&gt; -40% -&gt; -50% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="inlineStr"/>
+      <c r="Q283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -14473,11 +16620,19 @@
           <t>Chant time: -8% -&gt; -11% -&gt; -14% -&gt; -17% -&gt; -20% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14518,11 +16673,19 @@
           <t>TP Cost reduction: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="inlineStr"/>
+      <c r="Q285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14563,11 +16726,19 @@
           <t>Accuracy: 3% -&gt; 5% -&gt; 7% -&gt; 9% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="inlineStr"/>
+      <c r="Q286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -14608,11 +16779,19 @@
           <t>Enemy preemptive attack rate: -20% -&gt; -28% -&gt; -36% -&gt; -44% -&gt; -50% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr"/>
+      <c r="P287" t="inlineStr"/>
+      <c r="Q287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -14653,11 +16832,19 @@
           <t>Preemptive attack rate: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="inlineStr"/>
+      <c r="Q288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -14698,11 +16885,19 @@
           <t>Battle escape rate: 20% -&gt; 25% -&gt; 30% -&gt; 35% -&gt; 40% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
+      <c r="Q289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -14743,11 +16938,19 @@
           <t>Item drop rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr"/>
+      <c r="P290" t="inlineStr"/>
+      <c r="Q290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -14788,11 +16991,19 @@
           <t>Gold drop rate: 25% -&gt; 50% -&gt; 75% -&gt; 100% -&gt; 125% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr"/>
+      <c r="P291" t="inlineStr"/>
+      <c r="Q291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -14833,11 +17044,19 @@
           <t>Found item quality: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr"/>
+      <c r="P292" t="inlineStr"/>
+      <c r="Q292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -14879,11 +17098,19 @@
 Post-battle TP: 3% -&gt; 4% -&gt; 5% -&gt; 7% -&gt; 9%</t>
         </is>
       </c>
+      <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -14924,11 +17151,19 @@
           <t>Item keep rate: 25% -&gt; 27% -&gt; 29% -&gt; 32% -&gt; 35% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="inlineStr"/>
+      <c r="Q294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -14969,11 +17204,19 @@
           <t>Item effects: 10% -&gt; 20 -&gt; 30 -&gt; 40 -&gt; 50 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 90 -&gt; 100% (L10)</t>
         </is>
       </c>
+      <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr"/>
+      <c r="P295" t="inlineStr"/>
+      <c r="Q295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15014,11 +17257,19 @@
           <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
+      <c r="Q296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -15059,11 +17310,19 @@
           <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="inlineStr"/>
+      <c r="Q297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15104,11 +17363,19 @@
           <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="inlineStr"/>
+      <c r="Q298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -15149,11 +17416,19 @@
           <t>Sealbook ability: +15% -&gt; +18% -&gt; +21% -&gt; +24% -&gt; +27% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr"/>
+      <c r="P299" t="inlineStr"/>
+      <c r="Q299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -15194,11 +17469,19 @@
           <t>Maid skill bonus: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10% (L10)</t>
         </is>
       </c>
+      <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr"/>
+      <c r="P300" t="inlineStr"/>
+      <c r="Q300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -15239,11 +17522,19 @@
           <t>Singing skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
+      <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
+      <c r="O301" t="inlineStr"/>
+      <c r="P301" t="inlineStr"/>
+      <c r="Q301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -15284,11 +17575,19 @@
           <t>Dancing skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
+      <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr"/>
+      <c r="P302" t="inlineStr"/>
+      <c r="Q302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -15329,11 +17628,19 @@
           <t>Doll skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
+      <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr"/>
+      <c r="P303" t="inlineStr"/>
+      <c r="Q303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -15374,11 +17681,19 @@
           <t>Double attack rate: 20% -&gt; 21 -&gt; 22 -&gt; 23 -&gt; 24 -&gt; 25 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32% (L10)</t>
         </is>
       </c>
+      <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr"/>
+      <c r="P304" t="inlineStr"/>
+      <c r="Q304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -15419,11 +17734,19 @@
           <t>Song chant time: -10% -&gt; -11 -&gt; -12 -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -20%</t>
         </is>
       </c>
+      <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr"/>
+      <c r="P305" t="inlineStr"/>
+      <c r="Q305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -15464,11 +17787,19 @@
           <t>Negotiation rate: 10% -&gt; 14% -&gt; 18% -&gt; 22% -&gt; 25% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr"/>
+      <c r="P306" t="inlineStr"/>
+      <c r="Q306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -15509,11 +17840,19 @@
           <t>Occurrence rate: 3% -&gt; 4% -&gt; 5% -&gt; 6% -&gt; 7% (L1-5 Max)</t>
         </is>
       </c>
+      <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr"/>
+      <c r="P307" t="inlineStr"/>
+      <c r="Q307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -15539,16 +17878,26 @@
           <t>Nullify first hit of battle against user (does not work for status ailments).</t>
         </is>
       </c>
+      <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
           <t>Nullify first hit of battle against user (does not work for status ailments).</t>
         </is>
       </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="inlineStr"/>
+      <c r="Q308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -15574,16 +17923,26 @@
           <t>Heighten the probability of beneficial results for random effect skills.</t>
         </is>
       </c>
+      <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr">
         <is>
           <t>Heighten the probability of beneficial results for random effect skills.</t>
         </is>
       </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr"/>
+      <c r="P309" t="inlineStr"/>
+      <c r="Q309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -15609,16 +17968,26 @@
           <t>Whip skill. Strike back with a normal attack before a targeted attack hits you.</t>
         </is>
       </c>
+      <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr">
         <is>
           <t>Whip skill. Strike back with a normal attack before a targeted attack hits you.</t>
         </is>
       </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr"/>
+      <c r="Q310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -15644,16 +18013,26 @@
           <t>Occasionally get the first action regardless of speed.</t>
         </is>
       </c>
+      <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr">
         <is>
           <t>Occasionally get the first action regardless of speed.</t>
         </is>
       </c>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr"/>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="inlineStr"/>
+      <c r="Q311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -15679,16 +18058,26 @@
           <t>Occasionally land critical hits with offensive spells.</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
           <t>Occasionally land critical hits with offensive spells.</t>
         </is>
       </c>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr"/>
+      <c r="O312" t="inlineStr"/>
+      <c r="P312" t="inlineStr"/>
+      <c r="Q312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -15714,16 +18103,26 @@
           <t>Increase doll summon duration by 1 turn.</t>
         </is>
       </c>
+      <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr">
         <is>
           <t>Increase doll summon duration by 1 turn.</t>
         </is>
       </c>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr"/>
+      <c r="O313" t="inlineStr"/>
+      <c r="P313" t="inlineStr"/>
+      <c r="Q313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -15749,17 +18148,27 @@
           <t>Significantly increase damage according to Pep.</t>
         </is>
       </c>
+      <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr">
         <is>
           <t>Significantly increase damage according to Pep.
 Pep over 100 per +1% damage: 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3 -&gt; 2   |   Crown EX: 1</t>
         </is>
       </c>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr"/>
+      <c r="O314" t="inlineStr"/>
+      <c r="P314" t="inlineStr"/>
+      <c r="Q314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -15785,17 +18194,27 @@
           <t>Occasionally inflict enemies with status ailments or Dispel at random.</t>
         </is>
       </c>
+      <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr">
         <is>
           <t>Occasionally inflict enemies with status ailments or Dispel at random.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 25%</t>
         </is>
       </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr"/>
+      <c r="O315" t="inlineStr"/>
+      <c r="P315" t="inlineStr"/>
+      <c r="Q315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -15821,17 +18240,27 @@
           <t>May counter short-range attacks with Slow and a Speed decrease.</t>
         </is>
       </c>
+      <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr">
         <is>
           <t>May counter short-range attacks with Slow and a Speed decrease.
 Activation rate: 16% -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38%   |   Crown EX: 50%</t>
         </is>
       </c>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr"/>
+      <c r="P316" t="inlineStr"/>
+      <c r="Q316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -15857,17 +18286,27 @@
           <t>Increase weapon modifier when attacking with weapon-based skills.</t>
         </is>
       </c>
+      <c r="F317" t="inlineStr"/>
       <c r="G317" t="inlineStr">
         <is>
           <t>Increase weapon modifier when attacking with weapon-based skills.
 Weapon modifier: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18%   |   Crown EX: 25%</t>
         </is>
       </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
+      <c r="O317" t="inlineStr"/>
+      <c r="P317" t="inlineStr"/>
+      <c r="Q317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -15893,17 +18332,27 @@
           <t>May guarantee a hit and bypass DEF with physical attacks or skills.</t>
         </is>
       </c>
+      <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr">
         <is>
           <t>May guarantee a hit and bypass DEF with physical attacks or skills.
 Activation rate: 12% -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20%   |   Crown EX: 30%</t>
         </is>
       </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
       <c r="J318" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr"/>
+      <c r="P318" t="inlineStr"/>
+      <c r="Q318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -15929,17 +18378,27 @@
           <t>Occasionally nullify all damage received from enemies.</t>
         </is>
       </c>
+      <c r="F319" t="inlineStr"/>
       <c r="G319" t="inlineStr">
         <is>
           <t>Occasionally nullify all damage received from enemies.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr"/>
+      <c r="P319" t="inlineStr"/>
+      <c r="Q319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -15965,17 +18424,27 @@
           <t>Before acting, may erase enemy puppets, familiars, shikigami, or slaves.</t>
         </is>
       </c>
+      <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr">
         <is>
           <t>Before acting, may erase enemy puppets, familiars, shikigami, or slaves.
 Activation rate: 25% -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 49 -&gt; 53 -&gt; 57%   |   Crown EX: 75%</t>
         </is>
       </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="inlineStr"/>
+      <c r="Q320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -16001,17 +18470,27 @@
           <t>Before acting, may use an item from her own personal stock.</t>
         </is>
       </c>
+      <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr">
         <is>
           <t>Before acting, may use an item from her own personal stock.
 Activation rate: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18%   |   Crown EX: 25%</t>
         </is>
       </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr"/>
+      <c r="P321" t="inlineStr"/>
+      <c r="Q321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -16037,17 +18516,27 @@
           <t>Decrease turn delay after using skills or magic.</t>
         </is>
       </c>
+      <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr">
         <is>
           <t>Decrease turn delay after using skills or magic.
-Turn delay: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
-        </is>
-      </c>
+Speed added: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr"/>
+      <c r="P322" t="inlineStr"/>
+      <c r="Q322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -16073,17 +18562,27 @@
           <t>Increased effects for all maid skills.</t>
         </is>
       </c>
+      <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr">
         <is>
           <t>Increased effects for all maid skills.
 Maid skill effects: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 10%   |   Crown EX: 13%</t>
         </is>
       </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr"/>
+      <c r="P323" t="inlineStr"/>
+      <c r="Q323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -16109,17 +18608,27 @@
           <t>May occasionally act twice in one turn.</t>
         </is>
       </c>
+      <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr">
         <is>
           <t>May occasionally act twice in one turn.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr"/>
+      <c r="P324" t="inlineStr"/>
+      <c r="Q324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -16145,17 +18654,27 @@
           <t>If killed, revive after a certain number of turns.</t>
         </is>
       </c>
+      <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr">
         <is>
           <t>If killed, revive after a certain number of turns.
 Activation rate: 8% -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24%   |   Crown EX: 30%</t>
         </is>
       </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr"/>
+      <c r="P325" t="inlineStr"/>
+      <c r="Q325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -16181,17 +18700,27 @@
           <t>Whole row takes less damage from Demons, Undead, and Apparitions.</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr">
         <is>
           <t>Whole row takes less damage from Demons, Undead, and Apparitions.
 Taken: -12% -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -19 -&gt; -20%   |   Crown EX: -25%</t>
         </is>
       </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr"/>
+      <c r="P326" t="inlineStr"/>
+      <c r="Q326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -16217,17 +18746,28 @@
           <t>May lower all enemies' ATK and INT with heart-penetrating vocals.</t>
         </is>
       </c>
+      <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr">
         <is>
           <t>May lower all enemies' ATK and INT with heart-penetrating vocals.
-Activation rate: 7% -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13%   |   Crown EX: 20%</t>
-        </is>
-      </c>
+Activation rate: 7% -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13%   |   Crown EX: 20%
+Enemy ATK and INT: -10% for 4 turns</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr"/>
+      <c r="P327" t="inlineStr"/>
+      <c r="Q327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -16253,17 +18793,27 @@
           <t>Magic will occasionally activate immediately without the need to chant.</t>
         </is>
       </c>
+      <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr">
         <is>
           <t>Magic will occasionally activate immediately without the need to chant.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
       <c r="J328" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
+      <c r="O328" t="inlineStr"/>
+      <c r="P328" t="inlineStr"/>
+      <c r="Q328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -16289,6 +18839,7 @@
           <t>Occasionally reflects a percentage of damage taken as fixed damage.</t>
         </is>
       </c>
+      <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr">
         <is>
           <t>Occasionally reflects a percentage of damage taken as fixed damage.
@@ -16296,11 +18847,20 @@
 Activation rate: 15%</t>
         </is>
       </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr"/>
+      <c r="P329" t="inlineStr"/>
+      <c r="Q329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -16326,17 +18886,27 @@
           <t>Summons another self from the shadows to attack.</t>
         </is>
       </c>
+      <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr">
         <is>
           <t>Summons another self from the shadows to attack.
 Activation rate: 4% -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12%   |   Crown EX: 20%</t>
         </is>
       </c>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
+      <c r="O330" t="inlineStr"/>
+      <c r="P330" t="inlineStr"/>
+      <c r="Q330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -16362,17 +18932,27 @@
           <t>Increased effects for all class modifiers.</t>
         </is>
       </c>
+      <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr">
         <is>
           <t>Increased effects for all class modifiers.
 Class modifiers (%): 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Crown EX: 15</t>
         </is>
       </c>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr"/>
+      <c r="P331" t="inlineStr"/>
+      <c r="Q331" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16385,7 +18965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16431,58 +19011,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Edited by hand</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>261</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Skipped (internal)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -16491,28 +19071,50 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unchanged</t>
+          <t>Skipped (internal)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
         <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>13</v>
       </c>
     </row>

--- a/mod_project/data_tables/qol_skill_text.xlsx
+++ b/mod_project/data_tables/qol_skill_text.xlsx
@@ -580,19 +580,11 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5   |   Speed: 1.5x -&gt; 2x</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -635,19 +627,11 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | Speed: 1.25x -&gt; 1.77x</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -690,23 +674,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -749,23 +726,16 @@
 Accuracy: +20% (+2%/Lv)   |   TP Cost: 5 (+2-3/Lv) -&gt; 28   |   Speed: 0.8x -&gt; 0.9x</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -808,23 +778,16 @@
 Buff cancel rate: 68% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 5 (+1-2/Lv) -&gt; 18   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Buff cancel rate, TP Cost</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -867,14 +830,11 @@
 DEF: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%   |   Turns: 4 -&gt; 8   |   TP Cost: 8 (+2/Lv) -&gt; 16</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -885,9 +845,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -930,14 +887,11 @@
 ATK: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%   |   Turns: 4 -&gt; 8   |   TP Cost: 8 (+2/Lv) -&gt; 16</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -948,9 +902,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -993,14 +944,11 @@
 Stun: 30% -&gt; 32% -&gt; 34% -&gt; 36% -&gt; 38%   |   TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -1011,9 +959,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1056,14 +1001,11 @@
 Accuracy: +5% (+2-3%/Lv) -&gt; +28%   |   Paralysis: 20% -&gt; 50%   |   TP Cost: 6 (+2/Lv) -&gt; 24</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Accuracy, Paralysis</t>
@@ -1074,9 +1016,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1119,23 +1058,16 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1178,14 +1110,11 @@
 Instakill: 10% (+1-2%/Lv) -&gt; 20%   |   Power decrease: 10%   |   TP Cost: 38 (+4/Lv) -&gt; 74</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Instakill</t>
@@ -1196,9 +1125,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1241,19 +1167,11 @@
 Enemy DEF: -16% (-1%/Lv)   |   Turns: 4   |   TP Cost: 14 (+2/Lv) -&gt; 32   |   Speed: 0.8x</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1296,23 +1214,16 @@
 TP Cost: 22 -&gt; 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1355,23 +1266,16 @@
 Critical rate: 10%   |   TP Cost: 36 (+2-3/Lv) -&gt; 61   |   Speed: 0.7x -&gt; 0.8x</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1414,23 +1318,16 @@
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>HP Absorb</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1473,23 +1370,16 @@
 TP Absorb: 10% (+1-2%/Lv) -&gt; 20%   |   TP Cost: 6 (+2/Lv) -&gt; 24   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>TP Absorb</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1532,14 +1422,11 @@
 Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   Accuracy: +14%   |   TP Cost: 9 (+3/Lv) -&gt; 36</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Freeze</t>
@@ -1550,9 +1437,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1595,14 +1479,11 @@
 TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 37 -&gt; 42</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>ATK, Petrify</t>
@@ -1613,9 +1494,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1668,8 +1546,6 @@
           <t>Edited by hand</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -1680,9 +1556,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1725,23 +1598,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 10 -&gt; 14 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1784,23 +1650,16 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1843,14 +1702,11 @@
 Accuracy: +6% -&gt; +20%   |   Damage vs. unholy: +65%   |   TP Cost: 12 (+3/Lv) -&gt; 39</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -1861,9 +1717,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1906,23 +1759,16 @@
 Turns: 5   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1965,23 +1811,16 @@
 Turns: 5   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2024,23 +1863,16 @@
 Paralysis: 20% (+2-3%/Lv) -&gt; 40%   |   TP Cost: 26 (+4-5/Lv) -&gt; 64   |   Speed: 0.8x</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Paralysis, TP Cost</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2083,14 +1915,11 @@
 Silence: 20% (+3-4%/Lv) -&gt; 50%   |   Accuracy: +15%   |   TP Cost: 7 (+3/Lv) -&gt; 34</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Silence</t>
@@ -2101,9 +1930,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2146,23 +1972,16 @@
 Heavy Lance bonus: +20%   |   TP Cost: 36 (+3-6/Lv) -&gt; 71   |   Speed: 0.7x -&gt; 0.8x</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2205,23 +2024,16 @@
 Accuracy: +5% (+1-2%/Lv) -&gt; +15%   |   TP Cost: 32 (+3/Lv) -&gt; 59   |   Speed: 0.8x</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2264,19 +2076,11 @@
 Turns: 2   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Speed: 0.84x -&gt; 0.9x</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2318,19 +2122,11 @@
 Speed: 1x -&gt; 1.5x</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2372,19 +2168,11 @@
 Speed: 0.6x -&gt; 0.8x</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2427,19 +2215,11 @@
 TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 -&gt; 28 -&gt; 30   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2482,19 +2262,11 @@
 TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 35 -&gt; 38   |   Speed: 0.85x</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2537,23 +2309,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2596,19 +2361,11 @@
 TP Cost: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2651,14 +2408,11 @@
 Turns: 5 -&gt; 9   |   TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -2669,9 +2423,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2724,13 +2475,6 @@
           <t>Edited by hand</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2773,23 +2517,16 @@
 Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>Physical evasion, Magic evasion</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2832,23 +2569,16 @@
 Sleep: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>Sleep</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2891,23 +2621,16 @@
 Silence: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>Silence</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2950,23 +2673,16 @@
 Stun: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>Stun</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3019,17 +2735,11 @@
           <t>Edited by hand</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>ATK, Power decrease, TP Cost</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3072,19 +2782,11 @@
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16   |   Speed: 1x -&gt; 1.12x</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3127,19 +2829,11 @@
 TP Cost: 42 -&gt; 50 -&gt; 57 -&gt; 63 -&gt; 68   |   Speed: 0.4x</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3182,23 +2876,16 @@
 Poison: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>Poison</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3241,23 +2928,16 @@
 Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 8 (+2/Lv) -&gt; 26</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>Freeze</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3300,23 +2980,16 @@
 Paralysis: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 8 (+2/Lv) -&gt; 26</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>Paralysis</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3359,23 +3032,16 @@
 Slow: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 9 (+2/Lv) -&gt; 27   |   Speed: 0.95x</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>Slow</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3418,19 +3084,11 @@
 TP Cost: 20 -&gt; 23 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48   |   Speed: 0.65x</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3493,11 +3151,6 @@
           <t>effect_2</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3540,23 +3193,16 @@
 Critical rate: 5% (+1-3%/Lv) -&gt; 25%   |   TP Cost: 24 (+3-4/Lv) -&gt; 55   |   Speed: 0.7x</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>Critical rate, TP Cost</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3599,14 +3245,11 @@
 Turns: 4   |   TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>ATK, Speed decrease chance</t>
@@ -3617,9 +3260,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3662,14 +3302,11 @@
 Stun: 10% -&gt; 20%   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>Stun</t>
@@ -3680,9 +3317,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3724,19 +3358,11 @@
 TP Cost: 10 -&gt; 8 -&gt; 6 -&gt; 4 -&gt; 2</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3779,23 +3405,16 @@
 Magic accuracy: -2% (-2%/Lv)   |   Turns: 6   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 32</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3838,14 +3457,11 @@
 Accuracy: +10% (+2-4%/Lv) -&gt; +30%   |   ATK: 82%   |   TP Cost: 28 (+4/Lv) -&gt; 64</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -3856,9 +3472,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3901,23 +3514,16 @@
 Turns: 4   |   TP Cost: 25 -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 48 -&gt; 51 -&gt; 54 -&gt; 57</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3960,23 +3566,16 @@
 TP Cost: 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 57 -&gt; 62 -&gt; 67 -&gt; 73 -&gt; 79</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4019,14 +3618,11 @@
 Turns: 4 -&gt; 7   |   TP Cost: 22 -&gt; 25 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 56</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>Turns</t>
@@ -4037,9 +3633,6 @@
           <t>Speed</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4082,19 +3675,11 @@
 Turns: 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 6   |   TP Cost: 52 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 92   |   Speed: 1.25x</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4137,23 +3722,16 @@
 Accuracy: +10% (+1-2%/Lv) -&gt; +20%   |   TP Cost: 13 (+3-4/Lv) -&gt; 45   |   Speed: 0.9x -&gt; 1x</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4196,23 +3774,16 @@
 Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   Silence: 20% -&gt; 50%   |   TP Cost: 9 (+3/Lv) -&gt; 36</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>Freeze, Silence</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4255,19 +3826,11 @@
 TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 36 -&gt; 40 -&gt; 43 -&gt; 46 -&gt; 49 -&gt; 52 -&gt; 55</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4293,26 +3856,16 @@
           <t>Detect how many unopened treasure chests are left on the current floor.</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>Detect how many unopened treasure chests are left on this floor.</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4353,19 +3906,11 @@
           <t>HP recovery: 12% -&gt; 15% -&gt; 18% -&gt; 21% -&gt; 25% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4407,19 +3952,11 @@
 Speed: 0.85x</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4460,19 +3997,11 @@
           <t>TP transfer bonus: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4514,19 +4043,11 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4568,19 +4089,11 @@
 Speed: 0.9x</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4622,19 +4135,11 @@
 Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4676,19 +4181,11 @@
 Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4730,19 +4227,11 @@
 Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4784,19 +4273,11 @@
 Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4839,23 +4320,16 @@
 Total damage cap: 250 -&gt; 275 -&gt; 300 -&gt; 325 -&gt; 350 -&gt; 375 -&gt; 400 -&gt; 430 -&gt; 460 -&gt; 500</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4897,19 +4371,11 @@
 Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4951,19 +4417,11 @@
 Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5006,23 +4464,16 @@
 Power decrease: 10%   |   TP Cost: 22 (+3-4/Lv) -&gt; 50   |   Speed: 0.75x -&gt; 0.85x</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5065,19 +4516,11 @@
 TP Cost: 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46   |   Speed: 0.75x -&gt; 0.8x</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5120,23 +4563,16 @@
 Paralysis: 20% -&gt; 23% -&gt; 26% -&gt; 29% -&gt; 32%   |   TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5179,23 +4615,16 @@
 Accuracy: +20%   |   TP Cost: 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 56 -&gt; 60</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5238,19 +4667,11 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5276,26 +4697,16 @@
           <t>Spin the magic roulette. Nobody knows what will happen.</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>Spin the magic roulette. Nobody knows what will happen.</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5338,23 +4749,16 @@
 Instakill: 15% (+1-2%/Lv) -&gt; 25%   |   TP Cost: 17 (+2/Lv) -&gt; 35   |   Speed: 0.88x</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
           <t>Instakill</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5397,23 +4801,16 @@
 Stun: 40% (+3-4%/Lv) -&gt; 70%   |   TP Cost: 32 (+2/Lv) -&gt; 50   |   Speed: 0.65x</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
           <t>Stun</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5456,23 +4853,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5498,26 +4888,16 @@
           <t>Open a magic box. Nobody knows what will happen.</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>Open a magic box. Nobody knows what will happen.</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5560,19 +4940,11 @@
 TP Cost: 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32   |   Speed: 0.85x</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5615,23 +4987,16 @@
 Poison: 50% (+3-4%/Lv) -&gt; 80%   |   TP Cost: 22 (+4/Lv) -&gt; 58   |   Speed: 0.6x -&gt; 0.7x</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>Poison</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5674,23 +5039,16 @@
 Turn delay rate: 25% (+2%/Lv)   |   TP Cost: 10 (+2-3/Lv) -&gt; 32   |   Speed: 0.95x</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>TP Cost</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5716,7 +5074,6 @@
           <t>Fan skill. With increased ATK, deal long-range damage to one enemy.</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>Fan skill. With raised ATK, deal minor long-range damage to an enemy.</t>
@@ -5728,19 +5085,11 @@
 Speed: 1.15x</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5783,23 +5132,16 @@
 TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50   |   Speed: 0.75x</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>Slow</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5842,23 +5184,16 @@
 Turns: 6   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 23 -&gt; 25   |   Speed: 0.85x</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>Max HP reduction</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5901,19 +5236,11 @@
 Turns: 2   |   TP Cost: 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50   |   Speed: 1.15x</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5939,26 +5266,16 @@
           <t>Something emerges from the shadows. Nobody knows what will happen.</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>Something emerges from the shadows. Nobody knows what will happen.</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6001,7 +5318,6 @@
 Accuracy UP   |   TP Cost: 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -6012,16 +5328,11 @@
           <t>Accuracy UP</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6084,15 +5395,11 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6155,11 +5462,6 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6222,11 +5524,6 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6289,11 +5586,6 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6336,19 +5628,11 @@
 Duration: 5   |   TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 38   |   Speed: 1.15x</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6411,11 +5695,6 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6458,19 +5737,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6513,19 +5784,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6568,19 +5831,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6623,19 +5878,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6678,19 +5925,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6733,19 +5972,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6788,19 +6019,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6843,19 +6066,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6898,19 +6113,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6953,19 +6160,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7008,19 +6207,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7063,19 +6254,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7118,19 +6301,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7173,19 +6348,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7228,19 +6395,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7283,19 +6442,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7338,19 +6489,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7393,19 +6536,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7448,19 +6583,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7503,19 +6630,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7558,19 +6677,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7613,19 +6724,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7668,19 +6771,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7723,19 +6818,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7778,19 +6865,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7833,19 +6912,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7888,19 +6959,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7943,19 +7006,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7998,19 +7053,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8053,19 +7100,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8108,19 +7147,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8163,19 +7194,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8218,19 +7241,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8273,19 +7288,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8328,19 +7335,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8383,19 +7382,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8438,19 +7429,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8493,19 +7476,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8548,19 +7523,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8603,19 +7570,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8658,19 +7617,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8713,19 +7664,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8768,14 +7711,11 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -8786,9 +7726,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8831,14 +7768,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8849,9 +7783,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8894,14 +7825,11 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -8912,9 +7840,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8957,19 +7882,11 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9012,14 +7929,11 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -9030,9 +7944,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9075,14 +7986,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9093,9 +8001,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9138,14 +8043,11 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9156,9 +8058,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9201,19 +8100,11 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9256,14 +8147,11 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -9274,9 +8162,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9319,14 +8204,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9337,9 +8219,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9382,14 +8261,11 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9400,9 +8276,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9445,19 +8318,11 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9500,14 +8365,11 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -9518,9 +8380,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9563,14 +8422,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9581,9 +8437,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9626,14 +8479,11 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9644,9 +8494,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9689,19 +8536,11 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9744,14 +8583,11 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -9762,9 +8598,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9807,14 +8640,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9825,9 +8655,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9870,14 +8697,11 @@
 Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
           <t>Accuracy, TP Cost</t>
@@ -9888,9 +8712,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9933,19 +8754,11 @@
 TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9988,14 +8801,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   HP Absorb: 100%   |   TP Cost: 9 (+1/Lv) -&gt; 18</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -10006,9 +8816,6 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O165" t="inlineStr"/>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10051,23 +8858,16 @@
 TP Absorb: 100% | TP Cost: 6 (+1/Lv) -&gt; 15 | Speed: 1.75x | Chant: 1.25x -&gt; 1.07x</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10110,23 +8910,16 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 27 -&gt; 31 -&gt; 35 -&gt; 39 -&gt; 43   |   Speed: 1.5x</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10169,14 +8962,11 @@
 TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50   |   Speed: 1.5x</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
           <t>Pwr, Accuracy</t>
@@ -10187,9 +8977,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10232,19 +9019,11 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18   |   Speed: 0.8x -&gt; 0.92x   |   Chant: 1.25x</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10287,19 +9066,11 @@
 TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   Speed: 2.15x   |   Chant: 1.2x -&gt; 1.4x</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10342,19 +9113,11 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10397,19 +9160,11 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1x -&gt; 1.2x</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10452,19 +9207,11 @@
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10507,19 +9254,11 @@
 TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10562,19 +9301,11 @@
 TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10617,19 +9348,11 @@
 TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20   |   Chant: 0.75x -&gt; 0.87x</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10672,19 +9395,11 @@
 TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23   |   Chant: 1x -&gt; 1.12x</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10727,19 +9442,11 @@
 TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30   |   Speed: 0.4x -&gt; 0.5x   |   Chant: 1.25x</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10782,19 +9489,11 @@
 TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 18 -&gt; 22   |   Speed: 1.25x   |   Chant: 1.25x -&gt; 1.45x</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10837,14 +9536,11 @@
 TP Cost: 45 -&gt; 52 -&gt; 59 -&gt; 66 -&gt; 74 -&gt; 80 -&gt; 86 -&gt; 90 -&gt; 95 -&gt; 100   |   Speed: 1.75x</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
           <t>Pwr, Accuracy</t>
@@ -10855,9 +9551,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10900,19 +9593,11 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10955,19 +9640,11 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11010,19 +9687,11 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11065,19 +9734,11 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11120,19 +9781,11 @@
 Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11175,23 +9828,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O186" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11234,23 +9880,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11293,23 +9932,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11352,14 +9984,11 @@
 TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26   |   Speed: 1.75x</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
           <t>Heal Cap</t>
@@ -11370,9 +9999,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11415,14 +10041,11 @@
 TP Cost: 15 -&gt; 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 46 -&gt; 52 -&gt; 58 -&gt; 64   |   Speed: 1.35x</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr">
         <is>
           <t>Heal Cap</t>
@@ -11433,9 +10056,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11476,19 +10096,11 @@
           <t>TP Cost: 48 -&gt; 45 -&gt; 42 -&gt; 39 -&gt; 36 (L1-5 Max)   |   Speed: 1.15x   |   Chant: 1.5x -&gt; 1.75x</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11531,19 +10143,11 @@
 TP Cost: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   Speed: 2.25x   |   Chant: 2.75x</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11586,19 +10190,11 @@
 TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25 -&gt; 30 -&gt; 36   |   Speed: 1.5x   |   Chant: 2x</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11641,19 +10237,11 @@
 TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42   |   Speed: 1.25x   |   Chant: 1.3x -&gt; 1.5x</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11696,23 +10284,16 @@
 Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17   |   Chant: 1.25x</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11755,23 +10336,16 @@
 Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17   |   Chant: 1.25x</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11814,23 +10388,16 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32   |   Chant: 1.25x</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11873,23 +10440,16 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32   |   Chant: 1.25x</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -11932,23 +10492,16 @@
 Turns: 3   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Speed: 1.25x -&gt; 1.41x</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
-      <c r="O199" t="inlineStr"/>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -11991,23 +10544,16 @@
 Turns: 5 -&gt; 5 -&gt; 6 -&gt; 6 -&gt; 7 -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 18 (+3/Lv) -&gt; 45</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr">
         <is>
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12050,19 +10596,11 @@
 TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 21 -&gt; 24 -&gt; 28   |   Speed: 1.75x   |   Chant: 2.25x</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12105,19 +10643,11 @@
 Chant: 0.75x -&gt; 0.65x</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12160,19 +10690,11 @@
 Turns: 4   |   TP Cost: 24 -&gt; 28 -&gt; 33 -&gt; 37 -&gt; 42   |   Speed: 1.5x   |   Chant: 0.75x</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12215,23 +10737,16 @@
 Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 45   |   Speed: 1.5x</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
-      <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12272,19 +10787,11 @@
           <t>Turns: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12325,19 +10832,11 @@
           <t>TP Cost: 28 -&gt; 21 -&gt; 14 -&gt; 7 -&gt; 1 (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12379,19 +10878,11 @@
 Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12417,7 +10908,6 @@
           <t>Raise the party's chance of doing multiple strikes while song lasts.</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
           <t>Raise the party's chance of doing multiple strikes while song lasts.</t>
@@ -12428,19 +10918,11 @@
           <t>Speed: 1.35x   |   Chant: 1.4x</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12482,19 +10964,11 @@
 Speed: 1.35x   |   Chant: 1.4x -&gt; 2x</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12536,19 +11010,11 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12590,19 +11056,11 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr"/>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12644,19 +11102,11 @@
 Speed: 1.35x   |   Chant: 1.4x -&gt; 2x</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12698,19 +11148,11 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12752,19 +11194,11 @@
 Speed: 1.35x   |   Chant: 1.1x -&gt; 1.5x</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12806,19 +11240,11 @@
 Speed: 1.35x   |   Chant: 1.1x -&gt; 1.5x</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12860,19 +11286,11 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12914,19 +11332,11 @@
 Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12969,23 +11379,16 @@
 Turns: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5   |   TP Cost: 23 -&gt; 27 -&gt; 32 -&gt; 38 -&gt; 45   |   Speed: 0.85x</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
-      <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13028,19 +11431,11 @@
 Turns: 3 | TP Cost: 36 -&gt; 39 -&gt; 43 -&gt; 47 -&gt; 52 | Speed: 0.8x | Chant: 0.8x -&gt; 0.88x</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13083,19 +11478,11 @@
 Turns: 3   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Chant: 1.15x -&gt; 1.3x</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
-      <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13148,8 +11535,6 @@
           <t>Edited by hand</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -13160,9 +11545,6 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13205,14 +11587,11 @@
 Magic defense: -7% -&gt; -18%   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
           <t>Magic defense, Damage cap</t>
@@ -13223,9 +11602,6 @@
           <t>Turns, Speed, Chant</t>
         </is>
       </c>
-      <c r="O222" t="inlineStr"/>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13268,14 +11644,11 @@
 Speed decrease: 4% (+1%/Lv)   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -13286,9 +11659,6 @@
           <t>Turns, Speed, Chant</t>
         </is>
       </c>
-      <c r="O223" t="inlineStr"/>
-      <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13341,8 +11711,6 @@
           <t>Edited by hand</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -13353,9 +11721,6 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O224" t="inlineStr"/>
-      <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13408,8 +11773,6 @@
           <t>Edited by hand</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
           <t>Damage cap</t>
@@ -13420,9 +11783,6 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13465,14 +11825,11 @@
 Accuracy: 86% (+1%/Lv)   |   TP Cost: 22 (+4-6/Lv) -&gt; 66   |   Speed: 1.3x</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
           <t>TP Cost</t>
@@ -13483,9 +11840,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13528,23 +11882,16 @@
 TP Cost: 36 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 80 -&gt; 88 -&gt; 96   |   Speed: 1.5x</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr">
         <is>
           <t>Chant</t>
         </is>
       </c>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13587,23 +11934,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22   |   Chant: 1.15x</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13646,23 +11986,16 @@
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22   |   Chant: 1.15x</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="O229" t="inlineStr"/>
-      <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13705,19 +12038,11 @@
 Turns: 3   |   TP Cost: 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40   |   Speed: 0.75x   |   Chant: 1.75x</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
-      <c r="O230" t="inlineStr"/>
-      <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13760,19 +12085,11 @@
 TP Cost: 12 -&gt; 11 -&gt; 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13815,14 +12132,11 @@
 Recoverable status ailments: 1 (+1/Lv)   |   HP on revival: 10% (+5-10%/Lv) -&gt; 50%</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
           <t>HP on revival</t>
@@ -13833,9 +12147,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13888,8 +12199,6 @@
           <t>Edited by hand</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
         <is>
           <t>Magic defense, Accuracy, HP recovery, TP Cost</t>
@@ -13900,9 +12209,6 @@
           <t>Speed, Chant</t>
         </is>
       </c>
-      <c r="O233" t="inlineStr"/>
-      <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13945,14 +12251,11 @@
 Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 30 (+4/Lv) -&gt; 66   |   Speed: 0.85x</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
           <t>Accuracy</t>
@@ -13963,9 +12266,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O234" t="inlineStr"/>
-      <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14008,14 +12308,11 @@
 TP Cost: 32 -&gt; 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 52 -&gt; 54 -&gt; 56   |   Speed: 1.2x</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
           <t>Pwr</t>
@@ -14026,9 +12323,6 @@
           <t>Chant</t>
         </is>
       </c>
-      <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr"/>
-      <c r="Q235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14071,7 +12365,6 @@
 TP Cost: 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 (L1-5 Max)   |   Speed: 1.5x   |   Chant: 0.84x -&gt; 0.8x</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -14087,11 +12380,6 @@
           <t>effect_1</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr"/>
-      <c r="Q236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14134,19 +12422,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr"/>
-      <c r="P237" t="inlineStr"/>
-      <c r="Q237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14189,19 +12469,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
-      <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14244,19 +12516,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr"/>
-      <c r="P239" t="inlineStr"/>
-      <c r="Q239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14299,19 +12563,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr"/>
-      <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14354,19 +12610,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
-      <c r="O241" t="inlineStr"/>
-      <c r="P241" t="inlineStr"/>
-      <c r="Q241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14409,19 +12657,11 @@
 dummy</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
           <t>Skipped (internal)</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr"/>
-      <c r="P242" t="inlineStr"/>
-      <c r="Q242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14462,19 +12702,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr"/>
-      <c r="P243" t="inlineStr"/>
-      <c r="Q243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14515,19 +12747,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
-      <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14568,19 +12792,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17% (L10)</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
-      <c r="O245" t="inlineStr"/>
-      <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14621,19 +12837,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr"/>
-      <c r="P246" t="inlineStr"/>
-      <c r="Q246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14674,19 +12882,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr"/>
-      <c r="P247" t="inlineStr"/>
-      <c r="Q247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14727,19 +12927,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
-      <c r="O248" t="inlineStr"/>
-      <c r="P248" t="inlineStr"/>
-      <c r="Q248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14780,19 +12972,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
-      <c r="O249" t="inlineStr"/>
-      <c r="P249" t="inlineStr"/>
-      <c r="Q249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -14833,19 +13017,11 @@
           <t>ATK bonus: 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% (L10)</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr"/>
-      <c r="N250" t="inlineStr"/>
-      <c r="O250" t="inlineStr"/>
-      <c r="P250" t="inlineStr"/>
-      <c r="Q250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14886,19 +13062,11 @@
           <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17% (L10)</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr"/>
-      <c r="N251" t="inlineStr"/>
-      <c r="O251" t="inlineStr"/>
-      <c r="P251" t="inlineStr"/>
-      <c r="Q251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -14939,19 +13107,11 @@
           <t>ATK bonus: 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% (L10)</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
-      <c r="M252" t="inlineStr"/>
-      <c r="N252" t="inlineStr"/>
-      <c r="O252" t="inlineStr"/>
-      <c r="P252" t="inlineStr"/>
-      <c r="Q252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -14992,19 +13152,11 @@
           <t>ATK bonus: 2% -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 12% (L10)</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr"/>
-      <c r="N253" t="inlineStr"/>
-      <c r="O253" t="inlineStr"/>
-      <c r="P253" t="inlineStr"/>
-      <c r="Q253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -15045,19 +13197,11 @@
           <t>Magic attack bonus: 6% -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
-      <c r="O254" t="inlineStr"/>
-      <c r="P254" t="inlineStr"/>
-      <c r="Q254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -15099,19 +13243,11 @@
 Heal Cap: +10% -&gt; +20 -&gt; +30 -&gt; +40 -&gt; +50 -&gt; +60 -&gt; +70 -&gt; +80 -&gt; +90 -&gt; +100%</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
-      <c r="O255" t="inlineStr"/>
-      <c r="P255" t="inlineStr"/>
-      <c r="Q255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15152,19 +13288,11 @@
           <t>HP recovery: 2% -&gt; 4% -&gt; 6% -&gt; 8% -&gt; 10% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
-      <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
-      <c r="O256" t="inlineStr"/>
-      <c r="P256" t="inlineStr"/>
-      <c r="Q256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -15205,19 +13333,11 @@
           <t>HP recovery: 1% -&gt; 2% -&gt; 3% -&gt; 4% -&gt; 5% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr"/>
-      <c r="N257" t="inlineStr"/>
-      <c r="O257" t="inlineStr"/>
-      <c r="P257" t="inlineStr"/>
-      <c r="Q257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -15258,19 +13378,11 @@
           <t>TP recovery: 3 -&gt; 6 -&gt; 9 -&gt; 12 -&gt; 16 (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
-      <c r="O258" t="inlineStr"/>
-      <c r="P258" t="inlineStr"/>
-      <c r="Q258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -15311,19 +13423,11 @@
           <t>TP recovery: 1 -&gt; 3 -&gt; 5 -&gt; 7 -&gt; 9 (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
-      <c r="O259" t="inlineStr"/>
-      <c r="P259" t="inlineStr"/>
-      <c r="Q259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -15364,19 +13468,11 @@
           <t>Elemental resistance: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 (L10)</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr"/>
-      <c r="P260" t="inlineStr"/>
-      <c r="Q260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15417,19 +13513,11 @@
           <t>Counterattack rate: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
-      <c r="O261" t="inlineStr"/>
-      <c r="P261" t="inlineStr"/>
-      <c r="Q261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -15470,19 +13558,11 @@
           <t>Activation rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
-      <c r="O262" t="inlineStr"/>
-      <c r="P262" t="inlineStr"/>
-      <c r="Q262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15523,19 +13603,11 @@
           <t>Double attack rate: 9% -&gt; 12% -&gt; 15% -&gt; 18% -&gt; 21% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
-      <c r="O263" t="inlineStr"/>
-      <c r="P263" t="inlineStr"/>
-      <c r="Q263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -15576,19 +13648,11 @@
           <t>Triple attack rate: 5% -&gt; 8% -&gt; 11% -&gt; 14% -&gt; 17% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr"/>
-      <c r="N264" t="inlineStr"/>
-      <c r="O264" t="inlineStr"/>
-      <c r="P264" t="inlineStr"/>
-      <c r="Q264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -15629,19 +13693,11 @@
           <t>Evasion rate: 20% -&gt; 24% -&gt; 28% -&gt; 32% -&gt; 36% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-      <c r="M265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
-      <c r="O265" t="inlineStr"/>
-      <c r="P265" t="inlineStr"/>
-      <c r="Q265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15682,19 +13738,11 @@
           <t>Activation rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
-      <c r="O266" t="inlineStr"/>
-      <c r="P266" t="inlineStr"/>
-      <c r="Q266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -15735,19 +13783,11 @@
           <t>Survival rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr"/>
-      <c r="N267" t="inlineStr"/>
-      <c r="O267" t="inlineStr"/>
-      <c r="P267" t="inlineStr"/>
-      <c r="Q267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -15788,19 +13828,11 @@
           <t>Auto-guard rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr"/>
-      <c r="N268" t="inlineStr"/>
-      <c r="O268" t="inlineStr"/>
-      <c r="P268" t="inlineStr"/>
-      <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -15841,19 +13873,11 @@
           <t>Sub-weapon ATK: 30% -&gt; 35 -&gt; 40 -&gt; 45 -&gt; 50 -&gt; 54 -&gt; 58 -&gt; 62 -&gt; 68 -&gt; 72% (L10)</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
-      <c r="M269" t="inlineStr"/>
-      <c r="N269" t="inlineStr"/>
-      <c r="O269" t="inlineStr"/>
-      <c r="P269" t="inlineStr"/>
-      <c r="Q269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -15894,19 +13918,11 @@
           <t>TP conversion: 4% -&gt; 8% -&gt; 12% -&gt; 16% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
-      <c r="O270" t="inlineStr"/>
-      <c r="P270" t="inlineStr"/>
-      <c r="Q270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -15947,19 +13963,11 @@
           <t>Activation rate: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
-      <c r="O271" t="inlineStr"/>
-      <c r="P271" t="inlineStr"/>
-      <c r="Q271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -16000,19 +14008,11 @@
           <t>Activation rate: 2% -&gt; 3% -&gt; 4% -&gt; 5% -&gt; 6% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr"/>
-      <c r="N272" t="inlineStr"/>
-      <c r="O272" t="inlineStr"/>
-      <c r="P272" t="inlineStr"/>
-      <c r="Q272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -16053,19 +14053,11 @@
           <t>Activation rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr"/>
-      <c r="N273" t="inlineStr"/>
-      <c r="O273" t="inlineStr"/>
-      <c r="P273" t="inlineStr"/>
-      <c r="Q273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16106,19 +14098,11 @@
           <t>Speed increase: 15% -&gt; 16% -&gt; 17% -&gt; 18% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr"/>
-      <c r="N274" t="inlineStr"/>
-      <c r="O274" t="inlineStr"/>
-      <c r="P274" t="inlineStr"/>
-      <c r="Q274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -16159,19 +14143,11 @@
           <t>Number of possible debuffs: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 (L6)</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr"/>
-      <c r="N275" t="inlineStr"/>
-      <c r="O275" t="inlineStr"/>
-      <c r="P275" t="inlineStr"/>
-      <c r="Q275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -16212,19 +14188,11 @@
           <t>ATK: +15% -&gt; +18% -&gt; +21% -&gt; +24% -&gt; +27% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr"/>
-      <c r="N276" t="inlineStr"/>
-      <c r="O276" t="inlineStr"/>
-      <c r="P276" t="inlineStr"/>
-      <c r="Q276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -16250,26 +14218,16 @@
           <t>Nullify the effects of enemy Dark Auras.</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
           <t>Nullify the effects of enemy Dark Auras.</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
-      <c r="O277" t="inlineStr"/>
-      <c r="P277" t="inlineStr"/>
-      <c r="Q277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -16295,26 +14253,16 @@
           <t>No longer suffer counterattacks from enemies.</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
           <t>No longer suffer counterattacks from enemies.</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr"/>
-      <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr"/>
-      <c r="N278" t="inlineStr"/>
-      <c r="O278" t="inlineStr"/>
-      <c r="P278" t="inlineStr"/>
-      <c r="Q278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -16355,19 +14303,11 @@
           <t>Physical damage: -6% -&gt; -7% -&gt; -8% -&gt; -9% -&gt; -10% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
-      <c r="P279" t="inlineStr"/>
-      <c r="Q279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -16408,19 +14348,11 @@
           <t>Activation rate: 8% -&gt; 9% -&gt; 10% -&gt; 11% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="inlineStr"/>
-      <c r="N280" t="inlineStr"/>
-      <c r="O280" t="inlineStr"/>
-      <c r="P280" t="inlineStr"/>
-      <c r="Q280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -16461,19 +14393,11 @@
           <t>LvUp: Can cure poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; slow</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr"/>
-      <c r="N281" t="inlineStr"/>
-      <c r="O281" t="inlineStr"/>
-      <c r="P281" t="inlineStr"/>
-      <c r="Q281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -16514,19 +14438,11 @@
           <t>ATK/DEX: +10% -&gt; +11% -&gt; +12% -&gt; +13% -&gt; +15% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
-      <c r="M282" t="inlineStr"/>
-      <c r="N282" t="inlineStr"/>
-      <c r="O282" t="inlineStr"/>
-      <c r="P282" t="inlineStr"/>
-      <c r="Q282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -16564,22 +14480,24 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Interruption rate: -10% -&gt; -20% -&gt; -30% -&gt; -40% -&gt; -50% (L1-5 Max)</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr"/>
+          <t>LvUp: Interruption rate DOWN</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J283" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr"/>
-      <c r="N283" t="inlineStr"/>
-      <c r="O283" t="inlineStr"/>
-      <c r="P283" t="inlineStr"/>
-      <c r="Q283" t="inlineStr"/>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>Left as the game words it (the user, 2026-10-12): the program adds the value where it means to multiply (docs/FORMULAS.md 2.5), so no figure is true of it</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -16620,19 +14538,11 @@
           <t>Chant time: -8% -&gt; -11% -&gt; -14% -&gt; -17% -&gt; -20% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr"/>
-      <c r="O284" t="inlineStr"/>
-      <c r="P284" t="inlineStr"/>
-      <c r="Q284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -16673,19 +14583,11 @@
           <t>TP Cost reduction: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr"/>
-      <c r="N285" t="inlineStr"/>
-      <c r="O285" t="inlineStr"/>
-      <c r="P285" t="inlineStr"/>
-      <c r="Q285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -16726,19 +14628,11 @@
           <t>Accuracy: 3% -&gt; 5% -&gt; 7% -&gt; 9% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr"/>
-      <c r="N286" t="inlineStr"/>
-      <c r="O286" t="inlineStr"/>
-      <c r="P286" t="inlineStr"/>
-      <c r="Q286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -16779,19 +14673,11 @@
           <t>Enemy preemptive attack rate: -20% -&gt; -28% -&gt; -36% -&gt; -44% -&gt; -50% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
-      <c r="M287" t="inlineStr"/>
-      <c r="N287" t="inlineStr"/>
-      <c r="O287" t="inlineStr"/>
-      <c r="P287" t="inlineStr"/>
-      <c r="Q287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -16832,19 +14718,11 @@
           <t>Preemptive attack rate: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr"/>
-      <c r="N288" t="inlineStr"/>
-      <c r="O288" t="inlineStr"/>
-      <c r="P288" t="inlineStr"/>
-      <c r="Q288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -16885,19 +14763,11 @@
           <t>Battle escape rate: 20% -&gt; 25% -&gt; 30% -&gt; 35% -&gt; 40% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
-      <c r="M289" t="inlineStr"/>
-      <c r="N289" t="inlineStr"/>
-      <c r="O289" t="inlineStr"/>
-      <c r="P289" t="inlineStr"/>
-      <c r="Q289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -16938,19 +14808,11 @@
           <t>Item drop rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
-      <c r="M290" t="inlineStr"/>
-      <c r="N290" t="inlineStr"/>
-      <c r="O290" t="inlineStr"/>
-      <c r="P290" t="inlineStr"/>
-      <c r="Q290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -16991,19 +14853,11 @@
           <t>Gold drop rate: 25% -&gt; 50% -&gt; 75% -&gt; 100% -&gt; 125% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
-      <c r="M291" t="inlineStr"/>
-      <c r="N291" t="inlineStr"/>
-      <c r="O291" t="inlineStr"/>
-      <c r="P291" t="inlineStr"/>
-      <c r="Q291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -17044,19 +14898,11 @@
           <t>Found item quality: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr"/>
-      <c r="N292" t="inlineStr"/>
-      <c r="O292" t="inlineStr"/>
-      <c r="P292" t="inlineStr"/>
-      <c r="Q292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -17098,19 +14944,11 @@
 Post-battle TP: 3% -&gt; 4% -&gt; 5% -&gt; 7% -&gt; 9%</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" t="inlineStr"/>
-      <c r="N293" t="inlineStr"/>
-      <c r="O293" t="inlineStr"/>
-      <c r="P293" t="inlineStr"/>
-      <c r="Q293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -17151,19 +14989,11 @@
           <t>Item keep rate: 25% -&gt; 27% -&gt; 29% -&gt; 32% -&gt; 35% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
-      <c r="M294" t="inlineStr"/>
-      <c r="N294" t="inlineStr"/>
-      <c r="O294" t="inlineStr"/>
-      <c r="P294" t="inlineStr"/>
-      <c r="Q294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -17204,19 +15034,11 @@
           <t>Item effects: 10% -&gt; 20 -&gt; 30 -&gt; 40 -&gt; 50 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 90 -&gt; 100% (L10)</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr"/>
-      <c r="N295" t="inlineStr"/>
-      <c r="O295" t="inlineStr"/>
-      <c r="P295" t="inlineStr"/>
-      <c r="Q295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -17257,19 +15079,11 @@
           <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr"/>
-      <c r="O296" t="inlineStr"/>
-      <c r="P296" t="inlineStr"/>
-      <c r="Q296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -17310,19 +15124,11 @@
           <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
-      <c r="M297" t="inlineStr"/>
-      <c r="N297" t="inlineStr"/>
-      <c r="O297" t="inlineStr"/>
-      <c r="P297" t="inlineStr"/>
-      <c r="Q297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -17363,19 +15169,11 @@
           <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
-      <c r="M298" t="inlineStr"/>
-      <c r="N298" t="inlineStr"/>
-      <c r="O298" t="inlineStr"/>
-      <c r="P298" t="inlineStr"/>
-      <c r="Q298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -17416,19 +15214,11 @@
           <t>Sealbook ability: +15% -&gt; +18% -&gt; +21% -&gt; +24% -&gt; +27% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
-      <c r="L299" t="inlineStr"/>
-      <c r="M299" t="inlineStr"/>
-      <c r="N299" t="inlineStr"/>
-      <c r="O299" t="inlineStr"/>
-      <c r="P299" t="inlineStr"/>
-      <c r="Q299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -17469,19 +15259,11 @@
           <t>Maid skill bonus: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10% (L10)</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
-      <c r="L300" t="inlineStr"/>
-      <c r="M300" t="inlineStr"/>
-      <c r="N300" t="inlineStr"/>
-      <c r="O300" t="inlineStr"/>
-      <c r="P300" t="inlineStr"/>
-      <c r="Q300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -17522,19 +15304,11 @@
           <t>Singing skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
-      <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
-      <c r="L301" t="inlineStr"/>
-      <c r="M301" t="inlineStr"/>
-      <c r="N301" t="inlineStr"/>
-      <c r="O301" t="inlineStr"/>
-      <c r="P301" t="inlineStr"/>
-      <c r="Q301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -17575,19 +15349,11 @@
           <t>Dancing skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
-      <c r="L302" t="inlineStr"/>
-      <c r="M302" t="inlineStr"/>
-      <c r="N302" t="inlineStr"/>
-      <c r="O302" t="inlineStr"/>
-      <c r="P302" t="inlineStr"/>
-      <c r="Q302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -17628,19 +15394,11 @@
           <t>Doll skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
-      <c r="L303" t="inlineStr"/>
-      <c r="M303" t="inlineStr"/>
-      <c r="N303" t="inlineStr"/>
-      <c r="O303" t="inlineStr"/>
-      <c r="P303" t="inlineStr"/>
-      <c r="Q303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -17681,19 +15439,11 @@
           <t>Double attack rate: 20% -&gt; 21 -&gt; 22 -&gt; 23 -&gt; 24 -&gt; 25 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32% (L10)</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
-      <c r="L304" t="inlineStr"/>
-      <c r="M304" t="inlineStr"/>
-      <c r="N304" t="inlineStr"/>
-      <c r="O304" t="inlineStr"/>
-      <c r="P304" t="inlineStr"/>
-      <c r="Q304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -17734,19 +15484,11 @@
           <t>Song chant time: -10% -&gt; -11 -&gt; -12 -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -20%</t>
         </is>
       </c>
-      <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
-      <c r="L305" t="inlineStr"/>
-      <c r="M305" t="inlineStr"/>
-      <c r="N305" t="inlineStr"/>
-      <c r="O305" t="inlineStr"/>
-      <c r="P305" t="inlineStr"/>
-      <c r="Q305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -17787,19 +15529,11 @@
           <t>Negotiation rate: 10% -&gt; 14% -&gt; 18% -&gt; 22% -&gt; 25% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
-      <c r="L306" t="inlineStr"/>
-      <c r="M306" t="inlineStr"/>
-      <c r="N306" t="inlineStr"/>
-      <c r="O306" t="inlineStr"/>
-      <c r="P306" t="inlineStr"/>
-      <c r="Q306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -17840,19 +15574,11 @@
           <t>Occurrence rate: 3% -&gt; 4% -&gt; 5% -&gt; 6% -&gt; 7% (L1-5 Max)</t>
         </is>
       </c>
-      <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
-      <c r="L307" t="inlineStr"/>
-      <c r="M307" t="inlineStr"/>
-      <c r="N307" t="inlineStr"/>
-      <c r="O307" t="inlineStr"/>
-      <c r="P307" t="inlineStr"/>
-      <c r="Q307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -17878,26 +15604,16 @@
           <t>Nullify first hit of battle against user (does not work for status ailments).</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
           <t>Nullify first hit of battle against user (does not work for status ailments).</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr"/>
-      <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
-      <c r="L308" t="inlineStr"/>
-      <c r="M308" t="inlineStr"/>
-      <c r="N308" t="inlineStr"/>
-      <c r="O308" t="inlineStr"/>
-      <c r="P308" t="inlineStr"/>
-      <c r="Q308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -17923,26 +15639,16 @@
           <t>Heighten the probability of beneficial results for random effect skills.</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr">
         <is>
           <t>Heighten the probability of beneficial results for random effect skills.</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr"/>
-      <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
-      <c r="L309" t="inlineStr"/>
-      <c r="M309" t="inlineStr"/>
-      <c r="N309" t="inlineStr"/>
-      <c r="O309" t="inlineStr"/>
-      <c r="P309" t="inlineStr"/>
-      <c r="Q309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -17968,26 +15674,16 @@
           <t>Whip skill. Strike back with a normal attack before a targeted attack hits you.</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr">
         <is>
           <t>Whip skill. Strike back with a normal attack before a targeted attack hits you.</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr"/>
-      <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
-      <c r="L310" t="inlineStr"/>
-      <c r="M310" t="inlineStr"/>
-      <c r="N310" t="inlineStr"/>
-      <c r="O310" t="inlineStr"/>
-      <c r="P310" t="inlineStr"/>
-      <c r="Q310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -18013,26 +15709,16 @@
           <t>Occasionally get the first action regardless of speed.</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr">
         <is>
           <t>Occasionally get the first action regardless of speed.</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr"/>
-      <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
-      <c r="L311" t="inlineStr"/>
-      <c r="M311" t="inlineStr"/>
-      <c r="N311" t="inlineStr"/>
-      <c r="O311" t="inlineStr"/>
-      <c r="P311" t="inlineStr"/>
-      <c r="Q311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -18058,26 +15744,16 @@
           <t>Occasionally land critical hits with offensive spells.</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
           <t>Occasionally land critical hits with offensive spells.</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr"/>
-      <c r="M312" t="inlineStr"/>
-      <c r="N312" t="inlineStr"/>
-      <c r="O312" t="inlineStr"/>
-      <c r="P312" t="inlineStr"/>
-      <c r="Q312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -18103,26 +15779,16 @@
           <t>Increase doll summon duration by 1 turn.</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr">
         <is>
           <t>Increase doll summon duration by 1 turn.</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr">
         <is>
           <t>Unchanged</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
-      <c r="L313" t="inlineStr"/>
-      <c r="M313" t="inlineStr"/>
-      <c r="N313" t="inlineStr"/>
-      <c r="O313" t="inlineStr"/>
-      <c r="P313" t="inlineStr"/>
-      <c r="Q313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -18148,27 +15814,17 @@
           <t>Significantly increase damage according to Pep.</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr">
         <is>
           <t>Significantly increase damage according to Pep.
 Pep over 100 per +1% damage: 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3 -&gt; 2   |   Crown EX: 1</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr"/>
-      <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
-      <c r="L314" t="inlineStr"/>
-      <c r="M314" t="inlineStr"/>
-      <c r="N314" t="inlineStr"/>
-      <c r="O314" t="inlineStr"/>
-      <c r="P314" t="inlineStr"/>
-      <c r="Q314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -18194,27 +15850,17 @@
           <t>Occasionally inflict enemies with status ailments or Dispel at random.</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr">
         <is>
           <t>Occasionally inflict enemies with status ailments or Dispel at random.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 25%</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
-      <c r="L315" t="inlineStr"/>
-      <c r="M315" t="inlineStr"/>
-      <c r="N315" t="inlineStr"/>
-      <c r="O315" t="inlineStr"/>
-      <c r="P315" t="inlineStr"/>
-      <c r="Q315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -18240,27 +15886,17 @@
           <t>May counter short-range attacks with Slow and a Speed decrease.</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr">
         <is>
           <t>May counter short-range attacks with Slow and a Speed decrease.
 Activation rate: 16% -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38%   |   Crown EX: 50%</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
-      <c r="L316" t="inlineStr"/>
-      <c r="M316" t="inlineStr"/>
-      <c r="N316" t="inlineStr"/>
-      <c r="O316" t="inlineStr"/>
-      <c r="P316" t="inlineStr"/>
-      <c r="Q316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -18286,27 +15922,17 @@
           <t>Increase weapon modifier when attacking with weapon-based skills.</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr"/>
       <c r="G317" t="inlineStr">
         <is>
           <t>Increase weapon modifier when attacking with weapon-based skills.
 Weapon modifier: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18%   |   Crown EX: 25%</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
-      <c r="L317" t="inlineStr"/>
-      <c r="M317" t="inlineStr"/>
-      <c r="N317" t="inlineStr"/>
-      <c r="O317" t="inlineStr"/>
-      <c r="P317" t="inlineStr"/>
-      <c r="Q317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -18332,27 +15958,17 @@
           <t>May guarantee a hit and bypass DEF with physical attacks or skills.</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr">
         <is>
           <t>May guarantee a hit and bypass DEF with physical attacks or skills.
 Activation rate: 12% -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20%   |   Crown EX: 30%</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr"/>
       <c r="J318" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
-      <c r="L318" t="inlineStr"/>
-      <c r="M318" t="inlineStr"/>
-      <c r="N318" t="inlineStr"/>
-      <c r="O318" t="inlineStr"/>
-      <c r="P318" t="inlineStr"/>
-      <c r="Q318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -18378,27 +15994,17 @@
           <t>Occasionally nullify all damage received from enemies.</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr"/>
       <c r="G319" t="inlineStr">
         <is>
           <t>Occasionally nullify all damage received from enemies.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr"/>
-      <c r="M319" t="inlineStr"/>
-      <c r="N319" t="inlineStr"/>
-      <c r="O319" t="inlineStr"/>
-      <c r="P319" t="inlineStr"/>
-      <c r="Q319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -18424,27 +16030,17 @@
           <t>Before acting, may erase enemy puppets, familiars, shikigami, or slaves.</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr">
         <is>
           <t>Before acting, may erase enemy puppets, familiars, shikigami, or slaves.
 Activation rate: 25% -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 49 -&gt; 53 -&gt; 57%   |   Crown EX: 75%</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
-      <c r="L320" t="inlineStr"/>
-      <c r="M320" t="inlineStr"/>
-      <c r="N320" t="inlineStr"/>
-      <c r="O320" t="inlineStr"/>
-      <c r="P320" t="inlineStr"/>
-      <c r="Q320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -18470,27 +16066,17 @@
           <t>Before acting, may use an item from her own personal stock.</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr">
         <is>
           <t>Before acting, may use an item from her own personal stock.
 Activation rate: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18%   |   Crown EX: 25%</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
-      <c r="M321" t="inlineStr"/>
-      <c r="N321" t="inlineStr"/>
-      <c r="O321" t="inlineStr"/>
-      <c r="P321" t="inlineStr"/>
-      <c r="Q321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -18516,27 +16102,17 @@
           <t>Decrease turn delay after using skills or magic.</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr">
         <is>
           <t>Decrease turn delay after using skills or magic.
 Speed added: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
-      <c r="L322" t="inlineStr"/>
-      <c r="M322" t="inlineStr"/>
-      <c r="N322" t="inlineStr"/>
-      <c r="O322" t="inlineStr"/>
-      <c r="P322" t="inlineStr"/>
-      <c r="Q322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -18562,27 +16138,17 @@
           <t>Increased effects for all maid skills.</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr">
         <is>
           <t>Increased effects for all maid skills.
 Maid skill effects: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 10%   |   Crown EX: 13%</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
-      <c r="L323" t="inlineStr"/>
-      <c r="M323" t="inlineStr"/>
-      <c r="N323" t="inlineStr"/>
-      <c r="O323" t="inlineStr"/>
-      <c r="P323" t="inlineStr"/>
-      <c r="Q323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -18608,27 +16174,17 @@
           <t>May occasionally act twice in one turn.</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr">
         <is>
           <t>May occasionally act twice in one turn.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
-      <c r="L324" t="inlineStr"/>
-      <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr"/>
-      <c r="O324" t="inlineStr"/>
-      <c r="P324" t="inlineStr"/>
-      <c r="Q324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -18654,27 +16210,17 @@
           <t>If killed, revive after a certain number of turns.</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr">
         <is>
           <t>If killed, revive after a certain number of turns.
 Activation rate: 8% -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24%   |   Crown EX: 30%</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
-      <c r="L325" t="inlineStr"/>
-      <c r="M325" t="inlineStr"/>
-      <c r="N325" t="inlineStr"/>
-      <c r="O325" t="inlineStr"/>
-      <c r="P325" t="inlineStr"/>
-      <c r="Q325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -18700,27 +16246,17 @@
           <t>Whole row takes less damage from Demons, Undead, and Apparitions.</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr">
         <is>
           <t>Whole row takes less damage from Demons, Undead, and Apparitions.
 Taken: -12% -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -19 -&gt; -20%   |   Crown EX: -25%</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
-      <c r="L326" t="inlineStr"/>
-      <c r="M326" t="inlineStr"/>
-      <c r="N326" t="inlineStr"/>
-      <c r="O326" t="inlineStr"/>
-      <c r="P326" t="inlineStr"/>
-      <c r="Q326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -18746,7 +16282,6 @@
           <t>May lower all enemies' ATK and INT with heart-penetrating vocals.</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr">
         <is>
           <t>May lower all enemies' ATK and INT with heart-penetrating vocals.
@@ -18754,20 +16289,11 @@
 Enemy ATK and INT: -10% for 4 turns</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
-      <c r="L327" t="inlineStr"/>
-      <c r="M327" t="inlineStr"/>
-      <c r="N327" t="inlineStr"/>
-      <c r="O327" t="inlineStr"/>
-      <c r="P327" t="inlineStr"/>
-      <c r="Q327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -18793,27 +16319,17 @@
           <t>Magic will occasionally activate immediately without the need to chant.</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr">
         <is>
           <t>Magic will occasionally activate immediately without the need to chant.
 Activation rate: 7% -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15%   |   Crown EX: 20%</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr"/>
       <c r="J328" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
-      <c r="L328" t="inlineStr"/>
-      <c r="M328" t="inlineStr"/>
-      <c r="N328" t="inlineStr"/>
-      <c r="O328" t="inlineStr"/>
-      <c r="P328" t="inlineStr"/>
-      <c r="Q328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -18839,7 +16355,6 @@
           <t>Occasionally reflects a percentage of damage taken as fixed damage.</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr">
         <is>
           <t>Occasionally reflects a percentage of damage taken as fixed damage.
@@ -18847,20 +16362,11 @@
 Activation rate: 15%</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
-      <c r="L329" t="inlineStr"/>
-      <c r="M329" t="inlineStr"/>
-      <c r="N329" t="inlineStr"/>
-      <c r="O329" t="inlineStr"/>
-      <c r="P329" t="inlineStr"/>
-      <c r="Q329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -18886,27 +16392,17 @@
           <t>Summons another self from the shadows to attack.</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr">
         <is>
           <t>Summons another self from the shadows to attack.
 Activation rate: 4% -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12%   |   Crown EX: 20%</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
-      <c r="L330" t="inlineStr"/>
-      <c r="M330" t="inlineStr"/>
-      <c r="N330" t="inlineStr"/>
-      <c r="O330" t="inlineStr"/>
-      <c r="P330" t="inlineStr"/>
-      <c r="Q330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -18932,27 +16428,17 @@
           <t>Increased effects for all class modifiers.</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr">
         <is>
           <t>Increased effects for all class modifiers.
 Class modifiers (%): 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Crown EX: 15</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
-      <c r="L331" t="inlineStr"/>
-      <c r="M331" t="inlineStr"/>
-      <c r="N331" t="inlineStr"/>
-      <c r="O331" t="inlineStr"/>
-      <c r="P331" t="inlineStr"/>
-      <c r="Q331" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
